--- a/the_alternative_f1/The_Alternative_F1.xlsx
+++ b/the_alternative_f1/The_Alternative_F1.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2462" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3166" uniqueCount="435">
   <si>
     <t>Positions</t>
   </si>
@@ -2840,14 +2840,10 @@
       <c r="C2" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="16">
-        <v>1.0</v>
-      </c>
-      <c r="E2" s="17">
-        <v>16.0</v>
-      </c>
+      <c r="D2" s="16"/>
+      <c r="E2" s="17"/>
       <c r="F2" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>128</v>
@@ -2860,158 +2856,238 @@
       </c>
       <c r="J2" s="71">
         <f>IFERROR((VLOOKUP(D2,Scoring!$A:$B,2,0))+IF(F2="y",1,0)+IF(G2="y",1,0)+IF(H2="y",1,0)+IF(I2="y",1,0),0)</f>
-        <v>26</v>
-      </c>
-      <c r="K2" s="16">
-        <v>2.0</v>
-      </c>
-      <c r="L2" s="17">
-        <v>1.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K2" s="16"/>
+      <c r="L2" s="17"/>
       <c r="M2" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N2" s="19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O2" s="20" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P2" s="21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q2" s="71">
         <f>IFERROR((VLOOKUP(K2,Scoring!$A:$B,2,0))+IF(M2="y",1,0)+IF(N2="y",1,0)+IF(O2="y",1,0)+IF(P2="y",1,0),0)</f>
-        <v>22</v>
-      </c>
-      <c r="R2" s="16">
-        <v>16.0</v>
-      </c>
-      <c r="S2" s="17">
-        <v>16.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R2" s="16"/>
+      <c r="S2" s="17"/>
       <c r="T2" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="U2" s="19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="V2" s="20" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="W2" s="21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="X2" s="71">
         <f>IFERROR((VLOOKUP(R2,Scoring!$A:$B,2,0))+IF(T2="y",1,0)+IF(U2="y",1,0)+IF(V2="y",1,0)+IF(W2="y",1,0),0)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="16"/>
       <c r="Z2" s="17"/>
-      <c r="AA2" s="18"/>
-      <c r="AB2" s="19"/>
-      <c r="AC2" s="20"/>
-      <c r="AD2" s="21"/>
+      <c r="AA2" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB2" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC2" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD2" s="21" t="s">
+        <v>128</v>
+      </c>
       <c r="AE2" s="71">
         <f>IFERROR((VLOOKUP(Y2,Scoring!$A:$B,2,0))+IF(AA2="y",1,0)+IF(AB2="y",1,0)+IF(AC2="y",1,0)+IF(AD2="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AF2" s="16"/>
       <c r="AG2" s="17"/>
-      <c r="AH2" s="18"/>
-      <c r="AI2" s="19"/>
-      <c r="AJ2" s="20"/>
-      <c r="AK2" s="21"/>
+      <c r="AH2" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI2" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ2" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK2" s="21" t="s">
+        <v>128</v>
+      </c>
       <c r="AL2" s="71">
         <f>IFERROR((VLOOKUP(AF2,Scoring!$A:$B,2,0))+IF(AH2="y",1,0)+IF(AI2="y",1,0)+IF(AJ2="y",1,0)+IF(AK2="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AM2" s="16"/>
       <c r="AN2" s="17"/>
-      <c r="AO2" s="18"/>
-      <c r="AP2" s="19"/>
-      <c r="AQ2" s="20"/>
-      <c r="AR2" s="21"/>
+      <c r="AO2" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP2" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ2" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR2" s="21" t="s">
+        <v>128</v>
+      </c>
       <c r="AS2" s="71">
         <f>IFERROR((VLOOKUP(AM2,Scoring!$A:$B,2,0))+IF(AO2="y",1,0)+IF(AP2="y",1,0)+IF(AQ2="y",1,0)+IF(AR2="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AT2" s="16"/>
       <c r="AU2" s="17"/>
-      <c r="AV2" s="18"/>
-      <c r="AW2" s="19"/>
-      <c r="AX2" s="20"/>
-      <c r="AY2" s="21"/>
+      <c r="AV2" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="AW2" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX2" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="AY2" s="21" t="s">
+        <v>128</v>
+      </c>
       <c r="AZ2" s="71">
         <f>IFERROR((VLOOKUP(AT2,Scoring!$A:$B,2,0))+IF(AV2="y",1,0)+IF(AW2="y",1,0)+IF(AX2="y",1,0)+IF(AY2="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BA2" s="16"/>
       <c r="BB2" s="17"/>
-      <c r="BC2" s="18"/>
-      <c r="BD2" s="19"/>
-      <c r="BE2" s="20"/>
-      <c r="BF2" s="21"/>
+      <c r="BC2" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="BD2" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BE2" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="BF2" s="21" t="s">
+        <v>128</v>
+      </c>
       <c r="BG2" s="71">
         <f>IFERROR((VLOOKUP(BA2,Scoring!$A:$B,2,0))+IF(BC2="y",1,0)+IF(BD2="y",1,0)+IF(BE2="y",1,0)+IF(BF2="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BH2" s="16"/>
       <c r="BI2" s="17"/>
-      <c r="BJ2" s="18"/>
-      <c r="BK2" s="19"/>
-      <c r="BL2" s="20"/>
-      <c r="BM2" s="21"/>
+      <c r="BJ2" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK2" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL2" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM2" s="21" t="s">
+        <v>128</v>
+      </c>
       <c r="BN2" s="71">
         <f>IFERROR((VLOOKUP(BH2,Scoring!$A:$B,2,0))+IF(BJ2="y",1,0)+IF(BK2="y",1,0)+IF(BL2="y",1,0)+IF(BM2="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BO2" s="16"/>
       <c r="BP2" s="17"/>
-      <c r="BQ2" s="18"/>
-      <c r="BR2" s="19"/>
-      <c r="BS2" s="20"/>
-      <c r="BT2" s="21"/>
+      <c r="BQ2" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="BR2" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BS2" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="BT2" s="21" t="s">
+        <v>128</v>
+      </c>
       <c r="BU2" s="71">
         <f>IFERROR((VLOOKUP(BO2,Scoring!$A:$B,2,0))+IF(BQ2="y",1,0)+IF(BR2="y",1,0)+IF(BS2="y",1,0)+IF(BT2="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BV2" s="16"/>
       <c r="BW2" s="17"/>
-      <c r="BX2" s="18"/>
-      <c r="BY2" s="19"/>
-      <c r="BZ2" s="20"/>
-      <c r="CA2" s="21"/>
+      <c r="BX2" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY2" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ2" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA2" s="21" t="s">
+        <v>128</v>
+      </c>
       <c r="CB2" s="71">
         <f>IFERROR((VLOOKUP(BV2,Scoring!$A:$B,2,0))+IF(BX2="y",1,0)+IF(BY2="y",1,0)+IF(BZ2="y",1,0)+IF(CA2="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CC2" s="16"/>
       <c r="CD2" s="17"/>
-      <c r="CE2" s="18"/>
-      <c r="CF2" s="19"/>
-      <c r="CG2" s="20"/>
-      <c r="CH2" s="21"/>
+      <c r="CE2" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF2" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG2" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH2" s="21" t="s">
+        <v>128</v>
+      </c>
       <c r="CI2" s="71">
         <f>IFERROR((VLOOKUP(CC2,Scoring!$A:$B,2,0))+IF(CE2="y",1,0)+IF(CF2="y",1,0)+IF(CG2="y",1,0)+IF(CH2="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CJ2" s="16"/>
       <c r="CK2" s="17"/>
-      <c r="CL2" s="18"/>
-      <c r="CM2" s="19"/>
-      <c r="CN2" s="20"/>
-      <c r="CO2" s="21"/>
+      <c r="CL2" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM2" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN2" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO2" s="21" t="s">
+        <v>128</v>
+      </c>
       <c r="CP2" s="71">
         <f>IFERROR((VLOOKUP(CJ2,Scoring!$A:$B,2,0))+IF(CL2="y",1,0)+IF(CM2="y",1,0)+IF(CN2="y",1,0)+IF(CO2="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CQ2" s="16"/>
       <c r="CR2" s="17"/>
-      <c r="CS2" s="18"/>
-      <c r="CT2" s="19"/>
-      <c r="CU2" s="20"/>
-      <c r="CV2" s="21"/>
+      <c r="CS2" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="CT2" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CU2" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="CV2" s="21" t="s">
+        <v>128</v>
+      </c>
       <c r="CW2" s="71">
         <f>IFERROR((VLOOKUP(CQ2,Scoring!$A:$B,2,0))+IF(CS2="y",1,0)+IF(CT2="y",1,0)+IF(CU2="y",1,0)+IF(CV2="y",1,0),0)</f>
         <v>0</v>
@@ -3030,17 +3106,13 @@
       <c r="C3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="24">
-        <v>2.0</v>
-      </c>
-      <c r="E3" s="25">
-        <v>15.0</v>
-      </c>
+      <c r="D3" s="24"/>
+      <c r="E3" s="25"/>
       <c r="F3" s="26" t="s">
         <v>128</v>
       </c>
       <c r="G3" s="27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H3" s="28" t="s">
         <v>128</v>
@@ -3050,14 +3122,10 @@
       </c>
       <c r="J3" s="72">
         <f>IFERROR((VLOOKUP(D3,Scoring!$A:$B,2,0))+IF(F3="y",1,0)+IF(G3="y",1,0)+IF(H3="y",1,0)+IF(I3="y",1,0),0)</f>
-        <v>19</v>
-      </c>
-      <c r="K3" s="24">
-        <v>4.0</v>
-      </c>
-      <c r="L3" s="25">
-        <v>2.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K3" s="24"/>
+      <c r="L3" s="25"/>
       <c r="M3" s="26" t="s">
         <v>128</v>
       </c>
@@ -3072,14 +3140,10 @@
       </c>
       <c r="Q3" s="72">
         <f>IFERROR((VLOOKUP(K3,Scoring!$A:$B,2,0))+IF(M3="y",1,0)+IF(N3="y",1,0)+IF(O3="y",1,0)+IF(P3="y",1,0),0)</f>
-        <v>12</v>
-      </c>
-      <c r="R3" s="24">
-        <v>14.0</v>
-      </c>
-      <c r="S3" s="25">
-        <v>14.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R3" s="24"/>
+      <c r="S3" s="25"/>
       <c r="T3" s="26" t="s">
         <v>128</v>
       </c>
@@ -3094,114 +3158,202 @@
       </c>
       <c r="X3" s="72">
         <f>IFERROR((VLOOKUP(R3,Scoring!$A:$B,2,0))+IF(T3="y",1,0)+IF(U3="y",1,0)+IF(V3="y",1,0)+IF(W3="y",1,0),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="24"/>
       <c r="Z3" s="25"/>
-      <c r="AA3" s="26"/>
-      <c r="AB3" s="27"/>
-      <c r="AC3" s="28"/>
-      <c r="AD3" s="29"/>
+      <c r="AA3" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB3" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC3" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD3" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AE3" s="72">
         <f>IFERROR((VLOOKUP(Y3,Scoring!$A:$B,2,0))+IF(AA3="y",1,0)+IF(AB3="y",1,0)+IF(AC3="y",1,0)+IF(AD3="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AF3" s="24"/>
       <c r="AG3" s="25"/>
-      <c r="AH3" s="26"/>
-      <c r="AI3" s="27"/>
-      <c r="AJ3" s="28"/>
-      <c r="AK3" s="29"/>
+      <c r="AH3" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI3" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ3" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK3" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AL3" s="72">
         <f>IFERROR((VLOOKUP(AF3,Scoring!$A:$B,2,0))+IF(AH3="y",1,0)+IF(AI3="y",1,0)+IF(AJ3="y",1,0)+IF(AK3="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AM3" s="24"/>
       <c r="AN3" s="25"/>
-      <c r="AO3" s="26"/>
-      <c r="AP3" s="27"/>
-      <c r="AQ3" s="28"/>
-      <c r="AR3" s="29"/>
+      <c r="AO3" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP3" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ3" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR3" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AS3" s="72">
         <f>IFERROR((VLOOKUP(AM3,Scoring!$A:$B,2,0))+IF(AO3="y",1,0)+IF(AP3="y",1,0)+IF(AQ3="y",1,0)+IF(AR3="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AT3" s="24"/>
       <c r="AU3" s="25"/>
-      <c r="AV3" s="26"/>
-      <c r="AW3" s="27"/>
-      <c r="AX3" s="28"/>
-      <c r="AY3" s="29"/>
+      <c r="AV3" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AW3" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX3" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AY3" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AZ3" s="72">
         <f>IFERROR((VLOOKUP(AT3,Scoring!$A:$B,2,0))+IF(AV3="y",1,0)+IF(AW3="y",1,0)+IF(AX3="y",1,0)+IF(AY3="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BA3" s="24"/>
       <c r="BB3" s="25"/>
-      <c r="BC3" s="26"/>
-      <c r="BD3" s="27"/>
-      <c r="BE3" s="28"/>
-      <c r="BF3" s="29"/>
+      <c r="BC3" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BD3" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BE3" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="BF3" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="BG3" s="72">
         <f>IFERROR((VLOOKUP(BA3,Scoring!$A:$B,2,0))+IF(BC3="y",1,0)+IF(BD3="y",1,0)+IF(BE3="y",1,0)+IF(BF3="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BH3" s="24"/>
       <c r="BI3" s="25"/>
-      <c r="BJ3" s="26"/>
-      <c r="BK3" s="27"/>
-      <c r="BL3" s="28"/>
-      <c r="BM3" s="29"/>
+      <c r="BJ3" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK3" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL3" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM3" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="BN3" s="72">
         <f>IFERROR((VLOOKUP(BH3,Scoring!$A:$B,2,0))+IF(BJ3="y",1,0)+IF(BK3="y",1,0)+IF(BL3="y",1,0)+IF(BM3="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BO3" s="24"/>
       <c r="BP3" s="25"/>
-      <c r="BQ3" s="26"/>
-      <c r="BR3" s="27"/>
-      <c r="BS3" s="28"/>
-      <c r="BT3" s="29"/>
+      <c r="BQ3" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BR3" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BS3" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="BT3" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="BU3" s="72">
         <f>IFERROR((VLOOKUP(BO3,Scoring!$A:$B,2,0))+IF(BQ3="y",1,0)+IF(BR3="y",1,0)+IF(BS3="y",1,0)+IF(BT3="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BV3" s="24"/>
       <c r="BW3" s="25"/>
-      <c r="BX3" s="26"/>
-      <c r="BY3" s="27"/>
-      <c r="BZ3" s="28"/>
-      <c r="CA3" s="29"/>
+      <c r="BX3" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY3" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ3" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA3" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CB3" s="72">
         <f>IFERROR((VLOOKUP(BV3,Scoring!$A:$B,2,0))+IF(BX3="y",1,0)+IF(BY3="y",1,0)+IF(BZ3="y",1,0)+IF(CA3="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CC3" s="24"/>
       <c r="CD3" s="25"/>
-      <c r="CE3" s="26"/>
-      <c r="CF3" s="27"/>
-      <c r="CG3" s="28"/>
-      <c r="CH3" s="29"/>
+      <c r="CE3" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF3" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG3" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH3" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CI3" s="72">
         <f>IFERROR((VLOOKUP(CC3,Scoring!$A:$B,2,0))+IF(CE3="y",1,0)+IF(CF3="y",1,0)+IF(CG3="y",1,0)+IF(CH3="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CJ3" s="24"/>
       <c r="CK3" s="25"/>
-      <c r="CL3" s="26"/>
-      <c r="CM3" s="27"/>
-      <c r="CN3" s="28"/>
-      <c r="CO3" s="29"/>
+      <c r="CL3" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM3" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN3" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO3" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CP3" s="72">
         <f>IFERROR((VLOOKUP(CJ3,Scoring!$A:$B,2,0))+IF(CL3="y",1,0)+IF(CM3="y",1,0)+IF(CN3="y",1,0)+IF(CO3="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CQ3" s="24"/>
       <c r="CR3" s="25"/>
-      <c r="CS3" s="26"/>
-      <c r="CT3" s="27"/>
-      <c r="CU3" s="28"/>
-      <c r="CV3" s="29"/>
+      <c r="CS3" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CT3" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CU3" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CV3" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CW3" s="72">
         <f>IFERROR((VLOOKUP(CQ3,Scoring!$A:$B,2,0))+IF(CS3="y",1,0)+IF(CT3="y",1,0)+IF(CU3="y",1,0)+IF(CV3="y",1,0),0)</f>
         <v>0</v>
@@ -3220,12 +3372,8 @@
       <c r="C4" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="36">
-        <v>3.0</v>
-      </c>
-      <c r="E4" s="37">
-        <v>14.0</v>
-      </c>
+      <c r="D4" s="36"/>
+      <c r="E4" s="37"/>
       <c r="F4" s="38" t="s">
         <v>128</v>
       </c>
@@ -3233,21 +3381,17 @@
         <v>128</v>
       </c>
       <c r="H4" s="40" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I4" s="41" t="s">
         <v>128</v>
       </c>
       <c r="J4" s="71">
         <f>IFERROR((VLOOKUP(D4,Scoring!$A:$B,2,0))+IF(F4="y",1,0)+IF(G4="y",1,0)+IF(H4="y",1,0)+IF(I4="y",1,0),0)</f>
-        <v>16</v>
-      </c>
-      <c r="K4" s="36">
-        <v>6.0</v>
-      </c>
-      <c r="L4" s="37">
-        <v>3.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K4" s="36"/>
+      <c r="L4" s="37"/>
       <c r="M4" s="38" t="s">
         <v>128</v>
       </c>
@@ -3262,14 +3406,10 @@
       </c>
       <c r="Q4" s="71">
         <f>IFERROR((VLOOKUP(K4,Scoring!$A:$B,2,0))+IF(M4="y",1,0)+IF(N4="y",1,0)+IF(O4="y",1,0)+IF(P4="y",1,0),0)</f>
-        <v>8</v>
-      </c>
-      <c r="R4" s="36">
-        <v>12.0</v>
-      </c>
-      <c r="S4" s="37">
-        <v>12.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R4" s="36"/>
+      <c r="S4" s="37"/>
       <c r="T4" s="38" t="s">
         <v>128</v>
       </c>
@@ -3284,114 +3424,202 @@
       </c>
       <c r="X4" s="71">
         <f>IFERROR((VLOOKUP(R4,Scoring!$A:$B,2,0))+IF(T4="y",1,0)+IF(U4="y",1,0)+IF(V4="y",1,0)+IF(W4="y",1,0),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="36"/>
       <c r="Z4" s="37"/>
-      <c r="AA4" s="38"/>
-      <c r="AB4" s="39"/>
-      <c r="AC4" s="40"/>
-      <c r="AD4" s="41"/>
+      <c r="AA4" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB4" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC4" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD4" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="AE4" s="71">
         <f>IFERROR((VLOOKUP(Y4,Scoring!$A:$B,2,0))+IF(AA4="y",1,0)+IF(AB4="y",1,0)+IF(AC4="y",1,0)+IF(AD4="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AF4" s="36"/>
       <c r="AG4" s="37"/>
-      <c r="AH4" s="38"/>
-      <c r="AI4" s="39"/>
-      <c r="AJ4" s="40"/>
-      <c r="AK4" s="41"/>
+      <c r="AH4" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI4" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ4" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK4" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="AL4" s="71">
         <f>IFERROR((VLOOKUP(AF4,Scoring!$A:$B,2,0))+IF(AH4="y",1,0)+IF(AI4="y",1,0)+IF(AJ4="y",1,0)+IF(AK4="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AM4" s="36"/>
       <c r="AN4" s="37"/>
-      <c r="AO4" s="38"/>
-      <c r="AP4" s="39"/>
-      <c r="AQ4" s="40"/>
-      <c r="AR4" s="41"/>
+      <c r="AO4" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP4" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ4" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR4" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="AS4" s="71">
         <f>IFERROR((VLOOKUP(AM4,Scoring!$A:$B,2,0))+IF(AO4="y",1,0)+IF(AP4="y",1,0)+IF(AQ4="y",1,0)+IF(AR4="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AT4" s="36"/>
       <c r="AU4" s="37"/>
-      <c r="AV4" s="38"/>
-      <c r="AW4" s="39"/>
-      <c r="AX4" s="40"/>
-      <c r="AY4" s="41"/>
+      <c r="AV4" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="AW4" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX4" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="AY4" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="AZ4" s="71">
         <f>IFERROR((VLOOKUP(AT4,Scoring!$A:$B,2,0))+IF(AV4="y",1,0)+IF(AW4="y",1,0)+IF(AX4="y",1,0)+IF(AY4="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BA4" s="36"/>
       <c r="BB4" s="37"/>
-      <c r="BC4" s="38"/>
-      <c r="BD4" s="39"/>
-      <c r="BE4" s="40"/>
-      <c r="BF4" s="41"/>
+      <c r="BC4" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="BD4" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="BE4" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="BF4" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="BG4" s="71">
         <f>IFERROR((VLOOKUP(BA4,Scoring!$A:$B,2,0))+IF(BC4="y",1,0)+IF(BD4="y",1,0)+IF(BE4="y",1,0)+IF(BF4="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BH4" s="36"/>
       <c r="BI4" s="37"/>
-      <c r="BJ4" s="38"/>
-      <c r="BK4" s="39"/>
-      <c r="BL4" s="40"/>
-      <c r="BM4" s="41"/>
+      <c r="BJ4" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK4" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL4" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM4" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="BN4" s="71">
         <f>IFERROR((VLOOKUP(BH4,Scoring!$A:$B,2,0))+IF(BJ4="y",1,0)+IF(BK4="y",1,0)+IF(BL4="y",1,0)+IF(BM4="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BO4" s="36"/>
       <c r="BP4" s="37"/>
-      <c r="BQ4" s="38"/>
-      <c r="BR4" s="39"/>
-      <c r="BS4" s="40"/>
-      <c r="BT4" s="41"/>
+      <c r="BQ4" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="BR4" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="BS4" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="BT4" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="BU4" s="71">
         <f>IFERROR((VLOOKUP(BO4,Scoring!$A:$B,2,0))+IF(BQ4="y",1,0)+IF(BR4="y",1,0)+IF(BS4="y",1,0)+IF(BT4="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BV4" s="36"/>
       <c r="BW4" s="37"/>
-      <c r="BX4" s="38"/>
-      <c r="BY4" s="39"/>
-      <c r="BZ4" s="40"/>
-      <c r="CA4" s="41"/>
+      <c r="BX4" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY4" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ4" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA4" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="CB4" s="71">
         <f>IFERROR((VLOOKUP(BV4,Scoring!$A:$B,2,0))+IF(BX4="y",1,0)+IF(BY4="y",1,0)+IF(BZ4="y",1,0)+IF(CA4="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CC4" s="36"/>
       <c r="CD4" s="37"/>
-      <c r="CE4" s="38"/>
-      <c r="CF4" s="39"/>
-      <c r="CG4" s="40"/>
-      <c r="CH4" s="41"/>
+      <c r="CE4" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF4" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG4" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH4" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="CI4" s="71">
         <f>IFERROR((VLOOKUP(CC4,Scoring!$A:$B,2,0))+IF(CE4="y",1,0)+IF(CF4="y",1,0)+IF(CG4="y",1,0)+IF(CH4="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CJ4" s="36"/>
       <c r="CK4" s="37"/>
-      <c r="CL4" s="38"/>
-      <c r="CM4" s="39"/>
-      <c r="CN4" s="40"/>
-      <c r="CO4" s="41"/>
+      <c r="CL4" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM4" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN4" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO4" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="CP4" s="71">
         <f>IFERROR((VLOOKUP(CJ4,Scoring!$A:$B,2,0))+IF(CL4="y",1,0)+IF(CM4="y",1,0)+IF(CN4="y",1,0)+IF(CO4="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CQ4" s="36"/>
       <c r="CR4" s="37"/>
-      <c r="CS4" s="38"/>
-      <c r="CT4" s="39"/>
-      <c r="CU4" s="40"/>
-      <c r="CV4" s="41"/>
+      <c r="CS4" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="CT4" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="CU4" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="CV4" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="CW4" s="71">
         <f>IFERROR((VLOOKUP(CQ4,Scoring!$A:$B,2,0))+IF(CS4="y",1,0)+IF(CT4="y",1,0)+IF(CU4="y",1,0)+IF(CV4="y",1,0),0)</f>
         <v>0</v>
@@ -3410,12 +3638,8 @@
       <c r="C5" s="47" t="s">
         <v>395</v>
       </c>
-      <c r="D5" s="48">
-        <v>4.0</v>
-      </c>
-      <c r="E5" s="49">
-        <v>13.0</v>
-      </c>
+      <c r="D5" s="48"/>
+      <c r="E5" s="49"/>
       <c r="F5" s="50" t="s">
         <v>128</v>
       </c>
@@ -3426,18 +3650,14 @@
         <v>128</v>
       </c>
       <c r="I5" s="53" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J5" s="72">
         <f>IFERROR((VLOOKUP(D5,Scoring!$A:$B,2,0))+IF(F5="y",1,0)+IF(G5="y",1,0)+IF(H5="y",1,0)+IF(I5="y",1,0),0)</f>
-        <v>13</v>
-      </c>
-      <c r="K5" s="48">
-        <v>8.0</v>
-      </c>
-      <c r="L5" s="49">
-        <v>4.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K5" s="48"/>
+      <c r="L5" s="49"/>
       <c r="M5" s="50" t="s">
         <v>128</v>
       </c>
@@ -3452,14 +3672,10 @@
       </c>
       <c r="Q5" s="72">
         <f>IFERROR((VLOOKUP(K5,Scoring!$A:$B,2,0))+IF(M5="y",1,0)+IF(N5="y",1,0)+IF(O5="y",1,0)+IF(P5="y",1,0),0)</f>
-        <v>4</v>
-      </c>
-      <c r="R5" s="48">
-        <v>10.0</v>
-      </c>
-      <c r="S5" s="49">
-        <v>10.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R5" s="48"/>
+      <c r="S5" s="49"/>
       <c r="T5" s="50" t="s">
         <v>128</v>
       </c>
@@ -3474,114 +3690,202 @@
       </c>
       <c r="X5" s="72">
         <f>IFERROR((VLOOKUP(R5,Scoring!$A:$B,2,0))+IF(T5="y",1,0)+IF(U5="y",1,0)+IF(V5="y",1,0)+IF(W5="y",1,0),0)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="48"/>
       <c r="Z5" s="49"/>
-      <c r="AA5" s="50"/>
-      <c r="AB5" s="51"/>
-      <c r="AC5" s="52"/>
-      <c r="AD5" s="53"/>
+      <c r="AA5" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB5" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC5" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD5" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="AE5" s="72">
         <f>IFERROR((VLOOKUP(Y5,Scoring!$A:$B,2,0))+IF(AA5="y",1,0)+IF(AB5="y",1,0)+IF(AC5="y",1,0)+IF(AD5="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AF5" s="48"/>
       <c r="AG5" s="49"/>
-      <c r="AH5" s="50"/>
-      <c r="AI5" s="51"/>
-      <c r="AJ5" s="52"/>
-      <c r="AK5" s="53"/>
+      <c r="AH5" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI5" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ5" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK5" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="AL5" s="72">
         <f>IFERROR((VLOOKUP(AF5,Scoring!$A:$B,2,0))+IF(AH5="y",1,0)+IF(AI5="y",1,0)+IF(AJ5="y",1,0)+IF(AK5="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AM5" s="48"/>
       <c r="AN5" s="49"/>
-      <c r="AO5" s="50"/>
-      <c r="AP5" s="51"/>
-      <c r="AQ5" s="52"/>
-      <c r="AR5" s="53"/>
+      <c r="AO5" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP5" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ5" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR5" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="AS5" s="72">
         <f>IFERROR((VLOOKUP(AM5,Scoring!$A:$B,2,0))+IF(AO5="y",1,0)+IF(AP5="y",1,0)+IF(AQ5="y",1,0)+IF(AR5="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AT5" s="48"/>
       <c r="AU5" s="49"/>
-      <c r="AV5" s="50"/>
-      <c r="AW5" s="51"/>
-      <c r="AX5" s="52"/>
-      <c r="AY5" s="53"/>
+      <c r="AV5" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="AW5" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX5" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="AY5" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="AZ5" s="72">
         <f>IFERROR((VLOOKUP(AT5,Scoring!$A:$B,2,0))+IF(AV5="y",1,0)+IF(AW5="y",1,0)+IF(AX5="y",1,0)+IF(AY5="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BA5" s="48"/>
       <c r="BB5" s="49"/>
-      <c r="BC5" s="50"/>
-      <c r="BD5" s="51"/>
-      <c r="BE5" s="52"/>
-      <c r="BF5" s="53"/>
+      <c r="BC5" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="BD5" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="BE5" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="BF5" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="BG5" s="72">
         <f>IFERROR((VLOOKUP(BA5,Scoring!$A:$B,2,0))+IF(BC5="y",1,0)+IF(BD5="y",1,0)+IF(BE5="y",1,0)+IF(BF5="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BH5" s="48"/>
       <c r="BI5" s="49"/>
-      <c r="BJ5" s="50"/>
-      <c r="BK5" s="51"/>
-      <c r="BL5" s="52"/>
-      <c r="BM5" s="53"/>
+      <c r="BJ5" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK5" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL5" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM5" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="BN5" s="72">
         <f>IFERROR((VLOOKUP(BH5,Scoring!$A:$B,2,0))+IF(BJ5="y",1,0)+IF(BK5="y",1,0)+IF(BL5="y",1,0)+IF(BM5="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BO5" s="48"/>
       <c r="BP5" s="49"/>
-      <c r="BQ5" s="50"/>
-      <c r="BR5" s="51"/>
-      <c r="BS5" s="52"/>
-      <c r="BT5" s="53"/>
+      <c r="BQ5" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="BR5" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="BS5" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="BT5" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="BU5" s="72">
         <f>IFERROR((VLOOKUP(BO5,Scoring!$A:$B,2,0))+IF(BQ5="y",1,0)+IF(BR5="y",1,0)+IF(BS5="y",1,0)+IF(BT5="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BV5" s="48"/>
       <c r="BW5" s="49"/>
-      <c r="BX5" s="50"/>
-      <c r="BY5" s="51"/>
-      <c r="BZ5" s="52"/>
-      <c r="CA5" s="53"/>
+      <c r="BX5" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY5" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ5" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA5" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="CB5" s="72">
         <f>IFERROR((VLOOKUP(BV5,Scoring!$A:$B,2,0))+IF(BX5="y",1,0)+IF(BY5="y",1,0)+IF(BZ5="y",1,0)+IF(CA5="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CC5" s="48"/>
       <c r="CD5" s="49"/>
-      <c r="CE5" s="50"/>
-      <c r="CF5" s="51"/>
-      <c r="CG5" s="52"/>
-      <c r="CH5" s="53"/>
+      <c r="CE5" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF5" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG5" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH5" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="CI5" s="72">
         <f>IFERROR((VLOOKUP(CC5,Scoring!$A:$B,2,0))+IF(CE5="y",1,0)+IF(CF5="y",1,0)+IF(CG5="y",1,0)+IF(CH5="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CJ5" s="48"/>
       <c r="CK5" s="49"/>
-      <c r="CL5" s="50"/>
-      <c r="CM5" s="51"/>
-      <c r="CN5" s="52"/>
-      <c r="CO5" s="53"/>
+      <c r="CL5" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM5" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN5" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO5" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="CP5" s="72">
         <f>IFERROR((VLOOKUP(CJ5,Scoring!$A:$B,2,0))+IF(CL5="y",1,0)+IF(CM5="y",1,0)+IF(CN5="y",1,0)+IF(CO5="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CQ5" s="48"/>
       <c r="CR5" s="49"/>
-      <c r="CS5" s="50"/>
-      <c r="CT5" s="51"/>
-      <c r="CU5" s="52"/>
-      <c r="CV5" s="53"/>
+      <c r="CS5" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="CT5" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="CU5" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="CV5" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="CW5" s="72">
         <f>IFERROR((VLOOKUP(CQ5,Scoring!$A:$B,2,0))+IF(CS5="y",1,0)+IF(CT5="y",1,0)+IF(CU5="y",1,0)+IF(CV5="y",1,0),0)</f>
         <v>0</v>
@@ -3600,12 +3904,8 @@
       <c r="C6" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="24">
-        <v>5.0</v>
-      </c>
-      <c r="E6" s="25">
-        <v>12.0</v>
-      </c>
+      <c r="D6" s="24"/>
+      <c r="E6" s="25"/>
       <c r="F6" s="26" t="s">
         <v>128</v>
       </c>
@@ -3620,14 +3920,10 @@
       </c>
       <c r="J6" s="71">
         <f>IFERROR((VLOOKUP(D6,Scoring!$A:$B,2,0))+IF(F6="y",1,0)+IF(G6="y",1,0)+IF(H6="y",1,0)+IF(I6="y",1,0),0)</f>
-        <v>10</v>
-      </c>
-      <c r="K6" s="24">
-        <v>10.0</v>
-      </c>
-      <c r="L6" s="25">
-        <v>5.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K6" s="24"/>
+      <c r="L6" s="25"/>
       <c r="M6" s="26" t="s">
         <v>128</v>
       </c>
@@ -3642,14 +3938,10 @@
       </c>
       <c r="Q6" s="71">
         <f>IFERROR((VLOOKUP(K6,Scoring!$A:$B,2,0))+IF(M6="y",1,0)+IF(N6="y",1,0)+IF(O6="y",1,0)+IF(P6="y",1,0),0)</f>
-        <v>2</v>
-      </c>
-      <c r="R6" s="24">
-        <v>8.0</v>
-      </c>
-      <c r="S6" s="25">
-        <v>8.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R6" s="24"/>
+      <c r="S6" s="25"/>
       <c r="T6" s="26" t="s">
         <v>128</v>
       </c>
@@ -3664,114 +3956,202 @@
       </c>
       <c r="X6" s="71">
         <f>IFERROR((VLOOKUP(R6,Scoring!$A:$B,2,0))+IF(T6="y",1,0)+IF(U6="y",1,0)+IF(V6="y",1,0)+IF(W6="y",1,0),0)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="24"/>
       <c r="Z6" s="25"/>
-      <c r="AA6" s="26"/>
-      <c r="AB6" s="27"/>
-      <c r="AC6" s="28"/>
-      <c r="AD6" s="29"/>
+      <c r="AA6" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB6" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC6" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD6" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AE6" s="71">
         <f>IFERROR((VLOOKUP(Y6,Scoring!$A:$B,2,0))+IF(AA6="y",1,0)+IF(AB6="y",1,0)+IF(AC6="y",1,0)+IF(AD6="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AF6" s="24"/>
       <c r="AG6" s="25"/>
-      <c r="AH6" s="26"/>
-      <c r="AI6" s="27"/>
-      <c r="AJ6" s="28"/>
-      <c r="AK6" s="29"/>
+      <c r="AH6" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI6" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ6" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK6" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AL6" s="71">
         <f>IFERROR((VLOOKUP(AF6,Scoring!$A:$B,2,0))+IF(AH6="y",1,0)+IF(AI6="y",1,0)+IF(AJ6="y",1,0)+IF(AK6="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AM6" s="24"/>
       <c r="AN6" s="25"/>
-      <c r="AO6" s="26"/>
-      <c r="AP6" s="27"/>
-      <c r="AQ6" s="28"/>
-      <c r="AR6" s="29"/>
+      <c r="AO6" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP6" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ6" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR6" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AS6" s="71">
         <f>IFERROR((VLOOKUP(AM6,Scoring!$A:$B,2,0))+IF(AO6="y",1,0)+IF(AP6="y",1,0)+IF(AQ6="y",1,0)+IF(AR6="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AT6" s="24"/>
       <c r="AU6" s="25"/>
-      <c r="AV6" s="26"/>
-      <c r="AW6" s="27"/>
-      <c r="AX6" s="28"/>
-      <c r="AY6" s="29"/>
+      <c r="AV6" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AW6" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX6" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AY6" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AZ6" s="71">
         <f>IFERROR((VLOOKUP(AT6,Scoring!$A:$B,2,0))+IF(AV6="y",1,0)+IF(AW6="y",1,0)+IF(AX6="y",1,0)+IF(AY6="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BA6" s="24"/>
       <c r="BB6" s="25"/>
-      <c r="BC6" s="26"/>
-      <c r="BD6" s="27"/>
-      <c r="BE6" s="28"/>
-      <c r="BF6" s="29"/>
+      <c r="BC6" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BD6" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BE6" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="BF6" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="BG6" s="71">
         <f>IFERROR((VLOOKUP(BA6,Scoring!$A:$B,2,0))+IF(BC6="y",1,0)+IF(BD6="y",1,0)+IF(BE6="y",1,0)+IF(BF6="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BH6" s="24"/>
       <c r="BI6" s="25"/>
-      <c r="BJ6" s="26"/>
-      <c r="BK6" s="27"/>
-      <c r="BL6" s="28"/>
-      <c r="BM6" s="29"/>
+      <c r="BJ6" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK6" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL6" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM6" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="BN6" s="71">
         <f>IFERROR((VLOOKUP(BH6,Scoring!$A:$B,2,0))+IF(BJ6="y",1,0)+IF(BK6="y",1,0)+IF(BL6="y",1,0)+IF(BM6="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BO6" s="24"/>
       <c r="BP6" s="25"/>
-      <c r="BQ6" s="26"/>
-      <c r="BR6" s="27"/>
-      <c r="BS6" s="28"/>
-      <c r="BT6" s="29"/>
+      <c r="BQ6" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BR6" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BS6" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="BT6" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="BU6" s="71">
         <f>IFERROR((VLOOKUP(BO6,Scoring!$A:$B,2,0))+IF(BQ6="y",1,0)+IF(BR6="y",1,0)+IF(BS6="y",1,0)+IF(BT6="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BV6" s="24"/>
       <c r="BW6" s="25"/>
-      <c r="BX6" s="26"/>
-      <c r="BY6" s="27"/>
-      <c r="BZ6" s="28"/>
-      <c r="CA6" s="29"/>
+      <c r="BX6" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY6" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ6" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA6" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CB6" s="71">
         <f>IFERROR((VLOOKUP(BV6,Scoring!$A:$B,2,0))+IF(BX6="y",1,0)+IF(BY6="y",1,0)+IF(BZ6="y",1,0)+IF(CA6="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CC6" s="24"/>
       <c r="CD6" s="25"/>
-      <c r="CE6" s="26"/>
-      <c r="CF6" s="27"/>
-      <c r="CG6" s="28"/>
-      <c r="CH6" s="29"/>
+      <c r="CE6" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF6" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG6" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH6" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CI6" s="71">
         <f>IFERROR((VLOOKUP(CC6,Scoring!$A:$B,2,0))+IF(CE6="y",1,0)+IF(CF6="y",1,0)+IF(CG6="y",1,0)+IF(CH6="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CJ6" s="24"/>
       <c r="CK6" s="25"/>
-      <c r="CL6" s="26"/>
-      <c r="CM6" s="27"/>
-      <c r="CN6" s="28"/>
-      <c r="CO6" s="29"/>
+      <c r="CL6" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM6" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN6" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO6" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CP6" s="71">
         <f>IFERROR((VLOOKUP(CJ6,Scoring!$A:$B,2,0))+IF(CL6="y",1,0)+IF(CM6="y",1,0)+IF(CN6="y",1,0)+IF(CO6="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CQ6" s="24"/>
       <c r="CR6" s="25"/>
-      <c r="CS6" s="26"/>
-      <c r="CT6" s="27"/>
-      <c r="CU6" s="28"/>
-      <c r="CV6" s="29"/>
+      <c r="CS6" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CT6" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CU6" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CV6" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CW6" s="71">
         <f>IFERROR((VLOOKUP(CQ6,Scoring!$A:$B,2,0))+IF(CS6="y",1,0)+IF(CT6="y",1,0)+IF(CU6="y",1,0)+IF(CV6="y",1,0),0)</f>
         <v>0</v>
@@ -3790,12 +4170,8 @@
       <c r="C7" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="24">
-        <v>6.0</v>
-      </c>
-      <c r="E7" s="25">
-        <v>11.0</v>
-      </c>
+      <c r="D7" s="24"/>
+      <c r="E7" s="25"/>
       <c r="F7" s="26" t="s">
         <v>128</v>
       </c>
@@ -3810,14 +4186,10 @@
       </c>
       <c r="J7" s="72">
         <f>IFERROR((VLOOKUP(D7,Scoring!$A:$B,2,0))+IF(F7="y",1,0)+IF(G7="y",1,0)+IF(H7="y",1,0)+IF(I7="y",1,0),0)</f>
-        <v>8</v>
-      </c>
-      <c r="K7" s="24">
-        <v>12.0</v>
-      </c>
-      <c r="L7" s="25">
-        <v>6.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K7" s="24"/>
+      <c r="L7" s="25"/>
       <c r="M7" s="26" t="s">
         <v>128</v>
       </c>
@@ -3832,14 +4204,10 @@
       </c>
       <c r="Q7" s="72">
         <f>IFERROR((VLOOKUP(K7,Scoring!$A:$B,2,0))+IF(M7="y",1,0)+IF(N7="y",1,0)+IF(O7="y",1,0)+IF(P7="y",1,0),0)</f>
-        <v>1</v>
-      </c>
-      <c r="R7" s="24">
-        <v>6.0</v>
-      </c>
-      <c r="S7" s="25">
-        <v>6.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R7" s="24"/>
+      <c r="S7" s="25"/>
       <c r="T7" s="26" t="s">
         <v>128</v>
       </c>
@@ -3854,114 +4222,202 @@
       </c>
       <c r="X7" s="72">
         <f>IFERROR((VLOOKUP(R7,Scoring!$A:$B,2,0))+IF(T7="y",1,0)+IF(U7="y",1,0)+IF(V7="y",1,0)+IF(W7="y",1,0),0)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="24"/>
       <c r="Z7" s="25"/>
-      <c r="AA7" s="26"/>
-      <c r="AB7" s="27"/>
-      <c r="AC7" s="28"/>
-      <c r="AD7" s="29"/>
+      <c r="AA7" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB7" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC7" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD7" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AE7" s="72">
         <f>IFERROR((VLOOKUP(Y7,Scoring!$A:$B,2,0))+IF(AA7="y",1,0)+IF(AB7="y",1,0)+IF(AC7="y",1,0)+IF(AD7="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AF7" s="24"/>
       <c r="AG7" s="25"/>
-      <c r="AH7" s="26"/>
-      <c r="AI7" s="27"/>
-      <c r="AJ7" s="28"/>
-      <c r="AK7" s="29"/>
+      <c r="AH7" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI7" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ7" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK7" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AL7" s="72">
         <f>IFERROR((VLOOKUP(AF7,Scoring!$A:$B,2,0))+IF(AH7="y",1,0)+IF(AI7="y",1,0)+IF(AJ7="y",1,0)+IF(AK7="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AM7" s="24"/>
       <c r="AN7" s="25"/>
-      <c r="AO7" s="26"/>
-      <c r="AP7" s="27"/>
-      <c r="AQ7" s="28"/>
-      <c r="AR7" s="29"/>
+      <c r="AO7" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP7" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ7" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR7" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AS7" s="72">
         <f>IFERROR((VLOOKUP(AM7,Scoring!$A:$B,2,0))+IF(AO7="y",1,0)+IF(AP7="y",1,0)+IF(AQ7="y",1,0)+IF(AR7="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AT7" s="24"/>
       <c r="AU7" s="25"/>
-      <c r="AV7" s="26"/>
-      <c r="AW7" s="27"/>
-      <c r="AX7" s="28"/>
-      <c r="AY7" s="29"/>
+      <c r="AV7" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AW7" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX7" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AY7" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AZ7" s="72">
         <f>IFERROR((VLOOKUP(AT7,Scoring!$A:$B,2,0))+IF(AV7="y",1,0)+IF(AW7="y",1,0)+IF(AX7="y",1,0)+IF(AY7="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BA7" s="24"/>
       <c r="BB7" s="25"/>
-      <c r="BC7" s="26"/>
-      <c r="BD7" s="27"/>
-      <c r="BE7" s="28"/>
-      <c r="BF7" s="29"/>
+      <c r="BC7" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BD7" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BE7" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="BF7" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="BG7" s="72">
         <f>IFERROR((VLOOKUP(BA7,Scoring!$A:$B,2,0))+IF(BC7="y",1,0)+IF(BD7="y",1,0)+IF(BE7="y",1,0)+IF(BF7="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BH7" s="24"/>
       <c r="BI7" s="25"/>
-      <c r="BJ7" s="26"/>
-      <c r="BK7" s="27"/>
-      <c r="BL7" s="28"/>
-      <c r="BM7" s="29"/>
+      <c r="BJ7" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK7" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL7" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM7" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="BN7" s="72">
         <f>IFERROR((VLOOKUP(BH7,Scoring!$A:$B,2,0))+IF(BJ7="y",1,0)+IF(BK7="y",1,0)+IF(BL7="y",1,0)+IF(BM7="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BO7" s="24"/>
       <c r="BP7" s="25"/>
-      <c r="BQ7" s="26"/>
-      <c r="BR7" s="27"/>
-      <c r="BS7" s="28"/>
-      <c r="BT7" s="29"/>
+      <c r="BQ7" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BR7" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BS7" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="BT7" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="BU7" s="72">
         <f>IFERROR((VLOOKUP(BO7,Scoring!$A:$B,2,0))+IF(BQ7="y",1,0)+IF(BR7="y",1,0)+IF(BS7="y",1,0)+IF(BT7="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BV7" s="24"/>
       <c r="BW7" s="25"/>
-      <c r="BX7" s="26"/>
-      <c r="BY7" s="27"/>
-      <c r="BZ7" s="28"/>
-      <c r="CA7" s="29"/>
+      <c r="BX7" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY7" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ7" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA7" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CB7" s="72">
         <f>IFERROR((VLOOKUP(BV7,Scoring!$A:$B,2,0))+IF(BX7="y",1,0)+IF(BY7="y",1,0)+IF(BZ7="y",1,0)+IF(CA7="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CC7" s="24"/>
       <c r="CD7" s="25"/>
-      <c r="CE7" s="26"/>
-      <c r="CF7" s="27"/>
-      <c r="CG7" s="28"/>
-      <c r="CH7" s="29"/>
+      <c r="CE7" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF7" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG7" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH7" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CI7" s="72">
         <f>IFERROR((VLOOKUP(CC7,Scoring!$A:$B,2,0))+IF(CE7="y",1,0)+IF(CF7="y",1,0)+IF(CG7="y",1,0)+IF(CH7="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CJ7" s="24"/>
       <c r="CK7" s="25"/>
-      <c r="CL7" s="26"/>
-      <c r="CM7" s="27"/>
-      <c r="CN7" s="28"/>
-      <c r="CO7" s="29"/>
+      <c r="CL7" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM7" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN7" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO7" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CP7" s="72">
         <f>IFERROR((VLOOKUP(CJ7,Scoring!$A:$B,2,0))+IF(CL7="y",1,0)+IF(CM7="y",1,0)+IF(CN7="y",1,0)+IF(CO7="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CQ7" s="24"/>
       <c r="CR7" s="25"/>
-      <c r="CS7" s="26"/>
-      <c r="CT7" s="27"/>
-      <c r="CU7" s="28"/>
-      <c r="CV7" s="29"/>
+      <c r="CS7" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CT7" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CU7" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CV7" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CW7" s="72">
         <f>IFERROR((VLOOKUP(CQ7,Scoring!$A:$B,2,0))+IF(CS7="y",1,0)+IF(CT7="y",1,0)+IF(CU7="y",1,0)+IF(CV7="y",1,0),0)</f>
         <v>0</v>
@@ -3980,12 +4436,8 @@
       <c r="C8" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="36">
-        <v>7.0</v>
-      </c>
-      <c r="E8" s="37">
-        <v>10.0</v>
-      </c>
+      <c r="D8" s="36"/>
+      <c r="E8" s="37"/>
       <c r="F8" s="38" t="s">
         <v>128</v>
       </c>
@@ -4000,14 +4452,10 @@
       </c>
       <c r="J8" s="71">
         <f>IFERROR((VLOOKUP(D8,Scoring!$A:$B,2,0))+IF(F8="y",1,0)+IF(G8="y",1,0)+IF(H8="y",1,0)+IF(I8="y",1,0),0)</f>
-        <v>6</v>
-      </c>
-      <c r="K8" s="36">
-        <v>14.0</v>
-      </c>
-      <c r="L8" s="37">
-        <v>7.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K8" s="36"/>
+      <c r="L8" s="37"/>
       <c r="M8" s="38" t="s">
         <v>128</v>
       </c>
@@ -4022,14 +4470,10 @@
       </c>
       <c r="Q8" s="71">
         <f>IFERROR((VLOOKUP(K8,Scoring!$A:$B,2,0))+IF(M8="y",1,0)+IF(N8="y",1,0)+IF(O8="y",1,0)+IF(P8="y",1,0),0)</f>
-        <v>1</v>
-      </c>
-      <c r="R8" s="36">
-        <v>4.0</v>
-      </c>
-      <c r="S8" s="37">
-        <v>4.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R8" s="36"/>
+      <c r="S8" s="37"/>
       <c r="T8" s="38" t="s">
         <v>128</v>
       </c>
@@ -4044,114 +4488,202 @@
       </c>
       <c r="X8" s="71">
         <f>IFERROR((VLOOKUP(R8,Scoring!$A:$B,2,0))+IF(T8="y",1,0)+IF(U8="y",1,0)+IF(V8="y",1,0)+IF(W8="y",1,0),0)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="36"/>
       <c r="Z8" s="37"/>
-      <c r="AA8" s="38"/>
-      <c r="AB8" s="39"/>
-      <c r="AC8" s="40"/>
-      <c r="AD8" s="41"/>
+      <c r="AA8" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB8" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC8" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD8" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="AE8" s="71">
         <f>IFERROR((VLOOKUP(Y8,Scoring!$A:$B,2,0))+IF(AA8="y",1,0)+IF(AB8="y",1,0)+IF(AC8="y",1,0)+IF(AD8="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AF8" s="36"/>
       <c r="AG8" s="37"/>
-      <c r="AH8" s="38"/>
-      <c r="AI8" s="39"/>
-      <c r="AJ8" s="40"/>
-      <c r="AK8" s="41"/>
+      <c r="AH8" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI8" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ8" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK8" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="AL8" s="71">
         <f>IFERROR((VLOOKUP(AF8,Scoring!$A:$B,2,0))+IF(AH8="y",1,0)+IF(AI8="y",1,0)+IF(AJ8="y",1,0)+IF(AK8="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AM8" s="36"/>
       <c r="AN8" s="37"/>
-      <c r="AO8" s="38"/>
-      <c r="AP8" s="39"/>
-      <c r="AQ8" s="40"/>
-      <c r="AR8" s="41"/>
+      <c r="AO8" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP8" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ8" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR8" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="AS8" s="71">
         <f>IFERROR((VLOOKUP(AM8,Scoring!$A:$B,2,0))+IF(AO8="y",1,0)+IF(AP8="y",1,0)+IF(AQ8="y",1,0)+IF(AR8="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AT8" s="36"/>
       <c r="AU8" s="37"/>
-      <c r="AV8" s="38"/>
-      <c r="AW8" s="39"/>
-      <c r="AX8" s="40"/>
-      <c r="AY8" s="41"/>
+      <c r="AV8" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="AW8" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX8" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="AY8" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="AZ8" s="71">
         <f>IFERROR((VLOOKUP(AT8,Scoring!$A:$B,2,0))+IF(AV8="y",1,0)+IF(AW8="y",1,0)+IF(AX8="y",1,0)+IF(AY8="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BA8" s="36"/>
       <c r="BB8" s="37"/>
-      <c r="BC8" s="38"/>
-      <c r="BD8" s="39"/>
-      <c r="BE8" s="40"/>
-      <c r="BF8" s="41"/>
+      <c r="BC8" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="BD8" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="BE8" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="BF8" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="BG8" s="71">
         <f>IFERROR((VLOOKUP(BA8,Scoring!$A:$B,2,0))+IF(BC8="y",1,0)+IF(BD8="y",1,0)+IF(BE8="y",1,0)+IF(BF8="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BH8" s="36"/>
       <c r="BI8" s="37"/>
-      <c r="BJ8" s="38"/>
-      <c r="BK8" s="39"/>
-      <c r="BL8" s="40"/>
-      <c r="BM8" s="41"/>
+      <c r="BJ8" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK8" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL8" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM8" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="BN8" s="71">
         <f>IFERROR((VLOOKUP(BH8,Scoring!$A:$B,2,0))+IF(BJ8="y",1,0)+IF(BK8="y",1,0)+IF(BL8="y",1,0)+IF(BM8="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BO8" s="36"/>
       <c r="BP8" s="37"/>
-      <c r="BQ8" s="38"/>
-      <c r="BR8" s="39"/>
-      <c r="BS8" s="40"/>
-      <c r="BT8" s="41"/>
+      <c r="BQ8" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="BR8" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="BS8" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="BT8" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="BU8" s="71">
         <f>IFERROR((VLOOKUP(BO8,Scoring!$A:$B,2,0))+IF(BQ8="y",1,0)+IF(BR8="y",1,0)+IF(BS8="y",1,0)+IF(BT8="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BV8" s="36"/>
       <c r="BW8" s="37"/>
-      <c r="BX8" s="38"/>
-      <c r="BY8" s="39"/>
-      <c r="BZ8" s="40"/>
-      <c r="CA8" s="41"/>
+      <c r="BX8" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY8" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ8" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA8" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="CB8" s="71">
         <f>IFERROR((VLOOKUP(BV8,Scoring!$A:$B,2,0))+IF(BX8="y",1,0)+IF(BY8="y",1,0)+IF(BZ8="y",1,0)+IF(CA8="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CC8" s="36"/>
       <c r="CD8" s="37"/>
-      <c r="CE8" s="38"/>
-      <c r="CF8" s="39"/>
-      <c r="CG8" s="40"/>
-      <c r="CH8" s="41"/>
+      <c r="CE8" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF8" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG8" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH8" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="CI8" s="71">
         <f>IFERROR((VLOOKUP(CC8,Scoring!$A:$B,2,0))+IF(CE8="y",1,0)+IF(CF8="y",1,0)+IF(CG8="y",1,0)+IF(CH8="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CJ8" s="36"/>
       <c r="CK8" s="37"/>
-      <c r="CL8" s="38"/>
-      <c r="CM8" s="39"/>
-      <c r="CN8" s="40"/>
-      <c r="CO8" s="41"/>
+      <c r="CL8" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM8" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN8" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO8" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="CP8" s="71">
         <f>IFERROR((VLOOKUP(CJ8,Scoring!$A:$B,2,0))+IF(CL8="y",1,0)+IF(CM8="y",1,0)+IF(CN8="y",1,0)+IF(CO8="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CQ8" s="36"/>
       <c r="CR8" s="37"/>
-      <c r="CS8" s="38"/>
-      <c r="CT8" s="39"/>
-      <c r="CU8" s="40"/>
-      <c r="CV8" s="41"/>
+      <c r="CS8" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="CT8" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="CU8" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="CV8" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="CW8" s="71">
         <f>IFERROR((VLOOKUP(CQ8,Scoring!$A:$B,2,0))+IF(CS8="y",1,0)+IF(CT8="y",1,0)+IF(CU8="y",1,0)+IF(CV8="y",1,0),0)</f>
         <v>0</v>
@@ -4170,12 +4702,8 @@
       <c r="C9" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="48">
-        <v>8.0</v>
-      </c>
-      <c r="E9" s="49">
-        <v>9.0</v>
-      </c>
+      <c r="D9" s="48"/>
+      <c r="E9" s="49"/>
       <c r="F9" s="50" t="s">
         <v>128</v>
       </c>
@@ -4190,14 +4718,10 @@
       </c>
       <c r="J9" s="72">
         <f>IFERROR((VLOOKUP(D9,Scoring!$A:$B,2,0))+IF(F9="y",1,0)+IF(G9="y",1,0)+IF(H9="y",1,0)+IF(I9="y",1,0),0)</f>
-        <v>4</v>
-      </c>
-      <c r="K9" s="48">
-        <v>16.0</v>
-      </c>
-      <c r="L9" s="49">
-        <v>8.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K9" s="48"/>
+      <c r="L9" s="49"/>
       <c r="M9" s="50" t="s">
         <v>128</v>
       </c>
@@ -4212,14 +4736,10 @@
       </c>
       <c r="Q9" s="72">
         <f>IFERROR((VLOOKUP(K9,Scoring!$A:$B,2,0))+IF(M9="y",1,0)+IF(N9="y",1,0)+IF(O9="y",1,0)+IF(P9="y",1,0),0)</f>
-        <v>1</v>
-      </c>
-      <c r="R9" s="48">
-        <v>2.0</v>
-      </c>
-      <c r="S9" s="49">
-        <v>2.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R9" s="48"/>
+      <c r="S9" s="49"/>
       <c r="T9" s="50" t="s">
         <v>128</v>
       </c>
@@ -4234,114 +4754,202 @@
       </c>
       <c r="X9" s="72">
         <f>IFERROR((VLOOKUP(R9,Scoring!$A:$B,2,0))+IF(T9="y",1,0)+IF(U9="y",1,0)+IF(V9="y",1,0)+IF(W9="y",1,0),0)</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="48"/>
       <c r="Z9" s="49"/>
-      <c r="AA9" s="50"/>
-      <c r="AB9" s="51"/>
-      <c r="AC9" s="52"/>
-      <c r="AD9" s="53"/>
+      <c r="AA9" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB9" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC9" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD9" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="AE9" s="72">
         <f>IFERROR((VLOOKUP(Y9,Scoring!$A:$B,2,0))+IF(AA9="y",1,0)+IF(AB9="y",1,0)+IF(AC9="y",1,0)+IF(AD9="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AF9" s="48"/>
       <c r="AG9" s="49"/>
-      <c r="AH9" s="50"/>
-      <c r="AI9" s="51"/>
-      <c r="AJ9" s="52"/>
-      <c r="AK9" s="53"/>
+      <c r="AH9" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI9" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ9" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK9" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="AL9" s="72">
         <f>IFERROR((VLOOKUP(AF9,Scoring!$A:$B,2,0))+IF(AH9="y",1,0)+IF(AI9="y",1,0)+IF(AJ9="y",1,0)+IF(AK9="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AM9" s="48"/>
       <c r="AN9" s="49"/>
-      <c r="AO9" s="50"/>
-      <c r="AP9" s="51"/>
-      <c r="AQ9" s="52"/>
-      <c r="AR9" s="53"/>
+      <c r="AO9" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP9" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ9" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR9" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="AS9" s="72">
         <f>IFERROR((VLOOKUP(AM9,Scoring!$A:$B,2,0))+IF(AO9="y",1,0)+IF(AP9="y",1,0)+IF(AQ9="y",1,0)+IF(AR9="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AT9" s="48"/>
       <c r="AU9" s="49"/>
-      <c r="AV9" s="50"/>
-      <c r="AW9" s="51"/>
-      <c r="AX9" s="52"/>
-      <c r="AY9" s="53"/>
+      <c r="AV9" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="AW9" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX9" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="AY9" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="AZ9" s="72">
         <f>IFERROR((VLOOKUP(AT9,Scoring!$A:$B,2,0))+IF(AV9="y",1,0)+IF(AW9="y",1,0)+IF(AX9="y",1,0)+IF(AY9="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BA9" s="48"/>
       <c r="BB9" s="49"/>
-      <c r="BC9" s="50"/>
-      <c r="BD9" s="51"/>
-      <c r="BE9" s="52"/>
-      <c r="BF9" s="53"/>
+      <c r="BC9" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="BD9" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="BE9" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="BF9" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="BG9" s="72">
         <f>IFERROR((VLOOKUP(BA9,Scoring!$A:$B,2,0))+IF(BC9="y",1,0)+IF(BD9="y",1,0)+IF(BE9="y",1,0)+IF(BF9="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BH9" s="48"/>
       <c r="BI9" s="49"/>
-      <c r="BJ9" s="50"/>
-      <c r="BK9" s="51"/>
-      <c r="BL9" s="52"/>
-      <c r="BM9" s="53"/>
+      <c r="BJ9" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK9" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL9" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM9" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="BN9" s="72">
         <f>IFERROR((VLOOKUP(BH9,Scoring!$A:$B,2,0))+IF(BJ9="y",1,0)+IF(BK9="y",1,0)+IF(BL9="y",1,0)+IF(BM9="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BO9" s="48"/>
       <c r="BP9" s="49"/>
-      <c r="BQ9" s="50"/>
-      <c r="BR9" s="51"/>
-      <c r="BS9" s="52"/>
-      <c r="BT9" s="53"/>
+      <c r="BQ9" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="BR9" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="BS9" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="BT9" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="BU9" s="72">
         <f>IFERROR((VLOOKUP(BO9,Scoring!$A:$B,2,0))+IF(BQ9="y",1,0)+IF(BR9="y",1,0)+IF(BS9="y",1,0)+IF(BT9="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BV9" s="48"/>
       <c r="BW9" s="49"/>
-      <c r="BX9" s="50"/>
-      <c r="BY9" s="51"/>
-      <c r="BZ9" s="52"/>
-      <c r="CA9" s="53"/>
+      <c r="BX9" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY9" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ9" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA9" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="CB9" s="72">
         <f>IFERROR((VLOOKUP(BV9,Scoring!$A:$B,2,0))+IF(BX9="y",1,0)+IF(BY9="y",1,0)+IF(BZ9="y",1,0)+IF(CA9="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CC9" s="48"/>
       <c r="CD9" s="49"/>
-      <c r="CE9" s="50"/>
-      <c r="CF9" s="51"/>
-      <c r="CG9" s="52"/>
-      <c r="CH9" s="53"/>
+      <c r="CE9" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF9" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG9" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH9" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="CI9" s="72">
         <f>IFERROR((VLOOKUP(CC9,Scoring!$A:$B,2,0))+IF(CE9="y",1,0)+IF(CF9="y",1,0)+IF(CG9="y",1,0)+IF(CH9="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CJ9" s="48"/>
       <c r="CK9" s="49"/>
-      <c r="CL9" s="50"/>
-      <c r="CM9" s="51"/>
-      <c r="CN9" s="52"/>
-      <c r="CO9" s="53"/>
+      <c r="CL9" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM9" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN9" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO9" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="CP9" s="72">
         <f>IFERROR((VLOOKUP(CJ9,Scoring!$A:$B,2,0))+IF(CL9="y",1,0)+IF(CM9="y",1,0)+IF(CN9="y",1,0)+IF(CO9="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CQ9" s="48"/>
       <c r="CR9" s="49"/>
-      <c r="CS9" s="50"/>
-      <c r="CT9" s="51"/>
-      <c r="CU9" s="52"/>
-      <c r="CV9" s="53"/>
+      <c r="CS9" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="CT9" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="CU9" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="CV9" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="CW9" s="72">
         <f>IFERROR((VLOOKUP(CQ9,Scoring!$A:$B,2,0))+IF(CS9="y",1,0)+IF(CT9="y",1,0)+IF(CU9="y",1,0)+IF(CV9="y",1,0),0)</f>
         <v>0</v>
@@ -4360,12 +4968,8 @@
       <c r="C10" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="24">
-        <v>9.0</v>
-      </c>
-      <c r="E10" s="25">
-        <v>8.0</v>
-      </c>
+      <c r="D10" s="24"/>
+      <c r="E10" s="25"/>
       <c r="F10" s="26" t="s">
         <v>128</v>
       </c>
@@ -4380,14 +4984,10 @@
       </c>
       <c r="J10" s="71">
         <f>IFERROR((VLOOKUP(D10,Scoring!$A:$B,2,0))+IF(F10="y",1,0)+IF(G10="y",1,0)+IF(H10="y",1,0)+IF(I10="y",1,0),0)</f>
-        <v>3</v>
-      </c>
-      <c r="K10" s="24">
-        <v>1.0</v>
-      </c>
-      <c r="L10" s="25">
-        <v>9.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K10" s="24"/>
+      <c r="L10" s="25"/>
       <c r="M10" s="26" t="s">
         <v>128</v>
       </c>
@@ -4402,14 +5002,10 @@
       </c>
       <c r="Q10" s="71">
         <f>IFERROR((VLOOKUP(K10,Scoring!$A:$B,2,0))+IF(M10="y",1,0)+IF(N10="y",1,0)+IF(O10="y",1,0)+IF(P10="y",1,0),0)</f>
-        <v>25</v>
-      </c>
-      <c r="R10" s="24">
-        <v>15.0</v>
-      </c>
-      <c r="S10" s="25">
-        <v>1.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R10" s="24"/>
+      <c r="S10" s="25"/>
       <c r="T10" s="26" t="s">
         <v>128</v>
       </c>
@@ -4424,114 +5020,202 @@
       </c>
       <c r="X10" s="71">
         <f>IFERROR((VLOOKUP(R10,Scoring!$A:$B,2,0))+IF(T10="y",1,0)+IF(U10="y",1,0)+IF(V10="y",1,0)+IF(W10="y",1,0),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="24"/>
       <c r="Z10" s="25"/>
-      <c r="AA10" s="26"/>
-      <c r="AB10" s="27"/>
-      <c r="AC10" s="28"/>
-      <c r="AD10" s="29"/>
+      <c r="AA10" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB10" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC10" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD10" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AE10" s="71">
         <f>IFERROR((VLOOKUP(Y10,Scoring!$A:$B,2,0))+IF(AA10="y",1,0)+IF(AB10="y",1,0)+IF(AC10="y",1,0)+IF(AD10="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AF10" s="24"/>
       <c r="AG10" s="25"/>
-      <c r="AH10" s="26"/>
-      <c r="AI10" s="27"/>
-      <c r="AJ10" s="28"/>
-      <c r="AK10" s="29"/>
+      <c r="AH10" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI10" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ10" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK10" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AL10" s="71">
         <f>IFERROR((VLOOKUP(AF10,Scoring!$A:$B,2,0))+IF(AH10="y",1,0)+IF(AI10="y",1,0)+IF(AJ10="y",1,0)+IF(AK10="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AM10" s="24"/>
       <c r="AN10" s="25"/>
-      <c r="AO10" s="26"/>
-      <c r="AP10" s="27"/>
-      <c r="AQ10" s="28"/>
-      <c r="AR10" s="29"/>
+      <c r="AO10" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP10" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ10" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR10" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AS10" s="71">
         <f>IFERROR((VLOOKUP(AM10,Scoring!$A:$B,2,0))+IF(AO10="y",1,0)+IF(AP10="y",1,0)+IF(AQ10="y",1,0)+IF(AR10="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AT10" s="24"/>
       <c r="AU10" s="25"/>
-      <c r="AV10" s="26"/>
-      <c r="AW10" s="27"/>
-      <c r="AX10" s="28"/>
-      <c r="AY10" s="29"/>
+      <c r="AV10" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AW10" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX10" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AY10" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AZ10" s="71">
         <f>IFERROR((VLOOKUP(AT10,Scoring!$A:$B,2,0))+IF(AV10="y",1,0)+IF(AW10="y",1,0)+IF(AX10="y",1,0)+IF(AY10="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BA10" s="24"/>
       <c r="BB10" s="25"/>
-      <c r="BC10" s="26"/>
-      <c r="BD10" s="27"/>
-      <c r="BE10" s="28"/>
-      <c r="BF10" s="29"/>
+      <c r="BC10" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BD10" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BE10" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="BF10" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="BG10" s="71">
         <f>IFERROR((VLOOKUP(BA10,Scoring!$A:$B,2,0))+IF(BC10="y",1,0)+IF(BD10="y",1,0)+IF(BE10="y",1,0)+IF(BF10="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BH10" s="24"/>
       <c r="BI10" s="25"/>
-      <c r="BJ10" s="26"/>
-      <c r="BK10" s="27"/>
-      <c r="BL10" s="28"/>
-      <c r="BM10" s="29"/>
+      <c r="BJ10" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK10" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL10" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM10" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="BN10" s="71">
         <f>IFERROR((VLOOKUP(BH10,Scoring!$A:$B,2,0))+IF(BJ10="y",1,0)+IF(BK10="y",1,0)+IF(BL10="y",1,0)+IF(BM10="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BO10" s="24"/>
       <c r="BP10" s="25"/>
-      <c r="BQ10" s="26"/>
-      <c r="BR10" s="27"/>
-      <c r="BS10" s="28"/>
-      <c r="BT10" s="29"/>
+      <c r="BQ10" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BR10" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BS10" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="BT10" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="BU10" s="71">
         <f>IFERROR((VLOOKUP(BO10,Scoring!$A:$B,2,0))+IF(BQ10="y",1,0)+IF(BR10="y",1,0)+IF(BS10="y",1,0)+IF(BT10="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BV10" s="24"/>
       <c r="BW10" s="25"/>
-      <c r="BX10" s="26"/>
-      <c r="BY10" s="27"/>
-      <c r="BZ10" s="28"/>
-      <c r="CA10" s="29"/>
+      <c r="BX10" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY10" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ10" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA10" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CB10" s="71">
         <f>IFERROR((VLOOKUP(BV10,Scoring!$A:$B,2,0))+IF(BX10="y",1,0)+IF(BY10="y",1,0)+IF(BZ10="y",1,0)+IF(CA10="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CC10" s="24"/>
       <c r="CD10" s="25"/>
-      <c r="CE10" s="26"/>
-      <c r="CF10" s="27"/>
-      <c r="CG10" s="28"/>
-      <c r="CH10" s="29"/>
+      <c r="CE10" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF10" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG10" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH10" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CI10" s="71">
         <f>IFERROR((VLOOKUP(CC10,Scoring!$A:$B,2,0))+IF(CE10="y",1,0)+IF(CF10="y",1,0)+IF(CG10="y",1,0)+IF(CH10="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CJ10" s="24"/>
       <c r="CK10" s="25"/>
-      <c r="CL10" s="26"/>
-      <c r="CM10" s="27"/>
-      <c r="CN10" s="28"/>
-      <c r="CO10" s="29"/>
+      <c r="CL10" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM10" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN10" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO10" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CP10" s="71">
         <f>IFERROR((VLOOKUP(CJ10,Scoring!$A:$B,2,0))+IF(CL10="y",1,0)+IF(CM10="y",1,0)+IF(CN10="y",1,0)+IF(CO10="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CQ10" s="24"/>
       <c r="CR10" s="25"/>
-      <c r="CS10" s="26"/>
-      <c r="CT10" s="27"/>
-      <c r="CU10" s="28"/>
-      <c r="CV10" s="29"/>
+      <c r="CS10" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CT10" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CU10" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CV10" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CW10" s="71">
         <f>IFERROR((VLOOKUP(CQ10,Scoring!$A:$B,2,0))+IF(CS10="y",1,0)+IF(CT10="y",1,0)+IF(CU10="y",1,0)+IF(CV10="y",1,0),0)</f>
         <v>0</v>
@@ -4550,12 +5234,8 @@
       <c r="C11" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="D11" s="24">
-        <v>10.0</v>
-      </c>
-      <c r="E11" s="25">
-        <v>7.0</v>
-      </c>
+      <c r="D11" s="24"/>
+      <c r="E11" s="25"/>
       <c r="F11" s="26" t="s">
         <v>128</v>
       </c>
@@ -4570,14 +5250,10 @@
       </c>
       <c r="J11" s="72">
         <f>IFERROR((VLOOKUP(D11,Scoring!$A:$B,2,0))+IF(F11="y",1,0)+IF(G11="y",1,0)+IF(H11="y",1,0)+IF(I11="y",1,0),0)</f>
-        <v>2</v>
-      </c>
-      <c r="K11" s="24">
-        <v>3.0</v>
-      </c>
-      <c r="L11" s="25">
-        <v>10.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K11" s="24"/>
+      <c r="L11" s="25"/>
       <c r="M11" s="26" t="s">
         <v>128</v>
       </c>
@@ -4592,14 +5268,10 @@
       </c>
       <c r="Q11" s="72">
         <f>IFERROR((VLOOKUP(K11,Scoring!$A:$B,2,0))+IF(M11="y",1,0)+IF(N11="y",1,0)+IF(O11="y",1,0)+IF(P11="y",1,0),0)</f>
-        <v>15</v>
-      </c>
-      <c r="R11" s="24">
-        <v>13.0</v>
-      </c>
-      <c r="S11" s="25">
-        <v>3.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R11" s="24"/>
+      <c r="S11" s="25"/>
       <c r="T11" s="26" t="s">
         <v>128</v>
       </c>
@@ -4614,114 +5286,202 @@
       </c>
       <c r="X11" s="72">
         <f>IFERROR((VLOOKUP(R11,Scoring!$A:$B,2,0))+IF(T11="y",1,0)+IF(U11="y",1,0)+IF(V11="y",1,0)+IF(W11="y",1,0),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y11" s="24"/>
       <c r="Z11" s="25"/>
-      <c r="AA11" s="26"/>
-      <c r="AB11" s="27"/>
-      <c r="AC11" s="28"/>
-      <c r="AD11" s="29"/>
+      <c r="AA11" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB11" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC11" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD11" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AE11" s="72">
         <f>IFERROR((VLOOKUP(Y11,Scoring!$A:$B,2,0))+IF(AA11="y",1,0)+IF(AB11="y",1,0)+IF(AC11="y",1,0)+IF(AD11="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AF11" s="24"/>
       <c r="AG11" s="25"/>
-      <c r="AH11" s="26"/>
-      <c r="AI11" s="27"/>
-      <c r="AJ11" s="28"/>
-      <c r="AK11" s="29"/>
+      <c r="AH11" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI11" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ11" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK11" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AL11" s="72">
         <f>IFERROR((VLOOKUP(AF11,Scoring!$A:$B,2,0))+IF(AH11="y",1,0)+IF(AI11="y",1,0)+IF(AJ11="y",1,0)+IF(AK11="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AM11" s="24"/>
       <c r="AN11" s="25"/>
-      <c r="AO11" s="26"/>
-      <c r="AP11" s="27"/>
-      <c r="AQ11" s="28"/>
-      <c r="AR11" s="29"/>
+      <c r="AO11" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP11" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ11" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR11" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AS11" s="72">
         <f>IFERROR((VLOOKUP(AM11,Scoring!$A:$B,2,0))+IF(AO11="y",1,0)+IF(AP11="y",1,0)+IF(AQ11="y",1,0)+IF(AR11="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AT11" s="24"/>
       <c r="AU11" s="25"/>
-      <c r="AV11" s="26"/>
-      <c r="AW11" s="27"/>
-      <c r="AX11" s="28"/>
-      <c r="AY11" s="29"/>
+      <c r="AV11" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AW11" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX11" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AY11" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AZ11" s="72">
         <f>IFERROR((VLOOKUP(AT11,Scoring!$A:$B,2,0))+IF(AV11="y",1,0)+IF(AW11="y",1,0)+IF(AX11="y",1,0)+IF(AY11="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BA11" s="24"/>
       <c r="BB11" s="25"/>
-      <c r="BC11" s="26"/>
-      <c r="BD11" s="27"/>
-      <c r="BE11" s="28"/>
-      <c r="BF11" s="29"/>
+      <c r="BC11" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BD11" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BE11" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="BF11" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="BG11" s="72">
         <f>IFERROR((VLOOKUP(BA11,Scoring!$A:$B,2,0))+IF(BC11="y",1,0)+IF(BD11="y",1,0)+IF(BE11="y",1,0)+IF(BF11="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BH11" s="24"/>
       <c r="BI11" s="25"/>
-      <c r="BJ11" s="26"/>
-      <c r="BK11" s="27"/>
-      <c r="BL11" s="28"/>
-      <c r="BM11" s="29"/>
+      <c r="BJ11" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK11" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL11" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM11" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="BN11" s="72">
         <f>IFERROR((VLOOKUP(BH11,Scoring!$A:$B,2,0))+IF(BJ11="y",1,0)+IF(BK11="y",1,0)+IF(BL11="y",1,0)+IF(BM11="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BO11" s="24"/>
       <c r="BP11" s="25"/>
-      <c r="BQ11" s="26"/>
-      <c r="BR11" s="27"/>
-      <c r="BS11" s="28"/>
-      <c r="BT11" s="29"/>
+      <c r="BQ11" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BR11" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BS11" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="BT11" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="BU11" s="72">
         <f>IFERROR((VLOOKUP(BO11,Scoring!$A:$B,2,0))+IF(BQ11="y",1,0)+IF(BR11="y",1,0)+IF(BS11="y",1,0)+IF(BT11="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BV11" s="24"/>
       <c r="BW11" s="25"/>
-      <c r="BX11" s="26"/>
-      <c r="BY11" s="27"/>
-      <c r="BZ11" s="28"/>
-      <c r="CA11" s="29"/>
+      <c r="BX11" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY11" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ11" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA11" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CB11" s="72">
         <f>IFERROR((VLOOKUP(BV11,Scoring!$A:$B,2,0))+IF(BX11="y",1,0)+IF(BY11="y",1,0)+IF(BZ11="y",1,0)+IF(CA11="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CC11" s="24"/>
       <c r="CD11" s="25"/>
-      <c r="CE11" s="26"/>
-      <c r="CF11" s="27"/>
-      <c r="CG11" s="28"/>
-      <c r="CH11" s="29"/>
+      <c r="CE11" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF11" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG11" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH11" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CI11" s="72">
         <f>IFERROR((VLOOKUP(CC11,Scoring!$A:$B,2,0))+IF(CE11="y",1,0)+IF(CF11="y",1,0)+IF(CG11="y",1,0)+IF(CH11="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CJ11" s="24"/>
       <c r="CK11" s="25"/>
-      <c r="CL11" s="26"/>
-      <c r="CM11" s="27"/>
-      <c r="CN11" s="28"/>
-      <c r="CO11" s="29"/>
+      <c r="CL11" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM11" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN11" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO11" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CP11" s="72">
         <f>IFERROR((VLOOKUP(CJ11,Scoring!$A:$B,2,0))+IF(CL11="y",1,0)+IF(CM11="y",1,0)+IF(CN11="y",1,0)+IF(CO11="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CQ11" s="24"/>
       <c r="CR11" s="25"/>
-      <c r="CS11" s="26"/>
-      <c r="CT11" s="27"/>
-      <c r="CU11" s="28"/>
-      <c r="CV11" s="29"/>
+      <c r="CS11" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CT11" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CU11" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CV11" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CW11" s="72">
         <f>IFERROR((VLOOKUP(CQ11,Scoring!$A:$B,2,0))+IF(CS11="y",1,0)+IF(CT11="y",1,0)+IF(CU11="y",1,0)+IF(CV11="y",1,0),0)</f>
         <v>0</v>
@@ -4740,12 +5500,8 @@
       <c r="C12" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="36">
-        <v>11.0</v>
-      </c>
-      <c r="E12" s="37">
-        <v>6.0</v>
-      </c>
+      <c r="D12" s="36"/>
+      <c r="E12" s="37"/>
       <c r="F12" s="38" t="s">
         <v>128</v>
       </c>
@@ -4760,14 +5516,10 @@
       </c>
       <c r="J12" s="71">
         <f>IFERROR((VLOOKUP(D12,Scoring!$A:$B,2,0))+IF(F12="y",1,0)+IF(G12="y",1,0)+IF(H12="y",1,0)+IF(I12="y",1,0),0)</f>
-        <v>1</v>
-      </c>
-      <c r="K12" s="36">
-        <v>5.0</v>
-      </c>
-      <c r="L12" s="37">
-        <v>11.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K12" s="36"/>
+      <c r="L12" s="37"/>
       <c r="M12" s="38" t="s">
         <v>128</v>
       </c>
@@ -4782,14 +5534,10 @@
       </c>
       <c r="Q12" s="71">
         <f>IFERROR((VLOOKUP(K12,Scoring!$A:$B,2,0))+IF(M12="y",1,0)+IF(N12="y",1,0)+IF(O12="y",1,0)+IF(P12="y",1,0),0)</f>
-        <v>10</v>
-      </c>
-      <c r="R12" s="36">
-        <v>11.0</v>
-      </c>
-      <c r="S12" s="37">
-        <v>5.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R12" s="36"/>
+      <c r="S12" s="37"/>
       <c r="T12" s="38" t="s">
         <v>128</v>
       </c>
@@ -4804,114 +5552,202 @@
       </c>
       <c r="X12" s="71">
         <f>IFERROR((VLOOKUP(R12,Scoring!$A:$B,2,0))+IF(T12="y",1,0)+IF(U12="y",1,0)+IF(V12="y",1,0)+IF(W12="y",1,0),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="36"/>
       <c r="Z12" s="37"/>
-      <c r="AA12" s="38"/>
-      <c r="AB12" s="39"/>
-      <c r="AC12" s="40"/>
-      <c r="AD12" s="41"/>
+      <c r="AA12" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB12" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC12" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD12" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="AE12" s="71">
         <f>IFERROR((VLOOKUP(Y12,Scoring!$A:$B,2,0))+IF(AA12="y",1,0)+IF(AB12="y",1,0)+IF(AC12="y",1,0)+IF(AD12="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AF12" s="36"/>
       <c r="AG12" s="37"/>
-      <c r="AH12" s="38"/>
-      <c r="AI12" s="39"/>
-      <c r="AJ12" s="40"/>
-      <c r="AK12" s="41"/>
+      <c r="AH12" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI12" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ12" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK12" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="AL12" s="71">
         <f>IFERROR((VLOOKUP(AF12,Scoring!$A:$B,2,0))+IF(AH12="y",1,0)+IF(AI12="y",1,0)+IF(AJ12="y",1,0)+IF(AK12="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AM12" s="36"/>
       <c r="AN12" s="37"/>
-      <c r="AO12" s="38"/>
-      <c r="AP12" s="39"/>
-      <c r="AQ12" s="40"/>
-      <c r="AR12" s="41"/>
+      <c r="AO12" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP12" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ12" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR12" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="AS12" s="71">
         <f>IFERROR((VLOOKUP(AM12,Scoring!$A:$B,2,0))+IF(AO12="y",1,0)+IF(AP12="y",1,0)+IF(AQ12="y",1,0)+IF(AR12="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AT12" s="36"/>
       <c r="AU12" s="37"/>
-      <c r="AV12" s="38"/>
-      <c r="AW12" s="39"/>
-      <c r="AX12" s="40"/>
-      <c r="AY12" s="41"/>
+      <c r="AV12" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="AW12" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX12" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="AY12" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="AZ12" s="71">
         <f>IFERROR((VLOOKUP(AT12,Scoring!$A:$B,2,0))+IF(AV12="y",1,0)+IF(AW12="y",1,0)+IF(AX12="y",1,0)+IF(AY12="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BA12" s="36"/>
       <c r="BB12" s="37"/>
-      <c r="BC12" s="38"/>
-      <c r="BD12" s="39"/>
-      <c r="BE12" s="40"/>
-      <c r="BF12" s="41"/>
+      <c r="BC12" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="BD12" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="BE12" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="BF12" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="BG12" s="71">
         <f>IFERROR((VLOOKUP(BA12,Scoring!$A:$B,2,0))+IF(BC12="y",1,0)+IF(BD12="y",1,0)+IF(BE12="y",1,0)+IF(BF12="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BH12" s="36"/>
       <c r="BI12" s="37"/>
-      <c r="BJ12" s="38"/>
-      <c r="BK12" s="39"/>
-      <c r="BL12" s="40"/>
-      <c r="BM12" s="41"/>
+      <c r="BJ12" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK12" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL12" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM12" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="BN12" s="71">
         <f>IFERROR((VLOOKUP(BH12,Scoring!$A:$B,2,0))+IF(BJ12="y",1,0)+IF(BK12="y",1,0)+IF(BL12="y",1,0)+IF(BM12="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BO12" s="36"/>
       <c r="BP12" s="37"/>
-      <c r="BQ12" s="38"/>
-      <c r="BR12" s="39"/>
-      <c r="BS12" s="40"/>
-      <c r="BT12" s="41"/>
+      <c r="BQ12" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="BR12" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="BS12" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="BT12" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="BU12" s="71">
         <f>IFERROR((VLOOKUP(BO12,Scoring!$A:$B,2,0))+IF(BQ12="y",1,0)+IF(BR12="y",1,0)+IF(BS12="y",1,0)+IF(BT12="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BV12" s="36"/>
       <c r="BW12" s="37"/>
-      <c r="BX12" s="38"/>
-      <c r="BY12" s="39"/>
-      <c r="BZ12" s="40"/>
-      <c r="CA12" s="41"/>
+      <c r="BX12" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY12" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ12" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA12" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="CB12" s="71">
         <f>IFERROR((VLOOKUP(BV12,Scoring!$A:$B,2,0))+IF(BX12="y",1,0)+IF(BY12="y",1,0)+IF(BZ12="y",1,0)+IF(CA12="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CC12" s="36"/>
       <c r="CD12" s="37"/>
-      <c r="CE12" s="38"/>
-      <c r="CF12" s="39"/>
-      <c r="CG12" s="40"/>
-      <c r="CH12" s="41"/>
+      <c r="CE12" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF12" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG12" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH12" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="CI12" s="71">
         <f>IFERROR((VLOOKUP(CC12,Scoring!$A:$B,2,0))+IF(CE12="y",1,0)+IF(CF12="y",1,0)+IF(CG12="y",1,0)+IF(CH12="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CJ12" s="36"/>
       <c r="CK12" s="37"/>
-      <c r="CL12" s="38"/>
-      <c r="CM12" s="39"/>
-      <c r="CN12" s="40"/>
-      <c r="CO12" s="41"/>
+      <c r="CL12" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM12" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN12" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO12" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="CP12" s="71">
         <f>IFERROR((VLOOKUP(CJ12,Scoring!$A:$B,2,0))+IF(CL12="y",1,0)+IF(CM12="y",1,0)+IF(CN12="y",1,0)+IF(CO12="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CQ12" s="36"/>
       <c r="CR12" s="37"/>
-      <c r="CS12" s="38"/>
-      <c r="CT12" s="39"/>
-      <c r="CU12" s="40"/>
-      <c r="CV12" s="41"/>
+      <c r="CS12" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="CT12" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="CU12" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="CV12" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="CW12" s="71">
         <f>IFERROR((VLOOKUP(CQ12,Scoring!$A:$B,2,0))+IF(CS12="y",1,0)+IF(CT12="y",1,0)+IF(CU12="y",1,0)+IF(CV12="y",1,0),0)</f>
         <v>0</v>
@@ -4930,12 +5766,8 @@
       <c r="C13" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="D13" s="24">
-        <v>12.0</v>
-      </c>
-      <c r="E13" s="25">
-        <v>5.0</v>
-      </c>
+      <c r="D13" s="24"/>
+      <c r="E13" s="25"/>
       <c r="F13" s="26" t="s">
         <v>128</v>
       </c>
@@ -4950,14 +5782,10 @@
       </c>
       <c r="J13" s="72">
         <f>IFERROR((VLOOKUP(D13,Scoring!$A:$B,2,0))+IF(F13="y",1,0)+IF(G13="y",1,0)+IF(H13="y",1,0)+IF(I13="y",1,0),0)</f>
-        <v>1</v>
-      </c>
-      <c r="K13" s="24">
-        <v>7.0</v>
-      </c>
-      <c r="L13" s="25">
-        <v>12.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K13" s="24"/>
+      <c r="L13" s="25"/>
       <c r="M13" s="26" t="s">
         <v>128</v>
       </c>
@@ -4972,14 +5800,10 @@
       </c>
       <c r="Q13" s="72">
         <f>IFERROR((VLOOKUP(K13,Scoring!$A:$B,2,0))+IF(M13="y",1,0)+IF(N13="y",1,0)+IF(O13="y",1,0)+IF(P13="y",1,0),0)</f>
-        <v>6</v>
-      </c>
-      <c r="R13" s="24">
-        <v>9.0</v>
-      </c>
-      <c r="S13" s="25">
-        <v>7.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R13" s="24"/>
+      <c r="S13" s="25"/>
       <c r="T13" s="26" t="s">
         <v>128</v>
       </c>
@@ -4994,114 +5818,202 @@
       </c>
       <c r="X13" s="72">
         <f>IFERROR((VLOOKUP(R13,Scoring!$A:$B,2,0))+IF(T13="y",1,0)+IF(U13="y",1,0)+IF(V13="y",1,0)+IF(W13="y",1,0),0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y13" s="24"/>
       <c r="Z13" s="25"/>
-      <c r="AA13" s="26"/>
-      <c r="AB13" s="27"/>
-      <c r="AC13" s="28"/>
-      <c r="AD13" s="29"/>
+      <c r="AA13" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB13" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC13" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD13" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AE13" s="72">
         <f>IFERROR((VLOOKUP(Y13,Scoring!$A:$B,2,0))+IF(AA13="y",1,0)+IF(AB13="y",1,0)+IF(AC13="y",1,0)+IF(AD13="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AF13" s="24"/>
       <c r="AG13" s="25"/>
-      <c r="AH13" s="26"/>
-      <c r="AI13" s="27"/>
-      <c r="AJ13" s="28"/>
-      <c r="AK13" s="29"/>
+      <c r="AH13" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI13" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ13" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK13" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AL13" s="72">
         <f>IFERROR((VLOOKUP(AF13,Scoring!$A:$B,2,0))+IF(AH13="y",1,0)+IF(AI13="y",1,0)+IF(AJ13="y",1,0)+IF(AK13="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AM13" s="24"/>
       <c r="AN13" s="25"/>
-      <c r="AO13" s="26"/>
-      <c r="AP13" s="27"/>
-      <c r="AQ13" s="28"/>
-      <c r="AR13" s="29"/>
+      <c r="AO13" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP13" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ13" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR13" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AS13" s="72">
         <f>IFERROR((VLOOKUP(AM13,Scoring!$A:$B,2,0))+IF(AO13="y",1,0)+IF(AP13="y",1,0)+IF(AQ13="y",1,0)+IF(AR13="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AT13" s="24"/>
       <c r="AU13" s="25"/>
-      <c r="AV13" s="26"/>
-      <c r="AW13" s="27"/>
-      <c r="AX13" s="28"/>
-      <c r="AY13" s="29"/>
+      <c r="AV13" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AW13" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX13" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AY13" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AZ13" s="72">
         <f>IFERROR((VLOOKUP(AT13,Scoring!$A:$B,2,0))+IF(AV13="y",1,0)+IF(AW13="y",1,0)+IF(AX13="y",1,0)+IF(AY13="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BA13" s="24"/>
       <c r="BB13" s="25"/>
-      <c r="BC13" s="26"/>
-      <c r="BD13" s="27"/>
-      <c r="BE13" s="28"/>
-      <c r="BF13" s="29"/>
+      <c r="BC13" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BD13" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BE13" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="BF13" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="BG13" s="72">
         <f>IFERROR((VLOOKUP(BA13,Scoring!$A:$B,2,0))+IF(BC13="y",1,0)+IF(BD13="y",1,0)+IF(BE13="y",1,0)+IF(BF13="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BH13" s="24"/>
       <c r="BI13" s="25"/>
-      <c r="BJ13" s="26"/>
-      <c r="BK13" s="27"/>
-      <c r="BL13" s="28"/>
-      <c r="BM13" s="29"/>
+      <c r="BJ13" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK13" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL13" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM13" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="BN13" s="72">
         <f>IFERROR((VLOOKUP(BH13,Scoring!$A:$B,2,0))+IF(BJ13="y",1,0)+IF(BK13="y",1,0)+IF(BL13="y",1,0)+IF(BM13="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BO13" s="24"/>
       <c r="BP13" s="25"/>
-      <c r="BQ13" s="26"/>
-      <c r="BR13" s="27"/>
-      <c r="BS13" s="28"/>
-      <c r="BT13" s="29"/>
+      <c r="BQ13" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BR13" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BS13" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="BT13" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="BU13" s="72">
         <f>IFERROR((VLOOKUP(BO13,Scoring!$A:$B,2,0))+IF(BQ13="y",1,0)+IF(BR13="y",1,0)+IF(BS13="y",1,0)+IF(BT13="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BV13" s="24"/>
       <c r="BW13" s="25"/>
-      <c r="BX13" s="26"/>
-      <c r="BY13" s="27"/>
-      <c r="BZ13" s="28"/>
-      <c r="CA13" s="29"/>
+      <c r="BX13" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY13" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ13" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA13" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CB13" s="72">
         <f>IFERROR((VLOOKUP(BV13,Scoring!$A:$B,2,0))+IF(BX13="y",1,0)+IF(BY13="y",1,0)+IF(BZ13="y",1,0)+IF(CA13="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CC13" s="24"/>
       <c r="CD13" s="25"/>
-      <c r="CE13" s="26"/>
-      <c r="CF13" s="27"/>
-      <c r="CG13" s="28"/>
-      <c r="CH13" s="29"/>
+      <c r="CE13" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF13" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG13" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH13" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CI13" s="72">
         <f>IFERROR((VLOOKUP(CC13,Scoring!$A:$B,2,0))+IF(CE13="y",1,0)+IF(CF13="y",1,0)+IF(CG13="y",1,0)+IF(CH13="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CJ13" s="24"/>
       <c r="CK13" s="25"/>
-      <c r="CL13" s="26"/>
-      <c r="CM13" s="27"/>
-      <c r="CN13" s="28"/>
-      <c r="CO13" s="29"/>
+      <c r="CL13" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM13" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN13" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO13" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CP13" s="72">
         <f>IFERROR((VLOOKUP(CJ13,Scoring!$A:$B,2,0))+IF(CL13="y",1,0)+IF(CM13="y",1,0)+IF(CN13="y",1,0)+IF(CO13="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CQ13" s="24"/>
       <c r="CR13" s="25"/>
-      <c r="CS13" s="26"/>
-      <c r="CT13" s="27"/>
-      <c r="CU13" s="28"/>
-      <c r="CV13" s="29"/>
+      <c r="CS13" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CT13" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CU13" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CV13" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CW13" s="72">
         <f>IFERROR((VLOOKUP(CQ13,Scoring!$A:$B,2,0))+IF(CS13="y",1,0)+IF(CT13="y",1,0)+IF(CU13="y",1,0)+IF(CV13="y",1,0),0)</f>
         <v>0</v>
@@ -5120,12 +6032,8 @@
       <c r="C14" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="36">
-        <v>13.0</v>
-      </c>
-      <c r="E14" s="37">
-        <v>4.0</v>
-      </c>
+      <c r="D14" s="36"/>
+      <c r="E14" s="37"/>
       <c r="F14" s="38" t="s">
         <v>128</v>
       </c>
@@ -5140,14 +6048,10 @@
       </c>
       <c r="J14" s="71">
         <f>IFERROR((VLOOKUP(D14,Scoring!$A:$B,2,0))+IF(F14="y",1,0)+IF(G14="y",1,0)+IF(H14="y",1,0)+IF(I14="y",1,0),0)</f>
-        <v>1</v>
-      </c>
-      <c r="K14" s="36">
-        <v>9.0</v>
-      </c>
-      <c r="L14" s="37">
-        <v>13.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K14" s="36"/>
+      <c r="L14" s="37"/>
       <c r="M14" s="38" t="s">
         <v>128</v>
       </c>
@@ -5162,14 +6066,10 @@
       </c>
       <c r="Q14" s="71">
         <f>IFERROR((VLOOKUP(K14,Scoring!$A:$B,2,0))+IF(M14="y",1,0)+IF(N14="y",1,0)+IF(O14="y",1,0)+IF(P14="y",1,0),0)</f>
-        <v>3</v>
-      </c>
-      <c r="R14" s="36">
-        <v>7.0</v>
-      </c>
-      <c r="S14" s="37">
-        <v>9.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R14" s="36"/>
+      <c r="S14" s="37"/>
       <c r="T14" s="38" t="s">
         <v>128</v>
       </c>
@@ -5184,114 +6084,202 @@
       </c>
       <c r="X14" s="71">
         <f>IFERROR((VLOOKUP(R14,Scoring!$A:$B,2,0))+IF(T14="y",1,0)+IF(U14="y",1,0)+IF(V14="y",1,0)+IF(W14="y",1,0),0)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="36"/>
       <c r="Z14" s="37"/>
-      <c r="AA14" s="38"/>
-      <c r="AB14" s="39"/>
-      <c r="AC14" s="40"/>
-      <c r="AD14" s="41"/>
+      <c r="AA14" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB14" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC14" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD14" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="AE14" s="71">
         <f>IFERROR((VLOOKUP(Y14,Scoring!$A:$B,2,0))+IF(AA14="y",1,0)+IF(AB14="y",1,0)+IF(AC14="y",1,0)+IF(AD14="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AF14" s="36"/>
       <c r="AG14" s="37"/>
-      <c r="AH14" s="38"/>
-      <c r="AI14" s="39"/>
-      <c r="AJ14" s="40"/>
-      <c r="AK14" s="41"/>
+      <c r="AH14" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI14" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ14" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK14" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="AL14" s="71">
         <f>IFERROR((VLOOKUP(AF14,Scoring!$A:$B,2,0))+IF(AH14="y",1,0)+IF(AI14="y",1,0)+IF(AJ14="y",1,0)+IF(AK14="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AM14" s="36"/>
       <c r="AN14" s="37"/>
-      <c r="AO14" s="38"/>
-      <c r="AP14" s="39"/>
-      <c r="AQ14" s="40"/>
-      <c r="AR14" s="41"/>
+      <c r="AO14" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP14" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ14" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR14" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="AS14" s="71">
         <f>IFERROR((VLOOKUP(AM14,Scoring!$A:$B,2,0))+IF(AO14="y",1,0)+IF(AP14="y",1,0)+IF(AQ14="y",1,0)+IF(AR14="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AT14" s="36"/>
       <c r="AU14" s="37"/>
-      <c r="AV14" s="38"/>
-      <c r="AW14" s="39"/>
-      <c r="AX14" s="40"/>
-      <c r="AY14" s="41"/>
+      <c r="AV14" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="AW14" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX14" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="AY14" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="AZ14" s="71">
         <f>IFERROR((VLOOKUP(AT14,Scoring!$A:$B,2,0))+IF(AV14="y",1,0)+IF(AW14="y",1,0)+IF(AX14="y",1,0)+IF(AY14="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BA14" s="36"/>
       <c r="BB14" s="37"/>
-      <c r="BC14" s="38"/>
-      <c r="BD14" s="39"/>
-      <c r="BE14" s="40"/>
-      <c r="BF14" s="41"/>
+      <c r="BC14" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="BD14" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="BE14" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="BF14" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="BG14" s="71">
         <f>IFERROR((VLOOKUP(BA14,Scoring!$A:$B,2,0))+IF(BC14="y",1,0)+IF(BD14="y",1,0)+IF(BE14="y",1,0)+IF(BF14="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BH14" s="36"/>
       <c r="BI14" s="37"/>
-      <c r="BJ14" s="38"/>
-      <c r="BK14" s="39"/>
-      <c r="BL14" s="40"/>
-      <c r="BM14" s="41"/>
+      <c r="BJ14" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK14" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL14" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM14" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="BN14" s="71">
         <f>IFERROR((VLOOKUP(BH14,Scoring!$A:$B,2,0))+IF(BJ14="y",1,0)+IF(BK14="y",1,0)+IF(BL14="y",1,0)+IF(BM14="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BO14" s="36"/>
       <c r="BP14" s="37"/>
-      <c r="BQ14" s="38"/>
-      <c r="BR14" s="39"/>
-      <c r="BS14" s="40"/>
-      <c r="BT14" s="41"/>
+      <c r="BQ14" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="BR14" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="BS14" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="BT14" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="BU14" s="71">
         <f>IFERROR((VLOOKUP(BO14,Scoring!$A:$B,2,0))+IF(BQ14="y",1,0)+IF(BR14="y",1,0)+IF(BS14="y",1,0)+IF(BT14="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BV14" s="36"/>
       <c r="BW14" s="37"/>
-      <c r="BX14" s="38"/>
-      <c r="BY14" s="39"/>
-      <c r="BZ14" s="40"/>
-      <c r="CA14" s="41"/>
+      <c r="BX14" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY14" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ14" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA14" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="CB14" s="71">
         <f>IFERROR((VLOOKUP(BV14,Scoring!$A:$B,2,0))+IF(BX14="y",1,0)+IF(BY14="y",1,0)+IF(BZ14="y",1,0)+IF(CA14="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CC14" s="36"/>
       <c r="CD14" s="37"/>
-      <c r="CE14" s="38"/>
-      <c r="CF14" s="39"/>
-      <c r="CG14" s="40"/>
-      <c r="CH14" s="41"/>
+      <c r="CE14" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF14" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG14" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH14" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="CI14" s="71">
         <f>IFERROR((VLOOKUP(CC14,Scoring!$A:$B,2,0))+IF(CE14="y",1,0)+IF(CF14="y",1,0)+IF(CG14="y",1,0)+IF(CH14="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CJ14" s="36"/>
       <c r="CK14" s="37"/>
-      <c r="CL14" s="38"/>
-      <c r="CM14" s="39"/>
-      <c r="CN14" s="40"/>
-      <c r="CO14" s="41"/>
+      <c r="CL14" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM14" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN14" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO14" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="CP14" s="71">
         <f>IFERROR((VLOOKUP(CJ14,Scoring!$A:$B,2,0))+IF(CL14="y",1,0)+IF(CM14="y",1,0)+IF(CN14="y",1,0)+IF(CO14="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CQ14" s="36"/>
       <c r="CR14" s="37"/>
-      <c r="CS14" s="38"/>
-      <c r="CT14" s="39"/>
-      <c r="CU14" s="40"/>
-      <c r="CV14" s="41"/>
+      <c r="CS14" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="CT14" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="CU14" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="CV14" s="41" t="s">
+        <v>128</v>
+      </c>
       <c r="CW14" s="71">
         <f>IFERROR((VLOOKUP(CQ14,Scoring!$A:$B,2,0))+IF(CS14="y",1,0)+IF(CT14="y",1,0)+IF(CU14="y",1,0)+IF(CV14="y",1,0),0)</f>
         <v>0</v>
@@ -5310,12 +6298,8 @@
       <c r="C15" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="48">
-        <v>23.0</v>
-      </c>
-      <c r="E15" s="49">
-        <v>3.0</v>
-      </c>
+      <c r="D15" s="48"/>
+      <c r="E15" s="49"/>
       <c r="F15" s="50" t="s">
         <v>128</v>
       </c>
@@ -5332,12 +6316,8 @@
         <f>IFERROR((VLOOKUP(D15,Scoring!$A:$B,2,0))+IF(F15="y",1,0)+IF(G15="y",1,0)+IF(H15="y",1,0)+IF(I15="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="K15" s="48">
-        <v>11.0</v>
-      </c>
-      <c r="L15" s="49">
-        <v>14.0</v>
-      </c>
+      <c r="K15" s="48"/>
+      <c r="L15" s="49"/>
       <c r="M15" s="50" t="s">
         <v>128</v>
       </c>
@@ -5352,14 +6332,10 @@
       </c>
       <c r="Q15" s="72">
         <f>IFERROR((VLOOKUP(K15,Scoring!$A:$B,2,0))+IF(M15="y",1,0)+IF(N15="y",1,0)+IF(O15="y",1,0)+IF(P15="y",1,0),0)</f>
-        <v>1</v>
-      </c>
-      <c r="R15" s="48">
-        <v>5.0</v>
-      </c>
-      <c r="S15" s="49">
-        <v>11.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R15" s="48"/>
+      <c r="S15" s="49"/>
       <c r="T15" s="50" t="s">
         <v>128</v>
       </c>
@@ -5374,114 +6350,202 @@
       </c>
       <c r="X15" s="72">
         <f>IFERROR((VLOOKUP(R15,Scoring!$A:$B,2,0))+IF(T15="y",1,0)+IF(U15="y",1,0)+IF(V15="y",1,0)+IF(W15="y",1,0),0)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="48"/>
       <c r="Z15" s="49"/>
-      <c r="AA15" s="50"/>
-      <c r="AB15" s="51"/>
-      <c r="AC15" s="52"/>
-      <c r="AD15" s="53"/>
+      <c r="AA15" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB15" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC15" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD15" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="AE15" s="72">
         <f>IFERROR((VLOOKUP(Y15,Scoring!$A:$B,2,0))+IF(AA15="y",1,0)+IF(AB15="y",1,0)+IF(AC15="y",1,0)+IF(AD15="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AF15" s="48"/>
       <c r="AG15" s="49"/>
-      <c r="AH15" s="50"/>
-      <c r="AI15" s="51"/>
-      <c r="AJ15" s="52"/>
-      <c r="AK15" s="53"/>
+      <c r="AH15" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI15" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ15" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK15" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="AL15" s="72">
         <f>IFERROR((VLOOKUP(AF15,Scoring!$A:$B,2,0))+IF(AH15="y",1,0)+IF(AI15="y",1,0)+IF(AJ15="y",1,0)+IF(AK15="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AM15" s="48"/>
       <c r="AN15" s="49"/>
-      <c r="AO15" s="50"/>
-      <c r="AP15" s="51"/>
-      <c r="AQ15" s="52"/>
-      <c r="AR15" s="53"/>
+      <c r="AO15" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP15" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ15" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR15" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="AS15" s="72">
         <f>IFERROR((VLOOKUP(AM15,Scoring!$A:$B,2,0))+IF(AO15="y",1,0)+IF(AP15="y",1,0)+IF(AQ15="y",1,0)+IF(AR15="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AT15" s="48"/>
       <c r="AU15" s="49"/>
-      <c r="AV15" s="50"/>
-      <c r="AW15" s="51"/>
-      <c r="AX15" s="52"/>
-      <c r="AY15" s="53"/>
+      <c r="AV15" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="AW15" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX15" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="AY15" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="AZ15" s="72">
         <f>IFERROR((VLOOKUP(AT15,Scoring!$A:$B,2,0))+IF(AV15="y",1,0)+IF(AW15="y",1,0)+IF(AX15="y",1,0)+IF(AY15="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BA15" s="48"/>
       <c r="BB15" s="49"/>
-      <c r="BC15" s="50"/>
-      <c r="BD15" s="51"/>
-      <c r="BE15" s="52"/>
-      <c r="BF15" s="53"/>
+      <c r="BC15" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="BD15" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="BE15" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="BF15" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="BG15" s="72">
         <f>IFERROR((VLOOKUP(BA15,Scoring!$A:$B,2,0))+IF(BC15="y",1,0)+IF(BD15="y",1,0)+IF(BE15="y",1,0)+IF(BF15="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BH15" s="48"/>
       <c r="BI15" s="49"/>
-      <c r="BJ15" s="50"/>
-      <c r="BK15" s="51"/>
-      <c r="BL15" s="52"/>
-      <c r="BM15" s="53"/>
+      <c r="BJ15" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK15" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL15" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM15" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="BN15" s="72">
         <f>IFERROR((VLOOKUP(BH15,Scoring!$A:$B,2,0))+IF(BJ15="y",1,0)+IF(BK15="y",1,0)+IF(BL15="y",1,0)+IF(BM15="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BO15" s="48"/>
       <c r="BP15" s="49"/>
-      <c r="BQ15" s="50"/>
-      <c r="BR15" s="51"/>
-      <c r="BS15" s="52"/>
-      <c r="BT15" s="53"/>
+      <c r="BQ15" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="BR15" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="BS15" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="BT15" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="BU15" s="72">
         <f>IFERROR((VLOOKUP(BO15,Scoring!$A:$B,2,0))+IF(BQ15="y",1,0)+IF(BR15="y",1,0)+IF(BS15="y",1,0)+IF(BT15="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BV15" s="48"/>
       <c r="BW15" s="49"/>
-      <c r="BX15" s="50"/>
-      <c r="BY15" s="51"/>
-      <c r="BZ15" s="52"/>
-      <c r="CA15" s="53"/>
+      <c r="BX15" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY15" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ15" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA15" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="CB15" s="72">
         <f>IFERROR((VLOOKUP(BV15,Scoring!$A:$B,2,0))+IF(BX15="y",1,0)+IF(BY15="y",1,0)+IF(BZ15="y",1,0)+IF(CA15="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CC15" s="48"/>
       <c r="CD15" s="49"/>
-      <c r="CE15" s="50"/>
-      <c r="CF15" s="51"/>
-      <c r="CG15" s="52"/>
-      <c r="CH15" s="53"/>
+      <c r="CE15" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF15" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG15" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH15" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="CI15" s="72">
         <f>IFERROR((VLOOKUP(CC15,Scoring!$A:$B,2,0))+IF(CE15="y",1,0)+IF(CF15="y",1,0)+IF(CG15="y",1,0)+IF(CH15="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CJ15" s="48"/>
       <c r="CK15" s="49"/>
-      <c r="CL15" s="50"/>
-      <c r="CM15" s="51"/>
-      <c r="CN15" s="52"/>
-      <c r="CO15" s="53"/>
+      <c r="CL15" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM15" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN15" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO15" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="CP15" s="72">
         <f>IFERROR((VLOOKUP(CJ15,Scoring!$A:$B,2,0))+IF(CL15="y",1,0)+IF(CM15="y",1,0)+IF(CN15="y",1,0)+IF(CO15="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CQ15" s="48"/>
       <c r="CR15" s="49"/>
-      <c r="CS15" s="50"/>
-      <c r="CT15" s="51"/>
-      <c r="CU15" s="52"/>
-      <c r="CV15" s="53"/>
+      <c r="CS15" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="CT15" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="CU15" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="CV15" s="53" t="s">
+        <v>128</v>
+      </c>
       <c r="CW15" s="72">
         <f>IFERROR((VLOOKUP(CQ15,Scoring!$A:$B,2,0))+IF(CS15="y",1,0)+IF(CT15="y",1,0)+IF(CU15="y",1,0)+IF(CV15="y",1,0),0)</f>
         <v>0</v>
@@ -5500,12 +6564,8 @@
       <c r="C16" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="24">
-        <v>24.0</v>
-      </c>
-      <c r="E16" s="25">
-        <v>2.0</v>
-      </c>
+      <c r="D16" s="24"/>
+      <c r="E16" s="25"/>
       <c r="F16" s="26" t="s">
         <v>128</v>
       </c>
@@ -5522,12 +6582,8 @@
         <f>IFERROR((VLOOKUP(D16,Scoring!$A:$B,2,0))+IF(F16="y",1,0)+IF(G16="y",1,0)+IF(H16="y",1,0)+IF(I16="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="K16" s="24">
-        <v>13.0</v>
-      </c>
-      <c r="L16" s="25">
-        <v>15.0</v>
-      </c>
+      <c r="K16" s="24"/>
+      <c r="L16" s="25"/>
       <c r="M16" s="26" t="s">
         <v>128</v>
       </c>
@@ -5542,14 +6598,10 @@
       </c>
       <c r="Q16" s="71">
         <f>IFERROR((VLOOKUP(K16,Scoring!$A:$B,2,0))+IF(M16="y",1,0)+IF(N16="y",1,0)+IF(O16="y",1,0)+IF(P16="y",1,0),0)</f>
-        <v>1</v>
-      </c>
-      <c r="R16" s="24">
-        <v>3.0</v>
-      </c>
-      <c r="S16" s="25">
-        <v>13.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R16" s="24"/>
+      <c r="S16" s="25"/>
       <c r="T16" s="26" t="s">
         <v>128</v>
       </c>
@@ -5564,114 +6616,202 @@
       </c>
       <c r="X16" s="71">
         <f>IFERROR((VLOOKUP(R16,Scoring!$A:$B,2,0))+IF(T16="y",1,0)+IF(U16="y",1,0)+IF(V16="y",1,0)+IF(W16="y",1,0),0)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Y16" s="24"/>
       <c r="Z16" s="25"/>
-      <c r="AA16" s="26"/>
-      <c r="AB16" s="27"/>
-      <c r="AC16" s="28"/>
-      <c r="AD16" s="29"/>
+      <c r="AA16" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB16" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC16" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD16" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AE16" s="71">
         <f>IFERROR((VLOOKUP(Y16,Scoring!$A:$B,2,0))+IF(AA16="y",1,0)+IF(AB16="y",1,0)+IF(AC16="y",1,0)+IF(AD16="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AF16" s="24"/>
       <c r="AG16" s="25"/>
-      <c r="AH16" s="26"/>
-      <c r="AI16" s="27"/>
-      <c r="AJ16" s="28"/>
-      <c r="AK16" s="29"/>
+      <c r="AH16" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI16" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ16" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK16" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AL16" s="71">
         <f>IFERROR((VLOOKUP(AF16,Scoring!$A:$B,2,0))+IF(AH16="y",1,0)+IF(AI16="y",1,0)+IF(AJ16="y",1,0)+IF(AK16="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AM16" s="24"/>
       <c r="AN16" s="25"/>
-      <c r="AO16" s="26"/>
-      <c r="AP16" s="27"/>
-      <c r="AQ16" s="28"/>
-      <c r="AR16" s="29"/>
+      <c r="AO16" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP16" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ16" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR16" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AS16" s="71">
         <f>IFERROR((VLOOKUP(AM16,Scoring!$A:$B,2,0))+IF(AO16="y",1,0)+IF(AP16="y",1,0)+IF(AQ16="y",1,0)+IF(AR16="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AT16" s="24"/>
       <c r="AU16" s="25"/>
-      <c r="AV16" s="26"/>
-      <c r="AW16" s="27"/>
-      <c r="AX16" s="28"/>
-      <c r="AY16" s="29"/>
+      <c r="AV16" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="AW16" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX16" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="AY16" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="AZ16" s="71">
         <f>IFERROR((VLOOKUP(AT16,Scoring!$A:$B,2,0))+IF(AV16="y",1,0)+IF(AW16="y",1,0)+IF(AX16="y",1,0)+IF(AY16="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BA16" s="24"/>
       <c r="BB16" s="25"/>
-      <c r="BC16" s="26"/>
-      <c r="BD16" s="27"/>
-      <c r="BE16" s="28"/>
-      <c r="BF16" s="29"/>
+      <c r="BC16" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BD16" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BE16" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="BF16" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="BG16" s="71">
         <f>IFERROR((VLOOKUP(BA16,Scoring!$A:$B,2,0))+IF(BC16="y",1,0)+IF(BD16="y",1,0)+IF(BE16="y",1,0)+IF(BF16="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BH16" s="24"/>
       <c r="BI16" s="25"/>
-      <c r="BJ16" s="26"/>
-      <c r="BK16" s="27"/>
-      <c r="BL16" s="28"/>
-      <c r="BM16" s="29"/>
+      <c r="BJ16" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK16" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL16" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM16" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="BN16" s="71">
         <f>IFERROR((VLOOKUP(BH16,Scoring!$A:$B,2,0))+IF(BJ16="y",1,0)+IF(BK16="y",1,0)+IF(BL16="y",1,0)+IF(BM16="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BO16" s="24"/>
       <c r="BP16" s="25"/>
-      <c r="BQ16" s="26"/>
-      <c r="BR16" s="27"/>
-      <c r="BS16" s="28"/>
-      <c r="BT16" s="29"/>
+      <c r="BQ16" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BR16" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BS16" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="BT16" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="BU16" s="71">
         <f>IFERROR((VLOOKUP(BO16,Scoring!$A:$B,2,0))+IF(BQ16="y",1,0)+IF(BR16="y",1,0)+IF(BS16="y",1,0)+IF(BT16="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BV16" s="24"/>
       <c r="BW16" s="25"/>
-      <c r="BX16" s="26"/>
-      <c r="BY16" s="27"/>
-      <c r="BZ16" s="28"/>
-      <c r="CA16" s="29"/>
+      <c r="BX16" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY16" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ16" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA16" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CB16" s="71">
         <f>IFERROR((VLOOKUP(BV16,Scoring!$A:$B,2,0))+IF(BX16="y",1,0)+IF(BY16="y",1,0)+IF(BZ16="y",1,0)+IF(CA16="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CC16" s="24"/>
       <c r="CD16" s="25"/>
-      <c r="CE16" s="26"/>
-      <c r="CF16" s="27"/>
-      <c r="CG16" s="28"/>
-      <c r="CH16" s="29"/>
+      <c r="CE16" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF16" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG16" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH16" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CI16" s="71">
         <f>IFERROR((VLOOKUP(CC16,Scoring!$A:$B,2,0))+IF(CE16="y",1,0)+IF(CF16="y",1,0)+IF(CG16="y",1,0)+IF(CH16="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CJ16" s="24"/>
       <c r="CK16" s="25"/>
-      <c r="CL16" s="26"/>
-      <c r="CM16" s="27"/>
-      <c r="CN16" s="28"/>
-      <c r="CO16" s="29"/>
+      <c r="CL16" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM16" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN16" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO16" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CP16" s="71">
         <f>IFERROR((VLOOKUP(CJ16,Scoring!$A:$B,2,0))+IF(CL16="y",1,0)+IF(CM16="y",1,0)+IF(CN16="y",1,0)+IF(CO16="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CQ16" s="24"/>
       <c r="CR16" s="25"/>
-      <c r="CS16" s="26"/>
-      <c r="CT16" s="27"/>
-      <c r="CU16" s="28"/>
-      <c r="CV16" s="29"/>
+      <c r="CS16" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CT16" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CU16" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CV16" s="29" t="s">
+        <v>128</v>
+      </c>
       <c r="CW16" s="71">
         <f>IFERROR((VLOOKUP(CQ16,Scoring!$A:$B,2,0))+IF(CS16="y",1,0)+IF(CT16="y",1,0)+IF(CU16="y",1,0)+IF(CV16="y",1,0),0)</f>
         <v>0</v>
@@ -5690,12 +6830,8 @@
       <c r="C17" s="59" t="s">
         <v>395</v>
       </c>
-      <c r="D17" s="60">
-        <v>25.0</v>
-      </c>
-      <c r="E17" s="61">
-        <v>1.0</v>
-      </c>
+      <c r="D17" s="60"/>
+      <c r="E17" s="61"/>
       <c r="F17" s="62" t="s">
         <v>128</v>
       </c>
@@ -5712,12 +6848,8 @@
         <f>IFERROR((VLOOKUP(D17,Scoring!$A:$B,2,0))+IF(F17="y",1,0)+IF(G17="y",1,0)+IF(H17="y",1,0)+IF(I17="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="K17" s="60">
-        <v>15.0</v>
-      </c>
-      <c r="L17" s="61">
-        <v>16.0</v>
-      </c>
+      <c r="K17" s="60"/>
+      <c r="L17" s="61"/>
       <c r="M17" s="62" t="s">
         <v>128</v>
       </c>
@@ -5732,14 +6864,10 @@
       </c>
       <c r="Q17" s="73">
         <f>IFERROR((VLOOKUP(K17,Scoring!$A:$B,2,0))+IF(M17="y",1,0)+IF(N17="y",1,0)+IF(O17="y",1,0)+IF(P17="y",1,0),0)</f>
-        <v>1</v>
-      </c>
-      <c r="R17" s="60">
-        <v>1.0</v>
-      </c>
-      <c r="S17" s="61">
-        <v>15.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R17" s="60"/>
+      <c r="S17" s="61"/>
       <c r="T17" s="62" t="s">
         <v>128</v>
       </c>
@@ -5754,114 +6882,202 @@
       </c>
       <c r="X17" s="73">
         <f>IFERROR((VLOOKUP(R17,Scoring!$A:$B,2,0))+IF(T17="y",1,0)+IF(U17="y",1,0)+IF(V17="y",1,0)+IF(W17="y",1,0),0)</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Y17" s="60"/>
       <c r="Z17" s="61"/>
-      <c r="AA17" s="62"/>
-      <c r="AB17" s="63"/>
-      <c r="AC17" s="64"/>
-      <c r="AD17" s="65"/>
+      <c r="AA17" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB17" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC17" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD17" s="65" t="s">
+        <v>128</v>
+      </c>
       <c r="AE17" s="73">
         <f>IFERROR((VLOOKUP(Y17,Scoring!$A:$B,2,0))+IF(AA17="y",1,0)+IF(AB17="y",1,0)+IF(AC17="y",1,0)+IF(AD17="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AF17" s="60"/>
       <c r="AG17" s="61"/>
-      <c r="AH17" s="62"/>
-      <c r="AI17" s="63"/>
-      <c r="AJ17" s="64"/>
-      <c r="AK17" s="65"/>
+      <c r="AH17" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI17" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ17" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK17" s="65" t="s">
+        <v>128</v>
+      </c>
       <c r="AL17" s="73">
         <f>IFERROR((VLOOKUP(AF17,Scoring!$A:$B,2,0))+IF(AH17="y",1,0)+IF(AI17="y",1,0)+IF(AJ17="y",1,0)+IF(AK17="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AM17" s="60"/>
       <c r="AN17" s="61"/>
-      <c r="AO17" s="62"/>
-      <c r="AP17" s="63"/>
-      <c r="AQ17" s="64"/>
-      <c r="AR17" s="65"/>
+      <c r="AO17" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP17" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ17" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR17" s="65" t="s">
+        <v>128</v>
+      </c>
       <c r="AS17" s="73">
         <f>IFERROR((VLOOKUP(AM17,Scoring!$A:$B,2,0))+IF(AO17="y",1,0)+IF(AP17="y",1,0)+IF(AQ17="y",1,0)+IF(AR17="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AT17" s="60"/>
       <c r="AU17" s="61"/>
-      <c r="AV17" s="62"/>
-      <c r="AW17" s="63"/>
-      <c r="AX17" s="64"/>
-      <c r="AY17" s="65"/>
+      <c r="AV17" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="AW17" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX17" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="AY17" s="65" t="s">
+        <v>128</v>
+      </c>
       <c r="AZ17" s="73">
         <f>IFERROR((VLOOKUP(AT17,Scoring!$A:$B,2,0))+IF(AV17="y",1,0)+IF(AW17="y",1,0)+IF(AX17="y",1,0)+IF(AY17="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BA17" s="60"/>
       <c r="BB17" s="61"/>
-      <c r="BC17" s="62"/>
-      <c r="BD17" s="63"/>
-      <c r="BE17" s="64"/>
-      <c r="BF17" s="65"/>
+      <c r="BC17" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="BD17" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="BE17" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="BF17" s="65" t="s">
+        <v>128</v>
+      </c>
       <c r="BG17" s="73">
         <f>IFERROR((VLOOKUP(BA17,Scoring!$A:$B,2,0))+IF(BC17="y",1,0)+IF(BD17="y",1,0)+IF(BE17="y",1,0)+IF(BF17="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BH17" s="60"/>
       <c r="BI17" s="61"/>
-      <c r="BJ17" s="62"/>
-      <c r="BK17" s="63"/>
-      <c r="BL17" s="64"/>
-      <c r="BM17" s="65"/>
+      <c r="BJ17" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK17" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL17" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM17" s="65" t="s">
+        <v>128</v>
+      </c>
       <c r="BN17" s="73">
         <f>IFERROR((VLOOKUP(BH17,Scoring!$A:$B,2,0))+IF(BJ17="y",1,0)+IF(BK17="y",1,0)+IF(BL17="y",1,0)+IF(BM17="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BO17" s="60"/>
       <c r="BP17" s="61"/>
-      <c r="BQ17" s="62"/>
-      <c r="BR17" s="63"/>
-      <c r="BS17" s="64"/>
-      <c r="BT17" s="65"/>
+      <c r="BQ17" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="BR17" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="BS17" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="BT17" s="65" t="s">
+        <v>128</v>
+      </c>
       <c r="BU17" s="73">
         <f>IFERROR((VLOOKUP(BO17,Scoring!$A:$B,2,0))+IF(BQ17="y",1,0)+IF(BR17="y",1,0)+IF(BS17="y",1,0)+IF(BT17="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="BV17" s="60"/>
       <c r="BW17" s="61"/>
-      <c r="BX17" s="62"/>
-      <c r="BY17" s="63"/>
-      <c r="BZ17" s="64"/>
-      <c r="CA17" s="65"/>
+      <c r="BX17" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY17" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ17" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA17" s="65" t="s">
+        <v>128</v>
+      </c>
       <c r="CB17" s="73">
         <f>IFERROR((VLOOKUP(BV17,Scoring!$A:$B,2,0))+IF(BX17="y",1,0)+IF(BY17="y",1,0)+IF(BZ17="y",1,0)+IF(CA17="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CC17" s="60"/>
       <c r="CD17" s="61"/>
-      <c r="CE17" s="62"/>
-      <c r="CF17" s="63"/>
-      <c r="CG17" s="64"/>
-      <c r="CH17" s="65"/>
+      <c r="CE17" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF17" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG17" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH17" s="65" t="s">
+        <v>128</v>
+      </c>
       <c r="CI17" s="73">
         <f>IFERROR((VLOOKUP(CC17,Scoring!$A:$B,2,0))+IF(CE17="y",1,0)+IF(CF17="y",1,0)+IF(CG17="y",1,0)+IF(CH17="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CJ17" s="60"/>
       <c r="CK17" s="61"/>
-      <c r="CL17" s="62"/>
-      <c r="CM17" s="63"/>
-      <c r="CN17" s="64"/>
-      <c r="CO17" s="65"/>
+      <c r="CL17" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM17" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN17" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO17" s="65" t="s">
+        <v>128</v>
+      </c>
       <c r="CP17" s="73">
         <f>IFERROR((VLOOKUP(CJ17,Scoring!$A:$B,2,0))+IF(CL17="y",1,0)+IF(CM17="y",1,0)+IF(CN17="y",1,0)+IF(CO17="y",1,0),0)</f>
         <v>0</v>
       </c>
       <c r="CQ17" s="60"/>
       <c r="CR17" s="61"/>
-      <c r="CS17" s="62"/>
-      <c r="CT17" s="63"/>
-      <c r="CU17" s="64"/>
-      <c r="CV17" s="65"/>
+      <c r="CS17" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="CT17" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="CU17" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="CV17" s="65" t="s">
+        <v>128</v>
+      </c>
       <c r="CW17" s="73">
         <f>IFERROR((VLOOKUP(CQ17,Scoring!$A:$B,2,0))+IF(CS17="y",1,0)+IF(CT17="y",1,0)+IF(CU17="y",1,0)+IF(CV17="y",1,0),0)</f>
         <v>0</v>

--- a/the_alternative_f1/The_Alternative_F1.xlsx
+++ b/the_alternative_f1/The_Alternative_F1.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3166" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3314" uniqueCount="435">
   <si>
     <t>Positions</t>
   </si>
@@ -1143,67 +1143,73 @@
     <t>W-11Points</t>
   </si>
   <si>
-    <t>W-12Place</t>
-  </si>
-  <si>
-    <t>W-12Qualifying</t>
-  </si>
-  <si>
-    <t>W-12FastestLap</t>
-  </si>
-  <si>
-    <t>W-12DOTD</t>
-  </si>
-  <si>
-    <t>W-12MOT</t>
-  </si>
-  <si>
-    <t>W-12CD</t>
-  </si>
-  <si>
-    <t>W-12Points</t>
-  </si>
-  <si>
-    <t>W-13Place</t>
-  </si>
-  <si>
-    <t>W-13Qualifying</t>
-  </si>
-  <si>
-    <t>W-13FastestLap</t>
-  </si>
-  <si>
-    <t>W-13DOTD</t>
-  </si>
-  <si>
-    <t>W-13MOT</t>
-  </si>
-  <si>
-    <t>W-13CD</t>
-  </si>
-  <si>
-    <t>W-13Points</t>
-  </si>
-  <si>
-    <t>W-14Place</t>
-  </si>
-  <si>
-    <t>W-14Qualifying</t>
-  </si>
-  <si>
-    <t>W-14FastestLap</t>
-  </si>
-  <si>
-    <t>W-14DOTD</t>
-  </si>
-  <si>
-    <t>W-14MOT</t>
-  </si>
-  <si>
-    <t>W-14CD</t>
-  </si>
-  <si>
-    <t>W-14Points</t>
+    <t>ZandvoortSprintPlace</t>
+  </si>
+  <si>
+    <t>ZandvoortSprintQualifying</t>
+  </si>
+  <si>
+    <t>ZandvoortSprintFastestLap</t>
+  </si>
+  <si>
+    <t>ZandvoortSprintDOTD</t>
+  </si>
+  <si>
+    <t>ZandvoortSprintMOT</t>
+  </si>
+  <si>
+    <t>ZandvoortSprintCD</t>
+  </si>
+  <si>
+    <t>ZandvoortSprintPoints</t>
+  </si>
+  <si>
+    <t>QatarDOTD</t>
+  </si>
+  <si>
+    <t>QatarMOT</t>
+  </si>
+  <si>
+    <t>QatarCD</t>
+  </si>
+  <si>
+    <t>SingaporeSprintPlace</t>
+  </si>
+  <si>
+    <t>SingaporeSprintQualifying</t>
+  </si>
+  <si>
+    <t>SingaporeSprintFastestLap</t>
+  </si>
+  <si>
+    <t>SingaporeSprintDOTD</t>
+  </si>
+  <si>
+    <t>SingaporeSprintMOT</t>
+  </si>
+  <si>
+    <t>SingaporeSprintCD</t>
+  </si>
+  <si>
+    <t>SingaporeSprintPoints</t>
+  </si>
+  <si>
+    <t>SingaporeDOTD</t>
+  </si>
+  <si>
+    <t>SingaporeMOT</t>
+  </si>
+  <si>
+    <t>SingaporeCD</t>
+  </si>
+  <si>
+    <t>Cadillac</t>
+  </si>
+  <si>
+    <t>Haas</t>
+  </si>
+  <si>
+    <t>Williams</t>
   </si>
   <si>
     <t>Grayson</t>
@@ -1212,19 +1218,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>Cadillac</t>
-  </si>
-  <si>
-    <t>Haas</t>
-  </si>
-  <si>
-    <t>TBD1</t>
+    <t>Josh C.</t>
   </si>
   <si>
     <t>Audi</t>
   </si>
   <si>
-    <t>TBD2</t>
+    <t>Austin</t>
   </si>
   <si>
     <t>Randy</t>
@@ -1239,6 +1239,9 @@
     <t>8/19/2026</t>
   </si>
   <si>
+    <t>Pre-Season: Hungary</t>
+  </si>
+  <si>
     <t>8/26/2026</t>
   </si>
   <si>
@@ -1308,19 +1311,16 @@
     <t>12/30/2026</t>
   </si>
   <si>
-    <t>W-12</t>
+    <t>Zandvoort Sprint</t>
   </si>
   <si>
     <t>1/6/2027</t>
   </si>
   <si>
-    <t>W-13</t>
-  </si>
-  <si>
     <t>1/13/2027</t>
   </si>
   <si>
-    <t>W-14</t>
+    <t>Singapore Sprint</t>
   </si>
   <si>
     <t>1/27/2027</t>
@@ -1336,7 +1336,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1353,6 +1353,15 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1541,7 +1550,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="151">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1745,9 +1754,240 @@
     <xf borderId="3" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="4" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="3" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="3" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="8" fillId="8" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="8" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="14" fillId="8" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="14" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="7" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="9" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="10" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="10" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="10" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="10" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="10" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="9" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="10" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="10" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="10" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="10" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="10" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="12" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="13" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="13" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="13" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="13" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="13" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="12" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="13" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="13" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="13" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="13" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="13" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="17" fillId="8" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="15" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="16" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="16" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="16" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="16" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="16" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="17" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="15" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="16" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="16" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="16" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="16" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="16" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -2763,70 +3003,112 @@
       <c r="CB1" s="70" t="s">
         <v>372</v>
       </c>
-      <c r="CC1" s="6" t="s">
+      <c r="CC1" s="71" t="s">
         <v>373</v>
       </c>
-      <c r="CD1" s="7" t="s">
+      <c r="CD1" s="72" t="s">
         <v>374</v>
       </c>
-      <c r="CE1" s="8" t="s">
+      <c r="CE1" s="73" t="s">
         <v>375</v>
       </c>
-      <c r="CF1" s="9" t="s">
+      <c r="CF1" s="74" t="s">
         <v>376</v>
       </c>
-      <c r="CG1" s="10" t="s">
+      <c r="CG1" s="75" t="s">
         <v>377</v>
       </c>
-      <c r="CH1" s="11" t="s">
+      <c r="CH1" s="76" t="s">
         <v>378</v>
       </c>
-      <c r="CI1" s="70" t="s">
+      <c r="CI1" s="77" t="s">
         <v>379</v>
       </c>
-      <c r="CJ1" s="6" t="s">
+      <c r="CJ1" s="71" t="s">
+        <v>87</v>
+      </c>
+      <c r="CK1" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="CL1" s="73" t="s">
+        <v>89</v>
+      </c>
+      <c r="CM1" s="74" t="s">
+        <v>247</v>
+      </c>
+      <c r="CN1" s="75" t="s">
+        <v>248</v>
+      </c>
+      <c r="CO1" s="76" t="s">
+        <v>249</v>
+      </c>
+      <c r="CP1" s="77" t="s">
+        <v>90</v>
+      </c>
+      <c r="CQ1" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="CR1" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="CS1" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="CT1" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="CK1" s="7" t="s">
+      <c r="CU1" s="10" t="s">
         <v>381</v>
       </c>
-      <c r="CL1" s="8" t="s">
+      <c r="CV1" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="CM1" s="9" t="s">
+      <c r="CW1" s="70" t="s">
+        <v>106</v>
+      </c>
+      <c r="CX1" s="78" t="s">
         <v>383</v>
       </c>
-      <c r="CN1" s="10" t="s">
+      <c r="CY1" s="79" t="s">
         <v>384</v>
       </c>
-      <c r="CO1" s="11" t="s">
+      <c r="CZ1" s="80" t="s">
         <v>385</v>
       </c>
-      <c r="CP1" s="70" t="s">
+      <c r="DA1" s="81" t="s">
         <v>386</v>
       </c>
-      <c r="CQ1" s="6" t="s">
+      <c r="DB1" s="82" t="s">
         <v>387</v>
       </c>
-      <c r="CR1" s="7" t="s">
+      <c r="DC1" s="83" t="s">
         <v>388</v>
       </c>
-      <c r="CS1" s="8" t="s">
+      <c r="DD1" s="84" t="s">
         <v>389</v>
       </c>
-      <c r="CT1" s="9" t="s">
+      <c r="DE1" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="DF1" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="DG1" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="DH1" s="9" t="s">
         <v>390</v>
       </c>
-      <c r="CU1" s="10" t="s">
+      <c r="DI1" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="CV1" s="11" t="s">
+      <c r="DJ1" s="11" t="s">
         <v>392</v>
       </c>
-      <c r="CW1" s="70" t="s">
-        <v>393</v>
-      </c>
-      <c r="CX1" s="13" t="s">
+      <c r="DK1" s="70" t="s">
+        <v>98</v>
+      </c>
+      <c r="DL1" s="13" t="s">
         <v>127</v>
       </c>
     </row>
@@ -2854,7 +3136,7 @@
       <c r="I2" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="J2" s="71">
+      <c r="J2" s="85">
         <f>IFERROR((VLOOKUP(D2,Scoring!$A:$B,2,0))+IF(F2="y",1,0)+IF(G2="y",1,0)+IF(H2="y",1,0)+IF(I2="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -2872,7 +3154,7 @@
       <c r="P2" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="Q2" s="71">
+      <c r="Q2" s="85">
         <f>IFERROR((VLOOKUP(K2,Scoring!$A:$B,2,0))+IF(M2="y",1,0)+IF(N2="y",1,0)+IF(O2="y",1,0)+IF(P2="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -2890,7 +3172,7 @@
       <c r="W2" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="X2" s="71">
+      <c r="X2" s="85">
         <f>IFERROR((VLOOKUP(R2,Scoring!$A:$B,2,0))+IF(T2="y",1,0)+IF(U2="y",1,0)+IF(V2="y",1,0)+IF(W2="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -2908,7 +3190,7 @@
       <c r="AD2" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="AE2" s="71">
+      <c r="AE2" s="85">
         <f>IFERROR((VLOOKUP(Y2,Scoring!$A:$B,2,0))+IF(AA2="y",1,0)+IF(AB2="y",1,0)+IF(AC2="y",1,0)+IF(AD2="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -2926,7 +3208,7 @@
       <c r="AK2" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="AL2" s="71">
+      <c r="AL2" s="85">
         <f>IFERROR((VLOOKUP(AF2,Scoring!$A:$B,2,0))+IF(AH2="y",1,0)+IF(AI2="y",1,0)+IF(AJ2="y",1,0)+IF(AK2="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -2944,7 +3226,7 @@
       <c r="AR2" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="AS2" s="71">
+      <c r="AS2" s="85">
         <f>IFERROR((VLOOKUP(AM2,Scoring!$A:$B,2,0))+IF(AO2="y",1,0)+IF(AP2="y",1,0)+IF(AQ2="y",1,0)+IF(AR2="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -2962,7 +3244,7 @@
       <c r="AY2" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="AZ2" s="71">
+      <c r="AZ2" s="85">
         <f>IFERROR((VLOOKUP(AT2,Scoring!$A:$B,2,0))+IF(AV2="y",1,0)+IF(AW2="y",1,0)+IF(AX2="y",1,0)+IF(AY2="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -2980,7 +3262,7 @@
       <c r="BF2" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="BG2" s="71">
+      <c r="BG2" s="85">
         <f>IFERROR((VLOOKUP(BA2,Scoring!$A:$B,2,0))+IF(BC2="y",1,0)+IF(BD2="y",1,0)+IF(BE2="y",1,0)+IF(BF2="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -2998,7 +3280,7 @@
       <c r="BM2" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="BN2" s="71">
+      <c r="BN2" s="85">
         <f>IFERROR((VLOOKUP(BH2,Scoring!$A:$B,2,0))+IF(BJ2="y",1,0)+IF(BK2="y",1,0)+IF(BL2="y",1,0)+IF(BM2="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3016,7 +3298,7 @@
       <c r="BT2" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="BU2" s="71">
+      <c r="BU2" s="85">
         <f>IFERROR((VLOOKUP(BO2,Scoring!$A:$B,2,0))+IF(BQ2="y",1,0)+IF(BR2="y",1,0)+IF(BS2="y",1,0)+IF(BT2="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3034,43 +3316,43 @@
       <c r="CA2" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="CB2" s="71">
+      <c r="CB2" s="85">
         <f>IFERROR((VLOOKUP(BV2,Scoring!$A:$B,2,0))+IF(BX2="y",1,0)+IF(BY2="y",1,0)+IF(BZ2="y",1,0)+IF(CA2="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC2" s="16"/>
-      <c r="CD2" s="17"/>
-      <c r="CE2" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF2" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG2" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH2" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI2" s="71">
+      <c r="CC2" s="86"/>
+      <c r="CD2" s="87"/>
+      <c r="CE2" s="88" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF2" s="89" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG2" s="90" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH2" s="91" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI2" s="92">
         <f>IFERROR((VLOOKUP(CC2,Scoring!$A:$B,2,0))+IF(CE2="y",1,0)+IF(CF2="y",1,0)+IF(CG2="y",1,0)+IF(CH2="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ2" s="16"/>
-      <c r="CK2" s="17"/>
-      <c r="CL2" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM2" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN2" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO2" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP2" s="71">
+      <c r="CJ2" s="93"/>
+      <c r="CK2" s="94"/>
+      <c r="CL2" s="95" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM2" s="96" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN2" s="97" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO2" s="98" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP2" s="92">
         <f>IFERROR((VLOOKUP(CJ2,Scoring!$A:$B,2,0))+IF(CL2="y",1,0)+IF(CM2="y",1,0)+IF(CN2="y",1,0)+IF(CO2="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3088,11 +3370,47 @@
       <c r="CV2" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="CW2" s="71">
+      <c r="CW2" s="85">
         <f>IFERROR((VLOOKUP(CQ2,Scoring!$A:$B,2,0))+IF(CS2="y",1,0)+IF(CT2="y",1,0)+IF(CU2="y",1,0)+IF(CV2="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX2" s="13">
+      <c r="CX2" s="93"/>
+      <c r="CY2" s="94"/>
+      <c r="CZ2" s="95" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA2" s="96" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB2" s="97" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC2" s="98" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD2" s="92">
+        <f>IFERROR((VLOOKUP(CX2,Scoring!$A:$B,2,0))+IF(CZ2="y",1,0)+IF(DA2="y",1,0)+IF(DB2="y",1,0)+IF(DC2="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DE2" s="16"/>
+      <c r="DF2" s="17"/>
+      <c r="DG2" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH2" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI2" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ2" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK2" s="85">
+        <f>IFERROR((VLOOKUP(DE2,Scoring!$A:$B,2,0))+IF(DG2="y",1,0)+IF(DH2="y",1,0)+IF(DI2="y",1,0)+IF(DJ2="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DL2" s="13">
         <v>0.0</v>
       </c>
     </row>
@@ -3120,7 +3438,7 @@
       <c r="I3" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="J3" s="72">
+      <c r="J3" s="99">
         <f>IFERROR((VLOOKUP(D3,Scoring!$A:$B,2,0))+IF(F3="y",1,0)+IF(G3="y",1,0)+IF(H3="y",1,0)+IF(I3="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3138,7 +3456,7 @@
       <c r="P3" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="Q3" s="72">
+      <c r="Q3" s="99">
         <f>IFERROR((VLOOKUP(K3,Scoring!$A:$B,2,0))+IF(M3="y",1,0)+IF(N3="y",1,0)+IF(O3="y",1,0)+IF(P3="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3156,7 +3474,7 @@
       <c r="W3" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="X3" s="72">
+      <c r="X3" s="99">
         <f>IFERROR((VLOOKUP(R3,Scoring!$A:$B,2,0))+IF(T3="y",1,0)+IF(U3="y",1,0)+IF(V3="y",1,0)+IF(W3="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3174,7 +3492,7 @@
       <c r="AD3" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AE3" s="72">
+      <c r="AE3" s="99">
         <f>IFERROR((VLOOKUP(Y3,Scoring!$A:$B,2,0))+IF(AA3="y",1,0)+IF(AB3="y",1,0)+IF(AC3="y",1,0)+IF(AD3="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3192,7 +3510,7 @@
       <c r="AK3" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AL3" s="72">
+      <c r="AL3" s="99">
         <f>IFERROR((VLOOKUP(AF3,Scoring!$A:$B,2,0))+IF(AH3="y",1,0)+IF(AI3="y",1,0)+IF(AJ3="y",1,0)+IF(AK3="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3210,7 +3528,7 @@
       <c r="AR3" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AS3" s="72">
+      <c r="AS3" s="99">
         <f>IFERROR((VLOOKUP(AM3,Scoring!$A:$B,2,0))+IF(AO3="y",1,0)+IF(AP3="y",1,0)+IF(AQ3="y",1,0)+IF(AR3="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3228,7 +3546,7 @@
       <c r="AY3" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AZ3" s="72">
+      <c r="AZ3" s="99">
         <f>IFERROR((VLOOKUP(AT3,Scoring!$A:$B,2,0))+IF(AV3="y",1,0)+IF(AW3="y",1,0)+IF(AX3="y",1,0)+IF(AY3="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3246,7 +3564,7 @@
       <c r="BF3" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BG3" s="72">
+      <c r="BG3" s="99">
         <f>IFERROR((VLOOKUP(BA3,Scoring!$A:$B,2,0))+IF(BC3="y",1,0)+IF(BD3="y",1,0)+IF(BE3="y",1,0)+IF(BF3="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3264,7 +3582,7 @@
       <c r="BM3" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BN3" s="72">
+      <c r="BN3" s="99">
         <f>IFERROR((VLOOKUP(BH3,Scoring!$A:$B,2,0))+IF(BJ3="y",1,0)+IF(BK3="y",1,0)+IF(BL3="y",1,0)+IF(BM3="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3282,7 +3600,7 @@
       <c r="BT3" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BU3" s="72">
+      <c r="BU3" s="99">
         <f>IFERROR((VLOOKUP(BO3,Scoring!$A:$B,2,0))+IF(BQ3="y",1,0)+IF(BR3="y",1,0)+IF(BS3="y",1,0)+IF(BT3="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3300,43 +3618,43 @@
       <c r="CA3" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="CB3" s="72">
+      <c r="CB3" s="99">
         <f>IFERROR((VLOOKUP(BV3,Scoring!$A:$B,2,0))+IF(BX3="y",1,0)+IF(BY3="y",1,0)+IF(BZ3="y",1,0)+IF(CA3="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC3" s="24"/>
-      <c r="CD3" s="25"/>
-      <c r="CE3" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF3" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG3" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH3" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI3" s="72">
+      <c r="CC3" s="100"/>
+      <c r="CD3" s="101"/>
+      <c r="CE3" s="102" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF3" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG3" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH3" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI3" s="106">
         <f>IFERROR((VLOOKUP(CC3,Scoring!$A:$B,2,0))+IF(CE3="y",1,0)+IF(CF3="y",1,0)+IF(CG3="y",1,0)+IF(CH3="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ3" s="24"/>
-      <c r="CK3" s="25"/>
-      <c r="CL3" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM3" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN3" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO3" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP3" s="72">
+      <c r="CJ3" s="107"/>
+      <c r="CK3" s="108"/>
+      <c r="CL3" s="109" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM3" s="110" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN3" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO3" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP3" s="106">
         <f>IFERROR((VLOOKUP(CJ3,Scoring!$A:$B,2,0))+IF(CL3="y",1,0)+IF(CM3="y",1,0)+IF(CN3="y",1,0)+IF(CO3="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3354,11 +3672,47 @@
       <c r="CV3" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="CW3" s="72">
+      <c r="CW3" s="99">
         <f>IFERROR((VLOOKUP(CQ3,Scoring!$A:$B,2,0))+IF(CS3="y",1,0)+IF(CT3="y",1,0)+IF(CU3="y",1,0)+IF(CV3="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX3" s="13">
+      <c r="CX3" s="107"/>
+      <c r="CY3" s="108"/>
+      <c r="CZ3" s="109" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA3" s="110" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB3" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC3" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD3" s="106">
+        <f>IFERROR((VLOOKUP(CX3,Scoring!$A:$B,2,0))+IF(CZ3="y",1,0)+IF(DA3="y",1,0)+IF(DB3="y",1,0)+IF(DC3="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DE3" s="24"/>
+      <c r="DF3" s="25"/>
+      <c r="DG3" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH3" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI3" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ3" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK3" s="99">
+        <f>IFERROR((VLOOKUP(DE3,Scoring!$A:$B,2,0))+IF(DG3="y",1,0)+IF(DH3="y",1,0)+IF(DI3="y",1,0)+IF(DJ3="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DL3" s="13">
         <v>0.0</v>
       </c>
     </row>
@@ -3386,7 +3740,7 @@
       <c r="I4" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="J4" s="71">
+      <c r="J4" s="85">
         <f>IFERROR((VLOOKUP(D4,Scoring!$A:$B,2,0))+IF(F4="y",1,0)+IF(G4="y",1,0)+IF(H4="y",1,0)+IF(I4="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3404,7 +3758,7 @@
       <c r="P4" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="Q4" s="71">
+      <c r="Q4" s="85">
         <f>IFERROR((VLOOKUP(K4,Scoring!$A:$B,2,0))+IF(M4="y",1,0)+IF(N4="y",1,0)+IF(O4="y",1,0)+IF(P4="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3422,7 +3776,7 @@
       <c r="W4" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="X4" s="71">
+      <c r="X4" s="85">
         <f>IFERROR((VLOOKUP(R4,Scoring!$A:$B,2,0))+IF(T4="y",1,0)+IF(U4="y",1,0)+IF(V4="y",1,0)+IF(W4="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3440,7 +3794,7 @@
       <c r="AD4" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="AE4" s="71">
+      <c r="AE4" s="85">
         <f>IFERROR((VLOOKUP(Y4,Scoring!$A:$B,2,0))+IF(AA4="y",1,0)+IF(AB4="y",1,0)+IF(AC4="y",1,0)+IF(AD4="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3458,7 +3812,7 @@
       <c r="AK4" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="AL4" s="71">
+      <c r="AL4" s="85">
         <f>IFERROR((VLOOKUP(AF4,Scoring!$A:$B,2,0))+IF(AH4="y",1,0)+IF(AI4="y",1,0)+IF(AJ4="y",1,0)+IF(AK4="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3476,7 +3830,7 @@
       <c r="AR4" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="AS4" s="71">
+      <c r="AS4" s="85">
         <f>IFERROR((VLOOKUP(AM4,Scoring!$A:$B,2,0))+IF(AO4="y",1,0)+IF(AP4="y",1,0)+IF(AQ4="y",1,0)+IF(AR4="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3494,7 +3848,7 @@
       <c r="AY4" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="AZ4" s="71">
+      <c r="AZ4" s="85">
         <f>IFERROR((VLOOKUP(AT4,Scoring!$A:$B,2,0))+IF(AV4="y",1,0)+IF(AW4="y",1,0)+IF(AX4="y",1,0)+IF(AY4="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3512,7 +3866,7 @@
       <c r="BF4" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="BG4" s="71">
+      <c r="BG4" s="85">
         <f>IFERROR((VLOOKUP(BA4,Scoring!$A:$B,2,0))+IF(BC4="y",1,0)+IF(BD4="y",1,0)+IF(BE4="y",1,0)+IF(BF4="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3530,7 +3884,7 @@
       <c r="BM4" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="BN4" s="71">
+      <c r="BN4" s="85">
         <f>IFERROR((VLOOKUP(BH4,Scoring!$A:$B,2,0))+IF(BJ4="y",1,0)+IF(BK4="y",1,0)+IF(BL4="y",1,0)+IF(BM4="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3548,7 +3902,7 @@
       <c r="BT4" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="BU4" s="71">
+      <c r="BU4" s="85">
         <f>IFERROR((VLOOKUP(BO4,Scoring!$A:$B,2,0))+IF(BQ4="y",1,0)+IF(BR4="y",1,0)+IF(BS4="y",1,0)+IF(BT4="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3566,43 +3920,43 @@
       <c r="CA4" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="CB4" s="71">
+      <c r="CB4" s="85">
         <f>IFERROR((VLOOKUP(BV4,Scoring!$A:$B,2,0))+IF(BX4="y",1,0)+IF(BY4="y",1,0)+IF(BZ4="y",1,0)+IF(CA4="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC4" s="36"/>
-      <c r="CD4" s="37"/>
-      <c r="CE4" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF4" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG4" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH4" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI4" s="71">
+      <c r="CC4" s="113"/>
+      <c r="CD4" s="114"/>
+      <c r="CE4" s="115" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF4" s="116" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG4" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH4" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI4" s="92">
         <f>IFERROR((VLOOKUP(CC4,Scoring!$A:$B,2,0))+IF(CE4="y",1,0)+IF(CF4="y",1,0)+IF(CG4="y",1,0)+IF(CH4="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ4" s="36"/>
-      <c r="CK4" s="37"/>
-      <c r="CL4" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM4" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN4" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO4" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP4" s="71">
+      <c r="CJ4" s="119"/>
+      <c r="CK4" s="120"/>
+      <c r="CL4" s="121" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM4" s="122" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN4" s="123" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO4" s="124" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP4" s="92">
         <f>IFERROR((VLOOKUP(CJ4,Scoring!$A:$B,2,0))+IF(CL4="y",1,0)+IF(CM4="y",1,0)+IF(CN4="y",1,0)+IF(CO4="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3620,11 +3974,47 @@
       <c r="CV4" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="CW4" s="71">
+      <c r="CW4" s="85">
         <f>IFERROR((VLOOKUP(CQ4,Scoring!$A:$B,2,0))+IF(CS4="y",1,0)+IF(CT4="y",1,0)+IF(CU4="y",1,0)+IF(CV4="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX4" s="13">
+      <c r="CX4" s="119"/>
+      <c r="CY4" s="120"/>
+      <c r="CZ4" s="121" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA4" s="122" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB4" s="123" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC4" s="124" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD4" s="92">
+        <f>IFERROR((VLOOKUP(CX4,Scoring!$A:$B,2,0))+IF(CZ4="y",1,0)+IF(DA4="y",1,0)+IF(DB4="y",1,0)+IF(DC4="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DE4" s="36"/>
+      <c r="DF4" s="37"/>
+      <c r="DG4" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH4" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI4" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ4" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK4" s="85">
+        <f>IFERROR((VLOOKUP(DE4,Scoring!$A:$B,2,0))+IF(DG4="y",1,0)+IF(DH4="y",1,0)+IF(DI4="y",1,0)+IF(DJ4="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DL4" s="13">
         <v>0.0</v>
       </c>
     </row>
@@ -3633,10 +4023,10 @@
         <v>16</v>
       </c>
       <c r="B5" s="46" t="s">
-        <v>394</v>
+        <v>32</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>395</v>
+        <v>33</v>
       </c>
       <c r="D5" s="48"/>
       <c r="E5" s="49"/>
@@ -3652,7 +4042,7 @@
       <c r="I5" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="J5" s="72">
+      <c r="J5" s="99">
         <f>IFERROR((VLOOKUP(D5,Scoring!$A:$B,2,0))+IF(F5="y",1,0)+IF(G5="y",1,0)+IF(H5="y",1,0)+IF(I5="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3670,7 +4060,7 @@
       <c r="P5" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="Q5" s="72">
+      <c r="Q5" s="99">
         <f>IFERROR((VLOOKUP(K5,Scoring!$A:$B,2,0))+IF(M5="y",1,0)+IF(N5="y",1,0)+IF(O5="y",1,0)+IF(P5="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3688,7 +4078,7 @@
       <c r="W5" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="X5" s="72">
+      <c r="X5" s="99">
         <f>IFERROR((VLOOKUP(R5,Scoring!$A:$B,2,0))+IF(T5="y",1,0)+IF(U5="y",1,0)+IF(V5="y",1,0)+IF(W5="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3706,7 +4096,7 @@
       <c r="AD5" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="AE5" s="72">
+      <c r="AE5" s="99">
         <f>IFERROR((VLOOKUP(Y5,Scoring!$A:$B,2,0))+IF(AA5="y",1,0)+IF(AB5="y",1,0)+IF(AC5="y",1,0)+IF(AD5="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3724,7 +4114,7 @@
       <c r="AK5" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="AL5" s="72">
+      <c r="AL5" s="99">
         <f>IFERROR((VLOOKUP(AF5,Scoring!$A:$B,2,0))+IF(AH5="y",1,0)+IF(AI5="y",1,0)+IF(AJ5="y",1,0)+IF(AK5="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3742,7 +4132,7 @@
       <c r="AR5" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="AS5" s="72">
+      <c r="AS5" s="99">
         <f>IFERROR((VLOOKUP(AM5,Scoring!$A:$B,2,0))+IF(AO5="y",1,0)+IF(AP5="y",1,0)+IF(AQ5="y",1,0)+IF(AR5="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3760,7 +4150,7 @@
       <c r="AY5" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="AZ5" s="72">
+      <c r="AZ5" s="99">
         <f>IFERROR((VLOOKUP(AT5,Scoring!$A:$B,2,0))+IF(AV5="y",1,0)+IF(AW5="y",1,0)+IF(AX5="y",1,0)+IF(AY5="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3778,7 +4168,7 @@
       <c r="BF5" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="BG5" s="72">
+      <c r="BG5" s="99">
         <f>IFERROR((VLOOKUP(BA5,Scoring!$A:$B,2,0))+IF(BC5="y",1,0)+IF(BD5="y",1,0)+IF(BE5="y",1,0)+IF(BF5="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3796,7 +4186,7 @@
       <c r="BM5" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="BN5" s="72">
+      <c r="BN5" s="99">
         <f>IFERROR((VLOOKUP(BH5,Scoring!$A:$B,2,0))+IF(BJ5="y",1,0)+IF(BK5="y",1,0)+IF(BL5="y",1,0)+IF(BM5="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3814,7 +4204,7 @@
       <c r="BT5" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="BU5" s="72">
+      <c r="BU5" s="99">
         <f>IFERROR((VLOOKUP(BO5,Scoring!$A:$B,2,0))+IF(BQ5="y",1,0)+IF(BR5="y",1,0)+IF(BS5="y",1,0)+IF(BT5="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3832,43 +4222,43 @@
       <c r="CA5" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="CB5" s="72">
+      <c r="CB5" s="99">
         <f>IFERROR((VLOOKUP(BV5,Scoring!$A:$B,2,0))+IF(BX5="y",1,0)+IF(BY5="y",1,0)+IF(BZ5="y",1,0)+IF(CA5="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC5" s="48"/>
-      <c r="CD5" s="49"/>
-      <c r="CE5" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF5" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG5" s="52" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH5" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI5" s="72">
+      <c r="CC5" s="125"/>
+      <c r="CD5" s="126"/>
+      <c r="CE5" s="127" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF5" s="128" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG5" s="129" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH5" s="130" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI5" s="106">
         <f>IFERROR((VLOOKUP(CC5,Scoring!$A:$B,2,0))+IF(CE5="y",1,0)+IF(CF5="y",1,0)+IF(CG5="y",1,0)+IF(CH5="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ5" s="48"/>
-      <c r="CK5" s="49"/>
-      <c r="CL5" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM5" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN5" s="52" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO5" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP5" s="72">
+      <c r="CJ5" s="131"/>
+      <c r="CK5" s="132"/>
+      <c r="CL5" s="133" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM5" s="134" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN5" s="135" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO5" s="136" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP5" s="106">
         <f>IFERROR((VLOOKUP(CJ5,Scoring!$A:$B,2,0))+IF(CL5="y",1,0)+IF(CM5="y",1,0)+IF(CN5="y",1,0)+IF(CO5="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3886,17 +4276,53 @@
       <c r="CV5" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="CW5" s="72">
+      <c r="CW5" s="99">
         <f>IFERROR((VLOOKUP(CQ5,Scoring!$A:$B,2,0))+IF(CS5="y",1,0)+IF(CT5="y",1,0)+IF(CU5="y",1,0)+IF(CV5="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX5" s="13">
+      <c r="CX5" s="131"/>
+      <c r="CY5" s="132"/>
+      <c r="CZ5" s="133" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA5" s="134" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB5" s="135" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC5" s="136" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD5" s="106">
+        <f>IFERROR((VLOOKUP(CX5,Scoring!$A:$B,2,0))+IF(CZ5="y",1,0)+IF(DA5="y",1,0)+IF(DB5="y",1,0)+IF(DC5="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DE5" s="48"/>
+      <c r="DF5" s="49"/>
+      <c r="DG5" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH5" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI5" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ5" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK5" s="99">
+        <f>IFERROR((VLOOKUP(DE5,Scoring!$A:$B,2,0))+IF(DG5="y",1,0)+IF(DH5="y",1,0)+IF(DI5="y",1,0)+IF(DJ5="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DL5" s="13">
         <v>0.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>22</v>
@@ -3918,7 +4344,7 @@
       <c r="I6" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="J6" s="71">
+      <c r="J6" s="85">
         <f>IFERROR((VLOOKUP(D6,Scoring!$A:$B,2,0))+IF(F6="y",1,0)+IF(G6="y",1,0)+IF(H6="y",1,0)+IF(I6="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3936,7 +4362,7 @@
       <c r="P6" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="Q6" s="71">
+      <c r="Q6" s="85">
         <f>IFERROR((VLOOKUP(K6,Scoring!$A:$B,2,0))+IF(M6="y",1,0)+IF(N6="y",1,0)+IF(O6="y",1,0)+IF(P6="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3954,7 +4380,7 @@
       <c r="W6" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="X6" s="71">
+      <c r="X6" s="85">
         <f>IFERROR((VLOOKUP(R6,Scoring!$A:$B,2,0))+IF(T6="y",1,0)+IF(U6="y",1,0)+IF(V6="y",1,0)+IF(W6="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3972,7 +4398,7 @@
       <c r="AD6" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AE6" s="71">
+      <c r="AE6" s="85">
         <f>IFERROR((VLOOKUP(Y6,Scoring!$A:$B,2,0))+IF(AA6="y",1,0)+IF(AB6="y",1,0)+IF(AC6="y",1,0)+IF(AD6="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3990,7 +4416,7 @@
       <c r="AK6" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AL6" s="71">
+      <c r="AL6" s="85">
         <f>IFERROR((VLOOKUP(AF6,Scoring!$A:$B,2,0))+IF(AH6="y",1,0)+IF(AI6="y",1,0)+IF(AJ6="y",1,0)+IF(AK6="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4008,7 +4434,7 @@
       <c r="AR6" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AS6" s="71">
+      <c r="AS6" s="85">
         <f>IFERROR((VLOOKUP(AM6,Scoring!$A:$B,2,0))+IF(AO6="y",1,0)+IF(AP6="y",1,0)+IF(AQ6="y",1,0)+IF(AR6="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4026,7 +4452,7 @@
       <c r="AY6" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AZ6" s="71">
+      <c r="AZ6" s="85">
         <f>IFERROR((VLOOKUP(AT6,Scoring!$A:$B,2,0))+IF(AV6="y",1,0)+IF(AW6="y",1,0)+IF(AX6="y",1,0)+IF(AY6="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4044,7 +4470,7 @@
       <c r="BF6" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BG6" s="71">
+      <c r="BG6" s="85">
         <f>IFERROR((VLOOKUP(BA6,Scoring!$A:$B,2,0))+IF(BC6="y",1,0)+IF(BD6="y",1,0)+IF(BE6="y",1,0)+IF(BF6="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4062,7 +4488,7 @@
       <c r="BM6" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BN6" s="71">
+      <c r="BN6" s="85">
         <f>IFERROR((VLOOKUP(BH6,Scoring!$A:$B,2,0))+IF(BJ6="y",1,0)+IF(BK6="y",1,0)+IF(BL6="y",1,0)+IF(BM6="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4080,7 +4506,7 @@
       <c r="BT6" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BU6" s="71">
+      <c r="BU6" s="85">
         <f>IFERROR((VLOOKUP(BO6,Scoring!$A:$B,2,0))+IF(BQ6="y",1,0)+IF(BR6="y",1,0)+IF(BS6="y",1,0)+IF(BT6="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4098,43 +4524,43 @@
       <c r="CA6" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="CB6" s="71">
+      <c r="CB6" s="85">
         <f>IFERROR((VLOOKUP(BV6,Scoring!$A:$B,2,0))+IF(BX6="y",1,0)+IF(BY6="y",1,0)+IF(BZ6="y",1,0)+IF(CA6="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC6" s="24"/>
-      <c r="CD6" s="25"/>
-      <c r="CE6" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF6" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG6" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH6" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI6" s="71">
+      <c r="CC6" s="100"/>
+      <c r="CD6" s="101"/>
+      <c r="CE6" s="102" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF6" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG6" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH6" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI6" s="92">
         <f>IFERROR((VLOOKUP(CC6,Scoring!$A:$B,2,0))+IF(CE6="y",1,0)+IF(CF6="y",1,0)+IF(CG6="y",1,0)+IF(CH6="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ6" s="24"/>
-      <c r="CK6" s="25"/>
-      <c r="CL6" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM6" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN6" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO6" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP6" s="71">
+      <c r="CJ6" s="107"/>
+      <c r="CK6" s="108"/>
+      <c r="CL6" s="109" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM6" s="110" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN6" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO6" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP6" s="92">
         <f>IFERROR((VLOOKUP(CJ6,Scoring!$A:$B,2,0))+IF(CL6="y",1,0)+IF(CM6="y",1,0)+IF(CN6="y",1,0)+IF(CO6="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4152,17 +4578,53 @@
       <c r="CV6" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="CW6" s="71">
+      <c r="CW6" s="85">
         <f>IFERROR((VLOOKUP(CQ6,Scoring!$A:$B,2,0))+IF(CS6="y",1,0)+IF(CT6="y",1,0)+IF(CU6="y",1,0)+IF(CV6="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX6" s="13">
+      <c r="CX6" s="107"/>
+      <c r="CY6" s="108"/>
+      <c r="CZ6" s="109" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA6" s="110" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB6" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC6" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD6" s="92">
+        <f>IFERROR((VLOOKUP(CX6,Scoring!$A:$B,2,0))+IF(CZ6="y",1,0)+IF(DA6="y",1,0)+IF(DB6="y",1,0)+IF(DC6="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DE6" s="24"/>
+      <c r="DF6" s="25"/>
+      <c r="DG6" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH6" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI6" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ6" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK6" s="85">
+        <f>IFERROR((VLOOKUP(DE6,Scoring!$A:$B,2,0))+IF(DG6="y",1,0)+IF(DH6="y",1,0)+IF(DI6="y",1,0)+IF(DJ6="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DL6" s="13">
         <v>0.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>24</v>
@@ -4184,7 +4646,7 @@
       <c r="I7" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="J7" s="72">
+      <c r="J7" s="99">
         <f>IFERROR((VLOOKUP(D7,Scoring!$A:$B,2,0))+IF(F7="y",1,0)+IF(G7="y",1,0)+IF(H7="y",1,0)+IF(I7="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4202,7 +4664,7 @@
       <c r="P7" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="Q7" s="72">
+      <c r="Q7" s="99">
         <f>IFERROR((VLOOKUP(K7,Scoring!$A:$B,2,0))+IF(M7="y",1,0)+IF(N7="y",1,0)+IF(O7="y",1,0)+IF(P7="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4220,7 +4682,7 @@
       <c r="W7" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="X7" s="72">
+      <c r="X7" s="99">
         <f>IFERROR((VLOOKUP(R7,Scoring!$A:$B,2,0))+IF(T7="y",1,0)+IF(U7="y",1,0)+IF(V7="y",1,0)+IF(W7="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4238,7 +4700,7 @@
       <c r="AD7" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AE7" s="72">
+      <c r="AE7" s="99">
         <f>IFERROR((VLOOKUP(Y7,Scoring!$A:$B,2,0))+IF(AA7="y",1,0)+IF(AB7="y",1,0)+IF(AC7="y",1,0)+IF(AD7="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4256,7 +4718,7 @@
       <c r="AK7" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AL7" s="72">
+      <c r="AL7" s="99">
         <f>IFERROR((VLOOKUP(AF7,Scoring!$A:$B,2,0))+IF(AH7="y",1,0)+IF(AI7="y",1,0)+IF(AJ7="y",1,0)+IF(AK7="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4274,7 +4736,7 @@
       <c r="AR7" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AS7" s="72">
+      <c r="AS7" s="99">
         <f>IFERROR((VLOOKUP(AM7,Scoring!$A:$B,2,0))+IF(AO7="y",1,0)+IF(AP7="y",1,0)+IF(AQ7="y",1,0)+IF(AR7="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4292,7 +4754,7 @@
       <c r="AY7" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AZ7" s="72">
+      <c r="AZ7" s="99">
         <f>IFERROR((VLOOKUP(AT7,Scoring!$A:$B,2,0))+IF(AV7="y",1,0)+IF(AW7="y",1,0)+IF(AX7="y",1,0)+IF(AY7="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4310,7 +4772,7 @@
       <c r="BF7" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BG7" s="72">
+      <c r="BG7" s="99">
         <f>IFERROR((VLOOKUP(BA7,Scoring!$A:$B,2,0))+IF(BC7="y",1,0)+IF(BD7="y",1,0)+IF(BE7="y",1,0)+IF(BF7="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4328,7 +4790,7 @@
       <c r="BM7" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BN7" s="72">
+      <c r="BN7" s="99">
         <f>IFERROR((VLOOKUP(BH7,Scoring!$A:$B,2,0))+IF(BJ7="y",1,0)+IF(BK7="y",1,0)+IF(BL7="y",1,0)+IF(BM7="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4346,7 +4808,7 @@
       <c r="BT7" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BU7" s="72">
+      <c r="BU7" s="99">
         <f>IFERROR((VLOOKUP(BO7,Scoring!$A:$B,2,0))+IF(BQ7="y",1,0)+IF(BR7="y",1,0)+IF(BS7="y",1,0)+IF(BT7="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4364,43 +4826,43 @@
       <c r="CA7" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="CB7" s="72">
+      <c r="CB7" s="99">
         <f>IFERROR((VLOOKUP(BV7,Scoring!$A:$B,2,0))+IF(BX7="y",1,0)+IF(BY7="y",1,0)+IF(BZ7="y",1,0)+IF(CA7="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC7" s="24"/>
-      <c r="CD7" s="25"/>
-      <c r="CE7" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF7" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG7" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH7" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI7" s="72">
+      <c r="CC7" s="100"/>
+      <c r="CD7" s="101"/>
+      <c r="CE7" s="102" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF7" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG7" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH7" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI7" s="106">
         <f>IFERROR((VLOOKUP(CC7,Scoring!$A:$B,2,0))+IF(CE7="y",1,0)+IF(CF7="y",1,0)+IF(CG7="y",1,0)+IF(CH7="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ7" s="24"/>
-      <c r="CK7" s="25"/>
-      <c r="CL7" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM7" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN7" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO7" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP7" s="72">
+      <c r="CJ7" s="107"/>
+      <c r="CK7" s="108"/>
+      <c r="CL7" s="109" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM7" s="110" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN7" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO7" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP7" s="106">
         <f>IFERROR((VLOOKUP(CJ7,Scoring!$A:$B,2,0))+IF(CL7="y",1,0)+IF(CM7="y",1,0)+IF(CN7="y",1,0)+IF(CO7="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4418,17 +4880,53 @@
       <c r="CV7" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="CW7" s="72">
+      <c r="CW7" s="99">
         <f>IFERROR((VLOOKUP(CQ7,Scoring!$A:$B,2,0))+IF(CS7="y",1,0)+IF(CT7="y",1,0)+IF(CU7="y",1,0)+IF(CV7="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX7" s="13">
+      <c r="CX7" s="107"/>
+      <c r="CY7" s="108"/>
+      <c r="CZ7" s="109" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA7" s="110" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB7" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC7" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD7" s="106">
+        <f>IFERROR((VLOOKUP(CX7,Scoring!$A:$B,2,0))+IF(CZ7="y",1,0)+IF(DA7="y",1,0)+IF(DB7="y",1,0)+IF(DC7="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DE7" s="24"/>
+      <c r="DF7" s="25"/>
+      <c r="DG7" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH7" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI7" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ7" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK7" s="99">
+        <f>IFERROR((VLOOKUP(DE7,Scoring!$A:$B,2,0))+IF(DG7="y",1,0)+IF(DH7="y",1,0)+IF(DI7="y",1,0)+IF(DJ7="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DL7" s="13">
         <v>0.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="33" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>27</v>
@@ -4450,7 +4948,7 @@
       <c r="I8" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="J8" s="71">
+      <c r="J8" s="85">
         <f>IFERROR((VLOOKUP(D8,Scoring!$A:$B,2,0))+IF(F8="y",1,0)+IF(G8="y",1,0)+IF(H8="y",1,0)+IF(I8="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4468,7 +4966,7 @@
       <c r="P8" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="Q8" s="71">
+      <c r="Q8" s="85">
         <f>IFERROR((VLOOKUP(K8,Scoring!$A:$B,2,0))+IF(M8="y",1,0)+IF(N8="y",1,0)+IF(O8="y",1,0)+IF(P8="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4486,7 +4984,7 @@
       <c r="W8" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="X8" s="71">
+      <c r="X8" s="85">
         <f>IFERROR((VLOOKUP(R8,Scoring!$A:$B,2,0))+IF(T8="y",1,0)+IF(U8="y",1,0)+IF(V8="y",1,0)+IF(W8="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4504,7 +5002,7 @@
       <c r="AD8" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="AE8" s="71">
+      <c r="AE8" s="85">
         <f>IFERROR((VLOOKUP(Y8,Scoring!$A:$B,2,0))+IF(AA8="y",1,0)+IF(AB8="y",1,0)+IF(AC8="y",1,0)+IF(AD8="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4522,7 +5020,7 @@
       <c r="AK8" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="AL8" s="71">
+      <c r="AL8" s="85">
         <f>IFERROR((VLOOKUP(AF8,Scoring!$A:$B,2,0))+IF(AH8="y",1,0)+IF(AI8="y",1,0)+IF(AJ8="y",1,0)+IF(AK8="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4540,7 +5038,7 @@
       <c r="AR8" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="AS8" s="71">
+      <c r="AS8" s="85">
         <f>IFERROR((VLOOKUP(AM8,Scoring!$A:$B,2,0))+IF(AO8="y",1,0)+IF(AP8="y",1,0)+IF(AQ8="y",1,0)+IF(AR8="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4558,7 +5056,7 @@
       <c r="AY8" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="AZ8" s="71">
+      <c r="AZ8" s="85">
         <f>IFERROR((VLOOKUP(AT8,Scoring!$A:$B,2,0))+IF(AV8="y",1,0)+IF(AW8="y",1,0)+IF(AX8="y",1,0)+IF(AY8="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4576,7 +5074,7 @@
       <c r="BF8" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="BG8" s="71">
+      <c r="BG8" s="85">
         <f>IFERROR((VLOOKUP(BA8,Scoring!$A:$B,2,0))+IF(BC8="y",1,0)+IF(BD8="y",1,0)+IF(BE8="y",1,0)+IF(BF8="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4594,7 +5092,7 @@
       <c r="BM8" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="BN8" s="71">
+      <c r="BN8" s="85">
         <f>IFERROR((VLOOKUP(BH8,Scoring!$A:$B,2,0))+IF(BJ8="y",1,0)+IF(BK8="y",1,0)+IF(BL8="y",1,0)+IF(BM8="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4612,7 +5110,7 @@
       <c r="BT8" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="BU8" s="71">
+      <c r="BU8" s="85">
         <f>IFERROR((VLOOKUP(BO8,Scoring!$A:$B,2,0))+IF(BQ8="y",1,0)+IF(BR8="y",1,0)+IF(BS8="y",1,0)+IF(BT8="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4630,43 +5128,43 @@
       <c r="CA8" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="CB8" s="71">
+      <c r="CB8" s="85">
         <f>IFERROR((VLOOKUP(BV8,Scoring!$A:$B,2,0))+IF(BX8="y",1,0)+IF(BY8="y",1,0)+IF(BZ8="y",1,0)+IF(CA8="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC8" s="36"/>
-      <c r="CD8" s="37"/>
-      <c r="CE8" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF8" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG8" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH8" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI8" s="71">
+      <c r="CC8" s="113"/>
+      <c r="CD8" s="114"/>
+      <c r="CE8" s="115" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF8" s="116" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG8" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH8" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI8" s="92">
         <f>IFERROR((VLOOKUP(CC8,Scoring!$A:$B,2,0))+IF(CE8="y",1,0)+IF(CF8="y",1,0)+IF(CG8="y",1,0)+IF(CH8="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ8" s="36"/>
-      <c r="CK8" s="37"/>
-      <c r="CL8" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM8" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN8" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO8" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP8" s="71">
+      <c r="CJ8" s="119"/>
+      <c r="CK8" s="120"/>
+      <c r="CL8" s="121" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM8" s="122" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN8" s="123" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO8" s="124" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP8" s="92">
         <f>IFERROR((VLOOKUP(CJ8,Scoring!$A:$B,2,0))+IF(CL8="y",1,0)+IF(CM8="y",1,0)+IF(CN8="y",1,0)+IF(CO8="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4684,17 +5182,53 @@
       <c r="CV8" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="CW8" s="71">
+      <c r="CW8" s="85">
         <f>IFERROR((VLOOKUP(CQ8,Scoring!$A:$B,2,0))+IF(CS8="y",1,0)+IF(CT8="y",1,0)+IF(CU8="y",1,0)+IF(CV8="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX8" s="13">
+      <c r="CX8" s="119"/>
+      <c r="CY8" s="120"/>
+      <c r="CZ8" s="121" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA8" s="122" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB8" s="123" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC8" s="124" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD8" s="92">
+        <f>IFERROR((VLOOKUP(CX8,Scoring!$A:$B,2,0))+IF(CZ8="y",1,0)+IF(DA8="y",1,0)+IF(DB8="y",1,0)+IF(DC8="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DE8" s="36"/>
+      <c r="DF8" s="37"/>
+      <c r="DG8" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH8" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI8" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ8" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK8" s="85">
+        <f>IFERROR((VLOOKUP(DE8,Scoring!$A:$B,2,0))+IF(DG8="y",1,0)+IF(DH8="y",1,0)+IF(DI8="y",1,0)+IF(DJ8="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DL8" s="13">
         <v>0.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="45" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B9" s="46" t="s">
         <v>29</v>
@@ -4716,7 +5250,7 @@
       <c r="I9" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="J9" s="72">
+      <c r="J9" s="99">
         <f>IFERROR((VLOOKUP(D9,Scoring!$A:$B,2,0))+IF(F9="y",1,0)+IF(G9="y",1,0)+IF(H9="y",1,0)+IF(I9="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4734,7 +5268,7 @@
       <c r="P9" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="Q9" s="72">
+      <c r="Q9" s="99">
         <f>IFERROR((VLOOKUP(K9,Scoring!$A:$B,2,0))+IF(M9="y",1,0)+IF(N9="y",1,0)+IF(O9="y",1,0)+IF(P9="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4752,7 +5286,7 @@
       <c r="W9" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="X9" s="72">
+      <c r="X9" s="99">
         <f>IFERROR((VLOOKUP(R9,Scoring!$A:$B,2,0))+IF(T9="y",1,0)+IF(U9="y",1,0)+IF(V9="y",1,0)+IF(W9="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4770,7 +5304,7 @@
       <c r="AD9" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="AE9" s="72">
+      <c r="AE9" s="99">
         <f>IFERROR((VLOOKUP(Y9,Scoring!$A:$B,2,0))+IF(AA9="y",1,0)+IF(AB9="y",1,0)+IF(AC9="y",1,0)+IF(AD9="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4788,7 +5322,7 @@
       <c r="AK9" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="AL9" s="72">
+      <c r="AL9" s="99">
         <f>IFERROR((VLOOKUP(AF9,Scoring!$A:$B,2,0))+IF(AH9="y",1,0)+IF(AI9="y",1,0)+IF(AJ9="y",1,0)+IF(AK9="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4806,7 +5340,7 @@
       <c r="AR9" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="AS9" s="72">
+      <c r="AS9" s="99">
         <f>IFERROR((VLOOKUP(AM9,Scoring!$A:$B,2,0))+IF(AO9="y",1,0)+IF(AP9="y",1,0)+IF(AQ9="y",1,0)+IF(AR9="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4824,7 +5358,7 @@
       <c r="AY9" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="AZ9" s="72">
+      <c r="AZ9" s="99">
         <f>IFERROR((VLOOKUP(AT9,Scoring!$A:$B,2,0))+IF(AV9="y",1,0)+IF(AW9="y",1,0)+IF(AX9="y",1,0)+IF(AY9="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4842,7 +5376,7 @@
       <c r="BF9" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="BG9" s="72">
+      <c r="BG9" s="99">
         <f>IFERROR((VLOOKUP(BA9,Scoring!$A:$B,2,0))+IF(BC9="y",1,0)+IF(BD9="y",1,0)+IF(BE9="y",1,0)+IF(BF9="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4860,7 +5394,7 @@
       <c r="BM9" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="BN9" s="72">
+      <c r="BN9" s="99">
         <f>IFERROR((VLOOKUP(BH9,Scoring!$A:$B,2,0))+IF(BJ9="y",1,0)+IF(BK9="y",1,0)+IF(BL9="y",1,0)+IF(BM9="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4878,7 +5412,7 @@
       <c r="BT9" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="BU9" s="72">
+      <c r="BU9" s="99">
         <f>IFERROR((VLOOKUP(BO9,Scoring!$A:$B,2,0))+IF(BQ9="y",1,0)+IF(BR9="y",1,0)+IF(BS9="y",1,0)+IF(BT9="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4896,43 +5430,43 @@
       <c r="CA9" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="CB9" s="72">
+      <c r="CB9" s="99">
         <f>IFERROR((VLOOKUP(BV9,Scoring!$A:$B,2,0))+IF(BX9="y",1,0)+IF(BY9="y",1,0)+IF(BZ9="y",1,0)+IF(CA9="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC9" s="48"/>
-      <c r="CD9" s="49"/>
-      <c r="CE9" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF9" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG9" s="52" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH9" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI9" s="72">
+      <c r="CC9" s="125"/>
+      <c r="CD9" s="126"/>
+      <c r="CE9" s="127" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF9" s="128" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG9" s="129" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH9" s="130" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI9" s="106">
         <f>IFERROR((VLOOKUP(CC9,Scoring!$A:$B,2,0))+IF(CE9="y",1,0)+IF(CF9="y",1,0)+IF(CG9="y",1,0)+IF(CH9="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ9" s="48"/>
-      <c r="CK9" s="49"/>
-      <c r="CL9" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM9" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN9" s="52" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO9" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP9" s="72">
+      <c r="CJ9" s="131"/>
+      <c r="CK9" s="132"/>
+      <c r="CL9" s="133" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM9" s="134" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN9" s="135" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO9" s="136" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP9" s="106">
         <f>IFERROR((VLOOKUP(CJ9,Scoring!$A:$B,2,0))+IF(CL9="y",1,0)+IF(CM9="y",1,0)+IF(CN9="y",1,0)+IF(CO9="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4950,23 +5484,59 @@
       <c r="CV9" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="CW9" s="72">
+      <c r="CW9" s="99">
         <f>IFERROR((VLOOKUP(CQ9,Scoring!$A:$B,2,0))+IF(CS9="y",1,0)+IF(CT9="y",1,0)+IF(CU9="y",1,0)+IF(CV9="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX9" s="13">
+      <c r="CX9" s="131"/>
+      <c r="CY9" s="132"/>
+      <c r="CZ9" s="133" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA9" s="134" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB9" s="135" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC9" s="136" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD9" s="106">
+        <f>IFERROR((VLOOKUP(CX9,Scoring!$A:$B,2,0))+IF(CZ9="y",1,0)+IF(DA9="y",1,0)+IF(DB9="y",1,0)+IF(DC9="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DE9" s="48"/>
+      <c r="DF9" s="49"/>
+      <c r="DG9" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH9" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI9" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ9" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK9" s="99">
+        <f>IFERROR((VLOOKUP(DE9,Scoring!$A:$B,2,0))+IF(DG9="y",1,0)+IF(DH9="y",1,0)+IF(DI9="y",1,0)+IF(DJ9="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DL9" s="13">
         <v>0.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="s">
-        <v>31</v>
+        <v>395</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>32</v>
+        <v>396</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>33</v>
+        <v>397</v>
       </c>
       <c r="D10" s="24"/>
       <c r="E10" s="25"/>
@@ -4982,7 +5552,7 @@
       <c r="I10" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="J10" s="71">
+      <c r="J10" s="85">
         <f>IFERROR((VLOOKUP(D10,Scoring!$A:$B,2,0))+IF(F10="y",1,0)+IF(G10="y",1,0)+IF(H10="y",1,0)+IF(I10="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5000,7 +5570,7 @@
       <c r="P10" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="Q10" s="71">
+      <c r="Q10" s="85">
         <f>IFERROR((VLOOKUP(K10,Scoring!$A:$B,2,0))+IF(M10="y",1,0)+IF(N10="y",1,0)+IF(O10="y",1,0)+IF(P10="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5018,7 +5588,7 @@
       <c r="W10" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="X10" s="71">
+      <c r="X10" s="85">
         <f>IFERROR((VLOOKUP(R10,Scoring!$A:$B,2,0))+IF(T10="y",1,0)+IF(U10="y",1,0)+IF(V10="y",1,0)+IF(W10="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5036,7 +5606,7 @@
       <c r="AD10" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AE10" s="71">
+      <c r="AE10" s="85">
         <f>IFERROR((VLOOKUP(Y10,Scoring!$A:$B,2,0))+IF(AA10="y",1,0)+IF(AB10="y",1,0)+IF(AC10="y",1,0)+IF(AD10="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5054,7 +5624,7 @@
       <c r="AK10" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AL10" s="71">
+      <c r="AL10" s="85">
         <f>IFERROR((VLOOKUP(AF10,Scoring!$A:$B,2,0))+IF(AH10="y",1,0)+IF(AI10="y",1,0)+IF(AJ10="y",1,0)+IF(AK10="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5072,7 +5642,7 @@
       <c r="AR10" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AS10" s="71">
+      <c r="AS10" s="85">
         <f>IFERROR((VLOOKUP(AM10,Scoring!$A:$B,2,0))+IF(AO10="y",1,0)+IF(AP10="y",1,0)+IF(AQ10="y",1,0)+IF(AR10="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5090,7 +5660,7 @@
       <c r="AY10" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AZ10" s="71">
+      <c r="AZ10" s="85">
         <f>IFERROR((VLOOKUP(AT10,Scoring!$A:$B,2,0))+IF(AV10="y",1,0)+IF(AW10="y",1,0)+IF(AX10="y",1,0)+IF(AY10="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5108,7 +5678,7 @@
       <c r="BF10" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BG10" s="71">
+      <c r="BG10" s="85">
         <f>IFERROR((VLOOKUP(BA10,Scoring!$A:$B,2,0))+IF(BC10="y",1,0)+IF(BD10="y",1,0)+IF(BE10="y",1,0)+IF(BF10="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5126,7 +5696,7 @@
       <c r="BM10" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BN10" s="71">
+      <c r="BN10" s="85">
         <f>IFERROR((VLOOKUP(BH10,Scoring!$A:$B,2,0))+IF(BJ10="y",1,0)+IF(BK10="y",1,0)+IF(BL10="y",1,0)+IF(BM10="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5144,7 +5714,7 @@
       <c r="BT10" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BU10" s="71">
+      <c r="BU10" s="85">
         <f>IFERROR((VLOOKUP(BO10,Scoring!$A:$B,2,0))+IF(BQ10="y",1,0)+IF(BR10="y",1,0)+IF(BS10="y",1,0)+IF(BT10="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5162,43 +5732,43 @@
       <c r="CA10" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="CB10" s="71">
+      <c r="CB10" s="85">
         <f>IFERROR((VLOOKUP(BV10,Scoring!$A:$B,2,0))+IF(BX10="y",1,0)+IF(BY10="y",1,0)+IF(BZ10="y",1,0)+IF(CA10="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC10" s="24"/>
-      <c r="CD10" s="25"/>
-      <c r="CE10" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF10" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG10" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH10" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI10" s="71">
+      <c r="CC10" s="100"/>
+      <c r="CD10" s="101"/>
+      <c r="CE10" s="102" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF10" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG10" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH10" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI10" s="92">
         <f>IFERROR((VLOOKUP(CC10,Scoring!$A:$B,2,0))+IF(CE10="y",1,0)+IF(CF10="y",1,0)+IF(CG10="y",1,0)+IF(CH10="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ10" s="24"/>
-      <c r="CK10" s="25"/>
-      <c r="CL10" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM10" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN10" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO10" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP10" s="71">
+      <c r="CJ10" s="107"/>
+      <c r="CK10" s="108"/>
+      <c r="CL10" s="109" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM10" s="110" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN10" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO10" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP10" s="92">
         <f>IFERROR((VLOOKUP(CJ10,Scoring!$A:$B,2,0))+IF(CL10="y",1,0)+IF(CM10="y",1,0)+IF(CN10="y",1,0)+IF(CO10="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5216,23 +5786,59 @@
       <c r="CV10" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="CW10" s="71">
+      <c r="CW10" s="85">
         <f>IFERROR((VLOOKUP(CQ10,Scoring!$A:$B,2,0))+IF(CS10="y",1,0)+IF(CT10="y",1,0)+IF(CU10="y",1,0)+IF(CV10="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX10" s="13">
+      <c r="CX10" s="107"/>
+      <c r="CY10" s="108"/>
+      <c r="CZ10" s="109" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA10" s="110" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB10" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC10" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD10" s="92">
+        <f>IFERROR((VLOOKUP(CX10,Scoring!$A:$B,2,0))+IF(CZ10="y",1,0)+IF(DA10="y",1,0)+IF(DB10="y",1,0)+IF(DC10="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DE10" s="24"/>
+      <c r="DF10" s="25"/>
+      <c r="DG10" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH10" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI10" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ10" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK10" s="85">
+        <f>IFERROR((VLOOKUP(DE10,Scoring!$A:$B,2,0))+IF(DG10="y",1,0)+IF(DH10="y",1,0)+IF(DI10="y",1,0)+IF(DJ10="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DL10" s="13">
         <v>0.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="s">
-        <v>31</v>
+        <v>395</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>398</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="25"/>
@@ -5248,7 +5854,7 @@
       <c r="I11" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="J11" s="72">
+      <c r="J11" s="99">
         <f>IFERROR((VLOOKUP(D11,Scoring!$A:$B,2,0))+IF(F11="y",1,0)+IF(G11="y",1,0)+IF(H11="y",1,0)+IF(I11="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5266,7 +5872,7 @@
       <c r="P11" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="Q11" s="72">
+      <c r="Q11" s="99">
         <f>IFERROR((VLOOKUP(K11,Scoring!$A:$B,2,0))+IF(M11="y",1,0)+IF(N11="y",1,0)+IF(O11="y",1,0)+IF(P11="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5284,7 +5890,7 @@
       <c r="W11" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="X11" s="72">
+      <c r="X11" s="99">
         <f>IFERROR((VLOOKUP(R11,Scoring!$A:$B,2,0))+IF(T11="y",1,0)+IF(U11="y",1,0)+IF(V11="y",1,0)+IF(W11="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5302,7 +5908,7 @@
       <c r="AD11" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AE11" s="72">
+      <c r="AE11" s="99">
         <f>IFERROR((VLOOKUP(Y11,Scoring!$A:$B,2,0))+IF(AA11="y",1,0)+IF(AB11="y",1,0)+IF(AC11="y",1,0)+IF(AD11="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5320,7 +5926,7 @@
       <c r="AK11" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AL11" s="72">
+      <c r="AL11" s="99">
         <f>IFERROR((VLOOKUP(AF11,Scoring!$A:$B,2,0))+IF(AH11="y",1,0)+IF(AI11="y",1,0)+IF(AJ11="y",1,0)+IF(AK11="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5338,7 +5944,7 @@
       <c r="AR11" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AS11" s="72">
+      <c r="AS11" s="99">
         <f>IFERROR((VLOOKUP(AM11,Scoring!$A:$B,2,0))+IF(AO11="y",1,0)+IF(AP11="y",1,0)+IF(AQ11="y",1,0)+IF(AR11="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5356,7 +5962,7 @@
       <c r="AY11" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AZ11" s="72">
+      <c r="AZ11" s="99">
         <f>IFERROR((VLOOKUP(AT11,Scoring!$A:$B,2,0))+IF(AV11="y",1,0)+IF(AW11="y",1,0)+IF(AX11="y",1,0)+IF(AY11="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5374,7 +5980,7 @@
       <c r="BF11" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BG11" s="72">
+      <c r="BG11" s="99">
         <f>IFERROR((VLOOKUP(BA11,Scoring!$A:$B,2,0))+IF(BC11="y",1,0)+IF(BD11="y",1,0)+IF(BE11="y",1,0)+IF(BF11="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5392,7 +5998,7 @@
       <c r="BM11" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BN11" s="72">
+      <c r="BN11" s="99">
         <f>IFERROR((VLOOKUP(BH11,Scoring!$A:$B,2,0))+IF(BJ11="y",1,0)+IF(BK11="y",1,0)+IF(BL11="y",1,0)+IF(BM11="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5410,7 +6016,7 @@
       <c r="BT11" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BU11" s="72">
+      <c r="BU11" s="99">
         <f>IFERROR((VLOOKUP(BO11,Scoring!$A:$B,2,0))+IF(BQ11="y",1,0)+IF(BR11="y",1,0)+IF(BS11="y",1,0)+IF(BT11="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5428,43 +6034,43 @@
       <c r="CA11" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="CB11" s="72">
+      <c r="CB11" s="99">
         <f>IFERROR((VLOOKUP(BV11,Scoring!$A:$B,2,0))+IF(BX11="y",1,0)+IF(BY11="y",1,0)+IF(BZ11="y",1,0)+IF(CA11="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC11" s="24"/>
-      <c r="CD11" s="25"/>
-      <c r="CE11" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF11" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG11" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH11" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI11" s="72">
+      <c r="CC11" s="100"/>
+      <c r="CD11" s="101"/>
+      <c r="CE11" s="102" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF11" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG11" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH11" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI11" s="106">
         <f>IFERROR((VLOOKUP(CC11,Scoring!$A:$B,2,0))+IF(CE11="y",1,0)+IF(CF11="y",1,0)+IF(CG11="y",1,0)+IF(CH11="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ11" s="24"/>
-      <c r="CK11" s="25"/>
-      <c r="CL11" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM11" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN11" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO11" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP11" s="72">
+      <c r="CJ11" s="107"/>
+      <c r="CK11" s="108"/>
+      <c r="CL11" s="109" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM11" s="110" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN11" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO11" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP11" s="106">
         <f>IFERROR((VLOOKUP(CJ11,Scoring!$A:$B,2,0))+IF(CL11="y",1,0)+IF(CM11="y",1,0)+IF(CN11="y",1,0)+IF(CO11="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5482,11 +6088,47 @@
       <c r="CV11" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="CW11" s="72">
+      <c r="CW11" s="99">
         <f>IFERROR((VLOOKUP(CQ11,Scoring!$A:$B,2,0))+IF(CS11="y",1,0)+IF(CT11="y",1,0)+IF(CU11="y",1,0)+IF(CV11="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX11" s="13">
+      <c r="CX11" s="107"/>
+      <c r="CY11" s="108"/>
+      <c r="CZ11" s="109" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA11" s="110" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB11" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC11" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD11" s="106">
+        <f>IFERROR((VLOOKUP(CX11,Scoring!$A:$B,2,0))+IF(CZ11="y",1,0)+IF(DA11="y",1,0)+IF(DB11="y",1,0)+IF(DC11="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DE11" s="24"/>
+      <c r="DF11" s="25"/>
+      <c r="DG11" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH11" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI11" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ11" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK11" s="99">
+        <f>IFERROR((VLOOKUP(DE11,Scoring!$A:$B,2,0))+IF(DG11="y",1,0)+IF(DH11="y",1,0)+IF(DI11="y",1,0)+IF(DJ11="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DL11" s="13">
         <v>0.0</v>
       </c>
     </row>
@@ -5514,7 +6156,7 @@
       <c r="I12" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="J12" s="71">
+      <c r="J12" s="85">
         <f>IFERROR((VLOOKUP(D12,Scoring!$A:$B,2,0))+IF(F12="y",1,0)+IF(G12="y",1,0)+IF(H12="y",1,0)+IF(I12="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5532,7 +6174,7 @@
       <c r="P12" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="Q12" s="71">
+      <c r="Q12" s="85">
         <f>IFERROR((VLOOKUP(K12,Scoring!$A:$B,2,0))+IF(M12="y",1,0)+IF(N12="y",1,0)+IF(O12="y",1,0)+IF(P12="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5550,7 +6192,7 @@
       <c r="W12" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="X12" s="71">
+      <c r="X12" s="85">
         <f>IFERROR((VLOOKUP(R12,Scoring!$A:$B,2,0))+IF(T12="y",1,0)+IF(U12="y",1,0)+IF(V12="y",1,0)+IF(W12="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5568,7 +6210,7 @@
       <c r="AD12" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="AE12" s="71">
+      <c r="AE12" s="85">
         <f>IFERROR((VLOOKUP(Y12,Scoring!$A:$B,2,0))+IF(AA12="y",1,0)+IF(AB12="y",1,0)+IF(AC12="y",1,0)+IF(AD12="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5586,7 +6228,7 @@
       <c r="AK12" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="AL12" s="71">
+      <c r="AL12" s="85">
         <f>IFERROR((VLOOKUP(AF12,Scoring!$A:$B,2,0))+IF(AH12="y",1,0)+IF(AI12="y",1,0)+IF(AJ12="y",1,0)+IF(AK12="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5604,7 +6246,7 @@
       <c r="AR12" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="AS12" s="71">
+      <c r="AS12" s="85">
         <f>IFERROR((VLOOKUP(AM12,Scoring!$A:$B,2,0))+IF(AO12="y",1,0)+IF(AP12="y",1,0)+IF(AQ12="y",1,0)+IF(AR12="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5622,7 +6264,7 @@
       <c r="AY12" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="AZ12" s="71">
+      <c r="AZ12" s="85">
         <f>IFERROR((VLOOKUP(AT12,Scoring!$A:$B,2,0))+IF(AV12="y",1,0)+IF(AW12="y",1,0)+IF(AX12="y",1,0)+IF(AY12="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5640,7 +6282,7 @@
       <c r="BF12" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="BG12" s="71">
+      <c r="BG12" s="85">
         <f>IFERROR((VLOOKUP(BA12,Scoring!$A:$B,2,0))+IF(BC12="y",1,0)+IF(BD12="y",1,0)+IF(BE12="y",1,0)+IF(BF12="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5658,7 +6300,7 @@
       <c r="BM12" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="BN12" s="71">
+      <c r="BN12" s="85">
         <f>IFERROR((VLOOKUP(BH12,Scoring!$A:$B,2,0))+IF(BJ12="y",1,0)+IF(BK12="y",1,0)+IF(BL12="y",1,0)+IF(BM12="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5676,7 +6318,7 @@
       <c r="BT12" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="BU12" s="71">
+      <c r="BU12" s="85">
         <f>IFERROR((VLOOKUP(BO12,Scoring!$A:$B,2,0))+IF(BQ12="y",1,0)+IF(BR12="y",1,0)+IF(BS12="y",1,0)+IF(BT12="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5694,43 +6336,43 @@
       <c r="CA12" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="CB12" s="71">
+      <c r="CB12" s="85">
         <f>IFERROR((VLOOKUP(BV12,Scoring!$A:$B,2,0))+IF(BX12="y",1,0)+IF(BY12="y",1,0)+IF(BZ12="y",1,0)+IF(CA12="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC12" s="36"/>
-      <c r="CD12" s="37"/>
-      <c r="CE12" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF12" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG12" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH12" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI12" s="71">
+      <c r="CC12" s="113"/>
+      <c r="CD12" s="114"/>
+      <c r="CE12" s="115" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF12" s="116" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG12" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH12" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI12" s="92">
         <f>IFERROR((VLOOKUP(CC12,Scoring!$A:$B,2,0))+IF(CE12="y",1,0)+IF(CF12="y",1,0)+IF(CG12="y",1,0)+IF(CH12="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ12" s="36"/>
-      <c r="CK12" s="37"/>
-      <c r="CL12" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM12" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN12" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO12" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP12" s="71">
+      <c r="CJ12" s="119"/>
+      <c r="CK12" s="120"/>
+      <c r="CL12" s="121" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM12" s="122" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN12" s="123" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO12" s="124" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP12" s="92">
         <f>IFERROR((VLOOKUP(CJ12,Scoring!$A:$B,2,0))+IF(CL12="y",1,0)+IF(CM12="y",1,0)+IF(CN12="y",1,0)+IF(CO12="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5748,11 +6390,47 @@
       <c r="CV12" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="CW12" s="71">
+      <c r="CW12" s="85">
         <f>IFERROR((VLOOKUP(CQ12,Scoring!$A:$B,2,0))+IF(CS12="y",1,0)+IF(CT12="y",1,0)+IF(CU12="y",1,0)+IF(CV12="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX12" s="13">
+      <c r="CX12" s="119"/>
+      <c r="CY12" s="120"/>
+      <c r="CZ12" s="121" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA12" s="122" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB12" s="123" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC12" s="124" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD12" s="92">
+        <f>IFERROR((VLOOKUP(CX12,Scoring!$A:$B,2,0))+IF(CZ12="y",1,0)+IF(DA12="y",1,0)+IF(DB12="y",1,0)+IF(DC12="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DE12" s="36"/>
+      <c r="DF12" s="37"/>
+      <c r="DG12" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH12" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI12" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ12" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK12" s="85">
+        <f>IFERROR((VLOOKUP(DE12,Scoring!$A:$B,2,0))+IF(DG12="y",1,0)+IF(DH12="y",1,0)+IF(DI12="y",1,0)+IF(DJ12="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DL12" s="13">
         <v>0.0</v>
       </c>
     </row>
@@ -5764,7 +6442,7 @@
         <v>400</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D13" s="24"/>
       <c r="E13" s="25"/>
@@ -5780,7 +6458,7 @@
       <c r="I13" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="J13" s="72">
+      <c r="J13" s="99">
         <f>IFERROR((VLOOKUP(D13,Scoring!$A:$B,2,0))+IF(F13="y",1,0)+IF(G13="y",1,0)+IF(H13="y",1,0)+IF(I13="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5798,7 +6476,7 @@
       <c r="P13" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="Q13" s="72">
+      <c r="Q13" s="99">
         <f>IFERROR((VLOOKUP(K13,Scoring!$A:$B,2,0))+IF(M13="y",1,0)+IF(N13="y",1,0)+IF(O13="y",1,0)+IF(P13="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5816,7 +6494,7 @@
       <c r="W13" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="X13" s="72">
+      <c r="X13" s="99">
         <f>IFERROR((VLOOKUP(R13,Scoring!$A:$B,2,0))+IF(T13="y",1,0)+IF(U13="y",1,0)+IF(V13="y",1,0)+IF(W13="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5834,7 +6512,7 @@
       <c r="AD13" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AE13" s="72">
+      <c r="AE13" s="99">
         <f>IFERROR((VLOOKUP(Y13,Scoring!$A:$B,2,0))+IF(AA13="y",1,0)+IF(AB13="y",1,0)+IF(AC13="y",1,0)+IF(AD13="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5852,7 +6530,7 @@
       <c r="AK13" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AL13" s="72">
+      <c r="AL13" s="99">
         <f>IFERROR((VLOOKUP(AF13,Scoring!$A:$B,2,0))+IF(AH13="y",1,0)+IF(AI13="y",1,0)+IF(AJ13="y",1,0)+IF(AK13="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5870,7 +6548,7 @@
       <c r="AR13" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AS13" s="72">
+      <c r="AS13" s="99">
         <f>IFERROR((VLOOKUP(AM13,Scoring!$A:$B,2,0))+IF(AO13="y",1,0)+IF(AP13="y",1,0)+IF(AQ13="y",1,0)+IF(AR13="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5888,7 +6566,7 @@
       <c r="AY13" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AZ13" s="72">
+      <c r="AZ13" s="99">
         <f>IFERROR((VLOOKUP(AT13,Scoring!$A:$B,2,0))+IF(AV13="y",1,0)+IF(AW13="y",1,0)+IF(AX13="y",1,0)+IF(AY13="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5906,7 +6584,7 @@
       <c r="BF13" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BG13" s="72">
+      <c r="BG13" s="99">
         <f>IFERROR((VLOOKUP(BA13,Scoring!$A:$B,2,0))+IF(BC13="y",1,0)+IF(BD13="y",1,0)+IF(BE13="y",1,0)+IF(BF13="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5924,7 +6602,7 @@
       <c r="BM13" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BN13" s="72">
+      <c r="BN13" s="99">
         <f>IFERROR((VLOOKUP(BH13,Scoring!$A:$B,2,0))+IF(BJ13="y",1,0)+IF(BK13="y",1,0)+IF(BL13="y",1,0)+IF(BM13="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5942,7 +6620,7 @@
       <c r="BT13" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BU13" s="72">
+      <c r="BU13" s="99">
         <f>IFERROR((VLOOKUP(BO13,Scoring!$A:$B,2,0))+IF(BQ13="y",1,0)+IF(BR13="y",1,0)+IF(BS13="y",1,0)+IF(BT13="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5960,43 +6638,43 @@
       <c r="CA13" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="CB13" s="72">
+      <c r="CB13" s="99">
         <f>IFERROR((VLOOKUP(BV13,Scoring!$A:$B,2,0))+IF(BX13="y",1,0)+IF(BY13="y",1,0)+IF(BZ13="y",1,0)+IF(CA13="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC13" s="24"/>
-      <c r="CD13" s="25"/>
-      <c r="CE13" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF13" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG13" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH13" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI13" s="72">
+      <c r="CC13" s="100"/>
+      <c r="CD13" s="101"/>
+      <c r="CE13" s="102" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF13" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG13" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH13" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI13" s="106">
         <f>IFERROR((VLOOKUP(CC13,Scoring!$A:$B,2,0))+IF(CE13="y",1,0)+IF(CF13="y",1,0)+IF(CG13="y",1,0)+IF(CH13="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ13" s="24"/>
-      <c r="CK13" s="25"/>
-      <c r="CL13" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM13" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN13" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO13" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP13" s="72">
+      <c r="CJ13" s="107"/>
+      <c r="CK13" s="108"/>
+      <c r="CL13" s="109" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM13" s="110" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN13" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO13" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP13" s="106">
         <f>IFERROR((VLOOKUP(CJ13,Scoring!$A:$B,2,0))+IF(CL13="y",1,0)+IF(CM13="y",1,0)+IF(CN13="y",1,0)+IF(CO13="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6014,11 +6692,47 @@
       <c r="CV13" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="CW13" s="72">
+      <c r="CW13" s="99">
         <f>IFERROR((VLOOKUP(CQ13,Scoring!$A:$B,2,0))+IF(CS13="y",1,0)+IF(CT13="y",1,0)+IF(CU13="y",1,0)+IF(CV13="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX13" s="13">
+      <c r="CX13" s="107"/>
+      <c r="CY13" s="108"/>
+      <c r="CZ13" s="109" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA13" s="110" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB13" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC13" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD13" s="106">
+        <f>IFERROR((VLOOKUP(CX13,Scoring!$A:$B,2,0))+IF(CZ13="y",1,0)+IF(DA13="y",1,0)+IF(DB13="y",1,0)+IF(DC13="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DE13" s="24"/>
+      <c r="DF13" s="25"/>
+      <c r="DG13" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH13" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI13" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ13" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK13" s="99">
+        <f>IFERROR((VLOOKUP(DE13,Scoring!$A:$B,2,0))+IF(DG13="y",1,0)+IF(DH13="y",1,0)+IF(DI13="y",1,0)+IF(DJ13="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DL13" s="13">
         <v>0.0</v>
       </c>
     </row>
@@ -6046,7 +6760,7 @@
       <c r="I14" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="J14" s="71">
+      <c r="J14" s="85">
         <f>IFERROR((VLOOKUP(D14,Scoring!$A:$B,2,0))+IF(F14="y",1,0)+IF(G14="y",1,0)+IF(H14="y",1,0)+IF(I14="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6064,7 +6778,7 @@
       <c r="P14" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="Q14" s="71">
+      <c r="Q14" s="85">
         <f>IFERROR((VLOOKUP(K14,Scoring!$A:$B,2,0))+IF(M14="y",1,0)+IF(N14="y",1,0)+IF(O14="y",1,0)+IF(P14="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6082,7 +6796,7 @@
       <c r="W14" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="X14" s="71">
+      <c r="X14" s="85">
         <f>IFERROR((VLOOKUP(R14,Scoring!$A:$B,2,0))+IF(T14="y",1,0)+IF(U14="y",1,0)+IF(V14="y",1,0)+IF(W14="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6100,7 +6814,7 @@
       <c r="AD14" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="AE14" s="71">
+      <c r="AE14" s="85">
         <f>IFERROR((VLOOKUP(Y14,Scoring!$A:$B,2,0))+IF(AA14="y",1,0)+IF(AB14="y",1,0)+IF(AC14="y",1,0)+IF(AD14="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6118,7 +6832,7 @@
       <c r="AK14" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="AL14" s="71">
+      <c r="AL14" s="85">
         <f>IFERROR((VLOOKUP(AF14,Scoring!$A:$B,2,0))+IF(AH14="y",1,0)+IF(AI14="y",1,0)+IF(AJ14="y",1,0)+IF(AK14="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6136,7 +6850,7 @@
       <c r="AR14" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="AS14" s="71">
+      <c r="AS14" s="85">
         <f>IFERROR((VLOOKUP(AM14,Scoring!$A:$B,2,0))+IF(AO14="y",1,0)+IF(AP14="y",1,0)+IF(AQ14="y",1,0)+IF(AR14="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6154,7 +6868,7 @@
       <c r="AY14" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="AZ14" s="71">
+      <c r="AZ14" s="85">
         <f>IFERROR((VLOOKUP(AT14,Scoring!$A:$B,2,0))+IF(AV14="y",1,0)+IF(AW14="y",1,0)+IF(AX14="y",1,0)+IF(AY14="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6172,7 +6886,7 @@
       <c r="BF14" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="BG14" s="71">
+      <c r="BG14" s="85">
         <f>IFERROR((VLOOKUP(BA14,Scoring!$A:$B,2,0))+IF(BC14="y",1,0)+IF(BD14="y",1,0)+IF(BE14="y",1,0)+IF(BF14="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6190,7 +6904,7 @@
       <c r="BM14" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="BN14" s="71">
+      <c r="BN14" s="85">
         <f>IFERROR((VLOOKUP(BH14,Scoring!$A:$B,2,0))+IF(BJ14="y",1,0)+IF(BK14="y",1,0)+IF(BL14="y",1,0)+IF(BM14="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6208,7 +6922,7 @@
       <c r="BT14" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="BU14" s="71">
+      <c r="BU14" s="85">
         <f>IFERROR((VLOOKUP(BO14,Scoring!$A:$B,2,0))+IF(BQ14="y",1,0)+IF(BR14="y",1,0)+IF(BS14="y",1,0)+IF(BT14="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6226,43 +6940,43 @@
       <c r="CA14" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="CB14" s="71">
+      <c r="CB14" s="85">
         <f>IFERROR((VLOOKUP(BV14,Scoring!$A:$B,2,0))+IF(BX14="y",1,0)+IF(BY14="y",1,0)+IF(BZ14="y",1,0)+IF(CA14="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC14" s="36"/>
-      <c r="CD14" s="37"/>
-      <c r="CE14" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF14" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG14" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH14" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI14" s="71">
+      <c r="CC14" s="113"/>
+      <c r="CD14" s="114"/>
+      <c r="CE14" s="115" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF14" s="116" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG14" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH14" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI14" s="92">
         <f>IFERROR((VLOOKUP(CC14,Scoring!$A:$B,2,0))+IF(CE14="y",1,0)+IF(CF14="y",1,0)+IF(CG14="y",1,0)+IF(CH14="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ14" s="36"/>
-      <c r="CK14" s="37"/>
-      <c r="CL14" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM14" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN14" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO14" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP14" s="71">
+      <c r="CJ14" s="119"/>
+      <c r="CK14" s="120"/>
+      <c r="CL14" s="121" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM14" s="122" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN14" s="123" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO14" s="124" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP14" s="92">
         <f>IFERROR((VLOOKUP(CJ14,Scoring!$A:$B,2,0))+IF(CL14="y",1,0)+IF(CM14="y",1,0)+IF(CN14="y",1,0)+IF(CO14="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6280,11 +6994,47 @@
       <c r="CV14" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="CW14" s="71">
+      <c r="CW14" s="85">
         <f>IFERROR((VLOOKUP(CQ14,Scoring!$A:$B,2,0))+IF(CS14="y",1,0)+IF(CT14="y",1,0)+IF(CU14="y",1,0)+IF(CV14="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX14" s="13">
+      <c r="CX14" s="119"/>
+      <c r="CY14" s="120"/>
+      <c r="CZ14" s="121" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA14" s="122" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB14" s="123" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC14" s="124" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD14" s="92">
+        <f>IFERROR((VLOOKUP(CX14,Scoring!$A:$B,2,0))+IF(CZ14="y",1,0)+IF(DA14="y",1,0)+IF(DB14="y",1,0)+IF(DC14="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DE14" s="36"/>
+      <c r="DF14" s="37"/>
+      <c r="DG14" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH14" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI14" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ14" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK14" s="85">
+        <f>IFERROR((VLOOKUP(DE14,Scoring!$A:$B,2,0))+IF(DG14="y",1,0)+IF(DH14="y",1,0)+IF(DI14="y",1,0)+IF(DJ14="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DL14" s="13">
         <v>0.0</v>
       </c>
     </row>
@@ -6312,7 +7062,7 @@
       <c r="I15" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="J15" s="72">
+      <c r="J15" s="99">
         <f>IFERROR((VLOOKUP(D15,Scoring!$A:$B,2,0))+IF(F15="y",1,0)+IF(G15="y",1,0)+IF(H15="y",1,0)+IF(I15="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6330,7 +7080,7 @@
       <c r="P15" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="Q15" s="72">
+      <c r="Q15" s="99">
         <f>IFERROR((VLOOKUP(K15,Scoring!$A:$B,2,0))+IF(M15="y",1,0)+IF(N15="y",1,0)+IF(O15="y",1,0)+IF(P15="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6348,7 +7098,7 @@
       <c r="W15" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="X15" s="72">
+      <c r="X15" s="99">
         <f>IFERROR((VLOOKUP(R15,Scoring!$A:$B,2,0))+IF(T15="y",1,0)+IF(U15="y",1,0)+IF(V15="y",1,0)+IF(W15="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6366,7 +7116,7 @@
       <c r="AD15" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="AE15" s="72">
+      <c r="AE15" s="99">
         <f>IFERROR((VLOOKUP(Y15,Scoring!$A:$B,2,0))+IF(AA15="y",1,0)+IF(AB15="y",1,0)+IF(AC15="y",1,0)+IF(AD15="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6384,7 +7134,7 @@
       <c r="AK15" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="AL15" s="72">
+      <c r="AL15" s="99">
         <f>IFERROR((VLOOKUP(AF15,Scoring!$A:$B,2,0))+IF(AH15="y",1,0)+IF(AI15="y",1,0)+IF(AJ15="y",1,0)+IF(AK15="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6402,7 +7152,7 @@
       <c r="AR15" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="AS15" s="72">
+      <c r="AS15" s="99">
         <f>IFERROR((VLOOKUP(AM15,Scoring!$A:$B,2,0))+IF(AO15="y",1,0)+IF(AP15="y",1,0)+IF(AQ15="y",1,0)+IF(AR15="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6420,7 +7170,7 @@
       <c r="AY15" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="AZ15" s="72">
+      <c r="AZ15" s="99">
         <f>IFERROR((VLOOKUP(AT15,Scoring!$A:$B,2,0))+IF(AV15="y",1,0)+IF(AW15="y",1,0)+IF(AX15="y",1,0)+IF(AY15="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6438,7 +7188,7 @@
       <c r="BF15" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="BG15" s="72">
+      <c r="BG15" s="99">
         <f>IFERROR((VLOOKUP(BA15,Scoring!$A:$B,2,0))+IF(BC15="y",1,0)+IF(BD15="y",1,0)+IF(BE15="y",1,0)+IF(BF15="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6456,7 +7206,7 @@
       <c r="BM15" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="BN15" s="72">
+      <c r="BN15" s="99">
         <f>IFERROR((VLOOKUP(BH15,Scoring!$A:$B,2,0))+IF(BJ15="y",1,0)+IF(BK15="y",1,0)+IF(BL15="y",1,0)+IF(BM15="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6474,7 +7224,7 @@
       <c r="BT15" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="BU15" s="72">
+      <c r="BU15" s="99">
         <f>IFERROR((VLOOKUP(BO15,Scoring!$A:$B,2,0))+IF(BQ15="y",1,0)+IF(BR15="y",1,0)+IF(BS15="y",1,0)+IF(BT15="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6492,43 +7242,43 @@
       <c r="CA15" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="CB15" s="72">
+      <c r="CB15" s="99">
         <f>IFERROR((VLOOKUP(BV15,Scoring!$A:$B,2,0))+IF(BX15="y",1,0)+IF(BY15="y",1,0)+IF(BZ15="y",1,0)+IF(CA15="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC15" s="48"/>
-      <c r="CD15" s="49"/>
-      <c r="CE15" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF15" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG15" s="52" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH15" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI15" s="72">
+      <c r="CC15" s="125"/>
+      <c r="CD15" s="126"/>
+      <c r="CE15" s="127" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF15" s="128" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG15" s="129" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH15" s="130" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI15" s="106">
         <f>IFERROR((VLOOKUP(CC15,Scoring!$A:$B,2,0))+IF(CE15="y",1,0)+IF(CF15="y",1,0)+IF(CG15="y",1,0)+IF(CH15="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ15" s="48"/>
-      <c r="CK15" s="49"/>
-      <c r="CL15" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM15" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN15" s="52" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO15" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP15" s="72">
+      <c r="CJ15" s="131"/>
+      <c r="CK15" s="132"/>
+      <c r="CL15" s="133" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM15" s="134" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN15" s="135" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO15" s="136" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP15" s="106">
         <f>IFERROR((VLOOKUP(CJ15,Scoring!$A:$B,2,0))+IF(CL15="y",1,0)+IF(CM15="y",1,0)+IF(CN15="y",1,0)+IF(CO15="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6546,11 +7296,47 @@
       <c r="CV15" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="CW15" s="72">
+      <c r="CW15" s="99">
         <f>IFERROR((VLOOKUP(CQ15,Scoring!$A:$B,2,0))+IF(CS15="y",1,0)+IF(CT15="y",1,0)+IF(CU15="y",1,0)+IF(CV15="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX15" s="13">
+      <c r="CX15" s="131"/>
+      <c r="CY15" s="132"/>
+      <c r="CZ15" s="133" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA15" s="134" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB15" s="135" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC15" s="136" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD15" s="106">
+        <f>IFERROR((VLOOKUP(CX15,Scoring!$A:$B,2,0))+IF(CZ15="y",1,0)+IF(DA15="y",1,0)+IF(DB15="y",1,0)+IF(DC15="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DE15" s="48"/>
+      <c r="DF15" s="49"/>
+      <c r="DG15" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH15" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI15" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ15" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK15" s="99">
+        <f>IFERROR((VLOOKUP(DE15,Scoring!$A:$B,2,0))+IF(DG15="y",1,0)+IF(DH15="y",1,0)+IF(DI15="y",1,0)+IF(DJ15="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DL15" s="13">
         <v>0.0</v>
       </c>
     </row>
@@ -6578,7 +7364,7 @@
       <c r="I16" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="J16" s="71">
+      <c r="J16" s="85">
         <f>IFERROR((VLOOKUP(D16,Scoring!$A:$B,2,0))+IF(F16="y",1,0)+IF(G16="y",1,0)+IF(H16="y",1,0)+IF(I16="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6596,7 +7382,7 @@
       <c r="P16" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="Q16" s="71">
+      <c r="Q16" s="85">
         <f>IFERROR((VLOOKUP(K16,Scoring!$A:$B,2,0))+IF(M16="y",1,0)+IF(N16="y",1,0)+IF(O16="y",1,0)+IF(P16="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6614,7 +7400,7 @@
       <c r="W16" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="X16" s="71">
+      <c r="X16" s="85">
         <f>IFERROR((VLOOKUP(R16,Scoring!$A:$B,2,0))+IF(T16="y",1,0)+IF(U16="y",1,0)+IF(V16="y",1,0)+IF(W16="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6632,7 +7418,7 @@
       <c r="AD16" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AE16" s="71">
+      <c r="AE16" s="85">
         <f>IFERROR((VLOOKUP(Y16,Scoring!$A:$B,2,0))+IF(AA16="y",1,0)+IF(AB16="y",1,0)+IF(AC16="y",1,0)+IF(AD16="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6650,7 +7436,7 @@
       <c r="AK16" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AL16" s="71">
+      <c r="AL16" s="85">
         <f>IFERROR((VLOOKUP(AF16,Scoring!$A:$B,2,0))+IF(AH16="y",1,0)+IF(AI16="y",1,0)+IF(AJ16="y",1,0)+IF(AK16="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6668,7 +7454,7 @@
       <c r="AR16" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AS16" s="71">
+      <c r="AS16" s="85">
         <f>IFERROR((VLOOKUP(AM16,Scoring!$A:$B,2,0))+IF(AO16="y",1,0)+IF(AP16="y",1,0)+IF(AQ16="y",1,0)+IF(AR16="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6686,7 +7472,7 @@
       <c r="AY16" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AZ16" s="71">
+      <c r="AZ16" s="85">
         <f>IFERROR((VLOOKUP(AT16,Scoring!$A:$B,2,0))+IF(AV16="y",1,0)+IF(AW16="y",1,0)+IF(AX16="y",1,0)+IF(AY16="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6704,7 +7490,7 @@
       <c r="BF16" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BG16" s="71">
+      <c r="BG16" s="85">
         <f>IFERROR((VLOOKUP(BA16,Scoring!$A:$B,2,0))+IF(BC16="y",1,0)+IF(BD16="y",1,0)+IF(BE16="y",1,0)+IF(BF16="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6722,7 +7508,7 @@
       <c r="BM16" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BN16" s="71">
+      <c r="BN16" s="85">
         <f>IFERROR((VLOOKUP(BH16,Scoring!$A:$B,2,0))+IF(BJ16="y",1,0)+IF(BK16="y",1,0)+IF(BL16="y",1,0)+IF(BM16="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6740,7 +7526,7 @@
       <c r="BT16" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BU16" s="71">
+      <c r="BU16" s="85">
         <f>IFERROR((VLOOKUP(BO16,Scoring!$A:$B,2,0))+IF(BQ16="y",1,0)+IF(BR16="y",1,0)+IF(BS16="y",1,0)+IF(BT16="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6758,43 +7544,43 @@
       <c r="CA16" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="CB16" s="71">
+      <c r="CB16" s="85">
         <f>IFERROR((VLOOKUP(BV16,Scoring!$A:$B,2,0))+IF(BX16="y",1,0)+IF(BY16="y",1,0)+IF(BZ16="y",1,0)+IF(CA16="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC16" s="24"/>
-      <c r="CD16" s="25"/>
-      <c r="CE16" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF16" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG16" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH16" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI16" s="71">
+      <c r="CC16" s="100"/>
+      <c r="CD16" s="101"/>
+      <c r="CE16" s="102" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF16" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG16" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH16" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI16" s="92">
         <f>IFERROR((VLOOKUP(CC16,Scoring!$A:$B,2,0))+IF(CE16="y",1,0)+IF(CF16="y",1,0)+IF(CG16="y",1,0)+IF(CH16="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ16" s="24"/>
-      <c r="CK16" s="25"/>
-      <c r="CL16" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM16" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN16" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO16" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP16" s="71">
+      <c r="CJ16" s="107"/>
+      <c r="CK16" s="108"/>
+      <c r="CL16" s="109" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM16" s="110" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN16" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO16" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP16" s="92">
         <f>IFERROR((VLOOKUP(CJ16,Scoring!$A:$B,2,0))+IF(CL16="y",1,0)+IF(CM16="y",1,0)+IF(CN16="y",1,0)+IF(CO16="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6812,11 +7598,47 @@
       <c r="CV16" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="CW16" s="71">
+      <c r="CW16" s="85">
         <f>IFERROR((VLOOKUP(CQ16,Scoring!$A:$B,2,0))+IF(CS16="y",1,0)+IF(CT16="y",1,0)+IF(CU16="y",1,0)+IF(CV16="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX16" s="13">
+      <c r="CX16" s="107"/>
+      <c r="CY16" s="108"/>
+      <c r="CZ16" s="109" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA16" s="110" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB16" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC16" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD16" s="92">
+        <f>IFERROR((VLOOKUP(CX16,Scoring!$A:$B,2,0))+IF(CZ16="y",1,0)+IF(DA16="y",1,0)+IF(DB16="y",1,0)+IF(DC16="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DE16" s="24"/>
+      <c r="DF16" s="25"/>
+      <c r="DG16" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH16" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI16" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ16" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK16" s="85">
+        <f>IFERROR((VLOOKUP(DE16,Scoring!$A:$B,2,0))+IF(DG16="y",1,0)+IF(DH16="y",1,0)+IF(DI16="y",1,0)+IF(DJ16="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DL16" s="13">
         <v>0.0</v>
       </c>
     </row>
@@ -6828,7 +7650,7 @@
         <v>401</v>
       </c>
       <c r="C17" s="59" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D17" s="60"/>
       <c r="E17" s="61"/>
@@ -6844,7 +7666,7 @@
       <c r="I17" s="65" t="s">
         <v>128</v>
       </c>
-      <c r="J17" s="73">
+      <c r="J17" s="137">
         <f>IFERROR((VLOOKUP(D17,Scoring!$A:$B,2,0))+IF(F17="y",1,0)+IF(G17="y",1,0)+IF(H17="y",1,0)+IF(I17="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6862,7 +7684,7 @@
       <c r="P17" s="65" t="s">
         <v>128</v>
       </c>
-      <c r="Q17" s="73">
+      <c r="Q17" s="137">
         <f>IFERROR((VLOOKUP(K17,Scoring!$A:$B,2,0))+IF(M17="y",1,0)+IF(N17="y",1,0)+IF(O17="y",1,0)+IF(P17="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6880,7 +7702,7 @@
       <c r="W17" s="65" t="s">
         <v>128</v>
       </c>
-      <c r="X17" s="73">
+      <c r="X17" s="137">
         <f>IFERROR((VLOOKUP(R17,Scoring!$A:$B,2,0))+IF(T17="y",1,0)+IF(U17="y",1,0)+IF(V17="y",1,0)+IF(W17="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6898,7 +7720,7 @@
       <c r="AD17" s="65" t="s">
         <v>128</v>
       </c>
-      <c r="AE17" s="73">
+      <c r="AE17" s="137">
         <f>IFERROR((VLOOKUP(Y17,Scoring!$A:$B,2,0))+IF(AA17="y",1,0)+IF(AB17="y",1,0)+IF(AC17="y",1,0)+IF(AD17="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6916,7 +7738,7 @@
       <c r="AK17" s="65" t="s">
         <v>128</v>
       </c>
-      <c r="AL17" s="73">
+      <c r="AL17" s="137">
         <f>IFERROR((VLOOKUP(AF17,Scoring!$A:$B,2,0))+IF(AH17="y",1,0)+IF(AI17="y",1,0)+IF(AJ17="y",1,0)+IF(AK17="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6934,7 +7756,7 @@
       <c r="AR17" s="65" t="s">
         <v>128</v>
       </c>
-      <c r="AS17" s="73">
+      <c r="AS17" s="137">
         <f>IFERROR((VLOOKUP(AM17,Scoring!$A:$B,2,0))+IF(AO17="y",1,0)+IF(AP17="y",1,0)+IF(AQ17="y",1,0)+IF(AR17="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6952,7 +7774,7 @@
       <c r="AY17" s="65" t="s">
         <v>128</v>
       </c>
-      <c r="AZ17" s="73">
+      <c r="AZ17" s="137">
         <f>IFERROR((VLOOKUP(AT17,Scoring!$A:$B,2,0))+IF(AV17="y",1,0)+IF(AW17="y",1,0)+IF(AX17="y",1,0)+IF(AY17="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6970,7 +7792,7 @@
       <c r="BF17" s="65" t="s">
         <v>128</v>
       </c>
-      <c r="BG17" s="73">
+      <c r="BG17" s="137">
         <f>IFERROR((VLOOKUP(BA17,Scoring!$A:$B,2,0))+IF(BC17="y",1,0)+IF(BD17="y",1,0)+IF(BE17="y",1,0)+IF(BF17="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6988,7 +7810,7 @@
       <c r="BM17" s="65" t="s">
         <v>128</v>
       </c>
-      <c r="BN17" s="73">
+      <c r="BN17" s="137">
         <f>IFERROR((VLOOKUP(BH17,Scoring!$A:$B,2,0))+IF(BJ17="y",1,0)+IF(BK17="y",1,0)+IF(BL17="y",1,0)+IF(BM17="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -7006,7 +7828,7 @@
       <c r="BT17" s="65" t="s">
         <v>128</v>
       </c>
-      <c r="BU17" s="73">
+      <c r="BU17" s="137">
         <f>IFERROR((VLOOKUP(BO17,Scoring!$A:$B,2,0))+IF(BQ17="y",1,0)+IF(BR17="y",1,0)+IF(BS17="y",1,0)+IF(BT17="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -7024,43 +7846,43 @@
       <c r="CA17" s="65" t="s">
         <v>128</v>
       </c>
-      <c r="CB17" s="73">
+      <c r="CB17" s="137">
         <f>IFERROR((VLOOKUP(BV17,Scoring!$A:$B,2,0))+IF(BX17="y",1,0)+IF(BY17="y",1,0)+IF(BZ17="y",1,0)+IF(CA17="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC17" s="60"/>
-      <c r="CD17" s="61"/>
-      <c r="CE17" s="62" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF17" s="63" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG17" s="64" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH17" s="65" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI17" s="73">
+      <c r="CC17" s="138"/>
+      <c r="CD17" s="139"/>
+      <c r="CE17" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF17" s="141" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG17" s="142" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH17" s="143" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI17" s="144">
         <f>IFERROR((VLOOKUP(CC17,Scoring!$A:$B,2,0))+IF(CE17="y",1,0)+IF(CF17="y",1,0)+IF(CG17="y",1,0)+IF(CH17="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ17" s="60"/>
-      <c r="CK17" s="61"/>
-      <c r="CL17" s="62" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM17" s="63" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN17" s="64" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO17" s="65" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP17" s="73">
+      <c r="CJ17" s="145"/>
+      <c r="CK17" s="146"/>
+      <c r="CL17" s="147" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM17" s="148" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN17" s="149" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO17" s="150" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP17" s="144">
         <f>IFERROR((VLOOKUP(CJ17,Scoring!$A:$B,2,0))+IF(CL17="y",1,0)+IF(CM17="y",1,0)+IF(CN17="y",1,0)+IF(CO17="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -7078,11 +7900,47 @@
       <c r="CV17" s="65" t="s">
         <v>128</v>
       </c>
-      <c r="CW17" s="73">
+      <c r="CW17" s="137">
         <f>IFERROR((VLOOKUP(CQ17,Scoring!$A:$B,2,0))+IF(CS17="y",1,0)+IF(CT17="y",1,0)+IF(CU17="y",1,0)+IF(CV17="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX17" s="13">
+      <c r="CX17" s="145"/>
+      <c r="CY17" s="146"/>
+      <c r="CZ17" s="147" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA17" s="148" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB17" s="149" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC17" s="150" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD17" s="144">
+        <f>IFERROR((VLOOKUP(CX17,Scoring!$A:$B,2,0))+IF(CZ17="y",1,0)+IF(DA17="y",1,0)+IF(DB17="y",1,0)+IF(DC17="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DE17" s="60"/>
+      <c r="DF17" s="61"/>
+      <c r="DG17" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH17" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI17" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ17" s="65" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK17" s="137">
+        <f>IFERROR((VLOOKUP(DE17,Scoring!$A:$B,2,0))+IF(DG17="y",1,0)+IF(DH17="y",1,0)+IF(DI17="y",1,0)+IF(DJ17="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DL17" s="13">
         <v>0.0</v>
       </c>
     </row>
@@ -7136,10 +7994,10 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B4" s="69" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>292</v>
@@ -7147,10 +8005,10 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B5" s="69" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>292</v>
@@ -7158,10 +8016,10 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B6" s="69" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>292</v>
@@ -7169,10 +8027,10 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B7" s="69" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>292</v>
@@ -7180,10 +8038,10 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B8" s="69" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>292</v>
@@ -7191,10 +8049,10 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B9" s="69" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>292</v>
@@ -7202,10 +8060,10 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B10" s="69" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>292</v>
@@ -7213,10 +8071,10 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B11" s="69" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>292</v>
@@ -7224,10 +8082,10 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B12" s="69" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>292</v>
@@ -7235,10 +8093,10 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B13" s="69" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>292</v>
@@ -7246,10 +8104,10 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B14" s="69" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>292</v>
@@ -7257,10 +8115,10 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B15" s="69" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>292</v>
@@ -7268,10 +8126,10 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B16" s="69" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>292</v>
@@ -7279,10 +8137,10 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B17" s="69" t="s">
         <v>430</v>
-      </c>
-      <c r="B17" s="69" t="s">
-        <v>431</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>292</v>
@@ -7290,10 +8148,10 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>432</v>
+        <v>154</v>
       </c>
       <c r="B18" s="69" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>292</v>
@@ -7301,12 +8159,34 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B19" s="69" t="s">
+        <v>433</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B20" s="69" t="s">
+        <v>433</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B19" s="69" t="s">
+      <c r="B21" s="69" t="s">
         <v>434</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>292</v>
       </c>
     </row>

--- a/the_alternative_f1/The_Alternative_F1.xlsx
+++ b/the_alternative_f1/The_Alternative_F1.xlsx
@@ -9072,7 +9072,7 @@
         <v>0.0</v>
       </c>
       <c r="H3" s="1">
-        <v>0.0</v>
+        <v>22.0</v>
       </c>
       <c r="I3" s="1">
         <v>22.0</v>
@@ -10282,7 +10282,7 @@
         <v>2.0</v>
       </c>
       <c r="H8" s="1">
-        <v>0.0</v>
+        <v>22.0</v>
       </c>
       <c r="I8" s="1">
         <v>22.0</v>
@@ -10524,7 +10524,7 @@
         <v>1.0</v>
       </c>
       <c r="H9" s="1">
-        <v>0.0</v>
+        <v>22.0</v>
       </c>
       <c r="I9" s="1">
         <v>22.0</v>
@@ -10766,7 +10766,7 @@
         <v>0.0</v>
       </c>
       <c r="H10" s="1">
-        <v>0.0</v>
+        <v>22.0</v>
       </c>
       <c r="I10" s="1">
         <v>22.0</v>

--- a/the_alternative_f1/The_Alternative_F1.xlsx
+++ b/the_alternative_f1/The_Alternative_F1.xlsx
@@ -1224,7 +1224,7 @@
     <t>Audi</t>
   </si>
   <si>
-    <t>Austin</t>
+    <t>Evelo</t>
   </si>
   <si>
     <t>Randy</t>

--- a/the_alternative_f1/The_Alternative_F1.xlsx
+++ b/the_alternative_f1/The_Alternative_F1.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3314" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3320" uniqueCount="428">
   <si>
     <t>Positions</t>
   </si>
@@ -1230,12 +1230,18 @@
     <t>Randy</t>
   </si>
   <si>
-    <t>Pre-Season: TBD</t>
+    <t>Pre-Season: Mexico</t>
   </si>
   <si>
     <t>8/12/2026</t>
   </si>
   <si>
+    <t>Confirmed</t>
+  </si>
+  <si>
+    <t>Pre-Season: Vegas</t>
+  </si>
+  <si>
     <t>8/19/2026</t>
   </si>
   <si>
@@ -1245,67 +1251,40 @@
     <t>8/26/2026</t>
   </si>
   <si>
-    <t>W1</t>
-  </si>
-  <si>
     <t>9/9/2026</t>
   </si>
   <si>
-    <t>W2</t>
+    <t>Imola</t>
   </si>
   <si>
     <t>9/16/2026</t>
   </si>
   <si>
-    <t>W3</t>
-  </si>
-  <si>
     <t>9/30/2026</t>
   </si>
   <si>
-    <t>W4</t>
-  </si>
-  <si>
     <t>10/7/2026</t>
   </si>
   <si>
-    <t>W5</t>
-  </si>
-  <si>
     <t>10/14/2026</t>
   </si>
   <si>
-    <t>W6</t>
-  </si>
-  <si>
     <t>10/28/2026</t>
   </si>
   <si>
-    <t>W7</t>
+    <t>Silverstone Sprint</t>
   </si>
   <si>
     <t>11/4/2026</t>
   </si>
   <si>
-    <t>W8</t>
-  </si>
-  <si>
     <t>11/18/2026</t>
   </si>
   <si>
-    <t>W9</t>
-  </si>
-  <si>
     <t>12/2/2026</t>
   </si>
   <si>
-    <t>W-10</t>
-  </si>
-  <si>
     <t>12/9/2026</t>
-  </si>
-  <si>
-    <t>W-11</t>
   </si>
   <si>
     <t>12/30/2026</t>
@@ -3122,8 +3101,12 @@
       <c r="C2" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="17"/>
+      <c r="D2" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="E2" s="17">
+        <v>1.0</v>
+      </c>
       <c r="F2" s="18" t="s">
         <v>128</v>
       </c>
@@ -3138,10 +3121,14 @@
       </c>
       <c r="J2" s="85">
         <f>IFERROR((VLOOKUP(D2,Scoring!$A:$B,2,0))+IF(F2="y",1,0)+IF(G2="y",1,0)+IF(H2="y",1,0)+IF(I2="y",1,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="K2" s="16"/>
-      <c r="L2" s="17"/>
+        <v>18</v>
+      </c>
+      <c r="K2" s="16">
+        <v>3.0</v>
+      </c>
+      <c r="L2" s="17">
+        <v>3.0</v>
+      </c>
       <c r="M2" s="18" t="s">
         <v>128</v>
       </c>
@@ -3156,7 +3143,7 @@
       </c>
       <c r="Q2" s="85">
         <f>IFERROR((VLOOKUP(K2,Scoring!$A:$B,2,0))+IF(M2="y",1,0)+IF(N2="y",1,0)+IF(O2="y",1,0)+IF(P2="y",1,0),0)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R2" s="16"/>
       <c r="S2" s="17"/>
@@ -3424,8 +3411,12 @@
       <c r="C3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="24"/>
-      <c r="E3" s="25"/>
+      <c r="D3" s="24">
+        <v>3.0</v>
+      </c>
+      <c r="E3" s="25">
+        <v>2.0</v>
+      </c>
       <c r="F3" s="26" t="s">
         <v>128</v>
       </c>
@@ -3440,10 +3431,14 @@
       </c>
       <c r="J3" s="99">
         <f>IFERROR((VLOOKUP(D3,Scoring!$A:$B,2,0))+IF(F3="y",1,0)+IF(G3="y",1,0)+IF(H3="y",1,0)+IF(I3="y",1,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="24"/>
-      <c r="L3" s="25"/>
+        <v>15</v>
+      </c>
+      <c r="K3" s="24">
+        <v>4.0</v>
+      </c>
+      <c r="L3" s="25">
+        <v>4.0</v>
+      </c>
       <c r="M3" s="26" t="s">
         <v>128</v>
       </c>
@@ -3458,7 +3453,7 @@
       </c>
       <c r="Q3" s="99">
         <f>IFERROR((VLOOKUP(K3,Scoring!$A:$B,2,0))+IF(M3="y",1,0)+IF(N3="y",1,0)+IF(O3="y",1,0)+IF(P3="y",1,0),0)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R3" s="24"/>
       <c r="S3" s="25"/>
@@ -3726,8 +3721,12 @@
       <c r="C4" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="37"/>
+      <c r="D4" s="36">
+        <v>1.0</v>
+      </c>
+      <c r="E4" s="37">
+        <v>3.0</v>
+      </c>
       <c r="F4" s="38" t="s">
         <v>128</v>
       </c>
@@ -3742,10 +3741,14 @@
       </c>
       <c r="J4" s="85">
         <f>IFERROR((VLOOKUP(D4,Scoring!$A:$B,2,0))+IF(F4="y",1,0)+IF(G4="y",1,0)+IF(H4="y",1,0)+IF(I4="y",1,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="K4" s="36"/>
-      <c r="L4" s="37"/>
+        <v>25</v>
+      </c>
+      <c r="K4" s="36">
+        <v>5.0</v>
+      </c>
+      <c r="L4" s="37">
+        <v>5.0</v>
+      </c>
       <c r="M4" s="38" t="s">
         <v>128</v>
       </c>
@@ -3760,7 +3763,7 @@
       </c>
       <c r="Q4" s="85">
         <f>IFERROR((VLOOKUP(K4,Scoring!$A:$B,2,0))+IF(M4="y",1,0)+IF(N4="y",1,0)+IF(O4="y",1,0)+IF(P4="y",1,0),0)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R4" s="36"/>
       <c r="S4" s="37"/>
@@ -4028,8 +4031,12 @@
       <c r="C5" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="48"/>
-      <c r="E5" s="49"/>
+      <c r="D5" s="48">
+        <v>4.0</v>
+      </c>
+      <c r="E5" s="49">
+        <v>4.0</v>
+      </c>
       <c r="F5" s="50" t="s">
         <v>128</v>
       </c>
@@ -4044,10 +4051,14 @@
       </c>
       <c r="J5" s="99">
         <f>IFERROR((VLOOKUP(D5,Scoring!$A:$B,2,0))+IF(F5="y",1,0)+IF(G5="y",1,0)+IF(H5="y",1,0)+IF(I5="y",1,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="48"/>
-      <c r="L5" s="49"/>
+        <v>12</v>
+      </c>
+      <c r="K5" s="48">
+        <v>6.0</v>
+      </c>
+      <c r="L5" s="49">
+        <v>6.0</v>
+      </c>
       <c r="M5" s="50" t="s">
         <v>128</v>
       </c>
@@ -4062,7 +4073,7 @@
       </c>
       <c r="Q5" s="99">
         <f>IFERROR((VLOOKUP(K5,Scoring!$A:$B,2,0))+IF(M5="y",1,0)+IF(N5="y",1,0)+IF(O5="y",1,0)+IF(P5="y",1,0),0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R5" s="48"/>
       <c r="S5" s="49"/>
@@ -4330,8 +4341,12 @@
       <c r="C6" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="24"/>
-      <c r="E6" s="25"/>
+      <c r="D6" s="24">
+        <v>6.0</v>
+      </c>
+      <c r="E6" s="25">
+        <v>5.0</v>
+      </c>
       <c r="F6" s="26" t="s">
         <v>128</v>
       </c>
@@ -4346,10 +4361,14 @@
       </c>
       <c r="J6" s="85">
         <f>IFERROR((VLOOKUP(D6,Scoring!$A:$B,2,0))+IF(F6="y",1,0)+IF(G6="y",1,0)+IF(H6="y",1,0)+IF(I6="y",1,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="24"/>
-      <c r="L6" s="25"/>
+        <v>8</v>
+      </c>
+      <c r="K6" s="24">
+        <v>11.0</v>
+      </c>
+      <c r="L6" s="25">
+        <v>10.0</v>
+      </c>
       <c r="M6" s="26" t="s">
         <v>128</v>
       </c>
@@ -4364,7 +4383,7 @@
       </c>
       <c r="Q6" s="85">
         <f>IFERROR((VLOOKUP(K6,Scoring!$A:$B,2,0))+IF(M6="y",1,0)+IF(N6="y",1,0)+IF(O6="y",1,0)+IF(P6="y",1,0),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="24"/>
       <c r="S6" s="25"/>
@@ -4632,8 +4651,12 @@
       <c r="C7" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="25"/>
+      <c r="D7" s="24">
+        <v>5.0</v>
+      </c>
+      <c r="E7" s="25">
+        <v>6.0</v>
+      </c>
       <c r="F7" s="26" t="s">
         <v>128</v>
       </c>
@@ -4648,10 +4671,14 @@
       </c>
       <c r="J7" s="99">
         <f>IFERROR((VLOOKUP(D7,Scoring!$A:$B,2,0))+IF(F7="y",1,0)+IF(G7="y",1,0)+IF(H7="y",1,0)+IF(I7="y",1,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="24"/>
-      <c r="L7" s="25"/>
+        <v>10</v>
+      </c>
+      <c r="K7" s="24">
+        <v>10.0</v>
+      </c>
+      <c r="L7" s="25">
+        <v>11.0</v>
+      </c>
       <c r="M7" s="26" t="s">
         <v>128</v>
       </c>
@@ -4666,7 +4693,7 @@
       </c>
       <c r="Q7" s="99">
         <f>IFERROR((VLOOKUP(K7,Scoring!$A:$B,2,0))+IF(M7="y",1,0)+IF(N7="y",1,0)+IF(O7="y",1,0)+IF(P7="y",1,0),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R7" s="24"/>
       <c r="S7" s="25"/>
@@ -4934,8 +4961,12 @@
       <c r="C8" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="36"/>
-      <c r="E8" s="37"/>
+      <c r="D8" s="36">
+        <v>7.0</v>
+      </c>
+      <c r="E8" s="37">
+        <v>7.0</v>
+      </c>
       <c r="F8" s="38" t="s">
         <v>128</v>
       </c>
@@ -4950,10 +4981,14 @@
       </c>
       <c r="J8" s="85">
         <f>IFERROR((VLOOKUP(D8,Scoring!$A:$B,2,0))+IF(F8="y",1,0)+IF(G8="y",1,0)+IF(H8="y",1,0)+IF(I8="y",1,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="36"/>
-      <c r="L8" s="37"/>
+        <v>6</v>
+      </c>
+      <c r="K8" s="36">
+        <v>2.0</v>
+      </c>
+      <c r="L8" s="37">
+        <v>1.0</v>
+      </c>
       <c r="M8" s="38" t="s">
         <v>128</v>
       </c>
@@ -4968,7 +5003,7 @@
       </c>
       <c r="Q8" s="85">
         <f>IFERROR((VLOOKUP(K8,Scoring!$A:$B,2,0))+IF(M8="y",1,0)+IF(N8="y",1,0)+IF(O8="y",1,0)+IF(P8="y",1,0),0)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R8" s="36"/>
       <c r="S8" s="37"/>
@@ -5236,8 +5271,12 @@
       <c r="C9" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="48"/>
-      <c r="E9" s="49"/>
+      <c r="D9" s="48">
+        <v>8.0</v>
+      </c>
+      <c r="E9" s="49">
+        <v>8.0</v>
+      </c>
       <c r="F9" s="50" t="s">
         <v>128</v>
       </c>
@@ -5252,10 +5291,14 @@
       </c>
       <c r="J9" s="99">
         <f>IFERROR((VLOOKUP(D9,Scoring!$A:$B,2,0))+IF(F9="y",1,0)+IF(G9="y",1,0)+IF(H9="y",1,0)+IF(I9="y",1,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="48"/>
-      <c r="L9" s="49"/>
+        <v>4</v>
+      </c>
+      <c r="K9" s="48">
+        <v>1.0</v>
+      </c>
+      <c r="L9" s="49">
+        <v>2.0</v>
+      </c>
       <c r="M9" s="50" t="s">
         <v>128</v>
       </c>
@@ -5270,7 +5313,7 @@
       </c>
       <c r="Q9" s="99">
         <f>IFERROR((VLOOKUP(K9,Scoring!$A:$B,2,0))+IF(M9="y",1,0)+IF(N9="y",1,0)+IF(O9="y",1,0)+IF(P9="y",1,0),0)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R9" s="48"/>
       <c r="S9" s="49"/>
@@ -5538,8 +5581,12 @@
       <c r="C10" s="15" t="s">
         <v>397</v>
       </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="25"/>
+      <c r="D10" s="24">
+        <v>9.0</v>
+      </c>
+      <c r="E10" s="25">
+        <v>9.0</v>
+      </c>
       <c r="F10" s="26" t="s">
         <v>128</v>
       </c>
@@ -5554,10 +5601,14 @@
       </c>
       <c r="J10" s="85">
         <f>IFERROR((VLOOKUP(D10,Scoring!$A:$B,2,0))+IF(F10="y",1,0)+IF(G10="y",1,0)+IF(H10="y",1,0)+IF(I10="y",1,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="K10" s="24"/>
-      <c r="L10" s="25"/>
+        <v>3</v>
+      </c>
+      <c r="K10" s="24">
+        <v>7.0</v>
+      </c>
+      <c r="L10" s="25">
+        <v>9.0</v>
+      </c>
       <c r="M10" s="26" t="s">
         <v>128</v>
       </c>
@@ -5572,7 +5623,7 @@
       </c>
       <c r="Q10" s="85">
         <f>IFERROR((VLOOKUP(K10,Scoring!$A:$B,2,0))+IF(M10="y",1,0)+IF(N10="y",1,0)+IF(O10="y",1,0)+IF(P10="y",1,0),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R10" s="24"/>
       <c r="S10" s="25"/>
@@ -5840,8 +5891,12 @@
       <c r="C11" s="15" t="s">
         <v>397</v>
       </c>
-      <c r="D11" s="24"/>
-      <c r="E11" s="25"/>
+      <c r="D11" s="24">
+        <v>10.0</v>
+      </c>
+      <c r="E11" s="25">
+        <v>10.0</v>
+      </c>
       <c r="F11" s="26" t="s">
         <v>128</v>
       </c>
@@ -5856,10 +5911,14 @@
       </c>
       <c r="J11" s="99">
         <f>IFERROR((VLOOKUP(D11,Scoring!$A:$B,2,0))+IF(F11="y",1,0)+IF(G11="y",1,0)+IF(H11="y",1,0)+IF(I11="y",1,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="24"/>
-      <c r="L11" s="25"/>
+        <v>2</v>
+      </c>
+      <c r="K11" s="24">
+        <v>8.0</v>
+      </c>
+      <c r="L11" s="25">
+        <v>7.0</v>
+      </c>
       <c r="M11" s="26" t="s">
         <v>128</v>
       </c>
@@ -5874,7 +5933,7 @@
       </c>
       <c r="Q11" s="99">
         <f>IFERROR((VLOOKUP(K11,Scoring!$A:$B,2,0))+IF(M11="y",1,0)+IF(N11="y",1,0)+IF(O11="y",1,0)+IF(P11="y",1,0),0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R11" s="24"/>
       <c r="S11" s="25"/>
@@ -6142,8 +6201,12 @@
       <c r="C12" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="36"/>
-      <c r="E12" s="37"/>
+      <c r="D12" s="36">
+        <v>11.0</v>
+      </c>
+      <c r="E12" s="37">
+        <v>11.0</v>
+      </c>
       <c r="F12" s="38" t="s">
         <v>128</v>
       </c>
@@ -6158,10 +6221,14 @@
       </c>
       <c r="J12" s="85">
         <f>IFERROR((VLOOKUP(D12,Scoring!$A:$B,2,0))+IF(F12="y",1,0)+IF(G12="y",1,0)+IF(H12="y",1,0)+IF(I12="y",1,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="K12" s="36"/>
-      <c r="L12" s="37"/>
+        <v>1</v>
+      </c>
+      <c r="K12" s="36">
+        <v>9.0</v>
+      </c>
+      <c r="L12" s="37">
+        <v>8.0</v>
+      </c>
       <c r="M12" s="38" t="s">
         <v>128</v>
       </c>
@@ -6176,7 +6243,7 @@
       </c>
       <c r="Q12" s="85">
         <f>IFERROR((VLOOKUP(K12,Scoring!$A:$B,2,0))+IF(M12="y",1,0)+IF(N12="y",1,0)+IF(O12="y",1,0)+IF(P12="y",1,0),0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R12" s="36"/>
       <c r="S12" s="37"/>
@@ -6444,8 +6511,12 @@
       <c r="C13" s="15" t="s">
         <v>397</v>
       </c>
-      <c r="D13" s="24"/>
-      <c r="E13" s="25"/>
+      <c r="D13" s="24">
+        <v>12.0</v>
+      </c>
+      <c r="E13" s="25">
+        <v>12.0</v>
+      </c>
       <c r="F13" s="26" t="s">
         <v>128</v>
       </c>
@@ -6460,10 +6531,14 @@
       </c>
       <c r="J13" s="99">
         <f>IFERROR((VLOOKUP(D13,Scoring!$A:$B,2,0))+IF(F13="y",1,0)+IF(G13="y",1,0)+IF(H13="y",1,0)+IF(I13="y",1,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="24"/>
-      <c r="L13" s="25"/>
+        <v>1</v>
+      </c>
+      <c r="K13" s="24">
+        <v>12.0</v>
+      </c>
+      <c r="L13" s="25">
+        <v>12.0</v>
+      </c>
       <c r="M13" s="26" t="s">
         <v>128</v>
       </c>
@@ -6478,7 +6553,7 @@
       </c>
       <c r="Q13" s="99">
         <f>IFERROR((VLOOKUP(K13,Scoring!$A:$B,2,0))+IF(M13="y",1,0)+IF(N13="y",1,0)+IF(O13="y",1,0)+IF(P13="y",1,0),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" s="24"/>
       <c r="S13" s="25"/>
@@ -6746,8 +6821,12 @@
       <c r="C14" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="36"/>
-      <c r="E14" s="37"/>
+      <c r="D14" s="36">
+        <v>13.0</v>
+      </c>
+      <c r="E14" s="37">
+        <v>13.0</v>
+      </c>
       <c r="F14" s="38" t="s">
         <v>128</v>
       </c>
@@ -6762,10 +6841,14 @@
       </c>
       <c r="J14" s="85">
         <f>IFERROR((VLOOKUP(D14,Scoring!$A:$B,2,0))+IF(F14="y",1,0)+IF(G14="y",1,0)+IF(H14="y",1,0)+IF(I14="y",1,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="36"/>
-      <c r="L14" s="37"/>
+        <v>1</v>
+      </c>
+      <c r="K14" s="36">
+        <v>13.0</v>
+      </c>
+      <c r="L14" s="37">
+        <v>16.0</v>
+      </c>
       <c r="M14" s="38" t="s">
         <v>128</v>
       </c>
@@ -6780,7 +6863,7 @@
       </c>
       <c r="Q14" s="85">
         <f>IFERROR((VLOOKUP(K14,Scoring!$A:$B,2,0))+IF(M14="y",1,0)+IF(N14="y",1,0)+IF(O14="y",1,0)+IF(P14="y",1,0),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" s="36"/>
       <c r="S14" s="37"/>
@@ -7048,8 +7131,12 @@
       <c r="C15" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="48"/>
-      <c r="E15" s="49"/>
+      <c r="D15" s="48">
+        <v>14.0</v>
+      </c>
+      <c r="E15" s="49">
+        <v>14.0</v>
+      </c>
       <c r="F15" s="50" t="s">
         <v>128</v>
       </c>
@@ -7064,10 +7151,14 @@
       </c>
       <c r="J15" s="99">
         <f>IFERROR((VLOOKUP(D15,Scoring!$A:$B,2,0))+IF(F15="y",1,0)+IF(G15="y",1,0)+IF(H15="y",1,0)+IF(I15="y",1,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="48"/>
-      <c r="L15" s="49"/>
+        <v>1</v>
+      </c>
+      <c r="K15" s="48">
+        <v>14.0</v>
+      </c>
+      <c r="L15" s="49">
+        <v>15.0</v>
+      </c>
       <c r="M15" s="50" t="s">
         <v>128</v>
       </c>
@@ -7082,7 +7173,7 @@
       </c>
       <c r="Q15" s="99">
         <f>IFERROR((VLOOKUP(K15,Scoring!$A:$B,2,0))+IF(M15="y",1,0)+IF(N15="y",1,0)+IF(O15="y",1,0)+IF(P15="y",1,0),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="48"/>
       <c r="S15" s="49"/>
@@ -7350,8 +7441,12 @@
       <c r="C16" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="24"/>
-      <c r="E16" s="25"/>
+      <c r="D16" s="24">
+        <v>15.0</v>
+      </c>
+      <c r="E16" s="25">
+        <v>15.0</v>
+      </c>
       <c r="F16" s="26" t="s">
         <v>128</v>
       </c>
@@ -7366,10 +7461,14 @@
       </c>
       <c r="J16" s="85">
         <f>IFERROR((VLOOKUP(D16,Scoring!$A:$B,2,0))+IF(F16="y",1,0)+IF(G16="y",1,0)+IF(H16="y",1,0)+IF(I16="y",1,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="24"/>
-      <c r="L16" s="25"/>
+        <v>1</v>
+      </c>
+      <c r="K16" s="24">
+        <v>15.0</v>
+      </c>
+      <c r="L16" s="25">
+        <v>14.0</v>
+      </c>
       <c r="M16" s="26" t="s">
         <v>128</v>
       </c>
@@ -7384,7 +7483,7 @@
       </c>
       <c r="Q16" s="85">
         <f>IFERROR((VLOOKUP(K16,Scoring!$A:$B,2,0))+IF(M16="y",1,0)+IF(N16="y",1,0)+IF(O16="y",1,0)+IF(P16="y",1,0),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" s="24"/>
       <c r="S16" s="25"/>
@@ -7652,8 +7751,12 @@
       <c r="C17" s="59" t="s">
         <v>397</v>
       </c>
-      <c r="D17" s="60"/>
-      <c r="E17" s="61"/>
+      <c r="D17" s="60">
+        <v>16.0</v>
+      </c>
+      <c r="E17" s="61">
+        <v>16.0</v>
+      </c>
       <c r="F17" s="62" t="s">
         <v>128</v>
       </c>
@@ -7668,10 +7771,14 @@
       </c>
       <c r="J17" s="137">
         <f>IFERROR((VLOOKUP(D17,Scoring!$A:$B,2,0))+IF(F17="y",1,0)+IF(G17="y",1,0)+IF(H17="y",1,0)+IF(I17="y",1,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="60"/>
-      <c r="L17" s="61"/>
+        <v>1</v>
+      </c>
+      <c r="K17" s="60">
+        <v>16.0</v>
+      </c>
+      <c r="L17" s="61">
+        <v>13.0</v>
+      </c>
       <c r="M17" s="62" t="s">
         <v>128</v>
       </c>
@@ -7686,7 +7793,7 @@
       </c>
       <c r="Q17" s="137">
         <f>IFERROR((VLOOKUP(K17,Scoring!$A:$B,2,0))+IF(M17="y",1,0)+IF(N17="y",1,0)+IF(O17="y",1,0)+IF(P17="y",1,0),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="60"/>
       <c r="S17" s="61"/>
@@ -7978,37 +8085,37 @@
         <v>403</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>292</v>
+        <v>404</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B3" s="69" t="s">
+        <v>406</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>404</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B4" s="69" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>292</v>
+        <v>404</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>407</v>
+        <v>143</v>
       </c>
       <c r="B5" s="69" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>292</v>
@@ -8016,10 +8123,10 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B6" s="69" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>292</v>
@@ -8027,7 +8134,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>411</v>
+        <v>276</v>
       </c>
       <c r="B7" s="69" t="s">
         <v>412</v>
@@ -8038,10 +8145,10 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>413</v>
+        <v>144</v>
       </c>
       <c r="B8" s="69" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>292</v>
@@ -8049,10 +8156,10 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>415</v>
+        <v>151</v>
       </c>
       <c r="B9" s="69" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>292</v>
@@ -8060,10 +8167,10 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>417</v>
+        <v>149</v>
       </c>
       <c r="B10" s="69" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>292</v>
@@ -8071,10 +8178,10 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>419</v>
+        <v>157</v>
       </c>
       <c r="B11" s="69" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>292</v>
@@ -8082,10 +8189,10 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B12" s="69" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>292</v>
@@ -8093,10 +8200,10 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>423</v>
+        <v>148</v>
       </c>
       <c r="B13" s="69" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>292</v>
@@ -8104,10 +8211,10 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>425</v>
+        <v>153</v>
       </c>
       <c r="B14" s="69" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>292</v>
@@ -8115,10 +8222,10 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>427</v>
+        <v>159</v>
       </c>
       <c r="B15" s="69" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>292</v>
@@ -8126,10 +8233,10 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>429</v>
+        <v>141</v>
       </c>
       <c r="B16" s="69" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>292</v>
@@ -8137,10 +8244,10 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B17" s="69" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>292</v>
@@ -8148,10 +8255,10 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>154</v>
+        <v>422</v>
       </c>
       <c r="B18" s="69" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>292</v>
@@ -8159,10 +8266,10 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>432</v>
+        <v>150</v>
       </c>
       <c r="B19" s="69" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>292</v>
@@ -8170,10 +8277,10 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B20" s="69" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>292</v>
@@ -8181,12 +8288,34 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B21" s="69" t="s">
+        <v>426</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B22" s="69" t="s">
+        <v>426</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B21" s="69" t="s">
-        <v>434</v>
-      </c>
-      <c r="C21" s="1" t="s">
+      <c r="B23" s="69" t="s">
+        <v>427</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>292</v>
       </c>
     </row>

--- a/the_alternative_f1/The_Alternative_F1.xlsx
+++ b/the_alternative_f1/The_Alternative_F1.xlsx
@@ -3101,12 +3101,8 @@
       <c r="C2" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="16">
-        <v>2.0</v>
-      </c>
-      <c r="E2" s="17">
-        <v>1.0</v>
-      </c>
+      <c r="D2" s="16"/>
+      <c r="E2" s="17"/>
       <c r="F2" s="18" t="s">
         <v>128</v>
       </c>
@@ -3121,14 +3117,10 @@
       </c>
       <c r="J2" s="85">
         <f>IFERROR((VLOOKUP(D2,Scoring!$A:$B,2,0))+IF(F2="y",1,0)+IF(G2="y",1,0)+IF(H2="y",1,0)+IF(I2="y",1,0),0)</f>
-        <v>18</v>
-      </c>
-      <c r="K2" s="16">
-        <v>3.0</v>
-      </c>
-      <c r="L2" s="17">
-        <v>3.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K2" s="16"/>
+      <c r="L2" s="17"/>
       <c r="M2" s="18" t="s">
         <v>128</v>
       </c>
@@ -3143,7 +3135,7 @@
       </c>
       <c r="Q2" s="85">
         <f>IFERROR((VLOOKUP(K2,Scoring!$A:$B,2,0))+IF(M2="y",1,0)+IF(N2="y",1,0)+IF(O2="y",1,0)+IF(P2="y",1,0),0)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R2" s="16"/>
       <c r="S2" s="17"/>
@@ -3411,12 +3403,8 @@
       <c r="C3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="24">
-        <v>3.0</v>
-      </c>
-      <c r="E3" s="25">
-        <v>2.0</v>
-      </c>
+      <c r="D3" s="24"/>
+      <c r="E3" s="25"/>
       <c r="F3" s="26" t="s">
         <v>128</v>
       </c>
@@ -3431,14 +3419,10 @@
       </c>
       <c r="J3" s="99">
         <f>IFERROR((VLOOKUP(D3,Scoring!$A:$B,2,0))+IF(F3="y",1,0)+IF(G3="y",1,0)+IF(H3="y",1,0)+IF(I3="y",1,0),0)</f>
-        <v>15</v>
-      </c>
-      <c r="K3" s="24">
-        <v>4.0</v>
-      </c>
-      <c r="L3" s="25">
-        <v>4.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K3" s="24"/>
+      <c r="L3" s="25"/>
       <c r="M3" s="26" t="s">
         <v>128</v>
       </c>
@@ -3453,7 +3437,7 @@
       </c>
       <c r="Q3" s="99">
         <f>IFERROR((VLOOKUP(K3,Scoring!$A:$B,2,0))+IF(M3="y",1,0)+IF(N3="y",1,0)+IF(O3="y",1,0)+IF(P3="y",1,0),0)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R3" s="24"/>
       <c r="S3" s="25"/>
@@ -3721,12 +3705,8 @@
       <c r="C4" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="36">
-        <v>1.0</v>
-      </c>
-      <c r="E4" s="37">
-        <v>3.0</v>
-      </c>
+      <c r="D4" s="36"/>
+      <c r="E4" s="37"/>
       <c r="F4" s="38" t="s">
         <v>128</v>
       </c>
@@ -3741,14 +3721,10 @@
       </c>
       <c r="J4" s="85">
         <f>IFERROR((VLOOKUP(D4,Scoring!$A:$B,2,0))+IF(F4="y",1,0)+IF(G4="y",1,0)+IF(H4="y",1,0)+IF(I4="y",1,0),0)</f>
-        <v>25</v>
-      </c>
-      <c r="K4" s="36">
-        <v>5.0</v>
-      </c>
-      <c r="L4" s="37">
-        <v>5.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K4" s="36"/>
+      <c r="L4" s="37"/>
       <c r="M4" s="38" t="s">
         <v>128</v>
       </c>
@@ -3763,7 +3739,7 @@
       </c>
       <c r="Q4" s="85">
         <f>IFERROR((VLOOKUP(K4,Scoring!$A:$B,2,0))+IF(M4="y",1,0)+IF(N4="y",1,0)+IF(O4="y",1,0)+IF(P4="y",1,0),0)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R4" s="36"/>
       <c r="S4" s="37"/>
@@ -4031,12 +4007,8 @@
       <c r="C5" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="48">
-        <v>4.0</v>
-      </c>
-      <c r="E5" s="49">
-        <v>4.0</v>
-      </c>
+      <c r="D5" s="48"/>
+      <c r="E5" s="49"/>
       <c r="F5" s="50" t="s">
         <v>128</v>
       </c>
@@ -4051,14 +4023,10 @@
       </c>
       <c r="J5" s="99">
         <f>IFERROR((VLOOKUP(D5,Scoring!$A:$B,2,0))+IF(F5="y",1,0)+IF(G5="y",1,0)+IF(H5="y",1,0)+IF(I5="y",1,0),0)</f>
-        <v>12</v>
-      </c>
-      <c r="K5" s="48">
-        <v>6.0</v>
-      </c>
-      <c r="L5" s="49">
-        <v>6.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K5" s="48"/>
+      <c r="L5" s="49"/>
       <c r="M5" s="50" t="s">
         <v>128</v>
       </c>
@@ -4073,7 +4041,7 @@
       </c>
       <c r="Q5" s="99">
         <f>IFERROR((VLOOKUP(K5,Scoring!$A:$B,2,0))+IF(M5="y",1,0)+IF(N5="y",1,0)+IF(O5="y",1,0)+IF(P5="y",1,0),0)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R5" s="48"/>
       <c r="S5" s="49"/>
@@ -4341,12 +4309,8 @@
       <c r="C6" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="24">
-        <v>6.0</v>
-      </c>
-      <c r="E6" s="25">
-        <v>5.0</v>
-      </c>
+      <c r="D6" s="24"/>
+      <c r="E6" s="25"/>
       <c r="F6" s="26" t="s">
         <v>128</v>
       </c>
@@ -4361,14 +4325,10 @@
       </c>
       <c r="J6" s="85">
         <f>IFERROR((VLOOKUP(D6,Scoring!$A:$B,2,0))+IF(F6="y",1,0)+IF(G6="y",1,0)+IF(H6="y",1,0)+IF(I6="y",1,0),0)</f>
-        <v>8</v>
-      </c>
-      <c r="K6" s="24">
-        <v>11.0</v>
-      </c>
-      <c r="L6" s="25">
-        <v>10.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K6" s="24"/>
+      <c r="L6" s="25"/>
       <c r="M6" s="26" t="s">
         <v>128</v>
       </c>
@@ -4383,7 +4343,7 @@
       </c>
       <c r="Q6" s="85">
         <f>IFERROR((VLOOKUP(K6,Scoring!$A:$B,2,0))+IF(M6="y",1,0)+IF(N6="y",1,0)+IF(O6="y",1,0)+IF(P6="y",1,0),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" s="24"/>
       <c r="S6" s="25"/>
@@ -4651,12 +4611,8 @@
       <c r="C7" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="24">
-        <v>5.0</v>
-      </c>
-      <c r="E7" s="25">
-        <v>6.0</v>
-      </c>
+      <c r="D7" s="24"/>
+      <c r="E7" s="25"/>
       <c r="F7" s="26" t="s">
         <v>128</v>
       </c>
@@ -4671,14 +4627,10 @@
       </c>
       <c r="J7" s="99">
         <f>IFERROR((VLOOKUP(D7,Scoring!$A:$B,2,0))+IF(F7="y",1,0)+IF(G7="y",1,0)+IF(H7="y",1,0)+IF(I7="y",1,0),0)</f>
-        <v>10</v>
-      </c>
-      <c r="K7" s="24">
-        <v>10.0</v>
-      </c>
-      <c r="L7" s="25">
-        <v>11.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K7" s="24"/>
+      <c r="L7" s="25"/>
       <c r="M7" s="26" t="s">
         <v>128</v>
       </c>
@@ -4693,7 +4645,7 @@
       </c>
       <c r="Q7" s="99">
         <f>IFERROR((VLOOKUP(K7,Scoring!$A:$B,2,0))+IF(M7="y",1,0)+IF(N7="y",1,0)+IF(O7="y",1,0)+IF(P7="y",1,0),0)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R7" s="24"/>
       <c r="S7" s="25"/>
@@ -4961,12 +4913,8 @@
       <c r="C8" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="36">
-        <v>7.0</v>
-      </c>
-      <c r="E8" s="37">
-        <v>7.0</v>
-      </c>
+      <c r="D8" s="36"/>
+      <c r="E8" s="37"/>
       <c r="F8" s="38" t="s">
         <v>128</v>
       </c>
@@ -4981,14 +4929,10 @@
       </c>
       <c r="J8" s="85">
         <f>IFERROR((VLOOKUP(D8,Scoring!$A:$B,2,0))+IF(F8="y",1,0)+IF(G8="y",1,0)+IF(H8="y",1,0)+IF(I8="y",1,0),0)</f>
-        <v>6</v>
-      </c>
-      <c r="K8" s="36">
-        <v>2.0</v>
-      </c>
-      <c r="L8" s="37">
-        <v>1.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K8" s="36"/>
+      <c r="L8" s="37"/>
       <c r="M8" s="38" t="s">
         <v>128</v>
       </c>
@@ -5003,7 +4947,7 @@
       </c>
       <c r="Q8" s="85">
         <f>IFERROR((VLOOKUP(K8,Scoring!$A:$B,2,0))+IF(M8="y",1,0)+IF(N8="y",1,0)+IF(O8="y",1,0)+IF(P8="y",1,0),0)</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R8" s="36"/>
       <c r="S8" s="37"/>
@@ -5271,12 +5215,8 @@
       <c r="C9" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="48">
-        <v>8.0</v>
-      </c>
-      <c r="E9" s="49">
-        <v>8.0</v>
-      </c>
+      <c r="D9" s="48"/>
+      <c r="E9" s="49"/>
       <c r="F9" s="50" t="s">
         <v>128</v>
       </c>
@@ -5291,14 +5231,10 @@
       </c>
       <c r="J9" s="99">
         <f>IFERROR((VLOOKUP(D9,Scoring!$A:$B,2,0))+IF(F9="y",1,0)+IF(G9="y",1,0)+IF(H9="y",1,0)+IF(I9="y",1,0),0)</f>
-        <v>4</v>
-      </c>
-      <c r="K9" s="48">
-        <v>1.0</v>
-      </c>
-      <c r="L9" s="49">
-        <v>2.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K9" s="48"/>
+      <c r="L9" s="49"/>
       <c r="M9" s="50" t="s">
         <v>128</v>
       </c>
@@ -5313,7 +5249,7 @@
       </c>
       <c r="Q9" s="99">
         <f>IFERROR((VLOOKUP(K9,Scoring!$A:$B,2,0))+IF(M9="y",1,0)+IF(N9="y",1,0)+IF(O9="y",1,0)+IF(P9="y",1,0),0)</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="R9" s="48"/>
       <c r="S9" s="49"/>
@@ -5581,12 +5517,8 @@
       <c r="C10" s="15" t="s">
         <v>397</v>
       </c>
-      <c r="D10" s="24">
-        <v>9.0</v>
-      </c>
-      <c r="E10" s="25">
-        <v>9.0</v>
-      </c>
+      <c r="D10" s="24"/>
+      <c r="E10" s="25"/>
       <c r="F10" s="26" t="s">
         <v>128</v>
       </c>
@@ -5601,14 +5533,10 @@
       </c>
       <c r="J10" s="85">
         <f>IFERROR((VLOOKUP(D10,Scoring!$A:$B,2,0))+IF(F10="y",1,0)+IF(G10="y",1,0)+IF(H10="y",1,0)+IF(I10="y",1,0),0)</f>
-        <v>3</v>
-      </c>
-      <c r="K10" s="24">
-        <v>7.0</v>
-      </c>
-      <c r="L10" s="25">
-        <v>9.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K10" s="24"/>
+      <c r="L10" s="25"/>
       <c r="M10" s="26" t="s">
         <v>128</v>
       </c>
@@ -5623,7 +5551,7 @@
       </c>
       <c r="Q10" s="85">
         <f>IFERROR((VLOOKUP(K10,Scoring!$A:$B,2,0))+IF(M10="y",1,0)+IF(N10="y",1,0)+IF(O10="y",1,0)+IF(P10="y",1,0),0)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R10" s="24"/>
       <c r="S10" s="25"/>
@@ -5891,12 +5819,8 @@
       <c r="C11" s="15" t="s">
         <v>397</v>
       </c>
-      <c r="D11" s="24">
-        <v>10.0</v>
-      </c>
-      <c r="E11" s="25">
-        <v>10.0</v>
-      </c>
+      <c r="D11" s="24"/>
+      <c r="E11" s="25"/>
       <c r="F11" s="26" t="s">
         <v>128</v>
       </c>
@@ -5911,14 +5835,10 @@
       </c>
       <c r="J11" s="99">
         <f>IFERROR((VLOOKUP(D11,Scoring!$A:$B,2,0))+IF(F11="y",1,0)+IF(G11="y",1,0)+IF(H11="y",1,0)+IF(I11="y",1,0),0)</f>
-        <v>2</v>
-      </c>
-      <c r="K11" s="24">
-        <v>8.0</v>
-      </c>
-      <c r="L11" s="25">
-        <v>7.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K11" s="24"/>
+      <c r="L11" s="25"/>
       <c r="M11" s="26" t="s">
         <v>128</v>
       </c>
@@ -5933,7 +5853,7 @@
       </c>
       <c r="Q11" s="99">
         <f>IFERROR((VLOOKUP(K11,Scoring!$A:$B,2,0))+IF(M11="y",1,0)+IF(N11="y",1,0)+IF(O11="y",1,0)+IF(P11="y",1,0),0)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R11" s="24"/>
       <c r="S11" s="25"/>
@@ -6201,12 +6121,8 @@
       <c r="C12" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="36">
-        <v>11.0</v>
-      </c>
-      <c r="E12" s="37">
-        <v>11.0</v>
-      </c>
+      <c r="D12" s="36"/>
+      <c r="E12" s="37"/>
       <c r="F12" s="38" t="s">
         <v>128</v>
       </c>
@@ -6221,14 +6137,10 @@
       </c>
       <c r="J12" s="85">
         <f>IFERROR((VLOOKUP(D12,Scoring!$A:$B,2,0))+IF(F12="y",1,0)+IF(G12="y",1,0)+IF(H12="y",1,0)+IF(I12="y",1,0),0)</f>
-        <v>1</v>
-      </c>
-      <c r="K12" s="36">
-        <v>9.0</v>
-      </c>
-      <c r="L12" s="37">
-        <v>8.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K12" s="36"/>
+      <c r="L12" s="37"/>
       <c r="M12" s="38" t="s">
         <v>128</v>
       </c>
@@ -6243,7 +6155,7 @@
       </c>
       <c r="Q12" s="85">
         <f>IFERROR((VLOOKUP(K12,Scoring!$A:$B,2,0))+IF(M12="y",1,0)+IF(N12="y",1,0)+IF(O12="y",1,0)+IF(P12="y",1,0),0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R12" s="36"/>
       <c r="S12" s="37"/>
@@ -6511,12 +6423,8 @@
       <c r="C13" s="15" t="s">
         <v>397</v>
       </c>
-      <c r="D13" s="24">
-        <v>12.0</v>
-      </c>
-      <c r="E13" s="25">
-        <v>12.0</v>
-      </c>
+      <c r="D13" s="24"/>
+      <c r="E13" s="25"/>
       <c r="F13" s="26" t="s">
         <v>128</v>
       </c>
@@ -6531,14 +6439,10 @@
       </c>
       <c r="J13" s="99">
         <f>IFERROR((VLOOKUP(D13,Scoring!$A:$B,2,0))+IF(F13="y",1,0)+IF(G13="y",1,0)+IF(H13="y",1,0)+IF(I13="y",1,0),0)</f>
-        <v>1</v>
-      </c>
-      <c r="K13" s="24">
-        <v>12.0</v>
-      </c>
-      <c r="L13" s="25">
-        <v>12.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K13" s="24"/>
+      <c r="L13" s="25"/>
       <c r="M13" s="26" t="s">
         <v>128</v>
       </c>
@@ -6553,7 +6457,7 @@
       </c>
       <c r="Q13" s="99">
         <f>IFERROR((VLOOKUP(K13,Scoring!$A:$B,2,0))+IF(M13="y",1,0)+IF(N13="y",1,0)+IF(O13="y",1,0)+IF(P13="y",1,0),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" s="24"/>
       <c r="S13" s="25"/>
@@ -6821,12 +6725,8 @@
       <c r="C14" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="36">
-        <v>13.0</v>
-      </c>
-      <c r="E14" s="37">
-        <v>13.0</v>
-      </c>
+      <c r="D14" s="36"/>
+      <c r="E14" s="37"/>
       <c r="F14" s="38" t="s">
         <v>128</v>
       </c>
@@ -6841,14 +6741,10 @@
       </c>
       <c r="J14" s="85">
         <f>IFERROR((VLOOKUP(D14,Scoring!$A:$B,2,0))+IF(F14="y",1,0)+IF(G14="y",1,0)+IF(H14="y",1,0)+IF(I14="y",1,0),0)</f>
-        <v>1</v>
-      </c>
-      <c r="K14" s="36">
-        <v>13.0</v>
-      </c>
-      <c r="L14" s="37">
-        <v>16.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K14" s="36"/>
+      <c r="L14" s="37"/>
       <c r="M14" s="38" t="s">
         <v>128</v>
       </c>
@@ -6863,7 +6759,7 @@
       </c>
       <c r="Q14" s="85">
         <f>IFERROR((VLOOKUP(K14,Scoring!$A:$B,2,0))+IF(M14="y",1,0)+IF(N14="y",1,0)+IF(O14="y",1,0)+IF(P14="y",1,0),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" s="36"/>
       <c r="S14" s="37"/>
@@ -7131,12 +7027,8 @@
       <c r="C15" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="48">
-        <v>14.0</v>
-      </c>
-      <c r="E15" s="49">
-        <v>14.0</v>
-      </c>
+      <c r="D15" s="48"/>
+      <c r="E15" s="49"/>
       <c r="F15" s="50" t="s">
         <v>128</v>
       </c>
@@ -7151,14 +7043,10 @@
       </c>
       <c r="J15" s="99">
         <f>IFERROR((VLOOKUP(D15,Scoring!$A:$B,2,0))+IF(F15="y",1,0)+IF(G15="y",1,0)+IF(H15="y",1,0)+IF(I15="y",1,0),0)</f>
-        <v>1</v>
-      </c>
-      <c r="K15" s="48">
-        <v>14.0</v>
-      </c>
-      <c r="L15" s="49">
-        <v>15.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K15" s="48"/>
+      <c r="L15" s="49"/>
       <c r="M15" s="50" t="s">
         <v>128</v>
       </c>
@@ -7173,7 +7061,7 @@
       </c>
       <c r="Q15" s="99">
         <f>IFERROR((VLOOKUP(K15,Scoring!$A:$B,2,0))+IF(M15="y",1,0)+IF(N15="y",1,0)+IF(O15="y",1,0)+IF(P15="y",1,0),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" s="48"/>
       <c r="S15" s="49"/>
@@ -7441,12 +7329,8 @@
       <c r="C16" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="24">
-        <v>15.0</v>
-      </c>
-      <c r="E16" s="25">
-        <v>15.0</v>
-      </c>
+      <c r="D16" s="24"/>
+      <c r="E16" s="25"/>
       <c r="F16" s="26" t="s">
         <v>128</v>
       </c>
@@ -7461,14 +7345,10 @@
       </c>
       <c r="J16" s="85">
         <f>IFERROR((VLOOKUP(D16,Scoring!$A:$B,2,0))+IF(F16="y",1,0)+IF(G16="y",1,0)+IF(H16="y",1,0)+IF(I16="y",1,0),0)</f>
-        <v>1</v>
-      </c>
-      <c r="K16" s="24">
-        <v>15.0</v>
-      </c>
-      <c r="L16" s="25">
-        <v>14.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K16" s="24"/>
+      <c r="L16" s="25"/>
       <c r="M16" s="26" t="s">
         <v>128</v>
       </c>
@@ -7483,7 +7363,7 @@
       </c>
       <c r="Q16" s="85">
         <f>IFERROR((VLOOKUP(K16,Scoring!$A:$B,2,0))+IF(M16="y",1,0)+IF(N16="y",1,0)+IF(O16="y",1,0)+IF(P16="y",1,0),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" s="24"/>
       <c r="S16" s="25"/>
@@ -7751,12 +7631,8 @@
       <c r="C17" s="59" t="s">
         <v>397</v>
       </c>
-      <c r="D17" s="60">
-        <v>16.0</v>
-      </c>
-      <c r="E17" s="61">
-        <v>16.0</v>
-      </c>
+      <c r="D17" s="60"/>
+      <c r="E17" s="61"/>
       <c r="F17" s="62" t="s">
         <v>128</v>
       </c>
@@ -7771,14 +7647,10 @@
       </c>
       <c r="J17" s="137">
         <f>IFERROR((VLOOKUP(D17,Scoring!$A:$B,2,0))+IF(F17="y",1,0)+IF(G17="y",1,0)+IF(H17="y",1,0)+IF(I17="y",1,0),0)</f>
-        <v>1</v>
-      </c>
-      <c r="K17" s="60">
-        <v>16.0</v>
-      </c>
-      <c r="L17" s="61">
-        <v>13.0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K17" s="60"/>
+      <c r="L17" s="61"/>
       <c r="M17" s="62" t="s">
         <v>128</v>
       </c>
@@ -7793,7 +7665,7 @@
       </c>
       <c r="Q17" s="137">
         <f>IFERROR((VLOOKUP(K17,Scoring!$A:$B,2,0))+IF(M17="y",1,0)+IF(N17="y",1,0)+IF(O17="y",1,0)+IF(P17="y",1,0),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" s="60"/>
       <c r="S17" s="61"/>

--- a/the_alternative_f1/The_Alternative_F1.xlsx
+++ b/the_alternative_f1/The_Alternative_F1.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3320" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3610" uniqueCount="385">
   <si>
     <t>Positions</t>
   </si>
@@ -912,235 +912,103 @@
     <t>1/28/2026</t>
   </si>
   <si>
-    <t>W1Place</t>
-  </si>
-  <si>
-    <t>W1Qualifying</t>
-  </si>
-  <si>
-    <t>W1FastestLap</t>
-  </si>
-  <si>
-    <t>W1DOTD</t>
-  </si>
-  <si>
-    <t>W1MOT</t>
-  </si>
-  <si>
-    <t>W1CD</t>
-  </si>
-  <si>
-    <t>W1Points</t>
-  </si>
-  <si>
-    <t>W2Place</t>
-  </si>
-  <si>
-    <t>W2Qualifying</t>
-  </si>
-  <si>
-    <t>W2FastestLap</t>
-  </si>
-  <si>
-    <t>W2DOTD</t>
-  </si>
-  <si>
-    <t>W2MOT</t>
-  </si>
-  <si>
-    <t>W2CD</t>
-  </si>
-  <si>
-    <t>W2Points</t>
-  </si>
-  <si>
-    <t>W3Place</t>
-  </si>
-  <si>
-    <t>W3Qualifying</t>
-  </si>
-  <si>
-    <t>W3FastestLap</t>
-  </si>
-  <si>
-    <t>W3DOTD</t>
-  </si>
-  <si>
-    <t>W3MOT</t>
-  </si>
-  <si>
-    <t>W3CD</t>
-  </si>
-  <si>
-    <t>W3Points</t>
-  </si>
-  <si>
-    <t>W4Place</t>
-  </si>
-  <si>
-    <t>W4Qualifying</t>
-  </si>
-  <si>
-    <t>W4FastestLap</t>
-  </si>
-  <si>
-    <t>W4DOTD</t>
-  </si>
-  <si>
-    <t>W4MOT</t>
-  </si>
-  <si>
-    <t>W4CD</t>
-  </si>
-  <si>
-    <t>W4Points</t>
-  </si>
-  <si>
-    <t>W5Place</t>
-  </si>
-  <si>
-    <t>W5Qualifying</t>
-  </si>
-  <si>
-    <t>W5FastestLap</t>
-  </si>
-  <si>
-    <t>W5DOTD</t>
-  </si>
-  <si>
-    <t>W5MOT</t>
-  </si>
-  <si>
-    <t>W5CD</t>
-  </si>
-  <si>
-    <t>W5Points</t>
-  </si>
-  <si>
-    <t>W6Place</t>
-  </si>
-  <si>
-    <t>W6Qualifying</t>
-  </si>
-  <si>
-    <t>W6FastestLap</t>
-  </si>
-  <si>
-    <t>W6DOTD</t>
-  </si>
-  <si>
-    <t>W6MOT</t>
-  </si>
-  <si>
-    <t>W6CD</t>
-  </si>
-  <si>
-    <t>W6Points</t>
-  </si>
-  <si>
-    <t>W7Place</t>
-  </si>
-  <si>
-    <t>W7Qualifying</t>
-  </si>
-  <si>
-    <t>W7FastestLap</t>
-  </si>
-  <si>
-    <t>W7DOTD</t>
-  </si>
-  <si>
-    <t>W7MOT</t>
-  </si>
-  <si>
-    <t>W7CD</t>
-  </si>
-  <si>
-    <t>W7Points</t>
-  </si>
-  <si>
-    <t>W8Place</t>
-  </si>
-  <si>
-    <t>W8Qualifying</t>
-  </si>
-  <si>
-    <t>W8FastestLap</t>
-  </si>
-  <si>
-    <t>W8DOTD</t>
-  </si>
-  <si>
-    <t>W8MOT</t>
-  </si>
-  <si>
-    <t>W8CD</t>
-  </si>
-  <si>
-    <t>W8Points</t>
-  </si>
-  <si>
-    <t>W9Place</t>
-  </si>
-  <si>
-    <t>W9Qualifying</t>
-  </si>
-  <si>
-    <t>W9FastestLap</t>
-  </si>
-  <si>
-    <t>W9DOTD</t>
-  </si>
-  <si>
-    <t>W9MOT</t>
-  </si>
-  <si>
-    <t>W9CD</t>
-  </si>
-  <si>
-    <t>W9Points</t>
-  </si>
-  <si>
-    <t>W-10Place</t>
-  </si>
-  <si>
-    <t>W-10Qualifying</t>
-  </si>
-  <si>
-    <t>W-10FastestLap</t>
-  </si>
-  <si>
-    <t>W-10DOTD</t>
-  </si>
-  <si>
-    <t>W-10MOT</t>
-  </si>
-  <si>
-    <t>W-10CD</t>
-  </si>
-  <si>
-    <t>W-10Points</t>
-  </si>
-  <si>
-    <t>W-11Place</t>
-  </si>
-  <si>
-    <t>W-11Qualifying</t>
-  </si>
-  <si>
-    <t>W-11FastestLap</t>
-  </si>
-  <si>
-    <t>W-11DOTD</t>
-  </si>
-  <si>
-    <t>W-11MOT</t>
-  </si>
-  <si>
-    <t>W-11CD</t>
-  </si>
-  <si>
-    <t>W-11Points</t>
+    <t>AustraliaDOTD</t>
+  </si>
+  <si>
+    <t>AustraliaMOT</t>
+  </si>
+  <si>
+    <t>AustraliaCD</t>
+  </si>
+  <si>
+    <t>ImolaPlace</t>
+  </si>
+  <si>
+    <t>ImolaQualifying</t>
+  </si>
+  <si>
+    <t>ImolaFastestLap</t>
+  </si>
+  <si>
+    <t>ImolaDOTD</t>
+  </si>
+  <si>
+    <t>ImolaMOT</t>
+  </si>
+  <si>
+    <t>ImolaCD</t>
+  </si>
+  <si>
+    <t>ImolaPoints</t>
+  </si>
+  <si>
+    <t>Silverstone SprintPlace</t>
+  </si>
+  <si>
+    <t>Silverstone SprintQualifying</t>
+  </si>
+  <si>
+    <t>Silverstone SprintFastestLap</t>
+  </si>
+  <si>
+    <t>Silverstone SprintDOTD</t>
+  </si>
+  <si>
+    <t>Silverstone SprintMOT</t>
+  </si>
+  <si>
+    <t>Silverstone SprintCD</t>
+  </si>
+  <si>
+    <t>Silverstone SprintPoints</t>
+  </si>
+  <si>
+    <t>SilverstoneDOTD</t>
+  </si>
+  <si>
+    <t>SilverstoneMOT</t>
+  </si>
+  <si>
+    <t>SilverstoneCD</t>
+  </si>
+  <si>
+    <t>SuzukaDOTD</t>
+  </si>
+  <si>
+    <t>SuzukaMOT</t>
+  </si>
+  <si>
+    <t>SuzukaCD</t>
+  </si>
+  <si>
+    <t>Bahrain SprintPlace</t>
+  </si>
+  <si>
+    <t>Bahrain SprintQualifying</t>
+  </si>
+  <si>
+    <t>Bahrain SprintFastestLap</t>
+  </si>
+  <si>
+    <t>Bahrain SprintDOTD</t>
+  </si>
+  <si>
+    <t>Bahrain SprintMOT</t>
+  </si>
+  <si>
+    <t>Bahrain SprintCD</t>
+  </si>
+  <si>
+    <t>Bahrain SprintPoints</t>
+  </si>
+  <si>
+    <t>COTADOTD</t>
+  </si>
+  <si>
+    <t>COTAMOT</t>
+  </si>
+  <si>
+    <t>COTACD</t>
   </si>
   <si>
     <t>ZandvoortSprintPlace</t>
@@ -1282,6 +1150,9 @@
   </si>
   <si>
     <t>12/2/2026</t>
+  </si>
+  <si>
+    <t>Bahrain Sprint</t>
   </si>
   <si>
     <t>12/9/2026</t>
@@ -1529,7 +1400,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="154">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1734,6 +1605,27 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="3" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="5" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1754,27 +1646,6 @@
     <xf borderId="3" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="3" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="8" fillId="8" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -1793,6 +1664,9 @@
     </xf>
     <xf borderId="5" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="8" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="8" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -1833,6 +1707,9 @@
     </xf>
     <xf borderId="0" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="14" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="14" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -1945,6 +1822,9 @@
     </xf>
     <xf borderId="16" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="17" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="17" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -2752,342 +2632,426 @@
         <v>50</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="H1" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="I1" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="J1" s="70" t="s">
+        <v>62</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="L1" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="M1" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="J1" s="70" t="s">
+      <c r="N1" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="O1" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="P1" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="Q1" s="70" t="s">
         <v>305</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="R1" s="71" t="s">
+        <v>198</v>
+      </c>
+      <c r="S1" s="72" t="s">
+        <v>199</v>
+      </c>
+      <c r="T1" s="73" t="s">
+        <v>200</v>
+      </c>
+      <c r="U1" s="74" t="s">
+        <v>201</v>
+      </c>
+      <c r="V1" s="75" t="s">
+        <v>202</v>
+      </c>
+      <c r="W1" s="76" t="s">
+        <v>203</v>
+      </c>
+      <c r="X1" s="77" t="s">
+        <v>204</v>
+      </c>
+      <c r="Y1" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA1" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="AB1" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="AC1" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="AD1" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="AE1" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF1" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG1" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AH1" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI1" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="AJ1" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="AK1" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="AL1" s="70" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM1" s="71" t="s">
+        <v>224</v>
+      </c>
+      <c r="AN1" s="72" t="s">
+        <v>225</v>
+      </c>
+      <c r="AO1" s="73" t="s">
+        <v>226</v>
+      </c>
+      <c r="AP1" s="74" t="s">
+        <v>227</v>
+      </c>
+      <c r="AQ1" s="75" t="s">
+        <v>228</v>
+      </c>
+      <c r="AR1" s="76" t="s">
+        <v>229</v>
+      </c>
+      <c r="AS1" s="77" t="s">
+        <v>230</v>
+      </c>
+      <c r="AT1" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU1" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV1" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW1" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="AX1" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="AY1" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="AZ1" s="70" t="s">
+        <v>86</v>
+      </c>
+      <c r="BA1" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="BB1" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="BC1" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="BD1" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="BE1" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="BF1" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="BG1" s="70" t="s">
+        <v>118</v>
+      </c>
+      <c r="BH1" s="71" t="s">
         <v>306</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="BI1" s="72" t="s">
         <v>307</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="BJ1" s="73" t="s">
         <v>308</v>
       </c>
-      <c r="Q1" s="70" t="s">
+      <c r="BK1" s="74" t="s">
         <v>309</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="BL1" s="75" t="s">
         <v>310</v>
       </c>
-      <c r="S1" s="7" t="s">
+      <c r="BM1" s="76" t="s">
         <v>311</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="BN1" s="77" t="s">
         <v>312</v>
       </c>
-      <c r="U1" s="9" t="s">
+      <c r="BO1" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="BP1" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="BQ1" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="BR1" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="BS1" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="W1" s="11" t="s">
+      <c r="BT1" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="X1" s="70" t="s">
+      <c r="BU1" s="70" t="s">
+        <v>82</v>
+      </c>
+      <c r="BV1" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="BW1" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="BX1" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="BY1" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="BZ1" s="10" t="s">
         <v>317</v>
       </c>
-      <c r="Z1" s="7" t="s">
+      <c r="CA1" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="CB1" s="70" t="s">
+        <v>102</v>
+      </c>
+      <c r="CC1" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="CD1" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="CE1" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="CF1" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="CG1" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="CH1" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="CI1" s="70" t="s">
+        <v>126</v>
+      </c>
+      <c r="CJ1" s="71" t="s">
         <v>319</v>
       </c>
-      <c r="AB1" s="9" t="s">
+      <c r="CK1" s="72" t="s">
         <v>320</v>
       </c>
-      <c r="AC1" s="10" t="s">
+      <c r="CL1" s="73" t="s">
         <v>321</v>
       </c>
-      <c r="AD1" s="11" t="s">
+      <c r="CM1" s="74" t="s">
         <v>322</v>
       </c>
-      <c r="AE1" s="70" t="s">
+      <c r="CN1" s="75" t="s">
         <v>323</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="CO1" s="76" t="s">
         <v>324</v>
       </c>
-      <c r="AG1" s="7" t="s">
+      <c r="CP1" s="77" t="s">
         <v>325</v>
       </c>
-      <c r="AH1" s="8" t="s">
+      <c r="CQ1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="CR1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="CS1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="CT1" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="CU1" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="CV1" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="CW1" s="70" t="s">
+        <v>54</v>
+      </c>
+      <c r="CX1" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="CY1" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="CZ1" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="DA1" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="AI1" s="9" t="s">
+      <c r="DB1" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="AJ1" s="10" t="s">
+      <c r="DC1" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="AK1" s="11" t="s">
+      <c r="DD1" s="70" t="s">
+        <v>110</v>
+      </c>
+      <c r="DE1" s="78" t="s">
         <v>329</v>
       </c>
-      <c r="AL1" s="70" t="s">
+      <c r="DF1" s="79" t="s">
         <v>330</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="DG1" s="80" t="s">
         <v>331</v>
       </c>
-      <c r="AN1" s="7" t="s">
+      <c r="DH1" s="81" t="s">
         <v>332</v>
       </c>
-      <c r="AO1" s="8" t="s">
+      <c r="DI1" s="82" t="s">
         <v>333</v>
       </c>
-      <c r="AP1" s="9" t="s">
+      <c r="DJ1" s="83" t="s">
         <v>334</v>
       </c>
-      <c r="AQ1" s="10" t="s">
+      <c r="DK1" s="84" t="s">
         <v>335</v>
       </c>
-      <c r="AR1" s="11" t="s">
+      <c r="DL1" s="78" t="s">
+        <v>87</v>
+      </c>
+      <c r="DM1" s="79" t="s">
+        <v>88</v>
+      </c>
+      <c r="DN1" s="80" t="s">
+        <v>89</v>
+      </c>
+      <c r="DO1" s="81" t="s">
+        <v>247</v>
+      </c>
+      <c r="DP1" s="82" t="s">
+        <v>248</v>
+      </c>
+      <c r="DQ1" s="83" t="s">
+        <v>249</v>
+      </c>
+      <c r="DR1" s="84" t="s">
+        <v>90</v>
+      </c>
+      <c r="DS1" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="DT1" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="DU1" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="DV1" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="AS1" s="70" t="s">
+      <c r="DW1" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="DX1" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="AU1" s="7" t="s">
+      <c r="DY1" s="70" t="s">
+        <v>106</v>
+      </c>
+      <c r="DZ1" s="71" t="s">
         <v>339</v>
       </c>
-      <c r="AV1" s="8" t="s">
+      <c r="EA1" s="72" t="s">
         <v>340</v>
       </c>
-      <c r="AW1" s="9" t="s">
+      <c r="EB1" s="73" t="s">
         <v>341</v>
       </c>
-      <c r="AX1" s="10" t="s">
+      <c r="EC1" s="74" t="s">
         <v>342</v>
       </c>
-      <c r="AY1" s="11" t="s">
+      <c r="ED1" s="75" t="s">
         <v>343</v>
       </c>
-      <c r="AZ1" s="70" t="s">
+      <c r="EE1" s="76" t="s">
         <v>344</v>
       </c>
-      <c r="BA1" s="6" t="s">
+      <c r="EF1" s="77" t="s">
         <v>345</v>
       </c>
-      <c r="BB1" s="7" t="s">
+      <c r="EG1" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="EH1" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="EI1" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="EJ1" s="9" t="s">
         <v>346</v>
       </c>
-      <c r="BC1" s="8" t="s">
+      <c r="EK1" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="BD1" s="9" t="s">
+      <c r="EL1" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="BE1" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="BF1" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="BG1" s="70" t="s">
-        <v>351</v>
-      </c>
-      <c r="BH1" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="BI1" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="BJ1" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="BK1" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="BL1" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="BM1" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="BN1" s="70" t="s">
-        <v>358</v>
-      </c>
-      <c r="BO1" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="BP1" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="BQ1" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="BR1" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="BS1" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="BT1" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="BU1" s="70" t="s">
-        <v>365</v>
-      </c>
-      <c r="BV1" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="BW1" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="BX1" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="BY1" s="9" t="s">
-        <v>369</v>
-      </c>
-      <c r="BZ1" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="CA1" s="11" t="s">
-        <v>371</v>
-      </c>
-      <c r="CB1" s="70" t="s">
-        <v>372</v>
-      </c>
-      <c r="CC1" s="71" t="s">
-        <v>373</v>
-      </c>
-      <c r="CD1" s="72" t="s">
-        <v>374</v>
-      </c>
-      <c r="CE1" s="73" t="s">
-        <v>375</v>
-      </c>
-      <c r="CF1" s="74" t="s">
-        <v>376</v>
-      </c>
-      <c r="CG1" s="75" t="s">
-        <v>377</v>
-      </c>
-      <c r="CH1" s="76" t="s">
-        <v>378</v>
-      </c>
-      <c r="CI1" s="77" t="s">
-        <v>379</v>
-      </c>
-      <c r="CJ1" s="71" t="s">
-        <v>87</v>
-      </c>
-      <c r="CK1" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="CL1" s="73" t="s">
-        <v>89</v>
-      </c>
-      <c r="CM1" s="74" t="s">
-        <v>247</v>
-      </c>
-      <c r="CN1" s="75" t="s">
-        <v>248</v>
-      </c>
-      <c r="CO1" s="76" t="s">
-        <v>249</v>
-      </c>
-      <c r="CP1" s="77" t="s">
-        <v>90</v>
-      </c>
-      <c r="CQ1" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="CR1" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="CS1" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="CT1" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="CU1" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="CV1" s="11" t="s">
-        <v>382</v>
-      </c>
-      <c r="CW1" s="70" t="s">
-        <v>106</v>
-      </c>
-      <c r="CX1" s="78" t="s">
-        <v>383</v>
-      </c>
-      <c r="CY1" s="79" t="s">
-        <v>384</v>
-      </c>
-      <c r="CZ1" s="80" t="s">
-        <v>385</v>
-      </c>
-      <c r="DA1" s="81" t="s">
-        <v>386</v>
-      </c>
-      <c r="DB1" s="82" t="s">
-        <v>387</v>
-      </c>
-      <c r="DC1" s="83" t="s">
-        <v>388</v>
-      </c>
-      <c r="DD1" s="84" t="s">
-        <v>389</v>
-      </c>
-      <c r="DE1" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="DF1" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="DG1" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="DH1" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="DI1" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="DJ1" s="11" t="s">
-        <v>392</v>
-      </c>
-      <c r="DK1" s="70" t="s">
+      <c r="EM1" s="70" t="s">
         <v>98</v>
       </c>
-      <c r="DL1" s="13" t="s">
+      <c r="EN1" s="13" t="s">
         <v>127</v>
       </c>
     </row>
@@ -3137,21 +3101,21 @@
         <f>IFERROR((VLOOKUP(K2,Scoring!$A:$B,2,0))+IF(M2="y",1,0)+IF(N2="y",1,0)+IF(O2="y",1,0)+IF(P2="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="R2" s="16"/>
-      <c r="S2" s="17"/>
-      <c r="T2" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="U2" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="V2" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="W2" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="X2" s="85">
+      <c r="R2" s="86"/>
+      <c r="S2" s="87"/>
+      <c r="T2" s="88" t="s">
+        <v>128</v>
+      </c>
+      <c r="U2" s="89" t="s">
+        <v>128</v>
+      </c>
+      <c r="V2" s="90" t="s">
+        <v>128</v>
+      </c>
+      <c r="W2" s="91" t="s">
+        <v>128</v>
+      </c>
+      <c r="X2" s="92">
         <f>IFERROR((VLOOKUP(R2,Scoring!$A:$B,2,0))+IF(T2="y",1,0)+IF(U2="y",1,0)+IF(V2="y",1,0)+IF(W2="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3191,21 +3155,21 @@
         <f>IFERROR((VLOOKUP(AF2,Scoring!$A:$B,2,0))+IF(AH2="y",1,0)+IF(AI2="y",1,0)+IF(AJ2="y",1,0)+IF(AK2="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AM2" s="16"/>
-      <c r="AN2" s="17"/>
-      <c r="AO2" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="AP2" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="AQ2" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="AR2" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="AS2" s="85">
+      <c r="AM2" s="86"/>
+      <c r="AN2" s="87"/>
+      <c r="AO2" s="88" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP2" s="89" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ2" s="90" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR2" s="91" t="s">
+        <v>128</v>
+      </c>
+      <c r="AS2" s="92">
         <f>IFERROR((VLOOKUP(AM2,Scoring!$A:$B,2,0))+IF(AO2="y",1,0)+IF(AP2="y",1,0)+IF(AQ2="y",1,0)+IF(AR2="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3245,21 +3209,21 @@
         <f>IFERROR((VLOOKUP(BA2,Scoring!$A:$B,2,0))+IF(BC2="y",1,0)+IF(BD2="y",1,0)+IF(BE2="y",1,0)+IF(BF2="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="BH2" s="16"/>
-      <c r="BI2" s="17"/>
-      <c r="BJ2" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="BK2" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="BL2" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="BM2" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="BN2" s="85">
+      <c r="BH2" s="86"/>
+      <c r="BI2" s="87"/>
+      <c r="BJ2" s="88" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK2" s="89" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL2" s="90" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM2" s="91" t="s">
+        <v>128</v>
+      </c>
+      <c r="BN2" s="92">
         <f>IFERROR((VLOOKUP(BH2,Scoring!$A:$B,2,0))+IF(BJ2="y",1,0)+IF(BK2="y",1,0)+IF(BL2="y",1,0)+IF(BM2="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3299,36 +3263,36 @@
         <f>IFERROR((VLOOKUP(BV2,Scoring!$A:$B,2,0))+IF(BX2="y",1,0)+IF(BY2="y",1,0)+IF(BZ2="y",1,0)+IF(CA2="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC2" s="86"/>
-      <c r="CD2" s="87"/>
-      <c r="CE2" s="88" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF2" s="89" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG2" s="90" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH2" s="91" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI2" s="92">
+      <c r="CC2" s="16"/>
+      <c r="CD2" s="17"/>
+      <c r="CE2" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF2" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG2" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH2" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI2" s="85">
         <f>IFERROR((VLOOKUP(CC2,Scoring!$A:$B,2,0))+IF(CE2="y",1,0)+IF(CF2="y",1,0)+IF(CG2="y",1,0)+IF(CH2="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ2" s="93"/>
-      <c r="CK2" s="94"/>
-      <c r="CL2" s="95" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM2" s="96" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN2" s="97" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO2" s="98" t="s">
+      <c r="CJ2" s="86"/>
+      <c r="CK2" s="87"/>
+      <c r="CL2" s="88" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM2" s="89" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN2" s="90" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO2" s="91" t="s">
         <v>128</v>
       </c>
       <c r="CP2" s="92">
@@ -3353,43 +3317,115 @@
         <f>IFERROR((VLOOKUP(CQ2,Scoring!$A:$B,2,0))+IF(CS2="y",1,0)+IF(CT2="y",1,0)+IF(CU2="y",1,0)+IF(CV2="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX2" s="93"/>
-      <c r="CY2" s="94"/>
-      <c r="CZ2" s="95" t="s">
-        <v>128</v>
-      </c>
-      <c r="DA2" s="96" t="s">
-        <v>128</v>
-      </c>
-      <c r="DB2" s="97" t="s">
-        <v>128</v>
-      </c>
-      <c r="DC2" s="98" t="s">
-        <v>128</v>
-      </c>
-      <c r="DD2" s="92">
+      <c r="CX2" s="16"/>
+      <c r="CY2" s="17"/>
+      <c r="CZ2" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA2" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB2" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC2" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD2" s="85">
         <f>IFERROR((VLOOKUP(CX2,Scoring!$A:$B,2,0))+IF(CZ2="y",1,0)+IF(DA2="y",1,0)+IF(DB2="y",1,0)+IF(DC2="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DE2" s="16"/>
-      <c r="DF2" s="17"/>
-      <c r="DG2" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="DH2" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="DI2" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="DJ2" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="DK2" s="85">
+      <c r="DE2" s="86"/>
+      <c r="DF2" s="87"/>
+      <c r="DG2" s="88" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH2" s="89" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI2" s="90" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ2" s="91" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK2" s="93">
         <f>IFERROR((VLOOKUP(DE2,Scoring!$A:$B,2,0))+IF(DG2="y",1,0)+IF(DH2="y",1,0)+IF(DI2="y",1,0)+IF(DJ2="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DL2" s="13">
+      <c r="DL2" s="94"/>
+      <c r="DM2" s="95"/>
+      <c r="DN2" s="96" t="s">
+        <v>128</v>
+      </c>
+      <c r="DO2" s="97" t="s">
+        <v>128</v>
+      </c>
+      <c r="DP2" s="98" t="s">
+        <v>128</v>
+      </c>
+      <c r="DQ2" s="99" t="s">
+        <v>128</v>
+      </c>
+      <c r="DR2" s="93">
+        <f>IFERROR((VLOOKUP(DL2,Scoring!$A:$B,2,0))+IF(DN2="y",1,0)+IF(DO2="y",1,0)+IF(DP2="y",1,0)+IF(DQ2="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DS2" s="16"/>
+      <c r="DT2" s="17"/>
+      <c r="DU2" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="DV2" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="DW2" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="DX2" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="DY2" s="85">
+        <f>IFERROR((VLOOKUP(DS2,Scoring!$A:$B,2,0))+IF(DU2="y",1,0)+IF(DV2="y",1,0)+IF(DW2="y",1,0)+IF(DX2="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DZ2" s="94"/>
+      <c r="EA2" s="95"/>
+      <c r="EB2" s="96" t="s">
+        <v>128</v>
+      </c>
+      <c r="EC2" s="97" t="s">
+        <v>128</v>
+      </c>
+      <c r="ED2" s="98" t="s">
+        <v>128</v>
+      </c>
+      <c r="EE2" s="99" t="s">
+        <v>128</v>
+      </c>
+      <c r="EF2" s="93">
+        <f>IFERROR((VLOOKUP(DZ2,Scoring!$A:$B,2,0))+IF(EB2="y",1,0)+IF(EC2="y",1,0)+IF(ED2="y",1,0)+IF(EE2="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EG2" s="16"/>
+      <c r="EH2" s="17"/>
+      <c r="EI2" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="EJ2" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="EK2" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="EL2" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="EM2" s="85">
+        <f>IFERROR((VLOOKUP(EG2,Scoring!$A:$B,2,0))+IF(EI2="y",1,0)+IF(EJ2="y",1,0)+IF(EK2="y",1,0)+IF(EL2="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EN2" s="13">
         <v>0.0</v>
       </c>
     </row>
@@ -3417,7 +3453,7 @@
       <c r="I3" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="J3" s="99">
+      <c r="J3" s="100">
         <f>IFERROR((VLOOKUP(D3,Scoring!$A:$B,2,0))+IF(F3="y",1,0)+IF(G3="y",1,0)+IF(H3="y",1,0)+IF(I3="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3435,25 +3471,25 @@
       <c r="P3" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="Q3" s="99">
+      <c r="Q3" s="100">
         <f>IFERROR((VLOOKUP(K3,Scoring!$A:$B,2,0))+IF(M3="y",1,0)+IF(N3="y",1,0)+IF(O3="y",1,0)+IF(P3="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="R3" s="24"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="U3" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="V3" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="W3" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="X3" s="99">
+      <c r="R3" s="101"/>
+      <c r="S3" s="102"/>
+      <c r="T3" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="U3" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="V3" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="W3" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="X3" s="107">
         <f>IFERROR((VLOOKUP(R3,Scoring!$A:$B,2,0))+IF(T3="y",1,0)+IF(U3="y",1,0)+IF(V3="y",1,0)+IF(W3="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3471,7 +3507,7 @@
       <c r="AD3" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AE3" s="99">
+      <c r="AE3" s="100">
         <f>IFERROR((VLOOKUP(Y3,Scoring!$A:$B,2,0))+IF(AA3="y",1,0)+IF(AB3="y",1,0)+IF(AC3="y",1,0)+IF(AD3="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3489,25 +3525,25 @@
       <c r="AK3" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AL3" s="99">
+      <c r="AL3" s="100">
         <f>IFERROR((VLOOKUP(AF3,Scoring!$A:$B,2,0))+IF(AH3="y",1,0)+IF(AI3="y",1,0)+IF(AJ3="y",1,0)+IF(AK3="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AM3" s="24"/>
-      <c r="AN3" s="25"/>
-      <c r="AO3" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="AP3" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="AQ3" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="AR3" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AS3" s="99">
+      <c r="AM3" s="101"/>
+      <c r="AN3" s="102"/>
+      <c r="AO3" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP3" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ3" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR3" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="AS3" s="107">
         <f>IFERROR((VLOOKUP(AM3,Scoring!$A:$B,2,0))+IF(AO3="y",1,0)+IF(AP3="y",1,0)+IF(AQ3="y",1,0)+IF(AR3="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3525,7 +3561,7 @@
       <c r="AY3" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AZ3" s="99">
+      <c r="AZ3" s="100">
         <f>IFERROR((VLOOKUP(AT3,Scoring!$A:$B,2,0))+IF(AV3="y",1,0)+IF(AW3="y",1,0)+IF(AX3="y",1,0)+IF(AY3="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3543,25 +3579,25 @@
       <c r="BF3" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BG3" s="99">
+      <c r="BG3" s="100">
         <f>IFERROR((VLOOKUP(BA3,Scoring!$A:$B,2,0))+IF(BC3="y",1,0)+IF(BD3="y",1,0)+IF(BE3="y",1,0)+IF(BF3="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="BH3" s="24"/>
-      <c r="BI3" s="25"/>
-      <c r="BJ3" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="BK3" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="BL3" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="BM3" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="BN3" s="99">
+      <c r="BH3" s="101"/>
+      <c r="BI3" s="102"/>
+      <c r="BJ3" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK3" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL3" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM3" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="BN3" s="107">
         <f>IFERROR((VLOOKUP(BH3,Scoring!$A:$B,2,0))+IF(BJ3="y",1,0)+IF(BK3="y",1,0)+IF(BL3="y",1,0)+IF(BM3="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3579,7 +3615,7 @@
       <c r="BT3" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BU3" s="99">
+      <c r="BU3" s="100">
         <f>IFERROR((VLOOKUP(BO3,Scoring!$A:$B,2,0))+IF(BQ3="y",1,0)+IF(BR3="y",1,0)+IF(BS3="y",1,0)+IF(BT3="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3597,43 +3633,43 @@
       <c r="CA3" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="CB3" s="99">
+      <c r="CB3" s="100">
         <f>IFERROR((VLOOKUP(BV3,Scoring!$A:$B,2,0))+IF(BX3="y",1,0)+IF(BY3="y",1,0)+IF(BZ3="y",1,0)+IF(CA3="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC3" s="100"/>
-      <c r="CD3" s="101"/>
-      <c r="CE3" s="102" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF3" s="103" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG3" s="104" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH3" s="105" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI3" s="106">
+      <c r="CC3" s="24"/>
+      <c r="CD3" s="25"/>
+      <c r="CE3" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF3" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG3" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH3" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI3" s="100">
         <f>IFERROR((VLOOKUP(CC3,Scoring!$A:$B,2,0))+IF(CE3="y",1,0)+IF(CF3="y",1,0)+IF(CG3="y",1,0)+IF(CH3="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ3" s="107"/>
-      <c r="CK3" s="108"/>
-      <c r="CL3" s="109" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM3" s="110" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN3" s="111" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO3" s="112" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP3" s="106">
+      <c r="CJ3" s="101"/>
+      <c r="CK3" s="102"/>
+      <c r="CL3" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM3" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN3" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO3" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP3" s="107">
         <f>IFERROR((VLOOKUP(CJ3,Scoring!$A:$B,2,0))+IF(CL3="y",1,0)+IF(CM3="y",1,0)+IF(CN3="y",1,0)+IF(CO3="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3651,47 +3687,119 @@
       <c r="CV3" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="CW3" s="99">
+      <c r="CW3" s="100">
         <f>IFERROR((VLOOKUP(CQ3,Scoring!$A:$B,2,0))+IF(CS3="y",1,0)+IF(CT3="y",1,0)+IF(CU3="y",1,0)+IF(CV3="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX3" s="107"/>
-      <c r="CY3" s="108"/>
-      <c r="CZ3" s="109" t="s">
-        <v>128</v>
-      </c>
-      <c r="DA3" s="110" t="s">
-        <v>128</v>
-      </c>
-      <c r="DB3" s="111" t="s">
-        <v>128</v>
-      </c>
-      <c r="DC3" s="112" t="s">
-        <v>128</v>
-      </c>
-      <c r="DD3" s="106">
+      <c r="CX3" s="24"/>
+      <c r="CY3" s="25"/>
+      <c r="CZ3" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA3" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB3" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC3" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD3" s="100">
         <f>IFERROR((VLOOKUP(CX3,Scoring!$A:$B,2,0))+IF(CZ3="y",1,0)+IF(DA3="y",1,0)+IF(DB3="y",1,0)+IF(DC3="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DE3" s="24"/>
-      <c r="DF3" s="25"/>
-      <c r="DG3" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="DH3" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="DI3" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="DJ3" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="DK3" s="99">
+      <c r="DE3" s="101"/>
+      <c r="DF3" s="102"/>
+      <c r="DG3" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH3" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI3" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ3" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK3" s="108">
         <f>IFERROR((VLOOKUP(DE3,Scoring!$A:$B,2,0))+IF(DG3="y",1,0)+IF(DH3="y",1,0)+IF(DI3="y",1,0)+IF(DJ3="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DL3" s="13">
+      <c r="DL3" s="109"/>
+      <c r="DM3" s="110"/>
+      <c r="DN3" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="DO3" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="DP3" s="113" t="s">
+        <v>128</v>
+      </c>
+      <c r="DQ3" s="114" t="s">
+        <v>128</v>
+      </c>
+      <c r="DR3" s="108">
+        <f>IFERROR((VLOOKUP(DL3,Scoring!$A:$B,2,0))+IF(DN3="y",1,0)+IF(DO3="y",1,0)+IF(DP3="y",1,0)+IF(DQ3="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DS3" s="24"/>
+      <c r="DT3" s="25"/>
+      <c r="DU3" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="DV3" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="DW3" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="DX3" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="DY3" s="100">
+        <f>IFERROR((VLOOKUP(DS3,Scoring!$A:$B,2,0))+IF(DU3="y",1,0)+IF(DV3="y",1,0)+IF(DW3="y",1,0)+IF(DX3="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DZ3" s="109"/>
+      <c r="EA3" s="110"/>
+      <c r="EB3" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="EC3" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="ED3" s="113" t="s">
+        <v>128</v>
+      </c>
+      <c r="EE3" s="114" t="s">
+        <v>128</v>
+      </c>
+      <c r="EF3" s="108">
+        <f>IFERROR((VLOOKUP(DZ3,Scoring!$A:$B,2,0))+IF(EB3="y",1,0)+IF(EC3="y",1,0)+IF(ED3="y",1,0)+IF(EE3="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EG3" s="24"/>
+      <c r="EH3" s="25"/>
+      <c r="EI3" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="EJ3" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="EK3" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="EL3" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="EM3" s="100">
+        <f>IFERROR((VLOOKUP(EG3,Scoring!$A:$B,2,0))+IF(EI3="y",1,0)+IF(EJ3="y",1,0)+IF(EK3="y",1,0)+IF(EL3="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EN3" s="13">
         <v>0.0</v>
       </c>
     </row>
@@ -3741,21 +3849,21 @@
         <f>IFERROR((VLOOKUP(K4,Scoring!$A:$B,2,0))+IF(M4="y",1,0)+IF(N4="y",1,0)+IF(O4="y",1,0)+IF(P4="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="R4" s="36"/>
-      <c r="S4" s="37"/>
-      <c r="T4" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="U4" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="V4" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="W4" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="X4" s="85">
+      <c r="R4" s="115"/>
+      <c r="S4" s="116"/>
+      <c r="T4" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="U4" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="V4" s="119" t="s">
+        <v>128</v>
+      </c>
+      <c r="W4" s="120" t="s">
+        <v>128</v>
+      </c>
+      <c r="X4" s="92">
         <f>IFERROR((VLOOKUP(R4,Scoring!$A:$B,2,0))+IF(T4="y",1,0)+IF(U4="y",1,0)+IF(V4="y",1,0)+IF(W4="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3795,21 +3903,21 @@
         <f>IFERROR((VLOOKUP(AF4,Scoring!$A:$B,2,0))+IF(AH4="y",1,0)+IF(AI4="y",1,0)+IF(AJ4="y",1,0)+IF(AK4="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AM4" s="36"/>
-      <c r="AN4" s="37"/>
-      <c r="AO4" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="AP4" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="AQ4" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="AR4" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="AS4" s="85">
+      <c r="AM4" s="115"/>
+      <c r="AN4" s="116"/>
+      <c r="AO4" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP4" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ4" s="119" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR4" s="120" t="s">
+        <v>128</v>
+      </c>
+      <c r="AS4" s="92">
         <f>IFERROR((VLOOKUP(AM4,Scoring!$A:$B,2,0))+IF(AO4="y",1,0)+IF(AP4="y",1,0)+IF(AQ4="y",1,0)+IF(AR4="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3849,21 +3957,21 @@
         <f>IFERROR((VLOOKUP(BA4,Scoring!$A:$B,2,0))+IF(BC4="y",1,0)+IF(BD4="y",1,0)+IF(BE4="y",1,0)+IF(BF4="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="BH4" s="36"/>
-      <c r="BI4" s="37"/>
-      <c r="BJ4" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="BK4" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="BL4" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="BM4" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="BN4" s="85">
+      <c r="BH4" s="115"/>
+      <c r="BI4" s="116"/>
+      <c r="BJ4" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK4" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL4" s="119" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM4" s="120" t="s">
+        <v>128</v>
+      </c>
+      <c r="BN4" s="92">
         <f>IFERROR((VLOOKUP(BH4,Scoring!$A:$B,2,0))+IF(BJ4="y",1,0)+IF(BK4="y",1,0)+IF(BL4="y",1,0)+IF(BM4="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -3903,36 +4011,36 @@
         <f>IFERROR((VLOOKUP(BV4,Scoring!$A:$B,2,0))+IF(BX4="y",1,0)+IF(BY4="y",1,0)+IF(BZ4="y",1,0)+IF(CA4="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC4" s="113"/>
-      <c r="CD4" s="114"/>
-      <c r="CE4" s="115" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF4" s="116" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG4" s="117" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH4" s="118" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI4" s="92">
+      <c r="CC4" s="36"/>
+      <c r="CD4" s="37"/>
+      <c r="CE4" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF4" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG4" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH4" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI4" s="85">
         <f>IFERROR((VLOOKUP(CC4,Scoring!$A:$B,2,0))+IF(CE4="y",1,0)+IF(CF4="y",1,0)+IF(CG4="y",1,0)+IF(CH4="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ4" s="119"/>
-      <c r="CK4" s="120"/>
-      <c r="CL4" s="121" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM4" s="122" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN4" s="123" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO4" s="124" t="s">
+      <c r="CJ4" s="115"/>
+      <c r="CK4" s="116"/>
+      <c r="CL4" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM4" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN4" s="119" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO4" s="120" t="s">
         <v>128</v>
       </c>
       <c r="CP4" s="92">
@@ -3957,43 +4065,115 @@
         <f>IFERROR((VLOOKUP(CQ4,Scoring!$A:$B,2,0))+IF(CS4="y",1,0)+IF(CT4="y",1,0)+IF(CU4="y",1,0)+IF(CV4="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX4" s="119"/>
-      <c r="CY4" s="120"/>
-      <c r="CZ4" s="121" t="s">
-        <v>128</v>
-      </c>
-      <c r="DA4" s="122" t="s">
-        <v>128</v>
-      </c>
-      <c r="DB4" s="123" t="s">
-        <v>128</v>
-      </c>
-      <c r="DC4" s="124" t="s">
-        <v>128</v>
-      </c>
-      <c r="DD4" s="92">
+      <c r="CX4" s="36"/>
+      <c r="CY4" s="37"/>
+      <c r="CZ4" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA4" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB4" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC4" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD4" s="85">
         <f>IFERROR((VLOOKUP(CX4,Scoring!$A:$B,2,0))+IF(CZ4="y",1,0)+IF(DA4="y",1,0)+IF(DB4="y",1,0)+IF(DC4="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DE4" s="36"/>
-      <c r="DF4" s="37"/>
-      <c r="DG4" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="DH4" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="DI4" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="DJ4" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="DK4" s="85">
+      <c r="DE4" s="115"/>
+      <c r="DF4" s="116"/>
+      <c r="DG4" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH4" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI4" s="119" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ4" s="120" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK4" s="93">
         <f>IFERROR((VLOOKUP(DE4,Scoring!$A:$B,2,0))+IF(DG4="y",1,0)+IF(DH4="y",1,0)+IF(DI4="y",1,0)+IF(DJ4="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DL4" s="13">
+      <c r="DL4" s="121"/>
+      <c r="DM4" s="122"/>
+      <c r="DN4" s="123" t="s">
+        <v>128</v>
+      </c>
+      <c r="DO4" s="124" t="s">
+        <v>128</v>
+      </c>
+      <c r="DP4" s="125" t="s">
+        <v>128</v>
+      </c>
+      <c r="DQ4" s="126" t="s">
+        <v>128</v>
+      </c>
+      <c r="DR4" s="93">
+        <f>IFERROR((VLOOKUP(DL4,Scoring!$A:$B,2,0))+IF(DN4="y",1,0)+IF(DO4="y",1,0)+IF(DP4="y",1,0)+IF(DQ4="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DS4" s="36"/>
+      <c r="DT4" s="37"/>
+      <c r="DU4" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="DV4" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="DW4" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="DX4" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="DY4" s="85">
+        <f>IFERROR((VLOOKUP(DS4,Scoring!$A:$B,2,0))+IF(DU4="y",1,0)+IF(DV4="y",1,0)+IF(DW4="y",1,0)+IF(DX4="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DZ4" s="121"/>
+      <c r="EA4" s="122"/>
+      <c r="EB4" s="123" t="s">
+        <v>128</v>
+      </c>
+      <c r="EC4" s="124" t="s">
+        <v>128</v>
+      </c>
+      <c r="ED4" s="125" t="s">
+        <v>128</v>
+      </c>
+      <c r="EE4" s="126" t="s">
+        <v>128</v>
+      </c>
+      <c r="EF4" s="93">
+        <f>IFERROR((VLOOKUP(DZ4,Scoring!$A:$B,2,0))+IF(EB4="y",1,0)+IF(EC4="y",1,0)+IF(ED4="y",1,0)+IF(EE4="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EG4" s="36"/>
+      <c r="EH4" s="37"/>
+      <c r="EI4" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="EJ4" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="EK4" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="EL4" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="EM4" s="85">
+        <f>IFERROR((VLOOKUP(EG4,Scoring!$A:$B,2,0))+IF(EI4="y",1,0)+IF(EJ4="y",1,0)+IF(EK4="y",1,0)+IF(EL4="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EN4" s="13">
         <v>0.0</v>
       </c>
     </row>
@@ -4021,7 +4201,7 @@
       <c r="I5" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="J5" s="99">
+      <c r="J5" s="100">
         <f>IFERROR((VLOOKUP(D5,Scoring!$A:$B,2,0))+IF(F5="y",1,0)+IF(G5="y",1,0)+IF(H5="y",1,0)+IF(I5="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4039,25 +4219,25 @@
       <c r="P5" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="Q5" s="99">
+      <c r="Q5" s="100">
         <f>IFERROR((VLOOKUP(K5,Scoring!$A:$B,2,0))+IF(M5="y",1,0)+IF(N5="y",1,0)+IF(O5="y",1,0)+IF(P5="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="R5" s="48"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="U5" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="V5" s="52" t="s">
-        <v>128</v>
-      </c>
-      <c r="W5" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="X5" s="99">
+      <c r="R5" s="127"/>
+      <c r="S5" s="128"/>
+      <c r="T5" s="129" t="s">
+        <v>128</v>
+      </c>
+      <c r="U5" s="130" t="s">
+        <v>128</v>
+      </c>
+      <c r="V5" s="131" t="s">
+        <v>128</v>
+      </c>
+      <c r="W5" s="132" t="s">
+        <v>128</v>
+      </c>
+      <c r="X5" s="107">
         <f>IFERROR((VLOOKUP(R5,Scoring!$A:$B,2,0))+IF(T5="y",1,0)+IF(U5="y",1,0)+IF(V5="y",1,0)+IF(W5="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4075,7 +4255,7 @@
       <c r="AD5" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="AE5" s="99">
+      <c r="AE5" s="100">
         <f>IFERROR((VLOOKUP(Y5,Scoring!$A:$B,2,0))+IF(AA5="y",1,0)+IF(AB5="y",1,0)+IF(AC5="y",1,0)+IF(AD5="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4093,25 +4273,25 @@
       <c r="AK5" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="AL5" s="99">
+      <c r="AL5" s="100">
         <f>IFERROR((VLOOKUP(AF5,Scoring!$A:$B,2,0))+IF(AH5="y",1,0)+IF(AI5="y",1,0)+IF(AJ5="y",1,0)+IF(AK5="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AM5" s="48"/>
-      <c r="AN5" s="49"/>
-      <c r="AO5" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="AP5" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="AQ5" s="52" t="s">
-        <v>128</v>
-      </c>
-      <c r="AR5" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="AS5" s="99">
+      <c r="AM5" s="127"/>
+      <c r="AN5" s="128"/>
+      <c r="AO5" s="129" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP5" s="130" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ5" s="131" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR5" s="132" t="s">
+        <v>128</v>
+      </c>
+      <c r="AS5" s="107">
         <f>IFERROR((VLOOKUP(AM5,Scoring!$A:$B,2,0))+IF(AO5="y",1,0)+IF(AP5="y",1,0)+IF(AQ5="y",1,0)+IF(AR5="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4129,7 +4309,7 @@
       <c r="AY5" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="AZ5" s="99">
+      <c r="AZ5" s="100">
         <f>IFERROR((VLOOKUP(AT5,Scoring!$A:$B,2,0))+IF(AV5="y",1,0)+IF(AW5="y",1,0)+IF(AX5="y",1,0)+IF(AY5="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4147,25 +4327,25 @@
       <c r="BF5" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="BG5" s="99">
+      <c r="BG5" s="100">
         <f>IFERROR((VLOOKUP(BA5,Scoring!$A:$B,2,0))+IF(BC5="y",1,0)+IF(BD5="y",1,0)+IF(BE5="y",1,0)+IF(BF5="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="BH5" s="48"/>
-      <c r="BI5" s="49"/>
-      <c r="BJ5" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="BK5" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="BL5" s="52" t="s">
-        <v>128</v>
-      </c>
-      <c r="BM5" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="BN5" s="99">
+      <c r="BH5" s="127"/>
+      <c r="BI5" s="128"/>
+      <c r="BJ5" s="129" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK5" s="130" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL5" s="131" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM5" s="132" t="s">
+        <v>128</v>
+      </c>
+      <c r="BN5" s="107">
         <f>IFERROR((VLOOKUP(BH5,Scoring!$A:$B,2,0))+IF(BJ5="y",1,0)+IF(BK5="y",1,0)+IF(BL5="y",1,0)+IF(BM5="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4183,7 +4363,7 @@
       <c r="BT5" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="BU5" s="99">
+      <c r="BU5" s="100">
         <f>IFERROR((VLOOKUP(BO5,Scoring!$A:$B,2,0))+IF(BQ5="y",1,0)+IF(BR5="y",1,0)+IF(BS5="y",1,0)+IF(BT5="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4201,43 +4381,43 @@
       <c r="CA5" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="CB5" s="99">
+      <c r="CB5" s="100">
         <f>IFERROR((VLOOKUP(BV5,Scoring!$A:$B,2,0))+IF(BX5="y",1,0)+IF(BY5="y",1,0)+IF(BZ5="y",1,0)+IF(CA5="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC5" s="125"/>
-      <c r="CD5" s="126"/>
-      <c r="CE5" s="127" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF5" s="128" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG5" s="129" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH5" s="130" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI5" s="106">
+      <c r="CC5" s="48"/>
+      <c r="CD5" s="49"/>
+      <c r="CE5" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF5" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG5" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH5" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI5" s="100">
         <f>IFERROR((VLOOKUP(CC5,Scoring!$A:$B,2,0))+IF(CE5="y",1,0)+IF(CF5="y",1,0)+IF(CG5="y",1,0)+IF(CH5="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ5" s="131"/>
-      <c r="CK5" s="132"/>
-      <c r="CL5" s="133" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM5" s="134" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN5" s="135" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO5" s="136" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP5" s="106">
+      <c r="CJ5" s="127"/>
+      <c r="CK5" s="128"/>
+      <c r="CL5" s="129" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM5" s="130" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN5" s="131" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO5" s="132" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP5" s="107">
         <f>IFERROR((VLOOKUP(CJ5,Scoring!$A:$B,2,0))+IF(CL5="y",1,0)+IF(CM5="y",1,0)+IF(CN5="y",1,0)+IF(CO5="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4255,53 +4435,125 @@
       <c r="CV5" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="CW5" s="99">
+      <c r="CW5" s="100">
         <f>IFERROR((VLOOKUP(CQ5,Scoring!$A:$B,2,0))+IF(CS5="y",1,0)+IF(CT5="y",1,0)+IF(CU5="y",1,0)+IF(CV5="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX5" s="131"/>
-      <c r="CY5" s="132"/>
-      <c r="CZ5" s="133" t="s">
-        <v>128</v>
-      </c>
-      <c r="DA5" s="134" t="s">
-        <v>128</v>
-      </c>
-      <c r="DB5" s="135" t="s">
-        <v>128</v>
-      </c>
-      <c r="DC5" s="136" t="s">
-        <v>128</v>
-      </c>
-      <c r="DD5" s="106">
+      <c r="CX5" s="48"/>
+      <c r="CY5" s="49"/>
+      <c r="CZ5" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA5" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB5" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC5" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD5" s="100">
         <f>IFERROR((VLOOKUP(CX5,Scoring!$A:$B,2,0))+IF(CZ5="y",1,0)+IF(DA5="y",1,0)+IF(DB5="y",1,0)+IF(DC5="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DE5" s="48"/>
-      <c r="DF5" s="49"/>
-      <c r="DG5" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="DH5" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="DI5" s="52" t="s">
-        <v>128</v>
-      </c>
-      <c r="DJ5" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="DK5" s="99">
+      <c r="DE5" s="127"/>
+      <c r="DF5" s="128"/>
+      <c r="DG5" s="129" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH5" s="130" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI5" s="131" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ5" s="132" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK5" s="108">
         <f>IFERROR((VLOOKUP(DE5,Scoring!$A:$B,2,0))+IF(DG5="y",1,0)+IF(DH5="y",1,0)+IF(DI5="y",1,0)+IF(DJ5="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DL5" s="13">
+      <c r="DL5" s="133"/>
+      <c r="DM5" s="134"/>
+      <c r="DN5" s="135" t="s">
+        <v>128</v>
+      </c>
+      <c r="DO5" s="136" t="s">
+        <v>128</v>
+      </c>
+      <c r="DP5" s="137" t="s">
+        <v>128</v>
+      </c>
+      <c r="DQ5" s="138" t="s">
+        <v>128</v>
+      </c>
+      <c r="DR5" s="108">
+        <f>IFERROR((VLOOKUP(DL5,Scoring!$A:$B,2,0))+IF(DN5="y",1,0)+IF(DO5="y",1,0)+IF(DP5="y",1,0)+IF(DQ5="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DS5" s="48"/>
+      <c r="DT5" s="49"/>
+      <c r="DU5" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="DV5" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="DW5" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="DX5" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="DY5" s="100">
+        <f>IFERROR((VLOOKUP(DS5,Scoring!$A:$B,2,0))+IF(DU5="y",1,0)+IF(DV5="y",1,0)+IF(DW5="y",1,0)+IF(DX5="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DZ5" s="133"/>
+      <c r="EA5" s="134"/>
+      <c r="EB5" s="135" t="s">
+        <v>128</v>
+      </c>
+      <c r="EC5" s="136" t="s">
+        <v>128</v>
+      </c>
+      <c r="ED5" s="137" t="s">
+        <v>128</v>
+      </c>
+      <c r="EE5" s="138" t="s">
+        <v>128</v>
+      </c>
+      <c r="EF5" s="108">
+        <f>IFERROR((VLOOKUP(DZ5,Scoring!$A:$B,2,0))+IF(EB5="y",1,0)+IF(EC5="y",1,0)+IF(ED5="y",1,0)+IF(EE5="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EG5" s="48"/>
+      <c r="EH5" s="49"/>
+      <c r="EI5" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="EJ5" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="EK5" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="EL5" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="EM5" s="100">
+        <f>IFERROR((VLOOKUP(EG5,Scoring!$A:$B,2,0))+IF(EI5="y",1,0)+IF(EJ5="y",1,0)+IF(EK5="y",1,0)+IF(EL5="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EN5" s="13">
         <v>0.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="s">
-        <v>393</v>
+        <v>349</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>22</v>
@@ -4345,21 +4597,21 @@
         <f>IFERROR((VLOOKUP(K6,Scoring!$A:$B,2,0))+IF(M6="y",1,0)+IF(N6="y",1,0)+IF(O6="y",1,0)+IF(P6="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="R6" s="24"/>
-      <c r="S6" s="25"/>
-      <c r="T6" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="U6" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="V6" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="W6" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="X6" s="85">
+      <c r="R6" s="101"/>
+      <c r="S6" s="102"/>
+      <c r="T6" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="U6" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="V6" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="W6" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="X6" s="92">
         <f>IFERROR((VLOOKUP(R6,Scoring!$A:$B,2,0))+IF(T6="y",1,0)+IF(U6="y",1,0)+IF(V6="y",1,0)+IF(W6="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4399,21 +4651,21 @@
         <f>IFERROR((VLOOKUP(AF6,Scoring!$A:$B,2,0))+IF(AH6="y",1,0)+IF(AI6="y",1,0)+IF(AJ6="y",1,0)+IF(AK6="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AM6" s="24"/>
-      <c r="AN6" s="25"/>
-      <c r="AO6" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="AP6" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="AQ6" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="AR6" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AS6" s="85">
+      <c r="AM6" s="101"/>
+      <c r="AN6" s="102"/>
+      <c r="AO6" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP6" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ6" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR6" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="AS6" s="92">
         <f>IFERROR((VLOOKUP(AM6,Scoring!$A:$B,2,0))+IF(AO6="y",1,0)+IF(AP6="y",1,0)+IF(AQ6="y",1,0)+IF(AR6="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4453,21 +4705,21 @@
         <f>IFERROR((VLOOKUP(BA6,Scoring!$A:$B,2,0))+IF(BC6="y",1,0)+IF(BD6="y",1,0)+IF(BE6="y",1,0)+IF(BF6="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="BH6" s="24"/>
-      <c r="BI6" s="25"/>
-      <c r="BJ6" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="BK6" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="BL6" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="BM6" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="BN6" s="85">
+      <c r="BH6" s="101"/>
+      <c r="BI6" s="102"/>
+      <c r="BJ6" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK6" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL6" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM6" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="BN6" s="92">
         <f>IFERROR((VLOOKUP(BH6,Scoring!$A:$B,2,0))+IF(BJ6="y",1,0)+IF(BK6="y",1,0)+IF(BL6="y",1,0)+IF(BM6="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4507,36 +4759,36 @@
         <f>IFERROR((VLOOKUP(BV6,Scoring!$A:$B,2,0))+IF(BX6="y",1,0)+IF(BY6="y",1,0)+IF(BZ6="y",1,0)+IF(CA6="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC6" s="100"/>
-      <c r="CD6" s="101"/>
-      <c r="CE6" s="102" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF6" s="103" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG6" s="104" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH6" s="105" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI6" s="92">
+      <c r="CC6" s="24"/>
+      <c r="CD6" s="25"/>
+      <c r="CE6" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF6" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG6" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH6" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI6" s="85">
         <f>IFERROR((VLOOKUP(CC6,Scoring!$A:$B,2,0))+IF(CE6="y",1,0)+IF(CF6="y",1,0)+IF(CG6="y",1,0)+IF(CH6="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ6" s="107"/>
-      <c r="CK6" s="108"/>
-      <c r="CL6" s="109" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM6" s="110" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN6" s="111" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO6" s="112" t="s">
+      <c r="CJ6" s="101"/>
+      <c r="CK6" s="102"/>
+      <c r="CL6" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM6" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN6" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO6" s="106" t="s">
         <v>128</v>
       </c>
       <c r="CP6" s="92">
@@ -4561,49 +4813,121 @@
         <f>IFERROR((VLOOKUP(CQ6,Scoring!$A:$B,2,0))+IF(CS6="y",1,0)+IF(CT6="y",1,0)+IF(CU6="y",1,0)+IF(CV6="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX6" s="107"/>
-      <c r="CY6" s="108"/>
-      <c r="CZ6" s="109" t="s">
-        <v>128</v>
-      </c>
-      <c r="DA6" s="110" t="s">
-        <v>128</v>
-      </c>
-      <c r="DB6" s="111" t="s">
-        <v>128</v>
-      </c>
-      <c r="DC6" s="112" t="s">
-        <v>128</v>
-      </c>
-      <c r="DD6" s="92">
+      <c r="CX6" s="24"/>
+      <c r="CY6" s="25"/>
+      <c r="CZ6" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA6" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB6" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC6" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD6" s="85">
         <f>IFERROR((VLOOKUP(CX6,Scoring!$A:$B,2,0))+IF(CZ6="y",1,0)+IF(DA6="y",1,0)+IF(DB6="y",1,0)+IF(DC6="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DE6" s="24"/>
-      <c r="DF6" s="25"/>
-      <c r="DG6" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="DH6" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="DI6" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="DJ6" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="DK6" s="85">
+      <c r="DE6" s="101"/>
+      <c r="DF6" s="102"/>
+      <c r="DG6" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH6" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI6" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ6" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK6" s="93">
         <f>IFERROR((VLOOKUP(DE6,Scoring!$A:$B,2,0))+IF(DG6="y",1,0)+IF(DH6="y",1,0)+IF(DI6="y",1,0)+IF(DJ6="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DL6" s="13">
+      <c r="DL6" s="109"/>
+      <c r="DM6" s="110"/>
+      <c r="DN6" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="DO6" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="DP6" s="113" t="s">
+        <v>128</v>
+      </c>
+      <c r="DQ6" s="114" t="s">
+        <v>128</v>
+      </c>
+      <c r="DR6" s="93">
+        <f>IFERROR((VLOOKUP(DL6,Scoring!$A:$B,2,0))+IF(DN6="y",1,0)+IF(DO6="y",1,0)+IF(DP6="y",1,0)+IF(DQ6="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DS6" s="24"/>
+      <c r="DT6" s="25"/>
+      <c r="DU6" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="DV6" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="DW6" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="DX6" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="DY6" s="85">
+        <f>IFERROR((VLOOKUP(DS6,Scoring!$A:$B,2,0))+IF(DU6="y",1,0)+IF(DV6="y",1,0)+IF(DW6="y",1,0)+IF(DX6="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DZ6" s="109"/>
+      <c r="EA6" s="110"/>
+      <c r="EB6" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="EC6" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="ED6" s="113" t="s">
+        <v>128</v>
+      </c>
+      <c r="EE6" s="114" t="s">
+        <v>128</v>
+      </c>
+      <c r="EF6" s="93">
+        <f>IFERROR((VLOOKUP(DZ6,Scoring!$A:$B,2,0))+IF(EB6="y",1,0)+IF(EC6="y",1,0)+IF(ED6="y",1,0)+IF(EE6="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EG6" s="24"/>
+      <c r="EH6" s="25"/>
+      <c r="EI6" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="EJ6" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="EK6" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="EL6" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="EM6" s="85">
+        <f>IFERROR((VLOOKUP(EG6,Scoring!$A:$B,2,0))+IF(EI6="y",1,0)+IF(EJ6="y",1,0)+IF(EK6="y",1,0)+IF(EL6="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EN6" s="13">
         <v>0.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="s">
-        <v>393</v>
+        <v>349</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>24</v>
@@ -4625,7 +4949,7 @@
       <c r="I7" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="J7" s="99">
+      <c r="J7" s="100">
         <f>IFERROR((VLOOKUP(D7,Scoring!$A:$B,2,0))+IF(F7="y",1,0)+IF(G7="y",1,0)+IF(H7="y",1,0)+IF(I7="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4643,25 +4967,25 @@
       <c r="P7" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="Q7" s="99">
+      <c r="Q7" s="100">
         <f>IFERROR((VLOOKUP(K7,Scoring!$A:$B,2,0))+IF(M7="y",1,0)+IF(N7="y",1,0)+IF(O7="y",1,0)+IF(P7="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="R7" s="24"/>
-      <c r="S7" s="25"/>
-      <c r="T7" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="U7" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="V7" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="W7" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="X7" s="99">
+      <c r="R7" s="101"/>
+      <c r="S7" s="102"/>
+      <c r="T7" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="U7" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="V7" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="W7" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="X7" s="107">
         <f>IFERROR((VLOOKUP(R7,Scoring!$A:$B,2,0))+IF(T7="y",1,0)+IF(U7="y",1,0)+IF(V7="y",1,0)+IF(W7="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4679,7 +5003,7 @@
       <c r="AD7" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AE7" s="99">
+      <c r="AE7" s="100">
         <f>IFERROR((VLOOKUP(Y7,Scoring!$A:$B,2,0))+IF(AA7="y",1,0)+IF(AB7="y",1,0)+IF(AC7="y",1,0)+IF(AD7="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4697,25 +5021,25 @@
       <c r="AK7" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AL7" s="99">
+      <c r="AL7" s="100">
         <f>IFERROR((VLOOKUP(AF7,Scoring!$A:$B,2,0))+IF(AH7="y",1,0)+IF(AI7="y",1,0)+IF(AJ7="y",1,0)+IF(AK7="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AM7" s="24"/>
-      <c r="AN7" s="25"/>
-      <c r="AO7" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="AP7" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="AQ7" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="AR7" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AS7" s="99">
+      <c r="AM7" s="101"/>
+      <c r="AN7" s="102"/>
+      <c r="AO7" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP7" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ7" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR7" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="AS7" s="107">
         <f>IFERROR((VLOOKUP(AM7,Scoring!$A:$B,2,0))+IF(AO7="y",1,0)+IF(AP7="y",1,0)+IF(AQ7="y",1,0)+IF(AR7="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4733,7 +5057,7 @@
       <c r="AY7" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AZ7" s="99">
+      <c r="AZ7" s="100">
         <f>IFERROR((VLOOKUP(AT7,Scoring!$A:$B,2,0))+IF(AV7="y",1,0)+IF(AW7="y",1,0)+IF(AX7="y",1,0)+IF(AY7="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4751,25 +5075,25 @@
       <c r="BF7" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BG7" s="99">
+      <c r="BG7" s="100">
         <f>IFERROR((VLOOKUP(BA7,Scoring!$A:$B,2,0))+IF(BC7="y",1,0)+IF(BD7="y",1,0)+IF(BE7="y",1,0)+IF(BF7="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="BH7" s="24"/>
-      <c r="BI7" s="25"/>
-      <c r="BJ7" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="BK7" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="BL7" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="BM7" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="BN7" s="99">
+      <c r="BH7" s="101"/>
+      <c r="BI7" s="102"/>
+      <c r="BJ7" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK7" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL7" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM7" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="BN7" s="107">
         <f>IFERROR((VLOOKUP(BH7,Scoring!$A:$B,2,0))+IF(BJ7="y",1,0)+IF(BK7="y",1,0)+IF(BL7="y",1,0)+IF(BM7="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4787,7 +5111,7 @@
       <c r="BT7" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BU7" s="99">
+      <c r="BU7" s="100">
         <f>IFERROR((VLOOKUP(BO7,Scoring!$A:$B,2,0))+IF(BQ7="y",1,0)+IF(BR7="y",1,0)+IF(BS7="y",1,0)+IF(BT7="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4805,43 +5129,43 @@
       <c r="CA7" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="CB7" s="99">
+      <c r="CB7" s="100">
         <f>IFERROR((VLOOKUP(BV7,Scoring!$A:$B,2,0))+IF(BX7="y",1,0)+IF(BY7="y",1,0)+IF(BZ7="y",1,0)+IF(CA7="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC7" s="100"/>
-      <c r="CD7" s="101"/>
-      <c r="CE7" s="102" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF7" s="103" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG7" s="104" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH7" s="105" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI7" s="106">
+      <c r="CC7" s="24"/>
+      <c r="CD7" s="25"/>
+      <c r="CE7" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF7" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG7" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH7" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI7" s="100">
         <f>IFERROR((VLOOKUP(CC7,Scoring!$A:$B,2,0))+IF(CE7="y",1,0)+IF(CF7="y",1,0)+IF(CG7="y",1,0)+IF(CH7="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ7" s="107"/>
-      <c r="CK7" s="108"/>
-      <c r="CL7" s="109" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM7" s="110" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN7" s="111" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO7" s="112" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP7" s="106">
+      <c r="CJ7" s="101"/>
+      <c r="CK7" s="102"/>
+      <c r="CL7" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM7" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN7" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO7" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP7" s="107">
         <f>IFERROR((VLOOKUP(CJ7,Scoring!$A:$B,2,0))+IF(CL7="y",1,0)+IF(CM7="y",1,0)+IF(CN7="y",1,0)+IF(CO7="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -4859,53 +5183,125 @@
       <c r="CV7" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="CW7" s="99">
+      <c r="CW7" s="100">
         <f>IFERROR((VLOOKUP(CQ7,Scoring!$A:$B,2,0))+IF(CS7="y",1,0)+IF(CT7="y",1,0)+IF(CU7="y",1,0)+IF(CV7="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX7" s="107"/>
-      <c r="CY7" s="108"/>
-      <c r="CZ7" s="109" t="s">
-        <v>128</v>
-      </c>
-      <c r="DA7" s="110" t="s">
-        <v>128</v>
-      </c>
-      <c r="DB7" s="111" t="s">
-        <v>128</v>
-      </c>
-      <c r="DC7" s="112" t="s">
-        <v>128</v>
-      </c>
-      <c r="DD7" s="106">
+      <c r="CX7" s="24"/>
+      <c r="CY7" s="25"/>
+      <c r="CZ7" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA7" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB7" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC7" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD7" s="100">
         <f>IFERROR((VLOOKUP(CX7,Scoring!$A:$B,2,0))+IF(CZ7="y",1,0)+IF(DA7="y",1,0)+IF(DB7="y",1,0)+IF(DC7="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DE7" s="24"/>
-      <c r="DF7" s="25"/>
-      <c r="DG7" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="DH7" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="DI7" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="DJ7" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="DK7" s="99">
+      <c r="DE7" s="101"/>
+      <c r="DF7" s="102"/>
+      <c r="DG7" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH7" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI7" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ7" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK7" s="108">
         <f>IFERROR((VLOOKUP(DE7,Scoring!$A:$B,2,0))+IF(DG7="y",1,0)+IF(DH7="y",1,0)+IF(DI7="y",1,0)+IF(DJ7="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DL7" s="13">
+      <c r="DL7" s="109"/>
+      <c r="DM7" s="110"/>
+      <c r="DN7" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="DO7" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="DP7" s="113" t="s">
+        <v>128</v>
+      </c>
+      <c r="DQ7" s="114" t="s">
+        <v>128</v>
+      </c>
+      <c r="DR7" s="108">
+        <f>IFERROR((VLOOKUP(DL7,Scoring!$A:$B,2,0))+IF(DN7="y",1,0)+IF(DO7="y",1,0)+IF(DP7="y",1,0)+IF(DQ7="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DS7" s="24"/>
+      <c r="DT7" s="25"/>
+      <c r="DU7" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="DV7" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="DW7" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="DX7" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="DY7" s="100">
+        <f>IFERROR((VLOOKUP(DS7,Scoring!$A:$B,2,0))+IF(DU7="y",1,0)+IF(DV7="y",1,0)+IF(DW7="y",1,0)+IF(DX7="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DZ7" s="109"/>
+      <c r="EA7" s="110"/>
+      <c r="EB7" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="EC7" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="ED7" s="113" t="s">
+        <v>128</v>
+      </c>
+      <c r="EE7" s="114" t="s">
+        <v>128</v>
+      </c>
+      <c r="EF7" s="108">
+        <f>IFERROR((VLOOKUP(DZ7,Scoring!$A:$B,2,0))+IF(EB7="y",1,0)+IF(EC7="y",1,0)+IF(ED7="y",1,0)+IF(EE7="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EG7" s="24"/>
+      <c r="EH7" s="25"/>
+      <c r="EI7" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="EJ7" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="EK7" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="EL7" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="EM7" s="100">
+        <f>IFERROR((VLOOKUP(EG7,Scoring!$A:$B,2,0))+IF(EI7="y",1,0)+IF(EJ7="y",1,0)+IF(EK7="y",1,0)+IF(EL7="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EN7" s="13">
         <v>0.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="33" t="s">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>27</v>
@@ -4949,21 +5345,21 @@
         <f>IFERROR((VLOOKUP(K8,Scoring!$A:$B,2,0))+IF(M8="y",1,0)+IF(N8="y",1,0)+IF(O8="y",1,0)+IF(P8="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="R8" s="36"/>
-      <c r="S8" s="37"/>
-      <c r="T8" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="U8" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="V8" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="W8" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="X8" s="85">
+      <c r="R8" s="115"/>
+      <c r="S8" s="116"/>
+      <c r="T8" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="U8" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="V8" s="119" t="s">
+        <v>128</v>
+      </c>
+      <c r="W8" s="120" t="s">
+        <v>128</v>
+      </c>
+      <c r="X8" s="92">
         <f>IFERROR((VLOOKUP(R8,Scoring!$A:$B,2,0))+IF(T8="y",1,0)+IF(U8="y",1,0)+IF(V8="y",1,0)+IF(W8="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5003,21 +5399,21 @@
         <f>IFERROR((VLOOKUP(AF8,Scoring!$A:$B,2,0))+IF(AH8="y",1,0)+IF(AI8="y",1,0)+IF(AJ8="y",1,0)+IF(AK8="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AM8" s="36"/>
-      <c r="AN8" s="37"/>
-      <c r="AO8" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="AP8" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="AQ8" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="AR8" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="AS8" s="85">
+      <c r="AM8" s="115"/>
+      <c r="AN8" s="116"/>
+      <c r="AO8" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP8" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ8" s="119" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR8" s="120" t="s">
+        <v>128</v>
+      </c>
+      <c r="AS8" s="92">
         <f>IFERROR((VLOOKUP(AM8,Scoring!$A:$B,2,0))+IF(AO8="y",1,0)+IF(AP8="y",1,0)+IF(AQ8="y",1,0)+IF(AR8="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5057,21 +5453,21 @@
         <f>IFERROR((VLOOKUP(BA8,Scoring!$A:$B,2,0))+IF(BC8="y",1,0)+IF(BD8="y",1,0)+IF(BE8="y",1,0)+IF(BF8="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="BH8" s="36"/>
-      <c r="BI8" s="37"/>
-      <c r="BJ8" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="BK8" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="BL8" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="BM8" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="BN8" s="85">
+      <c r="BH8" s="115"/>
+      <c r="BI8" s="116"/>
+      <c r="BJ8" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK8" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL8" s="119" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM8" s="120" t="s">
+        <v>128</v>
+      </c>
+      <c r="BN8" s="92">
         <f>IFERROR((VLOOKUP(BH8,Scoring!$A:$B,2,0))+IF(BJ8="y",1,0)+IF(BK8="y",1,0)+IF(BL8="y",1,0)+IF(BM8="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5111,36 +5507,36 @@
         <f>IFERROR((VLOOKUP(BV8,Scoring!$A:$B,2,0))+IF(BX8="y",1,0)+IF(BY8="y",1,0)+IF(BZ8="y",1,0)+IF(CA8="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC8" s="113"/>
-      <c r="CD8" s="114"/>
-      <c r="CE8" s="115" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF8" s="116" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG8" s="117" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH8" s="118" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI8" s="92">
+      <c r="CC8" s="36"/>
+      <c r="CD8" s="37"/>
+      <c r="CE8" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF8" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG8" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH8" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI8" s="85">
         <f>IFERROR((VLOOKUP(CC8,Scoring!$A:$B,2,0))+IF(CE8="y",1,0)+IF(CF8="y",1,0)+IF(CG8="y",1,0)+IF(CH8="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ8" s="119"/>
-      <c r="CK8" s="120"/>
-      <c r="CL8" s="121" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM8" s="122" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN8" s="123" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO8" s="124" t="s">
+      <c r="CJ8" s="115"/>
+      <c r="CK8" s="116"/>
+      <c r="CL8" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM8" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN8" s="119" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO8" s="120" t="s">
         <v>128</v>
       </c>
       <c r="CP8" s="92">
@@ -5165,49 +5561,121 @@
         <f>IFERROR((VLOOKUP(CQ8,Scoring!$A:$B,2,0))+IF(CS8="y",1,0)+IF(CT8="y",1,0)+IF(CU8="y",1,0)+IF(CV8="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX8" s="119"/>
-      <c r="CY8" s="120"/>
-      <c r="CZ8" s="121" t="s">
-        <v>128</v>
-      </c>
-      <c r="DA8" s="122" t="s">
-        <v>128</v>
-      </c>
-      <c r="DB8" s="123" t="s">
-        <v>128</v>
-      </c>
-      <c r="DC8" s="124" t="s">
-        <v>128</v>
-      </c>
-      <c r="DD8" s="92">
+      <c r="CX8" s="36"/>
+      <c r="CY8" s="37"/>
+      <c r="CZ8" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA8" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB8" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC8" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD8" s="85">
         <f>IFERROR((VLOOKUP(CX8,Scoring!$A:$B,2,0))+IF(CZ8="y",1,0)+IF(DA8="y",1,0)+IF(DB8="y",1,0)+IF(DC8="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DE8" s="36"/>
-      <c r="DF8" s="37"/>
-      <c r="DG8" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="DH8" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="DI8" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="DJ8" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="DK8" s="85">
+      <c r="DE8" s="115"/>
+      <c r="DF8" s="116"/>
+      <c r="DG8" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH8" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI8" s="119" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ8" s="120" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK8" s="93">
         <f>IFERROR((VLOOKUP(DE8,Scoring!$A:$B,2,0))+IF(DG8="y",1,0)+IF(DH8="y",1,0)+IF(DI8="y",1,0)+IF(DJ8="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DL8" s="13">
+      <c r="DL8" s="121"/>
+      <c r="DM8" s="122"/>
+      <c r="DN8" s="123" t="s">
+        <v>128</v>
+      </c>
+      <c r="DO8" s="124" t="s">
+        <v>128</v>
+      </c>
+      <c r="DP8" s="125" t="s">
+        <v>128</v>
+      </c>
+      <c r="DQ8" s="126" t="s">
+        <v>128</v>
+      </c>
+      <c r="DR8" s="93">
+        <f>IFERROR((VLOOKUP(DL8,Scoring!$A:$B,2,0))+IF(DN8="y",1,0)+IF(DO8="y",1,0)+IF(DP8="y",1,0)+IF(DQ8="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DS8" s="36"/>
+      <c r="DT8" s="37"/>
+      <c r="DU8" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="DV8" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="DW8" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="DX8" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="DY8" s="85">
+        <f>IFERROR((VLOOKUP(DS8,Scoring!$A:$B,2,0))+IF(DU8="y",1,0)+IF(DV8="y",1,0)+IF(DW8="y",1,0)+IF(DX8="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DZ8" s="121"/>
+      <c r="EA8" s="122"/>
+      <c r="EB8" s="123" t="s">
+        <v>128</v>
+      </c>
+      <c r="EC8" s="124" t="s">
+        <v>128</v>
+      </c>
+      <c r="ED8" s="125" t="s">
+        <v>128</v>
+      </c>
+      <c r="EE8" s="126" t="s">
+        <v>128</v>
+      </c>
+      <c r="EF8" s="93">
+        <f>IFERROR((VLOOKUP(DZ8,Scoring!$A:$B,2,0))+IF(EB8="y",1,0)+IF(EC8="y",1,0)+IF(ED8="y",1,0)+IF(EE8="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EG8" s="36"/>
+      <c r="EH8" s="37"/>
+      <c r="EI8" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="EJ8" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="EK8" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="EL8" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="EM8" s="85">
+        <f>IFERROR((VLOOKUP(EG8,Scoring!$A:$B,2,0))+IF(EI8="y",1,0)+IF(EJ8="y",1,0)+IF(EK8="y",1,0)+IF(EL8="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EN8" s="13">
         <v>0.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="45" t="s">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="B9" s="46" t="s">
         <v>29</v>
@@ -5229,7 +5697,7 @@
       <c r="I9" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="J9" s="99">
+      <c r="J9" s="100">
         <f>IFERROR((VLOOKUP(D9,Scoring!$A:$B,2,0))+IF(F9="y",1,0)+IF(G9="y",1,0)+IF(H9="y",1,0)+IF(I9="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5247,25 +5715,25 @@
       <c r="P9" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="Q9" s="99">
+      <c r="Q9" s="100">
         <f>IFERROR((VLOOKUP(K9,Scoring!$A:$B,2,0))+IF(M9="y",1,0)+IF(N9="y",1,0)+IF(O9="y",1,0)+IF(P9="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="R9" s="48"/>
-      <c r="S9" s="49"/>
-      <c r="T9" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="U9" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="V9" s="52" t="s">
-        <v>128</v>
-      </c>
-      <c r="W9" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="X9" s="99">
+      <c r="R9" s="127"/>
+      <c r="S9" s="128"/>
+      <c r="T9" s="129" t="s">
+        <v>128</v>
+      </c>
+      <c r="U9" s="130" t="s">
+        <v>128</v>
+      </c>
+      <c r="V9" s="131" t="s">
+        <v>128</v>
+      </c>
+      <c r="W9" s="132" t="s">
+        <v>128</v>
+      </c>
+      <c r="X9" s="107">
         <f>IFERROR((VLOOKUP(R9,Scoring!$A:$B,2,0))+IF(T9="y",1,0)+IF(U9="y",1,0)+IF(V9="y",1,0)+IF(W9="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5283,7 +5751,7 @@
       <c r="AD9" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="AE9" s="99">
+      <c r="AE9" s="100">
         <f>IFERROR((VLOOKUP(Y9,Scoring!$A:$B,2,0))+IF(AA9="y",1,0)+IF(AB9="y",1,0)+IF(AC9="y",1,0)+IF(AD9="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5301,25 +5769,25 @@
       <c r="AK9" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="AL9" s="99">
+      <c r="AL9" s="100">
         <f>IFERROR((VLOOKUP(AF9,Scoring!$A:$B,2,0))+IF(AH9="y",1,0)+IF(AI9="y",1,0)+IF(AJ9="y",1,0)+IF(AK9="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AM9" s="48"/>
-      <c r="AN9" s="49"/>
-      <c r="AO9" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="AP9" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="AQ9" s="52" t="s">
-        <v>128</v>
-      </c>
-      <c r="AR9" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="AS9" s="99">
+      <c r="AM9" s="127"/>
+      <c r="AN9" s="128"/>
+      <c r="AO9" s="129" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP9" s="130" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ9" s="131" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR9" s="132" t="s">
+        <v>128</v>
+      </c>
+      <c r="AS9" s="107">
         <f>IFERROR((VLOOKUP(AM9,Scoring!$A:$B,2,0))+IF(AO9="y",1,0)+IF(AP9="y",1,0)+IF(AQ9="y",1,0)+IF(AR9="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5337,7 +5805,7 @@
       <c r="AY9" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="AZ9" s="99">
+      <c r="AZ9" s="100">
         <f>IFERROR((VLOOKUP(AT9,Scoring!$A:$B,2,0))+IF(AV9="y",1,0)+IF(AW9="y",1,0)+IF(AX9="y",1,0)+IF(AY9="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5355,25 +5823,25 @@
       <c r="BF9" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="BG9" s="99">
+      <c r="BG9" s="100">
         <f>IFERROR((VLOOKUP(BA9,Scoring!$A:$B,2,0))+IF(BC9="y",1,0)+IF(BD9="y",1,0)+IF(BE9="y",1,0)+IF(BF9="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="BH9" s="48"/>
-      <c r="BI9" s="49"/>
-      <c r="BJ9" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="BK9" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="BL9" s="52" t="s">
-        <v>128</v>
-      </c>
-      <c r="BM9" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="BN9" s="99">
+      <c r="BH9" s="127"/>
+      <c r="BI9" s="128"/>
+      <c r="BJ9" s="129" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK9" s="130" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL9" s="131" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM9" s="132" t="s">
+        <v>128</v>
+      </c>
+      <c r="BN9" s="107">
         <f>IFERROR((VLOOKUP(BH9,Scoring!$A:$B,2,0))+IF(BJ9="y",1,0)+IF(BK9="y",1,0)+IF(BL9="y",1,0)+IF(BM9="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5391,7 +5859,7 @@
       <c r="BT9" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="BU9" s="99">
+      <c r="BU9" s="100">
         <f>IFERROR((VLOOKUP(BO9,Scoring!$A:$B,2,0))+IF(BQ9="y",1,0)+IF(BR9="y",1,0)+IF(BS9="y",1,0)+IF(BT9="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5409,43 +5877,43 @@
       <c r="CA9" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="CB9" s="99">
+      <c r="CB9" s="100">
         <f>IFERROR((VLOOKUP(BV9,Scoring!$A:$B,2,0))+IF(BX9="y",1,0)+IF(BY9="y",1,0)+IF(BZ9="y",1,0)+IF(CA9="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC9" s="125"/>
-      <c r="CD9" s="126"/>
-      <c r="CE9" s="127" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF9" s="128" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG9" s="129" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH9" s="130" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI9" s="106">
+      <c r="CC9" s="48"/>
+      <c r="CD9" s="49"/>
+      <c r="CE9" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF9" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG9" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH9" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI9" s="100">
         <f>IFERROR((VLOOKUP(CC9,Scoring!$A:$B,2,0))+IF(CE9="y",1,0)+IF(CF9="y",1,0)+IF(CG9="y",1,0)+IF(CH9="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ9" s="131"/>
-      <c r="CK9" s="132"/>
-      <c r="CL9" s="133" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM9" s="134" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN9" s="135" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO9" s="136" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP9" s="106">
+      <c r="CJ9" s="127"/>
+      <c r="CK9" s="128"/>
+      <c r="CL9" s="129" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM9" s="130" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN9" s="131" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO9" s="132" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP9" s="107">
         <f>IFERROR((VLOOKUP(CJ9,Scoring!$A:$B,2,0))+IF(CL9="y",1,0)+IF(CM9="y",1,0)+IF(CN9="y",1,0)+IF(CO9="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5463,59 +5931,131 @@
       <c r="CV9" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="CW9" s="99">
+      <c r="CW9" s="100">
         <f>IFERROR((VLOOKUP(CQ9,Scoring!$A:$B,2,0))+IF(CS9="y",1,0)+IF(CT9="y",1,0)+IF(CU9="y",1,0)+IF(CV9="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX9" s="131"/>
-      <c r="CY9" s="132"/>
-      <c r="CZ9" s="133" t="s">
-        <v>128</v>
-      </c>
-      <c r="DA9" s="134" t="s">
-        <v>128</v>
-      </c>
-      <c r="DB9" s="135" t="s">
-        <v>128</v>
-      </c>
-      <c r="DC9" s="136" t="s">
-        <v>128</v>
-      </c>
-      <c r="DD9" s="106">
+      <c r="CX9" s="48"/>
+      <c r="CY9" s="49"/>
+      <c r="CZ9" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA9" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB9" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC9" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD9" s="100">
         <f>IFERROR((VLOOKUP(CX9,Scoring!$A:$B,2,0))+IF(CZ9="y",1,0)+IF(DA9="y",1,0)+IF(DB9="y",1,0)+IF(DC9="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DE9" s="48"/>
-      <c r="DF9" s="49"/>
-      <c r="DG9" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="DH9" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="DI9" s="52" t="s">
-        <v>128</v>
-      </c>
-      <c r="DJ9" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="DK9" s="99">
+      <c r="DE9" s="127"/>
+      <c r="DF9" s="128"/>
+      <c r="DG9" s="129" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH9" s="130" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI9" s="131" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ9" s="132" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK9" s="108">
         <f>IFERROR((VLOOKUP(DE9,Scoring!$A:$B,2,0))+IF(DG9="y",1,0)+IF(DH9="y",1,0)+IF(DI9="y",1,0)+IF(DJ9="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DL9" s="13">
+      <c r="DL9" s="133"/>
+      <c r="DM9" s="134"/>
+      <c r="DN9" s="135" t="s">
+        <v>128</v>
+      </c>
+      <c r="DO9" s="136" t="s">
+        <v>128</v>
+      </c>
+      <c r="DP9" s="137" t="s">
+        <v>128</v>
+      </c>
+      <c r="DQ9" s="138" t="s">
+        <v>128</v>
+      </c>
+      <c r="DR9" s="108">
+        <f>IFERROR((VLOOKUP(DL9,Scoring!$A:$B,2,0))+IF(DN9="y",1,0)+IF(DO9="y",1,0)+IF(DP9="y",1,0)+IF(DQ9="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DS9" s="48"/>
+      <c r="DT9" s="49"/>
+      <c r="DU9" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="DV9" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="DW9" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="DX9" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="DY9" s="100">
+        <f>IFERROR((VLOOKUP(DS9,Scoring!$A:$B,2,0))+IF(DU9="y",1,0)+IF(DV9="y",1,0)+IF(DW9="y",1,0)+IF(DX9="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DZ9" s="133"/>
+      <c r="EA9" s="134"/>
+      <c r="EB9" s="135" t="s">
+        <v>128</v>
+      </c>
+      <c r="EC9" s="136" t="s">
+        <v>128</v>
+      </c>
+      <c r="ED9" s="137" t="s">
+        <v>128</v>
+      </c>
+      <c r="EE9" s="138" t="s">
+        <v>128</v>
+      </c>
+      <c r="EF9" s="108">
+        <f>IFERROR((VLOOKUP(DZ9,Scoring!$A:$B,2,0))+IF(EB9="y",1,0)+IF(EC9="y",1,0)+IF(ED9="y",1,0)+IF(EE9="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EG9" s="48"/>
+      <c r="EH9" s="49"/>
+      <c r="EI9" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="EJ9" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="EK9" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="EL9" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="EM9" s="100">
+        <f>IFERROR((VLOOKUP(EG9,Scoring!$A:$B,2,0))+IF(EI9="y",1,0)+IF(EJ9="y",1,0)+IF(EK9="y",1,0)+IF(EL9="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EN9" s="13">
         <v>0.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="s">
-        <v>395</v>
+        <v>351</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>396</v>
+        <v>352</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>397</v>
+        <v>353</v>
       </c>
       <c r="D10" s="24"/>
       <c r="E10" s="25"/>
@@ -5553,21 +6093,21 @@
         <f>IFERROR((VLOOKUP(K10,Scoring!$A:$B,2,0))+IF(M10="y",1,0)+IF(N10="y",1,0)+IF(O10="y",1,0)+IF(P10="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="R10" s="24"/>
-      <c r="S10" s="25"/>
-      <c r="T10" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="U10" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="V10" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="W10" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="X10" s="85">
+      <c r="R10" s="101"/>
+      <c r="S10" s="102"/>
+      <c r="T10" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="U10" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="V10" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="W10" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="X10" s="92">
         <f>IFERROR((VLOOKUP(R10,Scoring!$A:$B,2,0))+IF(T10="y",1,0)+IF(U10="y",1,0)+IF(V10="y",1,0)+IF(W10="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5607,21 +6147,21 @@
         <f>IFERROR((VLOOKUP(AF10,Scoring!$A:$B,2,0))+IF(AH10="y",1,0)+IF(AI10="y",1,0)+IF(AJ10="y",1,0)+IF(AK10="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AM10" s="24"/>
-      <c r="AN10" s="25"/>
-      <c r="AO10" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="AP10" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="AQ10" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="AR10" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AS10" s="85">
+      <c r="AM10" s="101"/>
+      <c r="AN10" s="102"/>
+      <c r="AO10" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP10" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ10" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR10" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="AS10" s="92">
         <f>IFERROR((VLOOKUP(AM10,Scoring!$A:$B,2,0))+IF(AO10="y",1,0)+IF(AP10="y",1,0)+IF(AQ10="y",1,0)+IF(AR10="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5661,21 +6201,21 @@
         <f>IFERROR((VLOOKUP(BA10,Scoring!$A:$B,2,0))+IF(BC10="y",1,0)+IF(BD10="y",1,0)+IF(BE10="y",1,0)+IF(BF10="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="BH10" s="24"/>
-      <c r="BI10" s="25"/>
-      <c r="BJ10" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="BK10" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="BL10" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="BM10" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="BN10" s="85">
+      <c r="BH10" s="101"/>
+      <c r="BI10" s="102"/>
+      <c r="BJ10" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK10" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL10" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM10" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="BN10" s="92">
         <f>IFERROR((VLOOKUP(BH10,Scoring!$A:$B,2,0))+IF(BJ10="y",1,0)+IF(BK10="y",1,0)+IF(BL10="y",1,0)+IF(BM10="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5715,36 +6255,36 @@
         <f>IFERROR((VLOOKUP(BV10,Scoring!$A:$B,2,0))+IF(BX10="y",1,0)+IF(BY10="y",1,0)+IF(BZ10="y",1,0)+IF(CA10="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC10" s="100"/>
-      <c r="CD10" s="101"/>
-      <c r="CE10" s="102" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF10" s="103" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG10" s="104" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH10" s="105" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI10" s="92">
+      <c r="CC10" s="24"/>
+      <c r="CD10" s="25"/>
+      <c r="CE10" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF10" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG10" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH10" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI10" s="85">
         <f>IFERROR((VLOOKUP(CC10,Scoring!$A:$B,2,0))+IF(CE10="y",1,0)+IF(CF10="y",1,0)+IF(CG10="y",1,0)+IF(CH10="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ10" s="107"/>
-      <c r="CK10" s="108"/>
-      <c r="CL10" s="109" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM10" s="110" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN10" s="111" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO10" s="112" t="s">
+      <c r="CJ10" s="101"/>
+      <c r="CK10" s="102"/>
+      <c r="CL10" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM10" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN10" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO10" s="106" t="s">
         <v>128</v>
       </c>
       <c r="CP10" s="92">
@@ -5769,55 +6309,127 @@
         <f>IFERROR((VLOOKUP(CQ10,Scoring!$A:$B,2,0))+IF(CS10="y",1,0)+IF(CT10="y",1,0)+IF(CU10="y",1,0)+IF(CV10="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX10" s="107"/>
-      <c r="CY10" s="108"/>
-      <c r="CZ10" s="109" t="s">
-        <v>128</v>
-      </c>
-      <c r="DA10" s="110" t="s">
-        <v>128</v>
-      </c>
-      <c r="DB10" s="111" t="s">
-        <v>128</v>
-      </c>
-      <c r="DC10" s="112" t="s">
-        <v>128</v>
-      </c>
-      <c r="DD10" s="92">
+      <c r="CX10" s="24"/>
+      <c r="CY10" s="25"/>
+      <c r="CZ10" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA10" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB10" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC10" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD10" s="85">
         <f>IFERROR((VLOOKUP(CX10,Scoring!$A:$B,2,0))+IF(CZ10="y",1,0)+IF(DA10="y",1,0)+IF(DB10="y",1,0)+IF(DC10="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DE10" s="24"/>
-      <c r="DF10" s="25"/>
-      <c r="DG10" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="DH10" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="DI10" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="DJ10" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="DK10" s="85">
+      <c r="DE10" s="101"/>
+      <c r="DF10" s="102"/>
+      <c r="DG10" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH10" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI10" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ10" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK10" s="93">
         <f>IFERROR((VLOOKUP(DE10,Scoring!$A:$B,2,0))+IF(DG10="y",1,0)+IF(DH10="y",1,0)+IF(DI10="y",1,0)+IF(DJ10="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DL10" s="13">
+      <c r="DL10" s="109"/>
+      <c r="DM10" s="110"/>
+      <c r="DN10" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="DO10" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="DP10" s="113" t="s">
+        <v>128</v>
+      </c>
+      <c r="DQ10" s="114" t="s">
+        <v>128</v>
+      </c>
+      <c r="DR10" s="93">
+        <f>IFERROR((VLOOKUP(DL10,Scoring!$A:$B,2,0))+IF(DN10="y",1,0)+IF(DO10="y",1,0)+IF(DP10="y",1,0)+IF(DQ10="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DS10" s="24"/>
+      <c r="DT10" s="25"/>
+      <c r="DU10" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="DV10" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="DW10" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="DX10" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="DY10" s="85">
+        <f>IFERROR((VLOOKUP(DS10,Scoring!$A:$B,2,0))+IF(DU10="y",1,0)+IF(DV10="y",1,0)+IF(DW10="y",1,0)+IF(DX10="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DZ10" s="109"/>
+      <c r="EA10" s="110"/>
+      <c r="EB10" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="EC10" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="ED10" s="113" t="s">
+        <v>128</v>
+      </c>
+      <c r="EE10" s="114" t="s">
+        <v>128</v>
+      </c>
+      <c r="EF10" s="93">
+        <f>IFERROR((VLOOKUP(DZ10,Scoring!$A:$B,2,0))+IF(EB10="y",1,0)+IF(EC10="y",1,0)+IF(ED10="y",1,0)+IF(EE10="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EG10" s="24"/>
+      <c r="EH10" s="25"/>
+      <c r="EI10" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="EJ10" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="EK10" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="EL10" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="EM10" s="85">
+        <f>IFERROR((VLOOKUP(EG10,Scoring!$A:$B,2,0))+IF(EI10="y",1,0)+IF(EJ10="y",1,0)+IF(EK10="y",1,0)+IF(EL10="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EN10" s="13">
         <v>0.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="s">
-        <v>395</v>
+        <v>351</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>398</v>
+        <v>354</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>397</v>
+        <v>353</v>
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="25"/>
@@ -5833,7 +6445,7 @@
       <c r="I11" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="J11" s="99">
+      <c r="J11" s="100">
         <f>IFERROR((VLOOKUP(D11,Scoring!$A:$B,2,0))+IF(F11="y",1,0)+IF(G11="y",1,0)+IF(H11="y",1,0)+IF(I11="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5851,25 +6463,25 @@
       <c r="P11" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="Q11" s="99">
+      <c r="Q11" s="100">
         <f>IFERROR((VLOOKUP(K11,Scoring!$A:$B,2,0))+IF(M11="y",1,0)+IF(N11="y",1,0)+IF(O11="y",1,0)+IF(P11="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="R11" s="24"/>
-      <c r="S11" s="25"/>
-      <c r="T11" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="U11" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="V11" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="W11" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="X11" s="99">
+      <c r="R11" s="101"/>
+      <c r="S11" s="102"/>
+      <c r="T11" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="U11" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="V11" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="W11" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="X11" s="107">
         <f>IFERROR((VLOOKUP(R11,Scoring!$A:$B,2,0))+IF(T11="y",1,0)+IF(U11="y",1,0)+IF(V11="y",1,0)+IF(W11="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5887,7 +6499,7 @@
       <c r="AD11" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AE11" s="99">
+      <c r="AE11" s="100">
         <f>IFERROR((VLOOKUP(Y11,Scoring!$A:$B,2,0))+IF(AA11="y",1,0)+IF(AB11="y",1,0)+IF(AC11="y",1,0)+IF(AD11="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5905,25 +6517,25 @@
       <c r="AK11" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AL11" s="99">
+      <c r="AL11" s="100">
         <f>IFERROR((VLOOKUP(AF11,Scoring!$A:$B,2,0))+IF(AH11="y",1,0)+IF(AI11="y",1,0)+IF(AJ11="y",1,0)+IF(AK11="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AM11" s="24"/>
-      <c r="AN11" s="25"/>
-      <c r="AO11" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="AP11" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="AQ11" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="AR11" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AS11" s="99">
+      <c r="AM11" s="101"/>
+      <c r="AN11" s="102"/>
+      <c r="AO11" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP11" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ11" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR11" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="AS11" s="107">
         <f>IFERROR((VLOOKUP(AM11,Scoring!$A:$B,2,0))+IF(AO11="y",1,0)+IF(AP11="y",1,0)+IF(AQ11="y",1,0)+IF(AR11="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5941,7 +6553,7 @@
       <c r="AY11" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AZ11" s="99">
+      <c r="AZ11" s="100">
         <f>IFERROR((VLOOKUP(AT11,Scoring!$A:$B,2,0))+IF(AV11="y",1,0)+IF(AW11="y",1,0)+IF(AX11="y",1,0)+IF(AY11="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5959,25 +6571,25 @@
       <c r="BF11" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BG11" s="99">
+      <c r="BG11" s="100">
         <f>IFERROR((VLOOKUP(BA11,Scoring!$A:$B,2,0))+IF(BC11="y",1,0)+IF(BD11="y",1,0)+IF(BE11="y",1,0)+IF(BF11="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="BH11" s="24"/>
-      <c r="BI11" s="25"/>
-      <c r="BJ11" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="BK11" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="BL11" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="BM11" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="BN11" s="99">
+      <c r="BH11" s="101"/>
+      <c r="BI11" s="102"/>
+      <c r="BJ11" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK11" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL11" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM11" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="BN11" s="107">
         <f>IFERROR((VLOOKUP(BH11,Scoring!$A:$B,2,0))+IF(BJ11="y",1,0)+IF(BK11="y",1,0)+IF(BL11="y",1,0)+IF(BM11="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -5995,7 +6607,7 @@
       <c r="BT11" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BU11" s="99">
+      <c r="BU11" s="100">
         <f>IFERROR((VLOOKUP(BO11,Scoring!$A:$B,2,0))+IF(BQ11="y",1,0)+IF(BR11="y",1,0)+IF(BS11="y",1,0)+IF(BT11="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6013,43 +6625,43 @@
       <c r="CA11" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="CB11" s="99">
+      <c r="CB11" s="100">
         <f>IFERROR((VLOOKUP(BV11,Scoring!$A:$B,2,0))+IF(BX11="y",1,0)+IF(BY11="y",1,0)+IF(BZ11="y",1,0)+IF(CA11="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC11" s="100"/>
-      <c r="CD11" s="101"/>
-      <c r="CE11" s="102" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF11" s="103" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG11" s="104" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH11" s="105" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI11" s="106">
+      <c r="CC11" s="24"/>
+      <c r="CD11" s="25"/>
+      <c r="CE11" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF11" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG11" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH11" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI11" s="100">
         <f>IFERROR((VLOOKUP(CC11,Scoring!$A:$B,2,0))+IF(CE11="y",1,0)+IF(CF11="y",1,0)+IF(CG11="y",1,0)+IF(CH11="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ11" s="107"/>
-      <c r="CK11" s="108"/>
-      <c r="CL11" s="109" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM11" s="110" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN11" s="111" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO11" s="112" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP11" s="106">
+      <c r="CJ11" s="101"/>
+      <c r="CK11" s="102"/>
+      <c r="CL11" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM11" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN11" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO11" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP11" s="107">
         <f>IFERROR((VLOOKUP(CJ11,Scoring!$A:$B,2,0))+IF(CL11="y",1,0)+IF(CM11="y",1,0)+IF(CN11="y",1,0)+IF(CO11="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6067,53 +6679,125 @@
       <c r="CV11" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="CW11" s="99">
+      <c r="CW11" s="100">
         <f>IFERROR((VLOOKUP(CQ11,Scoring!$A:$B,2,0))+IF(CS11="y",1,0)+IF(CT11="y",1,0)+IF(CU11="y",1,0)+IF(CV11="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX11" s="107"/>
-      <c r="CY11" s="108"/>
-      <c r="CZ11" s="109" t="s">
-        <v>128</v>
-      </c>
-      <c r="DA11" s="110" t="s">
-        <v>128</v>
-      </c>
-      <c r="DB11" s="111" t="s">
-        <v>128</v>
-      </c>
-      <c r="DC11" s="112" t="s">
-        <v>128</v>
-      </c>
-      <c r="DD11" s="106">
+      <c r="CX11" s="24"/>
+      <c r="CY11" s="25"/>
+      <c r="CZ11" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA11" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB11" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC11" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD11" s="100">
         <f>IFERROR((VLOOKUP(CX11,Scoring!$A:$B,2,0))+IF(CZ11="y",1,0)+IF(DA11="y",1,0)+IF(DB11="y",1,0)+IF(DC11="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DE11" s="24"/>
-      <c r="DF11" s="25"/>
-      <c r="DG11" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="DH11" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="DI11" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="DJ11" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="DK11" s="99">
+      <c r="DE11" s="101"/>
+      <c r="DF11" s="102"/>
+      <c r="DG11" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH11" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI11" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ11" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK11" s="108">
         <f>IFERROR((VLOOKUP(DE11,Scoring!$A:$B,2,0))+IF(DG11="y",1,0)+IF(DH11="y",1,0)+IF(DI11="y",1,0)+IF(DJ11="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DL11" s="13">
+      <c r="DL11" s="109"/>
+      <c r="DM11" s="110"/>
+      <c r="DN11" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="DO11" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="DP11" s="113" t="s">
+        <v>128</v>
+      </c>
+      <c r="DQ11" s="114" t="s">
+        <v>128</v>
+      </c>
+      <c r="DR11" s="108">
+        <f>IFERROR((VLOOKUP(DL11,Scoring!$A:$B,2,0))+IF(DN11="y",1,0)+IF(DO11="y",1,0)+IF(DP11="y",1,0)+IF(DQ11="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DS11" s="24"/>
+      <c r="DT11" s="25"/>
+      <c r="DU11" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="DV11" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="DW11" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="DX11" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="DY11" s="100">
+        <f>IFERROR((VLOOKUP(DS11,Scoring!$A:$B,2,0))+IF(DU11="y",1,0)+IF(DV11="y",1,0)+IF(DW11="y",1,0)+IF(DX11="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DZ11" s="109"/>
+      <c r="EA11" s="110"/>
+      <c r="EB11" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="EC11" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="ED11" s="113" t="s">
+        <v>128</v>
+      </c>
+      <c r="EE11" s="114" t="s">
+        <v>128</v>
+      </c>
+      <c r="EF11" s="108">
+        <f>IFERROR((VLOOKUP(DZ11,Scoring!$A:$B,2,0))+IF(EB11="y",1,0)+IF(EC11="y",1,0)+IF(ED11="y",1,0)+IF(EE11="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EG11" s="24"/>
+      <c r="EH11" s="25"/>
+      <c r="EI11" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="EJ11" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="EK11" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="EL11" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="EM11" s="100">
+        <f>IFERROR((VLOOKUP(EG11,Scoring!$A:$B,2,0))+IF(EI11="y",1,0)+IF(EJ11="y",1,0)+IF(EK11="y",1,0)+IF(EL11="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EN11" s="13">
         <v>0.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="33" t="s">
-        <v>399</v>
+        <v>355</v>
       </c>
       <c r="B12" s="34" t="s">
         <v>34</v>
@@ -6157,21 +6841,21 @@
         <f>IFERROR((VLOOKUP(K12,Scoring!$A:$B,2,0))+IF(M12="y",1,0)+IF(N12="y",1,0)+IF(O12="y",1,0)+IF(P12="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="R12" s="36"/>
-      <c r="S12" s="37"/>
-      <c r="T12" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="U12" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="V12" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="W12" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="X12" s="85">
+      <c r="R12" s="115"/>
+      <c r="S12" s="116"/>
+      <c r="T12" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="U12" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="V12" s="119" t="s">
+        <v>128</v>
+      </c>
+      <c r="W12" s="120" t="s">
+        <v>128</v>
+      </c>
+      <c r="X12" s="92">
         <f>IFERROR((VLOOKUP(R12,Scoring!$A:$B,2,0))+IF(T12="y",1,0)+IF(U12="y",1,0)+IF(V12="y",1,0)+IF(W12="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6211,21 +6895,21 @@
         <f>IFERROR((VLOOKUP(AF12,Scoring!$A:$B,2,0))+IF(AH12="y",1,0)+IF(AI12="y",1,0)+IF(AJ12="y",1,0)+IF(AK12="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AM12" s="36"/>
-      <c r="AN12" s="37"/>
-      <c r="AO12" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="AP12" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="AQ12" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="AR12" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="AS12" s="85">
+      <c r="AM12" s="115"/>
+      <c r="AN12" s="116"/>
+      <c r="AO12" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP12" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ12" s="119" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR12" s="120" t="s">
+        <v>128</v>
+      </c>
+      <c r="AS12" s="92">
         <f>IFERROR((VLOOKUP(AM12,Scoring!$A:$B,2,0))+IF(AO12="y",1,0)+IF(AP12="y",1,0)+IF(AQ12="y",1,0)+IF(AR12="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6265,21 +6949,21 @@
         <f>IFERROR((VLOOKUP(BA12,Scoring!$A:$B,2,0))+IF(BC12="y",1,0)+IF(BD12="y",1,0)+IF(BE12="y",1,0)+IF(BF12="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="BH12" s="36"/>
-      <c r="BI12" s="37"/>
-      <c r="BJ12" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="BK12" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="BL12" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="BM12" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="BN12" s="85">
+      <c r="BH12" s="115"/>
+      <c r="BI12" s="116"/>
+      <c r="BJ12" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK12" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL12" s="119" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM12" s="120" t="s">
+        <v>128</v>
+      </c>
+      <c r="BN12" s="92">
         <f>IFERROR((VLOOKUP(BH12,Scoring!$A:$B,2,0))+IF(BJ12="y",1,0)+IF(BK12="y",1,0)+IF(BL12="y",1,0)+IF(BM12="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6319,36 +7003,36 @@
         <f>IFERROR((VLOOKUP(BV12,Scoring!$A:$B,2,0))+IF(BX12="y",1,0)+IF(BY12="y",1,0)+IF(BZ12="y",1,0)+IF(CA12="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC12" s="113"/>
-      <c r="CD12" s="114"/>
-      <c r="CE12" s="115" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF12" s="116" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG12" s="117" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH12" s="118" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI12" s="92">
+      <c r="CC12" s="36"/>
+      <c r="CD12" s="37"/>
+      <c r="CE12" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF12" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG12" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH12" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI12" s="85">
         <f>IFERROR((VLOOKUP(CC12,Scoring!$A:$B,2,0))+IF(CE12="y",1,0)+IF(CF12="y",1,0)+IF(CG12="y",1,0)+IF(CH12="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ12" s="119"/>
-      <c r="CK12" s="120"/>
-      <c r="CL12" s="121" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM12" s="122" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN12" s="123" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO12" s="124" t="s">
+      <c r="CJ12" s="115"/>
+      <c r="CK12" s="116"/>
+      <c r="CL12" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM12" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN12" s="119" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO12" s="120" t="s">
         <v>128</v>
       </c>
       <c r="CP12" s="92">
@@ -6373,55 +7057,127 @@
         <f>IFERROR((VLOOKUP(CQ12,Scoring!$A:$B,2,0))+IF(CS12="y",1,0)+IF(CT12="y",1,0)+IF(CU12="y",1,0)+IF(CV12="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX12" s="119"/>
-      <c r="CY12" s="120"/>
-      <c r="CZ12" s="121" t="s">
-        <v>128</v>
-      </c>
-      <c r="DA12" s="122" t="s">
-        <v>128</v>
-      </c>
-      <c r="DB12" s="123" t="s">
-        <v>128</v>
-      </c>
-      <c r="DC12" s="124" t="s">
-        <v>128</v>
-      </c>
-      <c r="DD12" s="92">
+      <c r="CX12" s="36"/>
+      <c r="CY12" s="37"/>
+      <c r="CZ12" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA12" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB12" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC12" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD12" s="85">
         <f>IFERROR((VLOOKUP(CX12,Scoring!$A:$B,2,0))+IF(CZ12="y",1,0)+IF(DA12="y",1,0)+IF(DB12="y",1,0)+IF(DC12="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DE12" s="36"/>
-      <c r="DF12" s="37"/>
-      <c r="DG12" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="DH12" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="DI12" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="DJ12" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="DK12" s="85">
+      <c r="DE12" s="115"/>
+      <c r="DF12" s="116"/>
+      <c r="DG12" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH12" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI12" s="119" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ12" s="120" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK12" s="93">
         <f>IFERROR((VLOOKUP(DE12,Scoring!$A:$B,2,0))+IF(DG12="y",1,0)+IF(DH12="y",1,0)+IF(DI12="y",1,0)+IF(DJ12="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DL12" s="13">
+      <c r="DL12" s="121"/>
+      <c r="DM12" s="122"/>
+      <c r="DN12" s="123" t="s">
+        <v>128</v>
+      </c>
+      <c r="DO12" s="124" t="s">
+        <v>128</v>
+      </c>
+      <c r="DP12" s="125" t="s">
+        <v>128</v>
+      </c>
+      <c r="DQ12" s="126" t="s">
+        <v>128</v>
+      </c>
+      <c r="DR12" s="93">
+        <f>IFERROR((VLOOKUP(DL12,Scoring!$A:$B,2,0))+IF(DN12="y",1,0)+IF(DO12="y",1,0)+IF(DP12="y",1,0)+IF(DQ12="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DS12" s="36"/>
+      <c r="DT12" s="37"/>
+      <c r="DU12" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="DV12" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="DW12" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="DX12" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="DY12" s="85">
+        <f>IFERROR((VLOOKUP(DS12,Scoring!$A:$B,2,0))+IF(DU12="y",1,0)+IF(DV12="y",1,0)+IF(DW12="y",1,0)+IF(DX12="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DZ12" s="121"/>
+      <c r="EA12" s="122"/>
+      <c r="EB12" s="123" t="s">
+        <v>128</v>
+      </c>
+      <c r="EC12" s="124" t="s">
+        <v>128</v>
+      </c>
+      <c r="ED12" s="125" t="s">
+        <v>128</v>
+      </c>
+      <c r="EE12" s="126" t="s">
+        <v>128</v>
+      </c>
+      <c r="EF12" s="93">
+        <f>IFERROR((VLOOKUP(DZ12,Scoring!$A:$B,2,0))+IF(EB12="y",1,0)+IF(EC12="y",1,0)+IF(ED12="y",1,0)+IF(EE12="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EG12" s="36"/>
+      <c r="EH12" s="37"/>
+      <c r="EI12" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="EJ12" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="EK12" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="EL12" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="EM12" s="85">
+        <f>IFERROR((VLOOKUP(EG12,Scoring!$A:$B,2,0))+IF(EI12="y",1,0)+IF(EJ12="y",1,0)+IF(EK12="y",1,0)+IF(EL12="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EN12" s="13">
         <v>0.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="s">
-        <v>399</v>
+        <v>355</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>400</v>
+        <v>356</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>397</v>
+        <v>353</v>
       </c>
       <c r="D13" s="24"/>
       <c r="E13" s="25"/>
@@ -6437,7 +7193,7 @@
       <c r="I13" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="J13" s="99">
+      <c r="J13" s="100">
         <f>IFERROR((VLOOKUP(D13,Scoring!$A:$B,2,0))+IF(F13="y",1,0)+IF(G13="y",1,0)+IF(H13="y",1,0)+IF(I13="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6455,25 +7211,25 @@
       <c r="P13" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="Q13" s="99">
+      <c r="Q13" s="100">
         <f>IFERROR((VLOOKUP(K13,Scoring!$A:$B,2,0))+IF(M13="y",1,0)+IF(N13="y",1,0)+IF(O13="y",1,0)+IF(P13="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="R13" s="24"/>
-      <c r="S13" s="25"/>
-      <c r="T13" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="U13" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="V13" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="W13" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="X13" s="99">
+      <c r="R13" s="101"/>
+      <c r="S13" s="102"/>
+      <c r="T13" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="U13" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="V13" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="W13" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="X13" s="107">
         <f>IFERROR((VLOOKUP(R13,Scoring!$A:$B,2,0))+IF(T13="y",1,0)+IF(U13="y",1,0)+IF(V13="y",1,0)+IF(W13="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6491,7 +7247,7 @@
       <c r="AD13" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AE13" s="99">
+      <c r="AE13" s="100">
         <f>IFERROR((VLOOKUP(Y13,Scoring!$A:$B,2,0))+IF(AA13="y",1,0)+IF(AB13="y",1,0)+IF(AC13="y",1,0)+IF(AD13="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6509,25 +7265,25 @@
       <c r="AK13" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AL13" s="99">
+      <c r="AL13" s="100">
         <f>IFERROR((VLOOKUP(AF13,Scoring!$A:$B,2,0))+IF(AH13="y",1,0)+IF(AI13="y",1,0)+IF(AJ13="y",1,0)+IF(AK13="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AM13" s="24"/>
-      <c r="AN13" s="25"/>
-      <c r="AO13" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="AP13" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="AQ13" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="AR13" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AS13" s="99">
+      <c r="AM13" s="101"/>
+      <c r="AN13" s="102"/>
+      <c r="AO13" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP13" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ13" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR13" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="AS13" s="107">
         <f>IFERROR((VLOOKUP(AM13,Scoring!$A:$B,2,0))+IF(AO13="y",1,0)+IF(AP13="y",1,0)+IF(AQ13="y",1,0)+IF(AR13="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6545,7 +7301,7 @@
       <c r="AY13" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AZ13" s="99">
+      <c r="AZ13" s="100">
         <f>IFERROR((VLOOKUP(AT13,Scoring!$A:$B,2,0))+IF(AV13="y",1,0)+IF(AW13="y",1,0)+IF(AX13="y",1,0)+IF(AY13="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6563,25 +7319,25 @@
       <c r="BF13" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BG13" s="99">
+      <c r="BG13" s="100">
         <f>IFERROR((VLOOKUP(BA13,Scoring!$A:$B,2,0))+IF(BC13="y",1,0)+IF(BD13="y",1,0)+IF(BE13="y",1,0)+IF(BF13="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="BH13" s="24"/>
-      <c r="BI13" s="25"/>
-      <c r="BJ13" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="BK13" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="BL13" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="BM13" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="BN13" s="99">
+      <c r="BH13" s="101"/>
+      <c r="BI13" s="102"/>
+      <c r="BJ13" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK13" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL13" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM13" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="BN13" s="107">
         <f>IFERROR((VLOOKUP(BH13,Scoring!$A:$B,2,0))+IF(BJ13="y",1,0)+IF(BK13="y",1,0)+IF(BL13="y",1,0)+IF(BM13="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6599,7 +7355,7 @@
       <c r="BT13" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="BU13" s="99">
+      <c r="BU13" s="100">
         <f>IFERROR((VLOOKUP(BO13,Scoring!$A:$B,2,0))+IF(BQ13="y",1,0)+IF(BR13="y",1,0)+IF(BS13="y",1,0)+IF(BT13="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6617,43 +7373,43 @@
       <c r="CA13" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="CB13" s="99">
+      <c r="CB13" s="100">
         <f>IFERROR((VLOOKUP(BV13,Scoring!$A:$B,2,0))+IF(BX13="y",1,0)+IF(BY13="y",1,0)+IF(BZ13="y",1,0)+IF(CA13="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC13" s="100"/>
-      <c r="CD13" s="101"/>
-      <c r="CE13" s="102" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF13" s="103" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG13" s="104" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH13" s="105" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI13" s="106">
+      <c r="CC13" s="24"/>
+      <c r="CD13" s="25"/>
+      <c r="CE13" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF13" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG13" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH13" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI13" s="100">
         <f>IFERROR((VLOOKUP(CC13,Scoring!$A:$B,2,0))+IF(CE13="y",1,0)+IF(CF13="y",1,0)+IF(CG13="y",1,0)+IF(CH13="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ13" s="107"/>
-      <c r="CK13" s="108"/>
-      <c r="CL13" s="109" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM13" s="110" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN13" s="111" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO13" s="112" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP13" s="106">
+      <c r="CJ13" s="101"/>
+      <c r="CK13" s="102"/>
+      <c r="CL13" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM13" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN13" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO13" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP13" s="107">
         <f>IFERROR((VLOOKUP(CJ13,Scoring!$A:$B,2,0))+IF(CL13="y",1,0)+IF(CM13="y",1,0)+IF(CN13="y",1,0)+IF(CO13="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6671,47 +7427,119 @@
       <c r="CV13" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="CW13" s="99">
+      <c r="CW13" s="100">
         <f>IFERROR((VLOOKUP(CQ13,Scoring!$A:$B,2,0))+IF(CS13="y",1,0)+IF(CT13="y",1,0)+IF(CU13="y",1,0)+IF(CV13="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX13" s="107"/>
-      <c r="CY13" s="108"/>
-      <c r="CZ13" s="109" t="s">
-        <v>128</v>
-      </c>
-      <c r="DA13" s="110" t="s">
-        <v>128</v>
-      </c>
-      <c r="DB13" s="111" t="s">
-        <v>128</v>
-      </c>
-      <c r="DC13" s="112" t="s">
-        <v>128</v>
-      </c>
-      <c r="DD13" s="106">
+      <c r="CX13" s="24"/>
+      <c r="CY13" s="25"/>
+      <c r="CZ13" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA13" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB13" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC13" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD13" s="100">
         <f>IFERROR((VLOOKUP(CX13,Scoring!$A:$B,2,0))+IF(CZ13="y",1,0)+IF(DA13="y",1,0)+IF(DB13="y",1,0)+IF(DC13="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DE13" s="24"/>
-      <c r="DF13" s="25"/>
-      <c r="DG13" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="DH13" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="DI13" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="DJ13" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="DK13" s="99">
+      <c r="DE13" s="101"/>
+      <c r="DF13" s="102"/>
+      <c r="DG13" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH13" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI13" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ13" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK13" s="108">
         <f>IFERROR((VLOOKUP(DE13,Scoring!$A:$B,2,0))+IF(DG13="y",1,0)+IF(DH13="y",1,0)+IF(DI13="y",1,0)+IF(DJ13="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DL13" s="13">
+      <c r="DL13" s="109"/>
+      <c r="DM13" s="110"/>
+      <c r="DN13" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="DO13" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="DP13" s="113" t="s">
+        <v>128</v>
+      </c>
+      <c r="DQ13" s="114" t="s">
+        <v>128</v>
+      </c>
+      <c r="DR13" s="108">
+        <f>IFERROR((VLOOKUP(DL13,Scoring!$A:$B,2,0))+IF(DN13="y",1,0)+IF(DO13="y",1,0)+IF(DP13="y",1,0)+IF(DQ13="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DS13" s="24"/>
+      <c r="DT13" s="25"/>
+      <c r="DU13" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="DV13" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="DW13" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="DX13" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="DY13" s="100">
+        <f>IFERROR((VLOOKUP(DS13,Scoring!$A:$B,2,0))+IF(DU13="y",1,0)+IF(DV13="y",1,0)+IF(DW13="y",1,0)+IF(DX13="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DZ13" s="109"/>
+      <c r="EA13" s="110"/>
+      <c r="EB13" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="EC13" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="ED13" s="113" t="s">
+        <v>128</v>
+      </c>
+      <c r="EE13" s="114" t="s">
+        <v>128</v>
+      </c>
+      <c r="EF13" s="108">
+        <f>IFERROR((VLOOKUP(DZ13,Scoring!$A:$B,2,0))+IF(EB13="y",1,0)+IF(EC13="y",1,0)+IF(ED13="y",1,0)+IF(EE13="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EG13" s="24"/>
+      <c r="EH13" s="25"/>
+      <c r="EI13" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="EJ13" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="EK13" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="EL13" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="EM13" s="100">
+        <f>IFERROR((VLOOKUP(EG13,Scoring!$A:$B,2,0))+IF(EI13="y",1,0)+IF(EJ13="y",1,0)+IF(EK13="y",1,0)+IF(EL13="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EN13" s="13">
         <v>0.0</v>
       </c>
     </row>
@@ -6761,21 +7589,21 @@
         <f>IFERROR((VLOOKUP(K14,Scoring!$A:$B,2,0))+IF(M14="y",1,0)+IF(N14="y",1,0)+IF(O14="y",1,0)+IF(P14="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="R14" s="36"/>
-      <c r="S14" s="37"/>
-      <c r="T14" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="U14" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="V14" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="W14" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="X14" s="85">
+      <c r="R14" s="115"/>
+      <c r="S14" s="116"/>
+      <c r="T14" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="U14" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="V14" s="119" t="s">
+        <v>128</v>
+      </c>
+      <c r="W14" s="120" t="s">
+        <v>128</v>
+      </c>
+      <c r="X14" s="92">
         <f>IFERROR((VLOOKUP(R14,Scoring!$A:$B,2,0))+IF(T14="y",1,0)+IF(U14="y",1,0)+IF(V14="y",1,0)+IF(W14="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6815,21 +7643,21 @@
         <f>IFERROR((VLOOKUP(AF14,Scoring!$A:$B,2,0))+IF(AH14="y",1,0)+IF(AI14="y",1,0)+IF(AJ14="y",1,0)+IF(AK14="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AM14" s="36"/>
-      <c r="AN14" s="37"/>
-      <c r="AO14" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="AP14" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="AQ14" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="AR14" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="AS14" s="85">
+      <c r="AM14" s="115"/>
+      <c r="AN14" s="116"/>
+      <c r="AO14" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP14" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ14" s="119" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR14" s="120" t="s">
+        <v>128</v>
+      </c>
+      <c r="AS14" s="92">
         <f>IFERROR((VLOOKUP(AM14,Scoring!$A:$B,2,0))+IF(AO14="y",1,0)+IF(AP14="y",1,0)+IF(AQ14="y",1,0)+IF(AR14="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6869,21 +7697,21 @@
         <f>IFERROR((VLOOKUP(BA14,Scoring!$A:$B,2,0))+IF(BC14="y",1,0)+IF(BD14="y",1,0)+IF(BE14="y",1,0)+IF(BF14="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="BH14" s="36"/>
-      <c r="BI14" s="37"/>
-      <c r="BJ14" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="BK14" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="BL14" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="BM14" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="BN14" s="85">
+      <c r="BH14" s="115"/>
+      <c r="BI14" s="116"/>
+      <c r="BJ14" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK14" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL14" s="119" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM14" s="120" t="s">
+        <v>128</v>
+      </c>
+      <c r="BN14" s="92">
         <f>IFERROR((VLOOKUP(BH14,Scoring!$A:$B,2,0))+IF(BJ14="y",1,0)+IF(BK14="y",1,0)+IF(BL14="y",1,0)+IF(BM14="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -6923,36 +7751,36 @@
         <f>IFERROR((VLOOKUP(BV14,Scoring!$A:$B,2,0))+IF(BX14="y",1,0)+IF(BY14="y",1,0)+IF(BZ14="y",1,0)+IF(CA14="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC14" s="113"/>
-      <c r="CD14" s="114"/>
-      <c r="CE14" s="115" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF14" s="116" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG14" s="117" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH14" s="118" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI14" s="92">
+      <c r="CC14" s="36"/>
+      <c r="CD14" s="37"/>
+      <c r="CE14" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF14" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG14" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH14" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI14" s="85">
         <f>IFERROR((VLOOKUP(CC14,Scoring!$A:$B,2,0))+IF(CE14="y",1,0)+IF(CF14="y",1,0)+IF(CG14="y",1,0)+IF(CH14="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ14" s="119"/>
-      <c r="CK14" s="120"/>
-      <c r="CL14" s="121" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM14" s="122" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN14" s="123" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO14" s="124" t="s">
+      <c r="CJ14" s="115"/>
+      <c r="CK14" s="116"/>
+      <c r="CL14" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM14" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN14" s="119" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO14" s="120" t="s">
         <v>128</v>
       </c>
       <c r="CP14" s="92">
@@ -6977,43 +7805,115 @@
         <f>IFERROR((VLOOKUP(CQ14,Scoring!$A:$B,2,0))+IF(CS14="y",1,0)+IF(CT14="y",1,0)+IF(CU14="y",1,0)+IF(CV14="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX14" s="119"/>
-      <c r="CY14" s="120"/>
-      <c r="CZ14" s="121" t="s">
-        <v>128</v>
-      </c>
-      <c r="DA14" s="122" t="s">
-        <v>128</v>
-      </c>
-      <c r="DB14" s="123" t="s">
-        <v>128</v>
-      </c>
-      <c r="DC14" s="124" t="s">
-        <v>128</v>
-      </c>
-      <c r="DD14" s="92">
+      <c r="CX14" s="36"/>
+      <c r="CY14" s="37"/>
+      <c r="CZ14" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA14" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB14" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC14" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD14" s="85">
         <f>IFERROR((VLOOKUP(CX14,Scoring!$A:$B,2,0))+IF(CZ14="y",1,0)+IF(DA14="y",1,0)+IF(DB14="y",1,0)+IF(DC14="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DE14" s="36"/>
-      <c r="DF14" s="37"/>
-      <c r="DG14" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="DH14" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="DI14" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="DJ14" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="DK14" s="85">
+      <c r="DE14" s="115"/>
+      <c r="DF14" s="116"/>
+      <c r="DG14" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH14" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI14" s="119" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ14" s="120" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK14" s="93">
         <f>IFERROR((VLOOKUP(DE14,Scoring!$A:$B,2,0))+IF(DG14="y",1,0)+IF(DH14="y",1,0)+IF(DI14="y",1,0)+IF(DJ14="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DL14" s="13">
+      <c r="DL14" s="121"/>
+      <c r="DM14" s="122"/>
+      <c r="DN14" s="123" t="s">
+        <v>128</v>
+      </c>
+      <c r="DO14" s="124" t="s">
+        <v>128</v>
+      </c>
+      <c r="DP14" s="125" t="s">
+        <v>128</v>
+      </c>
+      <c r="DQ14" s="126" t="s">
+        <v>128</v>
+      </c>
+      <c r="DR14" s="93">
+        <f>IFERROR((VLOOKUP(DL14,Scoring!$A:$B,2,0))+IF(DN14="y",1,0)+IF(DO14="y",1,0)+IF(DP14="y",1,0)+IF(DQ14="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DS14" s="36"/>
+      <c r="DT14" s="37"/>
+      <c r="DU14" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="DV14" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="DW14" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="DX14" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="DY14" s="85">
+        <f>IFERROR((VLOOKUP(DS14,Scoring!$A:$B,2,0))+IF(DU14="y",1,0)+IF(DV14="y",1,0)+IF(DW14="y",1,0)+IF(DX14="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DZ14" s="121"/>
+      <c r="EA14" s="122"/>
+      <c r="EB14" s="123" t="s">
+        <v>128</v>
+      </c>
+      <c r="EC14" s="124" t="s">
+        <v>128</v>
+      </c>
+      <c r="ED14" s="125" t="s">
+        <v>128</v>
+      </c>
+      <c r="EE14" s="126" t="s">
+        <v>128</v>
+      </c>
+      <c r="EF14" s="93">
+        <f>IFERROR((VLOOKUP(DZ14,Scoring!$A:$B,2,0))+IF(EB14="y",1,0)+IF(EC14="y",1,0)+IF(ED14="y",1,0)+IF(EE14="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EG14" s="36"/>
+      <c r="EH14" s="37"/>
+      <c r="EI14" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="EJ14" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="EK14" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="EL14" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="EM14" s="85">
+        <f>IFERROR((VLOOKUP(EG14,Scoring!$A:$B,2,0))+IF(EI14="y",1,0)+IF(EJ14="y",1,0)+IF(EK14="y",1,0)+IF(EL14="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EN14" s="13">
         <v>0.0</v>
       </c>
     </row>
@@ -7041,7 +7941,7 @@
       <c r="I15" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="J15" s="99">
+      <c r="J15" s="100">
         <f>IFERROR((VLOOKUP(D15,Scoring!$A:$B,2,0))+IF(F15="y",1,0)+IF(G15="y",1,0)+IF(H15="y",1,0)+IF(I15="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -7059,25 +7959,25 @@
       <c r="P15" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="Q15" s="99">
+      <c r="Q15" s="100">
         <f>IFERROR((VLOOKUP(K15,Scoring!$A:$B,2,0))+IF(M15="y",1,0)+IF(N15="y",1,0)+IF(O15="y",1,0)+IF(P15="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="R15" s="48"/>
-      <c r="S15" s="49"/>
-      <c r="T15" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="U15" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="V15" s="52" t="s">
-        <v>128</v>
-      </c>
-      <c r="W15" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="X15" s="99">
+      <c r="R15" s="127"/>
+      <c r="S15" s="128"/>
+      <c r="T15" s="129" t="s">
+        <v>128</v>
+      </c>
+      <c r="U15" s="130" t="s">
+        <v>128</v>
+      </c>
+      <c r="V15" s="131" t="s">
+        <v>128</v>
+      </c>
+      <c r="W15" s="132" t="s">
+        <v>128</v>
+      </c>
+      <c r="X15" s="107">
         <f>IFERROR((VLOOKUP(R15,Scoring!$A:$B,2,0))+IF(T15="y",1,0)+IF(U15="y",1,0)+IF(V15="y",1,0)+IF(W15="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -7095,7 +7995,7 @@
       <c r="AD15" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="AE15" s="99">
+      <c r="AE15" s="100">
         <f>IFERROR((VLOOKUP(Y15,Scoring!$A:$B,2,0))+IF(AA15="y",1,0)+IF(AB15="y",1,0)+IF(AC15="y",1,0)+IF(AD15="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -7113,25 +8013,25 @@
       <c r="AK15" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="AL15" s="99">
+      <c r="AL15" s="100">
         <f>IFERROR((VLOOKUP(AF15,Scoring!$A:$B,2,0))+IF(AH15="y",1,0)+IF(AI15="y",1,0)+IF(AJ15="y",1,0)+IF(AK15="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AM15" s="48"/>
-      <c r="AN15" s="49"/>
-      <c r="AO15" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="AP15" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="AQ15" s="52" t="s">
-        <v>128</v>
-      </c>
-      <c r="AR15" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="AS15" s="99">
+      <c r="AM15" s="127"/>
+      <c r="AN15" s="128"/>
+      <c r="AO15" s="129" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP15" s="130" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ15" s="131" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR15" s="132" t="s">
+        <v>128</v>
+      </c>
+      <c r="AS15" s="107">
         <f>IFERROR((VLOOKUP(AM15,Scoring!$A:$B,2,0))+IF(AO15="y",1,0)+IF(AP15="y",1,0)+IF(AQ15="y",1,0)+IF(AR15="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -7149,7 +8049,7 @@
       <c r="AY15" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="AZ15" s="99">
+      <c r="AZ15" s="100">
         <f>IFERROR((VLOOKUP(AT15,Scoring!$A:$B,2,0))+IF(AV15="y",1,0)+IF(AW15="y",1,0)+IF(AX15="y",1,0)+IF(AY15="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -7167,25 +8067,25 @@
       <c r="BF15" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="BG15" s="99">
+      <c r="BG15" s="100">
         <f>IFERROR((VLOOKUP(BA15,Scoring!$A:$B,2,0))+IF(BC15="y",1,0)+IF(BD15="y",1,0)+IF(BE15="y",1,0)+IF(BF15="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="BH15" s="48"/>
-      <c r="BI15" s="49"/>
-      <c r="BJ15" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="BK15" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="BL15" s="52" t="s">
-        <v>128</v>
-      </c>
-      <c r="BM15" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="BN15" s="99">
+      <c r="BH15" s="127"/>
+      <c r="BI15" s="128"/>
+      <c r="BJ15" s="129" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK15" s="130" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL15" s="131" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM15" s="132" t="s">
+        <v>128</v>
+      </c>
+      <c r="BN15" s="107">
         <f>IFERROR((VLOOKUP(BH15,Scoring!$A:$B,2,0))+IF(BJ15="y",1,0)+IF(BK15="y",1,0)+IF(BL15="y",1,0)+IF(BM15="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -7203,7 +8103,7 @@
       <c r="BT15" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="BU15" s="99">
+      <c r="BU15" s="100">
         <f>IFERROR((VLOOKUP(BO15,Scoring!$A:$B,2,0))+IF(BQ15="y",1,0)+IF(BR15="y",1,0)+IF(BS15="y",1,0)+IF(BT15="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -7221,43 +8121,43 @@
       <c r="CA15" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="CB15" s="99">
+      <c r="CB15" s="100">
         <f>IFERROR((VLOOKUP(BV15,Scoring!$A:$B,2,0))+IF(BX15="y",1,0)+IF(BY15="y",1,0)+IF(BZ15="y",1,0)+IF(CA15="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC15" s="125"/>
-      <c r="CD15" s="126"/>
-      <c r="CE15" s="127" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF15" s="128" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG15" s="129" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH15" s="130" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI15" s="106">
+      <c r="CC15" s="48"/>
+      <c r="CD15" s="49"/>
+      <c r="CE15" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF15" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG15" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH15" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI15" s="100">
         <f>IFERROR((VLOOKUP(CC15,Scoring!$A:$B,2,0))+IF(CE15="y",1,0)+IF(CF15="y",1,0)+IF(CG15="y",1,0)+IF(CH15="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ15" s="131"/>
-      <c r="CK15" s="132"/>
-      <c r="CL15" s="133" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM15" s="134" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN15" s="135" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO15" s="136" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP15" s="106">
+      <c r="CJ15" s="127"/>
+      <c r="CK15" s="128"/>
+      <c r="CL15" s="129" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM15" s="130" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN15" s="131" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO15" s="132" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP15" s="107">
         <f>IFERROR((VLOOKUP(CJ15,Scoring!$A:$B,2,0))+IF(CL15="y",1,0)+IF(CM15="y",1,0)+IF(CN15="y",1,0)+IF(CO15="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -7275,47 +8175,119 @@
       <c r="CV15" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="CW15" s="99">
+      <c r="CW15" s="100">
         <f>IFERROR((VLOOKUP(CQ15,Scoring!$A:$B,2,0))+IF(CS15="y",1,0)+IF(CT15="y",1,0)+IF(CU15="y",1,0)+IF(CV15="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX15" s="131"/>
-      <c r="CY15" s="132"/>
-      <c r="CZ15" s="133" t="s">
-        <v>128</v>
-      </c>
-      <c r="DA15" s="134" t="s">
-        <v>128</v>
-      </c>
-      <c r="DB15" s="135" t="s">
-        <v>128</v>
-      </c>
-      <c r="DC15" s="136" t="s">
-        <v>128</v>
-      </c>
-      <c r="DD15" s="106">
+      <c r="CX15" s="48"/>
+      <c r="CY15" s="49"/>
+      <c r="CZ15" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA15" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB15" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC15" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD15" s="100">
         <f>IFERROR((VLOOKUP(CX15,Scoring!$A:$B,2,0))+IF(CZ15="y",1,0)+IF(DA15="y",1,0)+IF(DB15="y",1,0)+IF(DC15="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DE15" s="48"/>
-      <c r="DF15" s="49"/>
-      <c r="DG15" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="DH15" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="DI15" s="52" t="s">
-        <v>128</v>
-      </c>
-      <c r="DJ15" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="DK15" s="99">
+      <c r="DE15" s="127"/>
+      <c r="DF15" s="128"/>
+      <c r="DG15" s="129" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH15" s="130" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI15" s="131" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ15" s="132" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK15" s="108">
         <f>IFERROR((VLOOKUP(DE15,Scoring!$A:$B,2,0))+IF(DG15="y",1,0)+IF(DH15="y",1,0)+IF(DI15="y",1,0)+IF(DJ15="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DL15" s="13">
+      <c r="DL15" s="133"/>
+      <c r="DM15" s="134"/>
+      <c r="DN15" s="135" t="s">
+        <v>128</v>
+      </c>
+      <c r="DO15" s="136" t="s">
+        <v>128</v>
+      </c>
+      <c r="DP15" s="137" t="s">
+        <v>128</v>
+      </c>
+      <c r="DQ15" s="138" t="s">
+        <v>128</v>
+      </c>
+      <c r="DR15" s="108">
+        <f>IFERROR((VLOOKUP(DL15,Scoring!$A:$B,2,0))+IF(DN15="y",1,0)+IF(DO15="y",1,0)+IF(DP15="y",1,0)+IF(DQ15="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DS15" s="48"/>
+      <c r="DT15" s="49"/>
+      <c r="DU15" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="DV15" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="DW15" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="DX15" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="DY15" s="100">
+        <f>IFERROR((VLOOKUP(DS15,Scoring!$A:$B,2,0))+IF(DU15="y",1,0)+IF(DV15="y",1,0)+IF(DW15="y",1,0)+IF(DX15="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DZ15" s="133"/>
+      <c r="EA15" s="134"/>
+      <c r="EB15" s="135" t="s">
+        <v>128</v>
+      </c>
+      <c r="EC15" s="136" t="s">
+        <v>128</v>
+      </c>
+      <c r="ED15" s="137" t="s">
+        <v>128</v>
+      </c>
+      <c r="EE15" s="138" t="s">
+        <v>128</v>
+      </c>
+      <c r="EF15" s="108">
+        <f>IFERROR((VLOOKUP(DZ15,Scoring!$A:$B,2,0))+IF(EB15="y",1,0)+IF(EC15="y",1,0)+IF(ED15="y",1,0)+IF(EE15="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EG15" s="48"/>
+      <c r="EH15" s="49"/>
+      <c r="EI15" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="EJ15" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="EK15" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="EL15" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="EM15" s="100">
+        <f>IFERROR((VLOOKUP(EG15,Scoring!$A:$B,2,0))+IF(EI15="y",1,0)+IF(EJ15="y",1,0)+IF(EK15="y",1,0)+IF(EL15="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EN15" s="13">
         <v>0.0</v>
       </c>
     </row>
@@ -7365,21 +8337,21 @@
         <f>IFERROR((VLOOKUP(K16,Scoring!$A:$B,2,0))+IF(M16="y",1,0)+IF(N16="y",1,0)+IF(O16="y",1,0)+IF(P16="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="R16" s="24"/>
-      <c r="S16" s="25"/>
-      <c r="T16" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="U16" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="V16" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="W16" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="X16" s="85">
+      <c r="R16" s="101"/>
+      <c r="S16" s="102"/>
+      <c r="T16" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="U16" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="V16" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="W16" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="X16" s="92">
         <f>IFERROR((VLOOKUP(R16,Scoring!$A:$B,2,0))+IF(T16="y",1,0)+IF(U16="y",1,0)+IF(V16="y",1,0)+IF(W16="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -7419,21 +8391,21 @@
         <f>IFERROR((VLOOKUP(AF16,Scoring!$A:$B,2,0))+IF(AH16="y",1,0)+IF(AI16="y",1,0)+IF(AJ16="y",1,0)+IF(AK16="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AM16" s="24"/>
-      <c r="AN16" s="25"/>
-      <c r="AO16" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="AP16" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="AQ16" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="AR16" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AS16" s="85">
+      <c r="AM16" s="101"/>
+      <c r="AN16" s="102"/>
+      <c r="AO16" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP16" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ16" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR16" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="AS16" s="92">
         <f>IFERROR((VLOOKUP(AM16,Scoring!$A:$B,2,0))+IF(AO16="y",1,0)+IF(AP16="y",1,0)+IF(AQ16="y",1,0)+IF(AR16="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -7473,21 +8445,21 @@
         <f>IFERROR((VLOOKUP(BA16,Scoring!$A:$B,2,0))+IF(BC16="y",1,0)+IF(BD16="y",1,0)+IF(BE16="y",1,0)+IF(BF16="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="BH16" s="24"/>
-      <c r="BI16" s="25"/>
-      <c r="BJ16" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="BK16" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="BL16" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="BM16" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="BN16" s="85">
+      <c r="BH16" s="101"/>
+      <c r="BI16" s="102"/>
+      <c r="BJ16" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK16" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL16" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM16" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="BN16" s="92">
         <f>IFERROR((VLOOKUP(BH16,Scoring!$A:$B,2,0))+IF(BJ16="y",1,0)+IF(BK16="y",1,0)+IF(BL16="y",1,0)+IF(BM16="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -7527,36 +8499,36 @@
         <f>IFERROR((VLOOKUP(BV16,Scoring!$A:$B,2,0))+IF(BX16="y",1,0)+IF(BY16="y",1,0)+IF(BZ16="y",1,0)+IF(CA16="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC16" s="100"/>
-      <c r="CD16" s="101"/>
-      <c r="CE16" s="102" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF16" s="103" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG16" s="104" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH16" s="105" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI16" s="92">
+      <c r="CC16" s="24"/>
+      <c r="CD16" s="25"/>
+      <c r="CE16" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF16" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG16" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH16" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI16" s="85">
         <f>IFERROR((VLOOKUP(CC16,Scoring!$A:$B,2,0))+IF(CE16="y",1,0)+IF(CF16="y",1,0)+IF(CG16="y",1,0)+IF(CH16="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ16" s="107"/>
-      <c r="CK16" s="108"/>
-      <c r="CL16" s="109" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM16" s="110" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN16" s="111" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO16" s="112" t="s">
+      <c r="CJ16" s="101"/>
+      <c r="CK16" s="102"/>
+      <c r="CL16" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM16" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN16" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO16" s="106" t="s">
         <v>128</v>
       </c>
       <c r="CP16" s="92">
@@ -7581,43 +8553,115 @@
         <f>IFERROR((VLOOKUP(CQ16,Scoring!$A:$B,2,0))+IF(CS16="y",1,0)+IF(CT16="y",1,0)+IF(CU16="y",1,0)+IF(CV16="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX16" s="107"/>
-      <c r="CY16" s="108"/>
-      <c r="CZ16" s="109" t="s">
-        <v>128</v>
-      </c>
-      <c r="DA16" s="110" t="s">
-        <v>128</v>
-      </c>
-      <c r="DB16" s="111" t="s">
-        <v>128</v>
-      </c>
-      <c r="DC16" s="112" t="s">
-        <v>128</v>
-      </c>
-      <c r="DD16" s="92">
+      <c r="CX16" s="24"/>
+      <c r="CY16" s="25"/>
+      <c r="CZ16" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA16" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB16" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC16" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD16" s="85">
         <f>IFERROR((VLOOKUP(CX16,Scoring!$A:$B,2,0))+IF(CZ16="y",1,0)+IF(DA16="y",1,0)+IF(DB16="y",1,0)+IF(DC16="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DE16" s="24"/>
-      <c r="DF16" s="25"/>
-      <c r="DG16" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="DH16" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="DI16" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="DJ16" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="DK16" s="85">
+      <c r="DE16" s="101"/>
+      <c r="DF16" s="102"/>
+      <c r="DG16" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH16" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI16" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ16" s="106" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK16" s="93">
         <f>IFERROR((VLOOKUP(DE16,Scoring!$A:$B,2,0))+IF(DG16="y",1,0)+IF(DH16="y",1,0)+IF(DI16="y",1,0)+IF(DJ16="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DL16" s="13">
+      <c r="DL16" s="109"/>
+      <c r="DM16" s="110"/>
+      <c r="DN16" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="DO16" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="DP16" s="113" t="s">
+        <v>128</v>
+      </c>
+      <c r="DQ16" s="114" t="s">
+        <v>128</v>
+      </c>
+      <c r="DR16" s="93">
+        <f>IFERROR((VLOOKUP(DL16,Scoring!$A:$B,2,0))+IF(DN16="y",1,0)+IF(DO16="y",1,0)+IF(DP16="y",1,0)+IF(DQ16="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DS16" s="24"/>
+      <c r="DT16" s="25"/>
+      <c r="DU16" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="DV16" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="DW16" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="DX16" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="DY16" s="85">
+        <f>IFERROR((VLOOKUP(DS16,Scoring!$A:$B,2,0))+IF(DU16="y",1,0)+IF(DV16="y",1,0)+IF(DW16="y",1,0)+IF(DX16="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DZ16" s="109"/>
+      <c r="EA16" s="110"/>
+      <c r="EB16" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="EC16" s="112" t="s">
+        <v>128</v>
+      </c>
+      <c r="ED16" s="113" t="s">
+        <v>128</v>
+      </c>
+      <c r="EE16" s="114" t="s">
+        <v>128</v>
+      </c>
+      <c r="EF16" s="93">
+        <f>IFERROR((VLOOKUP(DZ16,Scoring!$A:$B,2,0))+IF(EB16="y",1,0)+IF(EC16="y",1,0)+IF(ED16="y",1,0)+IF(EE16="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EG16" s="24"/>
+      <c r="EH16" s="25"/>
+      <c r="EI16" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="EJ16" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="EK16" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="EL16" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="EM16" s="85">
+        <f>IFERROR((VLOOKUP(EG16,Scoring!$A:$B,2,0))+IF(EI16="y",1,0)+IF(EJ16="y",1,0)+IF(EK16="y",1,0)+IF(EL16="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EN16" s="13">
         <v>0.0</v>
       </c>
     </row>
@@ -7626,10 +8670,10 @@
         <v>41</v>
       </c>
       <c r="B17" s="58" t="s">
-        <v>401</v>
+        <v>357</v>
       </c>
       <c r="C17" s="59" t="s">
-        <v>397</v>
+        <v>353</v>
       </c>
       <c r="D17" s="60"/>
       <c r="E17" s="61"/>
@@ -7645,7 +8689,7 @@
       <c r="I17" s="65" t="s">
         <v>128</v>
       </c>
-      <c r="J17" s="137">
+      <c r="J17" s="139">
         <f>IFERROR((VLOOKUP(D17,Scoring!$A:$B,2,0))+IF(F17="y",1,0)+IF(G17="y",1,0)+IF(H17="y",1,0)+IF(I17="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -7663,25 +8707,25 @@
       <c r="P17" s="65" t="s">
         <v>128</v>
       </c>
-      <c r="Q17" s="137">
+      <c r="Q17" s="139">
         <f>IFERROR((VLOOKUP(K17,Scoring!$A:$B,2,0))+IF(M17="y",1,0)+IF(N17="y",1,0)+IF(O17="y",1,0)+IF(P17="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="R17" s="60"/>
-      <c r="S17" s="61"/>
-      <c r="T17" s="62" t="s">
-        <v>128</v>
-      </c>
-      <c r="U17" s="63" t="s">
-        <v>128</v>
-      </c>
-      <c r="V17" s="64" t="s">
-        <v>128</v>
-      </c>
-      <c r="W17" s="65" t="s">
-        <v>128</v>
-      </c>
-      <c r="X17" s="137">
+      <c r="R17" s="140"/>
+      <c r="S17" s="141"/>
+      <c r="T17" s="142" t="s">
+        <v>128</v>
+      </c>
+      <c r="U17" s="143" t="s">
+        <v>128</v>
+      </c>
+      <c r="V17" s="144" t="s">
+        <v>128</v>
+      </c>
+      <c r="W17" s="145" t="s">
+        <v>128</v>
+      </c>
+      <c r="X17" s="146">
         <f>IFERROR((VLOOKUP(R17,Scoring!$A:$B,2,0))+IF(T17="y",1,0)+IF(U17="y",1,0)+IF(V17="y",1,0)+IF(W17="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -7699,7 +8743,7 @@
       <c r="AD17" s="65" t="s">
         <v>128</v>
       </c>
-      <c r="AE17" s="137">
+      <c r="AE17" s="139">
         <f>IFERROR((VLOOKUP(Y17,Scoring!$A:$B,2,0))+IF(AA17="y",1,0)+IF(AB17="y",1,0)+IF(AC17="y",1,0)+IF(AD17="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -7717,25 +8761,25 @@
       <c r="AK17" s="65" t="s">
         <v>128</v>
       </c>
-      <c r="AL17" s="137">
+      <c r="AL17" s="139">
         <f>IFERROR((VLOOKUP(AF17,Scoring!$A:$B,2,0))+IF(AH17="y",1,0)+IF(AI17="y",1,0)+IF(AJ17="y",1,0)+IF(AK17="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AM17" s="60"/>
-      <c r="AN17" s="61"/>
-      <c r="AO17" s="62" t="s">
-        <v>128</v>
-      </c>
-      <c r="AP17" s="63" t="s">
-        <v>128</v>
-      </c>
-      <c r="AQ17" s="64" t="s">
-        <v>128</v>
-      </c>
-      <c r="AR17" s="65" t="s">
-        <v>128</v>
-      </c>
-      <c r="AS17" s="137">
+      <c r="AM17" s="140"/>
+      <c r="AN17" s="141"/>
+      <c r="AO17" s="142" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP17" s="143" t="s">
+        <v>128</v>
+      </c>
+      <c r="AQ17" s="144" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR17" s="145" t="s">
+        <v>128</v>
+      </c>
+      <c r="AS17" s="146">
         <f>IFERROR((VLOOKUP(AM17,Scoring!$A:$B,2,0))+IF(AO17="y",1,0)+IF(AP17="y",1,0)+IF(AQ17="y",1,0)+IF(AR17="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -7753,7 +8797,7 @@
       <c r="AY17" s="65" t="s">
         <v>128</v>
       </c>
-      <c r="AZ17" s="137">
+      <c r="AZ17" s="139">
         <f>IFERROR((VLOOKUP(AT17,Scoring!$A:$B,2,0))+IF(AV17="y",1,0)+IF(AW17="y",1,0)+IF(AX17="y",1,0)+IF(AY17="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -7771,25 +8815,25 @@
       <c r="BF17" s="65" t="s">
         <v>128</v>
       </c>
-      <c r="BG17" s="137">
+      <c r="BG17" s="139">
         <f>IFERROR((VLOOKUP(BA17,Scoring!$A:$B,2,0))+IF(BC17="y",1,0)+IF(BD17="y",1,0)+IF(BE17="y",1,0)+IF(BF17="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="BH17" s="60"/>
-      <c r="BI17" s="61"/>
-      <c r="BJ17" s="62" t="s">
-        <v>128</v>
-      </c>
-      <c r="BK17" s="63" t="s">
-        <v>128</v>
-      </c>
-      <c r="BL17" s="64" t="s">
-        <v>128</v>
-      </c>
-      <c r="BM17" s="65" t="s">
-        <v>128</v>
-      </c>
-      <c r="BN17" s="137">
+      <c r="BH17" s="140"/>
+      <c r="BI17" s="141"/>
+      <c r="BJ17" s="142" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK17" s="143" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL17" s="144" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM17" s="145" t="s">
+        <v>128</v>
+      </c>
+      <c r="BN17" s="146">
         <f>IFERROR((VLOOKUP(BH17,Scoring!$A:$B,2,0))+IF(BJ17="y",1,0)+IF(BK17="y",1,0)+IF(BL17="y",1,0)+IF(BM17="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -7807,7 +8851,7 @@
       <c r="BT17" s="65" t="s">
         <v>128</v>
       </c>
-      <c r="BU17" s="137">
+      <c r="BU17" s="139">
         <f>IFERROR((VLOOKUP(BO17,Scoring!$A:$B,2,0))+IF(BQ17="y",1,0)+IF(BR17="y",1,0)+IF(BS17="y",1,0)+IF(BT17="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -7825,43 +8869,43 @@
       <c r="CA17" s="65" t="s">
         <v>128</v>
       </c>
-      <c r="CB17" s="137">
+      <c r="CB17" s="139">
         <f>IFERROR((VLOOKUP(BV17,Scoring!$A:$B,2,0))+IF(BX17="y",1,0)+IF(BY17="y",1,0)+IF(BZ17="y",1,0)+IF(CA17="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CC17" s="138"/>
-      <c r="CD17" s="139"/>
-      <c r="CE17" s="140" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF17" s="141" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG17" s="142" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH17" s="143" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI17" s="144">
+      <c r="CC17" s="60"/>
+      <c r="CD17" s="61"/>
+      <c r="CE17" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF17" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG17" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH17" s="65" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI17" s="139">
         <f>IFERROR((VLOOKUP(CC17,Scoring!$A:$B,2,0))+IF(CE17="y",1,0)+IF(CF17="y",1,0)+IF(CG17="y",1,0)+IF(CH17="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CJ17" s="145"/>
-      <c r="CK17" s="146"/>
-      <c r="CL17" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM17" s="148" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN17" s="149" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO17" s="150" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP17" s="144">
+      <c r="CJ17" s="140"/>
+      <c r="CK17" s="141"/>
+      <c r="CL17" s="142" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM17" s="143" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN17" s="144" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO17" s="145" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP17" s="146">
         <f>IFERROR((VLOOKUP(CJ17,Scoring!$A:$B,2,0))+IF(CL17="y",1,0)+IF(CM17="y",1,0)+IF(CN17="y",1,0)+IF(CO17="y",1,0),0)</f>
         <v>0</v>
       </c>
@@ -7879,47 +8923,119 @@
       <c r="CV17" s="65" t="s">
         <v>128</v>
       </c>
-      <c r="CW17" s="137">
+      <c r="CW17" s="139">
         <f>IFERROR((VLOOKUP(CQ17,Scoring!$A:$B,2,0))+IF(CS17="y",1,0)+IF(CT17="y",1,0)+IF(CU17="y",1,0)+IF(CV17="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="CX17" s="145"/>
-      <c r="CY17" s="146"/>
-      <c r="CZ17" s="147" t="s">
-        <v>128</v>
-      </c>
-      <c r="DA17" s="148" t="s">
-        <v>128</v>
-      </c>
-      <c r="DB17" s="149" t="s">
-        <v>128</v>
-      </c>
-      <c r="DC17" s="150" t="s">
-        <v>128</v>
-      </c>
-      <c r="DD17" s="144">
+      <c r="CX17" s="60"/>
+      <c r="CY17" s="61"/>
+      <c r="CZ17" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="DA17" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="DB17" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="DC17" s="65" t="s">
+        <v>128</v>
+      </c>
+      <c r="DD17" s="139">
         <f>IFERROR((VLOOKUP(CX17,Scoring!$A:$B,2,0))+IF(CZ17="y",1,0)+IF(DA17="y",1,0)+IF(DB17="y",1,0)+IF(DC17="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DE17" s="60"/>
-      <c r="DF17" s="61"/>
-      <c r="DG17" s="62" t="s">
-        <v>128</v>
-      </c>
-      <c r="DH17" s="63" t="s">
-        <v>128</v>
-      </c>
-      <c r="DI17" s="64" t="s">
-        <v>128</v>
-      </c>
-      <c r="DJ17" s="65" t="s">
-        <v>128</v>
-      </c>
-      <c r="DK17" s="137">
+      <c r="DE17" s="140"/>
+      <c r="DF17" s="141"/>
+      <c r="DG17" s="142" t="s">
+        <v>128</v>
+      </c>
+      <c r="DH17" s="143" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI17" s="144" t="s">
+        <v>128</v>
+      </c>
+      <c r="DJ17" s="145" t="s">
+        <v>128</v>
+      </c>
+      <c r="DK17" s="147">
         <f>IFERROR((VLOOKUP(DE17,Scoring!$A:$B,2,0))+IF(DG17="y",1,0)+IF(DH17="y",1,0)+IF(DI17="y",1,0)+IF(DJ17="y",1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DL17" s="13">
+      <c r="DL17" s="148"/>
+      <c r="DM17" s="149"/>
+      <c r="DN17" s="150" t="s">
+        <v>128</v>
+      </c>
+      <c r="DO17" s="151" t="s">
+        <v>128</v>
+      </c>
+      <c r="DP17" s="152" t="s">
+        <v>128</v>
+      </c>
+      <c r="DQ17" s="153" t="s">
+        <v>128</v>
+      </c>
+      <c r="DR17" s="147">
+        <f>IFERROR((VLOOKUP(DL17,Scoring!$A:$B,2,0))+IF(DN17="y",1,0)+IF(DO17="y",1,0)+IF(DP17="y",1,0)+IF(DQ17="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DS17" s="60"/>
+      <c r="DT17" s="61"/>
+      <c r="DU17" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="DV17" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="DW17" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="DX17" s="65" t="s">
+        <v>128</v>
+      </c>
+      <c r="DY17" s="139">
+        <f>IFERROR((VLOOKUP(DS17,Scoring!$A:$B,2,0))+IF(DU17="y",1,0)+IF(DV17="y",1,0)+IF(DW17="y",1,0)+IF(DX17="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="DZ17" s="148"/>
+      <c r="EA17" s="149"/>
+      <c r="EB17" s="150" t="s">
+        <v>128</v>
+      </c>
+      <c r="EC17" s="151" t="s">
+        <v>128</v>
+      </c>
+      <c r="ED17" s="152" t="s">
+        <v>128</v>
+      </c>
+      <c r="EE17" s="153" t="s">
+        <v>128</v>
+      </c>
+      <c r="EF17" s="147">
+        <f>IFERROR((VLOOKUP(DZ17,Scoring!$A:$B,2,0))+IF(EB17="y",1,0)+IF(EC17="y",1,0)+IF(ED17="y",1,0)+IF(EE17="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EG17" s="60"/>
+      <c r="EH17" s="61"/>
+      <c r="EI17" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="EJ17" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="EK17" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="EL17" s="65" t="s">
+        <v>128</v>
+      </c>
+      <c r="EM17" s="139">
+        <f>IFERROR((VLOOKUP(EG17,Scoring!$A:$B,2,0))+IF(EI17="y",1,0)+IF(EJ17="y",1,0)+IF(EK17="y",1,0)+IF(EL17="y",1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="EN17" s="13">
         <v>0.0</v>
       </c>
     </row>
@@ -7951,35 +9067,35 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>402</v>
+        <v>358</v>
       </c>
       <c r="B2" s="69" t="s">
-        <v>403</v>
+        <v>359</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>404</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>405</v>
+        <v>361</v>
       </c>
       <c r="B3" s="69" t="s">
-        <v>406</v>
+        <v>362</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>404</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>407</v>
+        <v>363</v>
       </c>
       <c r="B4" s="69" t="s">
-        <v>408</v>
+        <v>364</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>404</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5">
@@ -7987,21 +9103,27 @@
         <v>143</v>
       </c>
       <c r="B5" s="69" t="s">
-        <v>409</v>
+        <v>365</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>292</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>410</v>
+        <v>366</v>
       </c>
       <c r="B6" s="69" t="s">
-        <v>411</v>
+        <v>367</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>292</v>
+      </c>
+      <c r="D6" s="1">
+        <v>2.0</v>
       </c>
     </row>
     <row r="7">
@@ -8009,10 +9131,13 @@
         <v>276</v>
       </c>
       <c r="B7" s="69" t="s">
-        <v>412</v>
+        <v>368</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>292</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3.0</v>
       </c>
     </row>
     <row r="8">
@@ -8020,7 +9145,7 @@
         <v>144</v>
       </c>
       <c r="B8" s="69" t="s">
-        <v>412</v>
+        <v>368</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>292</v>
@@ -8031,7 +9156,7 @@
         <v>151</v>
       </c>
       <c r="B9" s="69" t="s">
-        <v>413</v>
+        <v>369</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>292</v>
@@ -8039,10 +9164,10 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>149</v>
+        <v>283</v>
       </c>
       <c r="B10" s="69" t="s">
-        <v>414</v>
+        <v>370</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>292</v>
@@ -8050,10 +9175,10 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B11" s="69" t="s">
-        <v>415</v>
+        <v>370</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>292</v>
@@ -8061,10 +9186,10 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>416</v>
+        <v>157</v>
       </c>
       <c r="B12" s="69" t="s">
-        <v>417</v>
+        <v>371</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>292</v>
@@ -8072,10 +9197,10 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>148</v>
+        <v>372</v>
       </c>
       <c r="B13" s="69" t="s">
-        <v>417</v>
+        <v>373</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>292</v>
@@ -8083,10 +9208,10 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B14" s="69" t="s">
-        <v>418</v>
+        <v>373</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>292</v>
@@ -8094,10 +9219,10 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B15" s="69" t="s">
-        <v>419</v>
+        <v>374</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>292</v>
@@ -8105,10 +9230,10 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="B16" s="69" t="s">
-        <v>420</v>
+        <v>375</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>292</v>
@@ -8116,10 +9241,10 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>155</v>
+        <v>376</v>
       </c>
       <c r="B17" s="69" t="s">
-        <v>421</v>
+        <v>377</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>292</v>
@@ -8127,10 +9252,10 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>422</v>
+        <v>141</v>
       </c>
       <c r="B18" s="69" t="s">
-        <v>423</v>
+        <v>377</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>292</v>
@@ -8138,10 +9263,10 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B19" s="69" t="s">
-        <v>423</v>
+        <v>378</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>292</v>
@@ -8149,10 +9274,10 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>154</v>
+        <v>379</v>
       </c>
       <c r="B20" s="69" t="s">
-        <v>424</v>
+        <v>380</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>292</v>
@@ -8160,10 +9285,10 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>425</v>
+        <v>150</v>
       </c>
       <c r="B21" s="69" t="s">
-        <v>426</v>
+        <v>380</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>292</v>
@@ -8171,10 +9296,10 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B22" s="69" t="s">
-        <v>426</v>
+        <v>381</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>292</v>
@@ -8182,12 +9307,34 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B23" s="69" t="s">
+        <v>383</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B24" s="69" t="s">
+        <v>383</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B23" s="69" t="s">
-        <v>427</v>
-      </c>
-      <c r="C23" s="1" t="s">
+      <c r="B25" s="69" t="s">
+        <v>384</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>292</v>
       </c>
     </row>

--- a/the_alternative_f1/The_Alternative_F1.xlsx
+++ b/the_alternative_f1/The_Alternative_F1.xlsx
@@ -9108,9 +9108,6 @@
       <c r="C5" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="D5" s="1">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
@@ -9122,9 +9119,6 @@
       <c r="C6" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="D6" s="1">
-        <v>2.0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
@@ -9135,9 +9129,6 @@
       </c>
       <c r="C7" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="D7" s="1">
-        <v>3.0</v>
       </c>
     </row>
     <row r="8">
